--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Wales Welsh Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Wales Welsh Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="258">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -565,6 +565,9 @@
     <t>['36', '76']</t>
   </si>
   <si>
+    <t>['80']</t>
+  </si>
+  <si>
     <t>['45+2']</t>
   </si>
   <si>
@@ -782,6 +785,9 @@
   </si>
   <si>
     <t>['31', '80']</t>
+  </si>
+  <si>
+    <t>['6', '14', '90+2']</t>
   </si>
 </sst>
 </file>
@@ -1143,7 +1149,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP138"/>
+  <dimension ref="A1:BP139"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1399,7 +1405,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q2">
         <v>1.83</v>
@@ -1605,7 +1611,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q3">
         <v>3.75</v>
@@ -1811,7 +1817,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -2223,7 +2229,7 @@
         <v>85</v>
       </c>
       <c r="P6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q6">
         <v>4</v>
@@ -2429,7 +2435,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q7">
         <v>11</v>
@@ -3125,7 +3131,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ10">
         <v>0.83</v>
@@ -3253,7 +3259,7 @@
         <v>89</v>
       </c>
       <c r="P11" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q11">
         <v>3.6</v>
@@ -3459,7 +3465,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q12">
         <v>2.9</v>
@@ -3743,7 +3749,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ13">
         <v>0.64</v>
@@ -3871,7 +3877,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q14">
         <v>4.33</v>
@@ -4283,7 +4289,7 @@
         <v>85</v>
       </c>
       <c r="P16" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q16">
         <v>2.63</v>
@@ -4364,7 +4370,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ16">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AR16">
         <v>2.12</v>
@@ -4695,7 +4701,7 @@
         <v>94</v>
       </c>
       <c r="P18" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q18">
         <v>3</v>
@@ -4901,7 +4907,7 @@
         <v>85</v>
       </c>
       <c r="P19" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q19">
         <v>4.75</v>
@@ -5931,7 +5937,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6137,7 +6143,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q25">
         <v>3.2</v>
@@ -6215,7 +6221,7 @@
         <v>2</v>
       </c>
       <c r="AP25">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ25">
         <v>2.17</v>
@@ -6343,7 +6349,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -6549,7 +6555,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q27">
         <v>5.5</v>
@@ -7042,7 +7048,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ29">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AR29">
         <v>2.16</v>
@@ -7373,7 +7379,7 @@
         <v>85</v>
       </c>
       <c r="P31" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q31">
         <v>13</v>
@@ -7579,7 +7585,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q32">
         <v>1.83</v>
@@ -7863,7 +7869,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ33">
         <v>1.45</v>
@@ -7991,7 +7997,7 @@
         <v>85</v>
       </c>
       <c r="P34" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q34">
         <v>3</v>
@@ -8481,7 +8487,7 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ36">
         <v>0.27</v>
@@ -9021,7 +9027,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q39">
         <v>1.83</v>
@@ -9433,7 +9439,7 @@
         <v>110</v>
       </c>
       <c r="P41" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q41">
         <v>7</v>
@@ -9639,7 +9645,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q42">
         <v>2.6</v>
@@ -9717,7 +9723,7 @@
         <v>1.33</v>
       </c>
       <c r="AP42">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ42">
         <v>0.82</v>
@@ -9845,7 +9851,7 @@
         <v>85</v>
       </c>
       <c r="P43" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q43">
         <v>3.75</v>
@@ -10338,7 +10344,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ45">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AR45">
         <v>1.74</v>
@@ -10463,7 +10469,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q46">
         <v>3.4</v>
@@ -10669,7 +10675,7 @@
         <v>115</v>
       </c>
       <c r="P47" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q47">
         <v>2.25</v>
@@ -10875,7 +10881,7 @@
         <v>116</v>
       </c>
       <c r="P48" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q48">
         <v>2.5</v>
@@ -11287,7 +11293,7 @@
         <v>117</v>
       </c>
       <c r="P50" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q50">
         <v>1.67</v>
@@ -11493,7 +11499,7 @@
         <v>118</v>
       </c>
       <c r="P51" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q51">
         <v>6</v>
@@ -11699,7 +11705,7 @@
         <v>119</v>
       </c>
       <c r="P52" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -11780,7 +11786,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ52">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AR52">
         <v>1.62</v>
@@ -12111,7 +12117,7 @@
         <v>114</v>
       </c>
       <c r="P54" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q54">
         <v>9.5</v>
@@ -12523,7 +12529,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q56">
         <v>7</v>
@@ -12729,7 +12735,7 @@
         <v>85</v>
       </c>
       <c r="P57" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q57">
         <v>6.5</v>
@@ -13347,7 +13353,7 @@
         <v>125</v>
       </c>
       <c r="P60" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q60">
         <v>2.3</v>
@@ -13553,7 +13559,7 @@
         <v>85</v>
       </c>
       <c r="P61" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q61">
         <v>2.88</v>
@@ -13631,7 +13637,7 @@
         <v>2</v>
       </c>
       <c r="AP61">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ61">
         <v>1.82</v>
@@ -13965,7 +13971,7 @@
         <v>87</v>
       </c>
       <c r="P63" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q63">
         <v>2.63</v>
@@ -14046,7 +14052,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ63">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AR63">
         <v>1.21</v>
@@ -14171,7 +14177,7 @@
         <v>127</v>
       </c>
       <c r="P64" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q64">
         <v>1.42</v>
@@ -14252,7 +14258,7 @@
         <v>2.45</v>
       </c>
       <c r="AQ64">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AR64">
         <v>3.13</v>
@@ -14583,7 +14589,7 @@
         <v>128</v>
       </c>
       <c r="P66" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -15201,7 +15207,7 @@
         <v>131</v>
       </c>
       <c r="P69" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15407,7 +15413,7 @@
         <v>85</v>
       </c>
       <c r="P70" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q70">
         <v>9</v>
@@ -15691,7 +15697,7 @@
         <v>1.33</v>
       </c>
       <c r="AP71">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ71">
         <v>1</v>
@@ -15819,7 +15825,7 @@
         <v>132</v>
       </c>
       <c r="P72" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q72">
         <v>7</v>
@@ -16025,7 +16031,7 @@
         <v>133</v>
       </c>
       <c r="P73" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q73">
         <v>1.73</v>
@@ -16437,7 +16443,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16849,7 +16855,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q77">
         <v>2.5</v>
@@ -17055,7 +17061,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17261,7 +17267,7 @@
         <v>139</v>
       </c>
       <c r="P79" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q79">
         <v>2.75</v>
@@ -17548,7 +17554,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ80">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AR80">
         <v>1.28</v>
@@ -17673,7 +17679,7 @@
         <v>140</v>
       </c>
       <c r="P81" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q81">
         <v>19</v>
@@ -17879,7 +17885,7 @@
         <v>141</v>
       </c>
       <c r="P82" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q82">
         <v>1.5</v>
@@ -18085,7 +18091,7 @@
         <v>142</v>
       </c>
       <c r="P83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18291,7 +18297,7 @@
         <v>143</v>
       </c>
       <c r="P84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q84">
         <v>11</v>
@@ -18497,7 +18503,7 @@
         <v>144</v>
       </c>
       <c r="P85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q85">
         <v>4.75</v>
@@ -19527,7 +19533,7 @@
         <v>148</v>
       </c>
       <c r="P90" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q90">
         <v>4.75</v>
@@ -19939,7 +19945,7 @@
         <v>150</v>
       </c>
       <c r="P92" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q92">
         <v>2.88</v>
@@ -20226,7 +20232,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ93">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AR93">
         <v>1.26</v>
@@ -20351,7 +20357,7 @@
         <v>151</v>
       </c>
       <c r="P94" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q94">
         <v>2.88</v>
@@ -20763,7 +20769,7 @@
         <v>153</v>
       </c>
       <c r="P96" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q96">
         <v>11</v>
@@ -21587,7 +21593,7 @@
         <v>156</v>
       </c>
       <c r="P100" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q100">
         <v>1.73</v>
@@ -21793,7 +21799,7 @@
         <v>85</v>
       </c>
       <c r="P101" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q101">
         <v>3.4</v>
@@ -21999,7 +22005,7 @@
         <v>157</v>
       </c>
       <c r="P102" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q102">
         <v>3</v>
@@ -22205,7 +22211,7 @@
         <v>158</v>
       </c>
       <c r="P103" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22286,7 +22292,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ103">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AR103">
         <v>1.45</v>
@@ -22695,7 +22701,7 @@
         <v>2.25</v>
       </c>
       <c r="AP105">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ105">
         <v>2.18</v>
@@ -23029,7 +23035,7 @@
         <v>162</v>
       </c>
       <c r="P107" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q107">
         <v>3</v>
@@ -23441,7 +23447,7 @@
         <v>164</v>
       </c>
       <c r="P109" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q109">
         <v>2.75</v>
@@ -23647,7 +23653,7 @@
         <v>165</v>
       </c>
       <c r="P110" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q110">
         <v>2.4</v>
@@ -23725,7 +23731,7 @@
         <v>1.22</v>
       </c>
       <c r="AP110">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ110">
         <v>1.25</v>
@@ -23934,7 +23940,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ111">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AR111">
         <v>0.97</v>
@@ -24059,7 +24065,7 @@
         <v>167</v>
       </c>
       <c r="P112" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q112">
         <v>1.4</v>
@@ -24265,7 +24271,7 @@
         <v>168</v>
       </c>
       <c r="P113" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q113">
         <v>4.75</v>
@@ -24471,7 +24477,7 @@
         <v>98</v>
       </c>
       <c r="P114" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q114">
         <v>2</v>
@@ -24677,7 +24683,7 @@
         <v>169</v>
       </c>
       <c r="P115" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q115">
         <v>6</v>
@@ -25089,7 +25095,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25295,7 +25301,7 @@
         <v>85</v>
       </c>
       <c r="P118" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q118">
         <v>3.75</v>
@@ -25913,7 +25919,7 @@
         <v>172</v>
       </c>
       <c r="P121" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q121">
         <v>2.1</v>
@@ -26943,7 +26949,7 @@
         <v>175</v>
       </c>
       <c r="P126" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q126">
         <v>1.44</v>
@@ -27149,7 +27155,7 @@
         <v>85</v>
       </c>
       <c r="P127" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q127">
         <v>2.3</v>
@@ -27227,10 +27233,10 @@
         <v>1.8</v>
       </c>
       <c r="AP127">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ127">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AR127">
         <v>1.34</v>
@@ -27355,7 +27361,7 @@
         <v>139</v>
       </c>
       <c r="P128" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q128">
         <v>2.75</v>
@@ -27767,7 +27773,7 @@
         <v>177</v>
       </c>
       <c r="P130" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q130">
         <v>7</v>
@@ -27973,7 +27979,7 @@
         <v>85</v>
       </c>
       <c r="P131" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q131">
         <v>5.5</v>
@@ -28385,7 +28391,7 @@
         <v>85</v>
       </c>
       <c r="P133" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q133">
         <v>2.75</v>
@@ -28591,7 +28597,7 @@
         <v>179</v>
       </c>
       <c r="P134" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q134">
         <v>4.75</v>
@@ -28797,7 +28803,7 @@
         <v>180</v>
       </c>
       <c r="P135" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q135">
         <v>2.5</v>
@@ -29003,7 +29009,7 @@
         <v>120</v>
       </c>
       <c r="P136" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q136">
         <v>3.75</v>
@@ -29209,7 +29215,7 @@
         <v>181</v>
       </c>
       <c r="P137" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q137">
         <v>2.38</v>
@@ -29572,6 +29578,212 @@
       </c>
       <c r="BP138">
         <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:68">
+      <c r="A139" s="1">
+        <v>138</v>
+      </c>
+      <c r="B139">
+        <v>7817175</v>
+      </c>
+      <c r="C139" t="s">
+        <v>68</v>
+      </c>
+      <c r="D139" t="s">
+        <v>69</v>
+      </c>
+      <c r="E139" s="2">
+        <v>45688.69791666666</v>
+      </c>
+      <c r="F139">
+        <v>2</v>
+      </c>
+      <c r="G139" t="s">
+        <v>77</v>
+      </c>
+      <c r="H139" t="s">
+        <v>79</v>
+      </c>
+      <c r="I139">
+        <v>0</v>
+      </c>
+      <c r="J139">
+        <v>2</v>
+      </c>
+      <c r="K139">
+        <v>2</v>
+      </c>
+      <c r="L139">
+        <v>1</v>
+      </c>
+      <c r="M139">
+        <v>3</v>
+      </c>
+      <c r="N139">
+        <v>4</v>
+      </c>
+      <c r="O139" t="s">
+        <v>183</v>
+      </c>
+      <c r="P139" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q139">
+        <v>2.7</v>
+      </c>
+      <c r="R139">
+        <v>2.1</v>
+      </c>
+      <c r="S139">
+        <v>3.6</v>
+      </c>
+      <c r="T139">
+        <v>1.37</v>
+      </c>
+      <c r="U139">
+        <v>2.8</v>
+      </c>
+      <c r="V139">
+        <v>2.65</v>
+      </c>
+      <c r="W139">
+        <v>1.42</v>
+      </c>
+      <c r="X139">
+        <v>6.5</v>
+      </c>
+      <c r="Y139">
+        <v>1.09</v>
+      </c>
+      <c r="Z139">
+        <v>2.15</v>
+      </c>
+      <c r="AA139">
+        <v>3.6</v>
+      </c>
+      <c r="AB139">
+        <v>3.05</v>
+      </c>
+      <c r="AC139">
+        <v>1.02</v>
+      </c>
+      <c r="AD139">
+        <v>10</v>
+      </c>
+      <c r="AE139">
+        <v>1.28</v>
+      </c>
+      <c r="AF139">
+        <v>3.5</v>
+      </c>
+      <c r="AG139">
+        <v>1.89</v>
+      </c>
+      <c r="AH139">
+        <v>1.89</v>
+      </c>
+      <c r="AI139">
+        <v>1.7</v>
+      </c>
+      <c r="AJ139">
+        <v>2</v>
+      </c>
+      <c r="AK139">
+        <v>1.32</v>
+      </c>
+      <c r="AL139">
+        <v>1.31</v>
+      </c>
+      <c r="AM139">
+        <v>1.65</v>
+      </c>
+      <c r="AN139">
+        <v>1.55</v>
+      </c>
+      <c r="AO139">
+        <v>1.91</v>
+      </c>
+      <c r="AP139">
+        <v>1.42</v>
+      </c>
+      <c r="AQ139">
+        <v>2</v>
+      </c>
+      <c r="AR139">
+        <v>1.37</v>
+      </c>
+      <c r="AS139">
+        <v>1.45</v>
+      </c>
+      <c r="AT139">
+        <v>2.82</v>
+      </c>
+      <c r="AU139">
+        <v>4</v>
+      </c>
+      <c r="AV139">
+        <v>10</v>
+      </c>
+      <c r="AW139">
+        <v>8</v>
+      </c>
+      <c r="AX139">
+        <v>6</v>
+      </c>
+      <c r="AY139">
+        <v>12</v>
+      </c>
+      <c r="AZ139">
+        <v>16</v>
+      </c>
+      <c r="BA139">
+        <v>7</v>
+      </c>
+      <c r="BB139">
+        <v>4</v>
+      </c>
+      <c r="BC139">
+        <v>11</v>
+      </c>
+      <c r="BD139">
+        <v>1.62</v>
+      </c>
+      <c r="BE139">
+        <v>6.55</v>
+      </c>
+      <c r="BF139">
+        <v>2.88</v>
+      </c>
+      <c r="BG139">
+        <v>1.29</v>
+      </c>
+      <c r="BH139">
+        <v>3.3</v>
+      </c>
+      <c r="BI139">
+        <v>1.45</v>
+      </c>
+      <c r="BJ139">
+        <v>2.49</v>
+      </c>
+      <c r="BK139">
+        <v>1.81</v>
+      </c>
+      <c r="BL139">
+        <v>1.96</v>
+      </c>
+      <c r="BM139">
+        <v>2.24</v>
+      </c>
+      <c r="BN139">
+        <v>1.56</v>
+      </c>
+      <c r="BO139">
+        <v>2.88</v>
+      </c>
+      <c r="BP139">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Wales Welsh Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Wales Welsh Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="926" uniqueCount="265">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -568,6 +568,18 @@
     <t>['80']</t>
   </si>
   <si>
+    <t>['17']</t>
+  </si>
+  <si>
+    <t>['50', '78']</t>
+  </si>
+  <si>
+    <t>['2', '53', '68']</t>
+  </si>
+  <si>
+    <t>['3', '32', '72']</t>
+  </si>
+  <si>
     <t>['45+2']</t>
   </si>
   <si>
@@ -788,6 +800,15 @@
   </si>
   <si>
     <t>['6', '14', '90+2']</t>
+  </si>
+  <si>
+    <t>['4', '58', '70']</t>
+  </si>
+  <si>
+    <t>['16']</t>
+  </si>
+  <si>
+    <t>['25']</t>
   </si>
 </sst>
 </file>
@@ -1149,7 +1170,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP139"/>
+  <dimension ref="A1:BP144"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1405,7 +1426,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q2">
         <v>1.83</v>
@@ -1486,7 +1507,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ2">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1611,7 +1632,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="Q3">
         <v>3.75</v>
@@ -1689,7 +1710,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ3">
         <v>1.25</v>
@@ -1817,7 +1838,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -1898,7 +1919,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ4">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2101,10 +2122,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ5">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2229,7 +2250,7 @@
         <v>85</v>
       </c>
       <c r="P6" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="Q6">
         <v>4</v>
@@ -2307,7 +2328,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ6">
         <v>2.17</v>
@@ -2435,7 +2456,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="Q7">
         <v>11</v>
@@ -2925,10 +2946,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ9">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3259,7 +3280,7 @@
         <v>89</v>
       </c>
       <c r="P11" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="Q11">
         <v>3.6</v>
@@ -3465,7 +3486,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="Q12">
         <v>2.9</v>
@@ -3546,7 +3567,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ12">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3752,7 +3773,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ13">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR13">
         <v>1.91</v>
@@ -3877,7 +3898,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="Q14">
         <v>4.33</v>
@@ -3955,10 +3976,10 @@
         <v>3</v>
       </c>
       <c r="AP14">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ14">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR14">
         <v>0.82</v>
@@ -4289,7 +4310,7 @@
         <v>85</v>
       </c>
       <c r="P16" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="Q16">
         <v>2.63</v>
@@ -4701,7 +4722,7 @@
         <v>94</v>
       </c>
       <c r="P18" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="Q18">
         <v>3</v>
@@ -4779,10 +4800,10 @@
         <v>1</v>
       </c>
       <c r="AP18">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ18">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR18">
         <v>1.28</v>
@@ -4907,7 +4928,7 @@
         <v>85</v>
       </c>
       <c r="P19" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="Q19">
         <v>4.75</v>
@@ -5194,7 +5215,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ20">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR20">
         <v>1.34</v>
@@ -5397,10 +5418,10 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ21">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AR21">
         <v>1.58</v>
@@ -5812,7 +5833,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ23">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR23">
         <v>1.19</v>
@@ -5937,7 +5958,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6018,7 +6039,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ24">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR24">
         <v>1.08</v>
@@ -6143,7 +6164,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="Q25">
         <v>3.2</v>
@@ -6349,7 +6370,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -6427,10 +6448,10 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ26">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR26">
         <v>1.77</v>
@@ -6555,7 +6576,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="Q27">
         <v>5.5</v>
@@ -6633,7 +6654,7 @@
         <v>2</v>
       </c>
       <c r="AP27">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ27">
         <v>1</v>
@@ -6839,10 +6860,10 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ28">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AR28">
         <v>0</v>
@@ -7045,7 +7066,7 @@
         <v>3</v>
       </c>
       <c r="AP29">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ29">
         <v>2</v>
@@ -7379,7 +7400,7 @@
         <v>85</v>
       </c>
       <c r="P31" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="Q31">
         <v>13</v>
@@ -7585,7 +7606,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="Q32">
         <v>1.83</v>
@@ -7663,7 +7684,7 @@
         <v>0.5</v>
       </c>
       <c r="AP32">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ32">
         <v>1.25</v>
@@ -7872,7 +7893,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ33">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR33">
         <v>1.47</v>
@@ -7997,7 +8018,7 @@
         <v>85</v>
       </c>
       <c r="P34" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="Q34">
         <v>3</v>
@@ -8078,7 +8099,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ34">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR34">
         <v>0.86</v>
@@ -8284,7 +8305,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ35">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR35">
         <v>1.94</v>
@@ -8490,7 +8511,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ36">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AR36">
         <v>1.37</v>
@@ -8696,7 +8717,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ37">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR37">
         <v>1.69</v>
@@ -8899,7 +8920,7 @@
         <v>1.33</v>
       </c>
       <c r="AP38">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ38">
         <v>1.25</v>
@@ -9027,7 +9048,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="Q39">
         <v>1.83</v>
@@ -9311,7 +9332,7 @@
         <v>2.33</v>
       </c>
       <c r="AP40">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ40">
         <v>2.17</v>
@@ -9439,7 +9460,7 @@
         <v>110</v>
       </c>
       <c r="P41" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="Q41">
         <v>7</v>
@@ -9517,7 +9538,7 @@
         <v>3</v>
       </c>
       <c r="AP41">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ41">
         <v>2.18</v>
@@ -9645,7 +9666,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="Q42">
         <v>2.6</v>
@@ -9726,7 +9747,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ42">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR42">
         <v>1.52</v>
@@ -9851,7 +9872,7 @@
         <v>85</v>
       </c>
       <c r="P43" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="Q43">
         <v>3.75</v>
@@ -9932,7 +9953,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ43">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR43">
         <v>0.99</v>
@@ -10341,7 +10362,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ45">
         <v>2</v>
@@ -10469,7 +10490,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="Q46">
         <v>3.4</v>
@@ -10547,10 +10568,10 @@
         <v>1</v>
       </c>
       <c r="AP46">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ46">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR46">
         <v>0.8100000000000001</v>
@@ -10675,7 +10696,7 @@
         <v>115</v>
       </c>
       <c r="P47" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="Q47">
         <v>2.25</v>
@@ -10753,10 +10774,10 @@
         <v>1.25</v>
       </c>
       <c r="AP47">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ47">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR47">
         <v>1.34</v>
@@ -10881,7 +10902,7 @@
         <v>116</v>
       </c>
       <c r="P48" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="Q48">
         <v>2.5</v>
@@ -11165,7 +11186,7 @@
         <v>0</v>
       </c>
       <c r="AP49">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ49">
         <v>0.83</v>
@@ -11293,7 +11314,7 @@
         <v>117</v>
       </c>
       <c r="P50" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="Q50">
         <v>1.67</v>
@@ -11371,7 +11392,7 @@
         <v>1</v>
       </c>
       <c r="AP50">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ50">
         <v>1.25</v>
@@ -11499,7 +11520,7 @@
         <v>118</v>
       </c>
       <c r="P51" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="Q51">
         <v>6</v>
@@ -11580,7 +11601,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ51">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR51">
         <v>0.9399999999999999</v>
@@ -11705,7 +11726,7 @@
         <v>119</v>
       </c>
       <c r="P52" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -11989,10 +12010,10 @@
         <v>0</v>
       </c>
       <c r="AP53">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ53">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AR53">
         <v>1.67</v>
@@ -12117,7 +12138,7 @@
         <v>114</v>
       </c>
       <c r="P54" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="Q54">
         <v>9.5</v>
@@ -12404,7 +12425,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ55">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR55">
         <v>1.17</v>
@@ -12529,7 +12550,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="Q56">
         <v>7</v>
@@ -12607,7 +12628,7 @@
         <v>1.67</v>
       </c>
       <c r="AP56">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ56">
         <v>1.25</v>
@@ -12735,7 +12756,7 @@
         <v>85</v>
       </c>
       <c r="P57" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="Q57">
         <v>6.5</v>
@@ -13225,7 +13246,7 @@
         <v>1</v>
       </c>
       <c r="AP59">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ59">
         <v>1.25</v>
@@ -13353,7 +13374,7 @@
         <v>125</v>
       </c>
       <c r="P60" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="Q60">
         <v>2.3</v>
@@ -13434,7 +13455,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ60">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR60">
         <v>1.7</v>
@@ -13559,7 +13580,7 @@
         <v>85</v>
       </c>
       <c r="P61" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="Q61">
         <v>2.88</v>
@@ -13640,7 +13661,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ61">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR61">
         <v>1.49</v>
@@ -13843,10 +13864,10 @@
         <v>0</v>
       </c>
       <c r="AP62">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ62">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AR62">
         <v>1.28</v>
@@ -13971,7 +13992,7 @@
         <v>87</v>
       </c>
       <c r="P63" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="Q63">
         <v>2.63</v>
@@ -14177,7 +14198,7 @@
         <v>127</v>
       </c>
       <c r="P64" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="Q64">
         <v>1.42</v>
@@ -14255,7 +14276,7 @@
         <v>2</v>
       </c>
       <c r="AP64">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ64">
         <v>2</v>
@@ -14589,7 +14610,7 @@
         <v>128</v>
       </c>
       <c r="P66" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -14873,10 +14894,10 @@
         <v>2.14</v>
       </c>
       <c r="AP67">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ67">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR67">
         <v>2.85</v>
@@ -15079,7 +15100,7 @@
         <v>0.75</v>
       </c>
       <c r="AP68">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ68">
         <v>0.83</v>
@@ -15207,7 +15228,7 @@
         <v>131</v>
       </c>
       <c r="P69" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15288,7 +15309,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ69">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR69">
         <v>1.2</v>
@@ -15413,7 +15434,7 @@
         <v>85</v>
       </c>
       <c r="P70" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Q70">
         <v>9</v>
@@ -15825,7 +15846,7 @@
         <v>132</v>
       </c>
       <c r="P72" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="Q72">
         <v>7</v>
@@ -15903,10 +15924,10 @@
         <v>2.17</v>
       </c>
       <c r="AP72">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ72">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR72">
         <v>1.05</v>
@@ -16031,7 +16052,7 @@
         <v>133</v>
       </c>
       <c r="P73" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="Q73">
         <v>1.73</v>
@@ -16112,7 +16133,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ73">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AR73">
         <v>1.35</v>
@@ -16443,7 +16464,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16727,10 +16748,10 @@
         <v>1.4</v>
       </c>
       <c r="AP76">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ76">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR76">
         <v>2.71</v>
@@ -16855,7 +16876,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Q77">
         <v>2.5</v>
@@ -16936,7 +16957,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ77">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR77">
         <v>1.29</v>
@@ -17061,7 +17082,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17267,7 +17288,7 @@
         <v>139</v>
       </c>
       <c r="P79" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Q79">
         <v>2.75</v>
@@ -17345,7 +17366,7 @@
         <v>1.4</v>
       </c>
       <c r="AP79">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ79">
         <v>1.25</v>
@@ -17679,7 +17700,7 @@
         <v>140</v>
       </c>
       <c r="P81" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="Q81">
         <v>19</v>
@@ -17885,7 +17906,7 @@
         <v>141</v>
       </c>
       <c r="P82" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="Q82">
         <v>1.5</v>
@@ -17963,7 +17984,7 @@
         <v>0.6</v>
       </c>
       <c r="AP82">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ82">
         <v>0.83</v>
@@ -18091,7 +18112,7 @@
         <v>142</v>
       </c>
       <c r="P83" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18169,7 +18190,7 @@
         <v>2.4</v>
       </c>
       <c r="AP83">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ83">
         <v>2.18</v>
@@ -18297,7 +18318,7 @@
         <v>143</v>
       </c>
       <c r="P84" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q84">
         <v>11</v>
@@ -18375,7 +18396,7 @@
         <v>2.5</v>
       </c>
       <c r="AP84">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ84">
         <v>2.18</v>
@@ -18503,7 +18524,7 @@
         <v>144</v>
       </c>
       <c r="P85" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q85">
         <v>4.75</v>
@@ -18787,10 +18808,10 @@
         <v>1.88</v>
       </c>
       <c r="AP86">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ86">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR86">
         <v>1.39</v>
@@ -18996,7 +19017,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ87">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR87">
         <v>1.32</v>
@@ -19405,10 +19426,10 @@
         <v>0.43</v>
       </c>
       <c r="AP89">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ89">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AR89">
         <v>1.09</v>
@@ -19533,7 +19554,7 @@
         <v>148</v>
       </c>
       <c r="P90" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="Q90">
         <v>4.75</v>
@@ -19614,7 +19635,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ90">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR90">
         <v>0.87</v>
@@ -19817,10 +19838,10 @@
         <v>1</v>
       </c>
       <c r="AP91">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ91">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR91">
         <v>1.97</v>
@@ -19945,7 +19966,7 @@
         <v>150</v>
       </c>
       <c r="P92" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="Q92">
         <v>2.88</v>
@@ -20023,7 +20044,7 @@
         <v>1.29</v>
       </c>
       <c r="AP92">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ92">
         <v>1</v>
@@ -20229,7 +20250,7 @@
         <v>2</v>
       </c>
       <c r="AP93">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ93">
         <v>2</v>
@@ -20357,7 +20378,7 @@
         <v>151</v>
       </c>
       <c r="P94" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q94">
         <v>2.88</v>
@@ -20641,10 +20662,10 @@
         <v>2.29</v>
       </c>
       <c r="AP95">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ95">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR95">
         <v>2.71</v>
@@ -20769,7 +20790,7 @@
         <v>153</v>
       </c>
       <c r="P96" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Q96">
         <v>11</v>
@@ -20847,7 +20868,7 @@
         <v>2.57</v>
       </c>
       <c r="AP96">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ96">
         <v>2.18</v>
@@ -21056,7 +21077,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ97">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AR97">
         <v>1.22</v>
@@ -21593,7 +21614,7 @@
         <v>156</v>
       </c>
       <c r="P100" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="Q100">
         <v>1.73</v>
@@ -21671,7 +21692,7 @@
         <v>2.5</v>
       </c>
       <c r="AP100">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ100">
         <v>2.17</v>
@@ -21799,7 +21820,7 @@
         <v>85</v>
       </c>
       <c r="P101" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q101">
         <v>3.4</v>
@@ -22005,7 +22026,7 @@
         <v>157</v>
       </c>
       <c r="P102" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="Q102">
         <v>3</v>
@@ -22083,10 +22104,10 @@
         <v>1.13</v>
       </c>
       <c r="AP102">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ102">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR102">
         <v>1.32</v>
@@ -22211,7 +22232,7 @@
         <v>158</v>
       </c>
       <c r="P103" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22289,7 +22310,7 @@
         <v>2.13</v>
       </c>
       <c r="AP103">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ103">
         <v>2</v>
@@ -22495,10 +22516,10 @@
         <v>2</v>
       </c>
       <c r="AP104">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ104">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR104">
         <v>1.93</v>
@@ -22910,7 +22931,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ106">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AR106">
         <v>1.69</v>
@@ -23035,7 +23056,7 @@
         <v>162</v>
       </c>
       <c r="P107" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Q107">
         <v>3</v>
@@ -23113,10 +23134,10 @@
         <v>1.67</v>
       </c>
       <c r="AP107">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ107">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR107">
         <v>1.55</v>
@@ -23322,7 +23343,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ108">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR108">
         <v>1.26</v>
@@ -23447,7 +23468,7 @@
         <v>164</v>
       </c>
       <c r="P109" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q109">
         <v>2.75</v>
@@ -23653,7 +23674,7 @@
         <v>165</v>
       </c>
       <c r="P110" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q110">
         <v>2.4</v>
@@ -24065,7 +24086,7 @@
         <v>167</v>
       </c>
       <c r="P112" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Q112">
         <v>1.4</v>
@@ -24143,7 +24164,7 @@
         <v>0.43</v>
       </c>
       <c r="AP112">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ112">
         <v>0.83</v>
@@ -24271,7 +24292,7 @@
         <v>168</v>
       </c>
       <c r="P113" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="Q113">
         <v>4.75</v>
@@ -24349,7 +24370,7 @@
         <v>2.22</v>
       </c>
       <c r="AP113">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ113">
         <v>2.17</v>
@@ -24477,7 +24498,7 @@
         <v>98</v>
       </c>
       <c r="P114" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q114">
         <v>2</v>
@@ -24683,7 +24704,7 @@
         <v>169</v>
       </c>
       <c r="P115" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Q115">
         <v>6</v>
@@ -25095,7 +25116,7 @@
         <v>170</v>
       </c>
       <c r="P117" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25173,10 +25194,10 @@
         <v>0.78</v>
       </c>
       <c r="AP117">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ117">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR117">
         <v>1.49</v>
@@ -25301,7 +25322,7 @@
         <v>85</v>
       </c>
       <c r="P118" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="Q118">
         <v>3.75</v>
@@ -25382,7 +25403,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ118">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR118">
         <v>1.68</v>
@@ -25585,7 +25606,7 @@
         <v>1.1</v>
       </c>
       <c r="AP119">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AQ119">
         <v>1.25</v>
@@ -25791,7 +25812,7 @@
         <v>1.33</v>
       </c>
       <c r="AP120">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ120">
         <v>1</v>
@@ -25919,7 +25940,7 @@
         <v>172</v>
       </c>
       <c r="P121" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Q121">
         <v>2.1</v>
@@ -25997,10 +26018,10 @@
         <v>1.5</v>
       </c>
       <c r="AP121">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ121">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR121">
         <v>1.88</v>
@@ -26206,7 +26227,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ122">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR122">
         <v>1.73</v>
@@ -26412,7 +26433,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ123">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AR123">
         <v>1.34</v>
@@ -26821,7 +26842,7 @@
         <v>1.2</v>
       </c>
       <c r="AP125">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ125">
         <v>1</v>
@@ -26949,7 +26970,7 @@
         <v>175</v>
       </c>
       <c r="P126" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="Q126">
         <v>1.44</v>
@@ -27027,10 +27048,10 @@
         <v>0.9</v>
       </c>
       <c r="AP126">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ126">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR126">
         <v>2.58</v>
@@ -27155,7 +27176,7 @@
         <v>85</v>
       </c>
       <c r="P127" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="Q127">
         <v>2.3</v>
@@ -27361,7 +27382,7 @@
         <v>139</v>
       </c>
       <c r="P128" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="Q128">
         <v>2.75</v>
@@ -27645,10 +27666,10 @@
         <v>1.9</v>
       </c>
       <c r="AP129">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ129">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AR129">
         <v>1.46</v>
@@ -27773,7 +27794,7 @@
         <v>177</v>
       </c>
       <c r="P130" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Q130">
         <v>7</v>
@@ -27979,7 +28000,7 @@
         <v>85</v>
       </c>
       <c r="P131" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q131">
         <v>5.5</v>
@@ -28266,7 +28287,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ132">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AR132">
         <v>1.37</v>
@@ -28391,7 +28412,7 @@
         <v>85</v>
       </c>
       <c r="P133" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Q133">
         <v>2.75</v>
@@ -28469,7 +28490,7 @@
         <v>1.2</v>
       </c>
       <c r="AP133">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ133">
         <v>1.25</v>
@@ -28597,7 +28618,7 @@
         <v>179</v>
       </c>
       <c r="P134" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q134">
         <v>4.75</v>
@@ -28803,7 +28824,7 @@
         <v>180</v>
       </c>
       <c r="P135" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q135">
         <v>2.5</v>
@@ -29009,7 +29030,7 @@
         <v>120</v>
       </c>
       <c r="P136" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="Q136">
         <v>3.75</v>
@@ -29215,7 +29236,7 @@
         <v>181</v>
       </c>
       <c r="P137" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="Q137">
         <v>2.38</v>
@@ -29627,7 +29648,7 @@
         <v>183</v>
       </c>
       <c r="P139" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q139">
         <v>2.7</v>
@@ -29784,6 +29805,1036 @@
       </c>
       <c r="BP139">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="140" spans="1:68">
+      <c r="A140" s="1">
+        <v>139</v>
+      </c>
+      <c r="B140">
+        <v>7817176</v>
+      </c>
+      <c r="C140" t="s">
+        <v>68</v>
+      </c>
+      <c r="D140" t="s">
+        <v>69</v>
+      </c>
+      <c r="E140" s="2">
+        <v>45689.38541666666</v>
+      </c>
+      <c r="F140">
+        <v>2</v>
+      </c>
+      <c r="G140" t="s">
+        <v>76</v>
+      </c>
+      <c r="H140" t="s">
+        <v>80</v>
+      </c>
+      <c r="I140">
+        <v>0</v>
+      </c>
+      <c r="J140">
+        <v>0</v>
+      </c>
+      <c r="K140">
+        <v>0</v>
+      </c>
+      <c r="L140">
+        <v>0</v>
+      </c>
+      <c r="M140">
+        <v>0</v>
+      </c>
+      <c r="N140">
+        <v>0</v>
+      </c>
+      <c r="O140" t="s">
+        <v>85</v>
+      </c>
+      <c r="P140" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q140">
+        <v>3</v>
+      </c>
+      <c r="R140">
+        <v>1.95</v>
+      </c>
+      <c r="S140">
+        <v>3.75</v>
+      </c>
+      <c r="T140">
+        <v>1.5</v>
+      </c>
+      <c r="U140">
+        <v>2.5</v>
+      </c>
+      <c r="V140">
+        <v>3.5</v>
+      </c>
+      <c r="W140">
+        <v>1.29</v>
+      </c>
+      <c r="X140">
+        <v>8.5</v>
+      </c>
+      <c r="Y140">
+        <v>1.05</v>
+      </c>
+      <c r="Z140">
+        <v>1.87</v>
+      </c>
+      <c r="AA140">
+        <v>3.5</v>
+      </c>
+      <c r="AB140">
+        <v>4</v>
+      </c>
+      <c r="AC140">
+        <v>1.07</v>
+      </c>
+      <c r="AD140">
+        <v>7.5</v>
+      </c>
+      <c r="AE140">
+        <v>1.3</v>
+      </c>
+      <c r="AF140">
+        <v>3.1</v>
+      </c>
+      <c r="AG140">
+        <v>2.2</v>
+      </c>
+      <c r="AH140">
+        <v>1.55</v>
+      </c>
+      <c r="AI140">
+        <v>2</v>
+      </c>
+      <c r="AJ140">
+        <v>1.73</v>
+      </c>
+      <c r="AK140">
+        <v>1.29</v>
+      </c>
+      <c r="AL140">
+        <v>1.29</v>
+      </c>
+      <c r="AM140">
+        <v>1.67</v>
+      </c>
+      <c r="AN140">
+        <v>2.18</v>
+      </c>
+      <c r="AO140">
+        <v>1.82</v>
+      </c>
+      <c r="AP140">
+        <v>2.08</v>
+      </c>
+      <c r="AQ140">
+        <v>1.75</v>
+      </c>
+      <c r="AR140">
+        <v>1.75</v>
+      </c>
+      <c r="AS140">
+        <v>1.37</v>
+      </c>
+      <c r="AT140">
+        <v>3.12</v>
+      </c>
+      <c r="AU140">
+        <v>2</v>
+      </c>
+      <c r="AV140">
+        <v>3</v>
+      </c>
+      <c r="AW140">
+        <v>2</v>
+      </c>
+      <c r="AX140">
+        <v>3</v>
+      </c>
+      <c r="AY140">
+        <v>4</v>
+      </c>
+      <c r="AZ140">
+        <v>6</v>
+      </c>
+      <c r="BA140">
+        <v>3</v>
+      </c>
+      <c r="BB140">
+        <v>7</v>
+      </c>
+      <c r="BC140">
+        <v>10</v>
+      </c>
+      <c r="BD140">
+        <v>0</v>
+      </c>
+      <c r="BE140">
+        <v>0</v>
+      </c>
+      <c r="BF140">
+        <v>0</v>
+      </c>
+      <c r="BG140">
+        <v>0</v>
+      </c>
+      <c r="BH140">
+        <v>0</v>
+      </c>
+      <c r="BI140">
+        <v>0</v>
+      </c>
+      <c r="BJ140">
+        <v>0</v>
+      </c>
+      <c r="BK140">
+        <v>0</v>
+      </c>
+      <c r="BL140">
+        <v>0</v>
+      </c>
+      <c r="BM140">
+        <v>0</v>
+      </c>
+      <c r="BN140">
+        <v>0</v>
+      </c>
+      <c r="BO140">
+        <v>0</v>
+      </c>
+      <c r="BP140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:68">
+      <c r="A141" s="1">
+        <v>140</v>
+      </c>
+      <c r="B141">
+        <v>7817180</v>
+      </c>
+      <c r="C141" t="s">
+        <v>68</v>
+      </c>
+      <c r="D141" t="s">
+        <v>69</v>
+      </c>
+      <c r="E141" s="2">
+        <v>45689.47916666666</v>
+      </c>
+      <c r="F141">
+        <v>2</v>
+      </c>
+      <c r="G141" t="s">
+        <v>73</v>
+      </c>
+      <c r="H141" t="s">
+        <v>70</v>
+      </c>
+      <c r="I141">
+        <v>1</v>
+      </c>
+      <c r="J141">
+        <v>0</v>
+      </c>
+      <c r="K141">
+        <v>1</v>
+      </c>
+      <c r="L141">
+        <v>1</v>
+      </c>
+      <c r="M141">
+        <v>0</v>
+      </c>
+      <c r="N141">
+        <v>1</v>
+      </c>
+      <c r="O141" t="s">
+        <v>184</v>
+      </c>
+      <c r="P141" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q141">
+        <v>2.1</v>
+      </c>
+      <c r="R141">
+        <v>2.3</v>
+      </c>
+      <c r="S141">
+        <v>5</v>
+      </c>
+      <c r="T141">
+        <v>1.33</v>
+      </c>
+      <c r="U141">
+        <v>3.25</v>
+      </c>
+      <c r="V141">
+        <v>2.63</v>
+      </c>
+      <c r="W141">
+        <v>1.44</v>
+      </c>
+      <c r="X141">
+        <v>6</v>
+      </c>
+      <c r="Y141">
+        <v>1.11</v>
+      </c>
+      <c r="Z141">
+        <v>1.6</v>
+      </c>
+      <c r="AA141">
+        <v>3.95</v>
+      </c>
+      <c r="AB141">
+        <v>5.2</v>
+      </c>
+      <c r="AC141">
+        <v>1.01</v>
+      </c>
+      <c r="AD141">
+        <v>13</v>
+      </c>
+      <c r="AE141">
+        <v>1.22</v>
+      </c>
+      <c r="AF141">
+        <v>3.95</v>
+      </c>
+      <c r="AG141">
+        <v>1.65</v>
+      </c>
+      <c r="AH141">
+        <v>2</v>
+      </c>
+      <c r="AI141">
+        <v>1.8</v>
+      </c>
+      <c r="AJ141">
+        <v>1.91</v>
+      </c>
+      <c r="AK141">
+        <v>1.17</v>
+      </c>
+      <c r="AL141">
+        <v>1.22</v>
+      </c>
+      <c r="AM141">
+        <v>2.13</v>
+      </c>
+      <c r="AN141">
+        <v>1.27</v>
+      </c>
+      <c r="AO141">
+        <v>0.82</v>
+      </c>
+      <c r="AP141">
+        <v>1.42</v>
+      </c>
+      <c r="AQ141">
+        <v>0.75</v>
+      </c>
+      <c r="AR141">
+        <v>1.54</v>
+      </c>
+      <c r="AS141">
+        <v>1.27</v>
+      </c>
+      <c r="AT141">
+        <v>2.81</v>
+      </c>
+      <c r="AU141">
+        <v>4</v>
+      </c>
+      <c r="AV141">
+        <v>2</v>
+      </c>
+      <c r="AW141">
+        <v>4</v>
+      </c>
+      <c r="AX141">
+        <v>4</v>
+      </c>
+      <c r="AY141">
+        <v>8</v>
+      </c>
+      <c r="AZ141">
+        <v>6</v>
+      </c>
+      <c r="BA141">
+        <v>9</v>
+      </c>
+      <c r="BB141">
+        <v>5</v>
+      </c>
+      <c r="BC141">
+        <v>14</v>
+      </c>
+      <c r="BD141">
+        <v>1.43</v>
+      </c>
+      <c r="BE141">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF141">
+        <v>3.22</v>
+      </c>
+      <c r="BG141">
+        <v>1.2</v>
+      </c>
+      <c r="BH141">
+        <v>4</v>
+      </c>
+      <c r="BI141">
+        <v>1.33</v>
+      </c>
+      <c r="BJ141">
+        <v>3</v>
+      </c>
+      <c r="BK141">
+        <v>1.49</v>
+      </c>
+      <c r="BL141">
+        <v>2.37</v>
+      </c>
+      <c r="BM141">
+        <v>1.92</v>
+      </c>
+      <c r="BN141">
+        <v>1.85</v>
+      </c>
+      <c r="BO141">
+        <v>2.28</v>
+      </c>
+      <c r="BP141">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="142" spans="1:68">
+      <c r="A142" s="1">
+        <v>141</v>
+      </c>
+      <c r="B142">
+        <v>7817179</v>
+      </c>
+      <c r="C142" t="s">
+        <v>68</v>
+      </c>
+      <c r="D142" t="s">
+        <v>69</v>
+      </c>
+      <c r="E142" s="2">
+        <v>45689.47916666666</v>
+      </c>
+      <c r="F142">
+        <v>2</v>
+      </c>
+      <c r="G142" t="s">
+        <v>74</v>
+      </c>
+      <c r="H142" t="s">
+        <v>78</v>
+      </c>
+      <c r="I142">
+        <v>0</v>
+      </c>
+      <c r="J142">
+        <v>1</v>
+      </c>
+      <c r="K142">
+        <v>1</v>
+      </c>
+      <c r="L142">
+        <v>2</v>
+      </c>
+      <c r="M142">
+        <v>3</v>
+      </c>
+      <c r="N142">
+        <v>5</v>
+      </c>
+      <c r="O142" t="s">
+        <v>185</v>
+      </c>
+      <c r="P142" t="s">
+        <v>262</v>
+      </c>
+      <c r="Q142">
+        <v>2.1</v>
+      </c>
+      <c r="R142">
+        <v>2.4</v>
+      </c>
+      <c r="S142">
+        <v>4.5</v>
+      </c>
+      <c r="T142">
+        <v>1.29</v>
+      </c>
+      <c r="U142">
+        <v>3.5</v>
+      </c>
+      <c r="V142">
+        <v>2.25</v>
+      </c>
+      <c r="W142">
+        <v>1.57</v>
+      </c>
+      <c r="X142">
+        <v>5</v>
+      </c>
+      <c r="Y142">
+        <v>1.14</v>
+      </c>
+      <c r="Z142">
+        <v>1.65</v>
+      </c>
+      <c r="AA142">
+        <v>4.2</v>
+      </c>
+      <c r="AB142">
+        <v>4.5</v>
+      </c>
+      <c r="AC142">
+        <v>1</v>
+      </c>
+      <c r="AD142">
+        <v>17</v>
+      </c>
+      <c r="AE142">
+        <v>1.18</v>
+      </c>
+      <c r="AF142">
+        <v>4.4</v>
+      </c>
+      <c r="AG142">
+        <v>1.65</v>
+      </c>
+      <c r="AH142">
+        <v>2.05</v>
+      </c>
+      <c r="AI142">
+        <v>1.62</v>
+      </c>
+      <c r="AJ142">
+        <v>2.2</v>
+      </c>
+      <c r="AK142">
+        <v>1.19</v>
+      </c>
+      <c r="AL142">
+        <v>1.22</v>
+      </c>
+      <c r="AM142">
+        <v>2.06</v>
+      </c>
+      <c r="AN142">
+        <v>1.09</v>
+      </c>
+      <c r="AO142">
+        <v>0.27</v>
+      </c>
+      <c r="AP142">
+        <v>1</v>
+      </c>
+      <c r="AQ142">
+        <v>0.5</v>
+      </c>
+      <c r="AR142">
+        <v>1.39</v>
+      </c>
+      <c r="AS142">
+        <v>0.91</v>
+      </c>
+      <c r="AT142">
+        <v>2.3</v>
+      </c>
+      <c r="AU142">
+        <v>5</v>
+      </c>
+      <c r="AV142">
+        <v>8</v>
+      </c>
+      <c r="AW142">
+        <v>5</v>
+      </c>
+      <c r="AX142">
+        <v>8</v>
+      </c>
+      <c r="AY142">
+        <v>10</v>
+      </c>
+      <c r="AZ142">
+        <v>16</v>
+      </c>
+      <c r="BA142">
+        <v>4</v>
+      </c>
+      <c r="BB142">
+        <v>7</v>
+      </c>
+      <c r="BC142">
+        <v>11</v>
+      </c>
+      <c r="BD142">
+        <v>0</v>
+      </c>
+      <c r="BE142">
+        <v>0</v>
+      </c>
+      <c r="BF142">
+        <v>0</v>
+      </c>
+      <c r="BG142">
+        <v>0</v>
+      </c>
+      <c r="BH142">
+        <v>0</v>
+      </c>
+      <c r="BI142">
+        <v>0</v>
+      </c>
+      <c r="BJ142">
+        <v>0</v>
+      </c>
+      <c r="BK142">
+        <v>0</v>
+      </c>
+      <c r="BL142">
+        <v>0</v>
+      </c>
+      <c r="BM142">
+        <v>0</v>
+      </c>
+      <c r="BN142">
+        <v>0</v>
+      </c>
+      <c r="BO142">
+        <v>0</v>
+      </c>
+      <c r="BP142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:68">
+      <c r="A143" s="1">
+        <v>142</v>
+      </c>
+      <c r="B143">
+        <v>7817177</v>
+      </c>
+      <c r="C143" t="s">
+        <v>68</v>
+      </c>
+      <c r="D143" t="s">
+        <v>69</v>
+      </c>
+      <c r="E143" s="2">
+        <v>45689.47916666666</v>
+      </c>
+      <c r="F143">
+        <v>2</v>
+      </c>
+      <c r="G143" t="s">
+        <v>81</v>
+      </c>
+      <c r="H143" t="s">
+        <v>75</v>
+      </c>
+      <c r="I143">
+        <v>1</v>
+      </c>
+      <c r="J143">
+        <v>1</v>
+      </c>
+      <c r="K143">
+        <v>2</v>
+      </c>
+      <c r="L143">
+        <v>3</v>
+      </c>
+      <c r="M143">
+        <v>1</v>
+      </c>
+      <c r="N143">
+        <v>4</v>
+      </c>
+      <c r="O143" t="s">
+        <v>186</v>
+      </c>
+      <c r="P143" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q143">
+        <v>1.53</v>
+      </c>
+      <c r="R143">
+        <v>2.88</v>
+      </c>
+      <c r="S143">
+        <v>9.5</v>
+      </c>
+      <c r="T143">
+        <v>1.22</v>
+      </c>
+      <c r="U143">
+        <v>4</v>
+      </c>
+      <c r="V143">
+        <v>2.1</v>
+      </c>
+      <c r="W143">
+        <v>1.67</v>
+      </c>
+      <c r="X143">
+        <v>4.33</v>
+      </c>
+      <c r="Y143">
+        <v>1.2</v>
+      </c>
+      <c r="Z143">
+        <v>1.17</v>
+      </c>
+      <c r="AA143">
+        <v>6.25</v>
+      </c>
+      <c r="AB143">
+        <v>12</v>
+      </c>
+      <c r="AC143">
+        <v>1</v>
+      </c>
+      <c r="AD143">
+        <v>19</v>
+      </c>
+      <c r="AE143">
+        <v>1.1</v>
+      </c>
+      <c r="AF143">
+        <v>6.2</v>
+      </c>
+      <c r="AG143">
+        <v>1.44</v>
+      </c>
+      <c r="AH143">
+        <v>2.63</v>
+      </c>
+      <c r="AI143">
+        <v>2.1</v>
+      </c>
+      <c r="AJ143">
+        <v>1.67</v>
+      </c>
+      <c r="AK143">
+        <v>1.03</v>
+      </c>
+      <c r="AL143">
+        <v>1.06</v>
+      </c>
+      <c r="AM143">
+        <v>4.6</v>
+      </c>
+      <c r="AN143">
+        <v>2.45</v>
+      </c>
+      <c r="AO143">
+        <v>1.45</v>
+      </c>
+      <c r="AP143">
+        <v>2.5</v>
+      </c>
+      <c r="AQ143">
+        <v>1.33</v>
+      </c>
+      <c r="AR143">
+        <v>2.6</v>
+      </c>
+      <c r="AS143">
+        <v>1.36</v>
+      </c>
+      <c r="AT143">
+        <v>3.96</v>
+      </c>
+      <c r="AU143">
+        <v>12</v>
+      </c>
+      <c r="AV143">
+        <v>3</v>
+      </c>
+      <c r="AW143">
+        <v>9</v>
+      </c>
+      <c r="AX143">
+        <v>2</v>
+      </c>
+      <c r="AY143">
+        <v>21</v>
+      </c>
+      <c r="AZ143">
+        <v>5</v>
+      </c>
+      <c r="BA143">
+        <v>6</v>
+      </c>
+      <c r="BB143">
+        <v>0</v>
+      </c>
+      <c r="BC143">
+        <v>6</v>
+      </c>
+      <c r="BD143">
+        <v>0</v>
+      </c>
+      <c r="BE143">
+        <v>0</v>
+      </c>
+      <c r="BF143">
+        <v>0</v>
+      </c>
+      <c r="BG143">
+        <v>0</v>
+      </c>
+      <c r="BH143">
+        <v>0</v>
+      </c>
+      <c r="BI143">
+        <v>0</v>
+      </c>
+      <c r="BJ143">
+        <v>0</v>
+      </c>
+      <c r="BK143">
+        <v>0</v>
+      </c>
+      <c r="BL143">
+        <v>0</v>
+      </c>
+      <c r="BM143">
+        <v>0</v>
+      </c>
+      <c r="BN143">
+        <v>0</v>
+      </c>
+      <c r="BO143">
+        <v>0</v>
+      </c>
+      <c r="BP143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:68">
+      <c r="A144" s="1">
+        <v>143</v>
+      </c>
+      <c r="B144">
+        <v>7817178</v>
+      </c>
+      <c r="C144" t="s">
+        <v>68</v>
+      </c>
+      <c r="D144" t="s">
+        <v>69</v>
+      </c>
+      <c r="E144" s="2">
+        <v>45689.47916666666</v>
+      </c>
+      <c r="F144">
+        <v>2</v>
+      </c>
+      <c r="G144" t="s">
+        <v>71</v>
+      </c>
+      <c r="H144" t="s">
+        <v>72</v>
+      </c>
+      <c r="I144">
+        <v>2</v>
+      </c>
+      <c r="J144">
+        <v>1</v>
+      </c>
+      <c r="K144">
+        <v>3</v>
+      </c>
+      <c r="L144">
+        <v>3</v>
+      </c>
+      <c r="M144">
+        <v>1</v>
+      </c>
+      <c r="N144">
+        <v>4</v>
+      </c>
+      <c r="O144" t="s">
+        <v>187</v>
+      </c>
+      <c r="P144" t="s">
+        <v>264</v>
+      </c>
+      <c r="Q144">
+        <v>2.4</v>
+      </c>
+      <c r="R144">
+        <v>2.3</v>
+      </c>
+      <c r="S144">
+        <v>3.75</v>
+      </c>
+      <c r="T144">
+        <v>1.3</v>
+      </c>
+      <c r="U144">
+        <v>3.4</v>
+      </c>
+      <c r="V144">
+        <v>2.38</v>
+      </c>
+      <c r="W144">
+        <v>1.53</v>
+      </c>
+      <c r="X144">
+        <v>5.5</v>
+      </c>
+      <c r="Y144">
+        <v>1.13</v>
+      </c>
+      <c r="Z144">
+        <v>1.71</v>
+      </c>
+      <c r="AA144">
+        <v>3.91</v>
+      </c>
+      <c r="AB144">
+        <v>4.4</v>
+      </c>
+      <c r="AC144">
+        <v>1.01</v>
+      </c>
+      <c r="AD144">
+        <v>15</v>
+      </c>
+      <c r="AE144">
+        <v>1.18</v>
+      </c>
+      <c r="AF144">
+        <v>4.5</v>
+      </c>
+      <c r="AG144">
+        <v>1.57</v>
+      </c>
+      <c r="AH144">
+        <v>2.15</v>
+      </c>
+      <c r="AI144">
+        <v>1.57</v>
+      </c>
+      <c r="AJ144">
+        <v>2.25</v>
+      </c>
+      <c r="AK144">
+        <v>1.26</v>
+      </c>
+      <c r="AL144">
+        <v>1.25</v>
+      </c>
+      <c r="AM144">
+        <v>1.8</v>
+      </c>
+      <c r="AN144">
+        <v>1.64</v>
+      </c>
+      <c r="AO144">
+        <v>0.64</v>
+      </c>
+      <c r="AP144">
+        <v>1.75</v>
+      </c>
+      <c r="AQ144">
+        <v>0.58</v>
+      </c>
+      <c r="AR144">
+        <v>1.44</v>
+      </c>
+      <c r="AS144">
+        <v>1.47</v>
+      </c>
+      <c r="AT144">
+        <v>2.91</v>
+      </c>
+      <c r="AU144">
+        <v>5</v>
+      </c>
+      <c r="AV144">
+        <v>4</v>
+      </c>
+      <c r="AW144">
+        <v>3</v>
+      </c>
+      <c r="AX144">
+        <v>4</v>
+      </c>
+      <c r="AY144">
+        <v>8</v>
+      </c>
+      <c r="AZ144">
+        <v>8</v>
+      </c>
+      <c r="BA144">
+        <v>6</v>
+      </c>
+      <c r="BB144">
+        <v>1</v>
+      </c>
+      <c r="BC144">
+        <v>7</v>
+      </c>
+      <c r="BD144">
+        <v>1.61</v>
+      </c>
+      <c r="BE144">
+        <v>8.6</v>
+      </c>
+      <c r="BF144">
+        <v>2.62</v>
+      </c>
+      <c r="BG144">
+        <v>1.22</v>
+      </c>
+      <c r="BH144">
+        <v>3.8</v>
+      </c>
+      <c r="BI144">
+        <v>1.38</v>
+      </c>
+      <c r="BJ144">
+        <v>2.8</v>
+      </c>
+      <c r="BK144">
+        <v>1.61</v>
+      </c>
+      <c r="BL144">
+        <v>2.2</v>
+      </c>
+      <c r="BM144">
+        <v>1.99</v>
+      </c>
+      <c r="BN144">
+        <v>1.76</v>
+      </c>
+      <c r="BO144">
+        <v>2.4</v>
+      </c>
+      <c r="BP144">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Wales Welsh Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Wales Welsh Premier League_20242025.xlsx
@@ -505,10 +505,10 @@
     <t>['46', '54']</t>
   </si>
   <si>
-    <t>['83', '88']</t>
+    <t>['35', '44', '82']</t>
   </si>
   <si>
-    <t>['35', '44', '82']</t>
+    <t>['83', '88']</t>
   </si>
   <si>
     <t>['37', '70', '89']</t>
@@ -523,10 +523,10 @@
     <t>['22']</t>
   </si>
   <si>
-    <t>['5', '18']</t>
+    <t>['21', '24', '29', '31', '39', '44', '63']</t>
   </si>
   <si>
-    <t>['21', '24', '29', '31', '39', '44', '63']</t>
+    <t>['5', '18']</t>
   </si>
   <si>
     <t>['27', '36']</t>
@@ -538,19 +538,19 @@
     <t>['53', '87']</t>
   </si>
   <si>
+    <t>['63', '90+9']</t>
+  </si>
+  <si>
     <t>['43', '51', '55', '62', '63']</t>
   </si>
   <si>
-    <t>['63', '90+9']</t>
-  </si>
-  <si>
-    <t>['24']</t>
+    <t>['47', '80', '84']</t>
   </si>
   <si>
     <t>['51']</t>
   </si>
   <si>
-    <t>['47', '80', '84']</t>
+    <t>['24']</t>
   </si>
   <si>
     <t>['63', '90+4']</t>
@@ -571,13 +571,13 @@
     <t>['17']</t>
   </si>
   <si>
+    <t>['3', '32', '72']</t>
+  </si>
+  <si>
     <t>['50', '78']</t>
   </si>
   <si>
     <t>['2', '53', '68']</t>
-  </si>
-  <si>
-    <t>['3', '32', '72']</t>
   </si>
   <si>
     <t>['45+2']</t>
@@ -757,13 +757,13 @@
     <t>['25', '70', '83']</t>
   </si>
   <si>
-    <t>['2', '11', '40', '73', '74']</t>
+    <t>['10', '71']</t>
   </si>
   <si>
     <t>['33', '69']</t>
   </si>
   <si>
-    <t>['10', '71']</t>
+    <t>['2', '11', '40', '73', '74']</t>
   </si>
   <si>
     <t>['63', '70']</t>
@@ -778,10 +778,10 @@
     <t>['11', '28', '49', '54', '89', '90+2']</t>
   </si>
   <si>
-    <t>['5', '47']</t>
+    <t>['39', '89']</t>
   </si>
   <si>
-    <t>['39', '89']</t>
+    <t>['5', '47']</t>
   </si>
   <si>
     <t>['59', '65']</t>
@@ -802,13 +802,13 @@
     <t>['6', '14', '90+2']</t>
   </si>
   <si>
+    <t>['25']</t>
+  </si>
+  <si>
     <t>['4', '58', '70']</t>
   </si>
   <si>
     <t>['16']</t>
-  </si>
-  <si>
-    <t>['25']</t>
   </si>
 </sst>
 </file>
@@ -23220,7 +23220,7 @@
         <v>107</v>
       </c>
       <c r="B108">
-        <v>7727610</v>
+        <v>7727594</v>
       </c>
       <c r="C108" t="s">
         <v>68</v>
@@ -23232,58 +23232,58 @@
         <v>45640.47916666666</v>
       </c>
       <c r="F108">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G108" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H108" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I108">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J108">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K108">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L108">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M108">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N108">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O108" t="s">
         <v>163</v>
       </c>
       <c r="P108" t="s">
-        <v>85</v>
+        <v>242</v>
       </c>
       <c r="Q108">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="R108">
         <v>2.3</v>
       </c>
       <c r="S108">
-        <v>4.75</v>
+        <v>3.25</v>
       </c>
       <c r="T108">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="U108">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="V108">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="W108">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="X108">
         <v>5.5</v>
@@ -23292,94 +23292,94 @@
         <v>1.13</v>
       </c>
       <c r="Z108">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AA108">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AB108">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="AC108">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AD108">
+        <v>16</v>
+      </c>
+      <c r="AE108">
+        <v>1.16</v>
+      </c>
+      <c r="AF108">
+        <v>5</v>
+      </c>
+      <c r="AG108">
+        <v>1.57</v>
+      </c>
+      <c r="AH108">
+        <v>2.25</v>
+      </c>
+      <c r="AI108">
+        <v>1.53</v>
+      </c>
+      <c r="AJ108">
+        <v>2.38</v>
+      </c>
+      <c r="AK108">
+        <v>1.28</v>
+      </c>
+      <c r="AL108">
+        <v>1.23</v>
+      </c>
+      <c r="AM108">
+        <v>1.59</v>
+      </c>
+      <c r="AN108">
+        <v>0.88</v>
+      </c>
+      <c r="AO108">
+        <v>1.38</v>
+      </c>
+      <c r="AP108">
+        <v>1.18</v>
+      </c>
+      <c r="AQ108">
+        <v>1.25</v>
+      </c>
+      <c r="AR108">
+        <v>1.33</v>
+      </c>
+      <c r="AS108">
+        <v>1.32</v>
+      </c>
+      <c r="AT108">
+        <v>2.65</v>
+      </c>
+      <c r="AU108">
         <v>11</v>
       </c>
-      <c r="AE108">
-        <v>1.22</v>
-      </c>
-      <c r="AF108">
-        <v>4</v>
-      </c>
-      <c r="AG108">
-        <v>1.7</v>
-      </c>
-      <c r="AH108">
-        <v>2.05</v>
-      </c>
-      <c r="AI108">
-        <v>1.73</v>
-      </c>
-      <c r="AJ108">
-        <v>2</v>
-      </c>
-      <c r="AK108">
-        <v>1.19</v>
-      </c>
-      <c r="AL108">
-        <v>1.21</v>
-      </c>
-      <c r="AM108">
-        <v>1.81</v>
-      </c>
-      <c r="AN108">
-        <v>1.63</v>
-      </c>
-      <c r="AO108">
-        <v>0.88</v>
-      </c>
-      <c r="AP108">
-        <v>1.58</v>
-      </c>
-      <c r="AQ108">
-        <v>0.58</v>
-      </c>
-      <c r="AR108">
-        <v>1.26</v>
-      </c>
-      <c r="AS108">
-        <v>1.45</v>
-      </c>
-      <c r="AT108">
-        <v>2.71</v>
-      </c>
-      <c r="AU108">
+      <c r="AV108">
+        <v>7</v>
+      </c>
+      <c r="AW108">
+        <v>3</v>
+      </c>
+      <c r="AX108">
+        <v>5</v>
+      </c>
+      <c r="AY108">
+        <v>18</v>
+      </c>
+      <c r="AZ108">
         <v>15</v>
       </c>
-      <c r="AV108">
-        <v>8</v>
-      </c>
-      <c r="AW108">
-        <v>6</v>
-      </c>
-      <c r="AX108">
-        <v>6</v>
-      </c>
-      <c r="AY108">
-        <v>21</v>
-      </c>
-      <c r="AZ108">
-        <v>14</v>
-      </c>
       <c r="BA108">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="BB108">
         <v>3</v>
       </c>
       <c r="BC108">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="BD108">
         <v>0</v>
@@ -23426,7 +23426,7 @@
         <v>108</v>
       </c>
       <c r="B109">
-        <v>7727594</v>
+        <v>7727610</v>
       </c>
       <c r="C109" t="s">
         <v>68</v>
@@ -23438,58 +23438,58 @@
         <v>45640.47916666666</v>
       </c>
       <c r="F109">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G109" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H109" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I109">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J109">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K109">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L109">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M109">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N109">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O109" t="s">
         <v>164</v>
       </c>
       <c r="P109" t="s">
-        <v>242</v>
+        <v>85</v>
       </c>
       <c r="Q109">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="R109">
         <v>2.3</v>
       </c>
       <c r="S109">
+        <v>4.75</v>
+      </c>
+      <c r="T109">
+        <v>1.33</v>
+      </c>
+      <c r="U109">
         <v>3.25</v>
       </c>
-      <c r="T109">
-        <v>1.3</v>
-      </c>
-      <c r="U109">
-        <v>3.4</v>
-      </c>
       <c r="V109">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="W109">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="X109">
         <v>5.5</v>
@@ -23498,94 +23498,94 @@
         <v>1.13</v>
       </c>
       <c r="Z109">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AA109">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AB109">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="AC109">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AD109">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AE109">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AF109">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG109">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AH109">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AI109">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AJ109">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AK109">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AL109">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AM109">
-        <v>1.59</v>
+        <v>1.81</v>
       </c>
       <c r="AN109">
+        <v>1.63</v>
+      </c>
+      <c r="AO109">
         <v>0.88</v>
       </c>
-      <c r="AO109">
-        <v>1.38</v>
-      </c>
       <c r="AP109">
-        <v>1.18</v>
+        <v>1.58</v>
       </c>
       <c r="AQ109">
-        <v>1.25</v>
+        <v>0.58</v>
       </c>
       <c r="AR109">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AS109">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="AT109">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="AU109">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AV109">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW109">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AX109">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY109">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AZ109">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA109">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="BB109">
         <v>3</v>
       </c>
       <c r="BC109">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="BD109">
         <v>0</v>
@@ -24662,7 +24662,7 @@
         <v>114</v>
       </c>
       <c r="B115">
-        <v>7727615</v>
+        <v>7727617</v>
       </c>
       <c r="C115" t="s">
         <v>68</v>
@@ -24677,190 +24677,190 @@
         <v>20</v>
       </c>
       <c r="G115" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="H115" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I115">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J115">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K115">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L115">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M115">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N115">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O115" t="s">
-        <v>169</v>
+        <v>85</v>
       </c>
       <c r="P115" t="s">
         <v>247</v>
       </c>
       <c r="Q115">
-        <v>6</v>
+        <v>3.75</v>
       </c>
       <c r="R115">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="S115">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="T115">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="U115">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="V115">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="W115">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="X115">
-        <v>4.33</v>
+        <v>7</v>
       </c>
       <c r="Y115">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="Z115">
-        <v>6</v>
+        <v>3.4</v>
       </c>
       <c r="AA115">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="AB115">
-        <v>1.36</v>
+        <v>1.9</v>
       </c>
       <c r="AC115">
         <v>1.01</v>
       </c>
       <c r="AD115">
-        <v>19.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AE115">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="AF115">
-        <v>5.1</v>
+        <v>3.22</v>
       </c>
       <c r="AG115">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="AH115">
-        <v>2.63</v>
+        <v>1.8</v>
       </c>
       <c r="AI115">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AJ115">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AK115">
-        <v>2.83</v>
+        <v>1.64</v>
       </c>
       <c r="AL115">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="AM115">
-        <v>1.07</v>
+        <v>1.29</v>
       </c>
       <c r="AN115">
         <v>1.11</v>
       </c>
       <c r="AO115">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AP115">
-        <v>1.18</v>
+        <v>0.92</v>
       </c>
       <c r="AQ115">
-        <v>2.18</v>
+        <v>1.75</v>
       </c>
       <c r="AR115">
+        <v>1.68</v>
+      </c>
+      <c r="AS115">
+        <v>1.33</v>
+      </c>
+      <c r="AT115">
+        <v>3.01</v>
+      </c>
+      <c r="AU115">
+        <v>2</v>
+      </c>
+      <c r="AV115">
+        <v>6</v>
+      </c>
+      <c r="AW115">
+        <v>7</v>
+      </c>
+      <c r="AX115">
+        <v>4</v>
+      </c>
+      <c r="AY115">
+        <v>9</v>
+      </c>
+      <c r="AZ115">
+        <v>11</v>
+      </c>
+      <c r="BA115">
+        <v>4</v>
+      </c>
+      <c r="BB115">
+        <v>3</v>
+      </c>
+      <c r="BC115">
+        <v>7</v>
+      </c>
+      <c r="BD115">
+        <v>2.96</v>
+      </c>
+      <c r="BE115">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF115">
+        <v>1.52</v>
+      </c>
+      <c r="BG115">
         <v>1.4</v>
       </c>
-      <c r="AS115">
-        <v>2.24</v>
-      </c>
-      <c r="AT115">
-        <v>3.64</v>
-      </c>
-      <c r="AU115">
-        <v>5</v>
-      </c>
-      <c r="AV115">
-        <v>12</v>
-      </c>
-      <c r="AW115">
-        <v>3</v>
-      </c>
-      <c r="AX115">
-        <v>6</v>
-      </c>
-      <c r="AY115">
-        <v>11</v>
-      </c>
-      <c r="AZ115">
-        <v>23</v>
-      </c>
-      <c r="BA115">
-        <v>6</v>
-      </c>
-      <c r="BB115">
-        <v>6</v>
-      </c>
-      <c r="BC115">
-        <v>12</v>
-      </c>
-      <c r="BD115">
-        <v>6.5</v>
-      </c>
-      <c r="BE115">
-        <v>12.25</v>
-      </c>
-      <c r="BF115">
-        <v>1.13</v>
-      </c>
-      <c r="BG115">
-        <v>1.21</v>
-      </c>
       <c r="BH115">
-        <v>4.15</v>
+        <v>2.8</v>
       </c>
       <c r="BI115">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="BJ115">
-        <v>2.83</v>
+        <v>2.11</v>
       </c>
       <c r="BK115">
-        <v>1.59</v>
+        <v>2.12</v>
       </c>
       <c r="BL115">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="BM115">
-        <v>2.05</v>
+        <v>2.77</v>
       </c>
       <c r="BN115">
-        <v>1.7</v>
+        <v>1.41</v>
       </c>
       <c r="BO115">
-        <v>2.56</v>
+        <v>3.85</v>
       </c>
       <c r="BP115">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="116" spans="1:68">
@@ -25113,7 +25113,7 @@
         <v>9</v>
       </c>
       <c r="O117" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P117" t="s">
         <v>248</v>
@@ -25280,7 +25280,7 @@
         <v>117</v>
       </c>
       <c r="B118">
-        <v>7727617</v>
+        <v>7727615</v>
       </c>
       <c r="C118" t="s">
         <v>68</v>
@@ -25295,190 +25295,190 @@
         <v>20</v>
       </c>
       <c r="G118" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="H118" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I118">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J118">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K118">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L118">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M118">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N118">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O118" t="s">
-        <v>85</v>
+        <v>170</v>
       </c>
       <c r="P118" t="s">
         <v>249</v>
       </c>
       <c r="Q118">
+        <v>6</v>
+      </c>
+      <c r="R118">
+        <v>2.6</v>
+      </c>
+      <c r="S118">
+        <v>1.8</v>
+      </c>
+      <c r="T118">
+        <v>1.25</v>
+      </c>
+      <c r="U118">
         <v>3.75</v>
       </c>
-      <c r="R118">
+      <c r="V118">
         <v>2.1</v>
       </c>
-      <c r="S118">
-        <v>2.75</v>
-      </c>
-      <c r="T118">
-        <v>1.4</v>
-      </c>
-      <c r="U118">
-        <v>2.75</v>
-      </c>
-      <c r="V118">
-        <v>3</v>
-      </c>
       <c r="W118">
+        <v>1.67</v>
+      </c>
+      <c r="X118">
+        <v>4.33</v>
+      </c>
+      <c r="Y118">
+        <v>1.2</v>
+      </c>
+      <c r="Z118">
+        <v>6</v>
+      </c>
+      <c r="AA118">
+        <v>4.75</v>
+      </c>
+      <c r="AB118">
         <v>1.36</v>
-      </c>
-      <c r="X118">
-        <v>7</v>
-      </c>
-      <c r="Y118">
-        <v>1.08</v>
-      </c>
-      <c r="Z118">
-        <v>3.4</v>
-      </c>
-      <c r="AA118">
-        <v>3.4</v>
-      </c>
-      <c r="AB118">
-        <v>1.9</v>
       </c>
       <c r="AC118">
         <v>1.01</v>
       </c>
       <c r="AD118">
-        <v>8.699999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="AE118">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="AF118">
-        <v>3.22</v>
+        <v>5.1</v>
       </c>
       <c r="AG118">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="AH118">
-        <v>1.8</v>
+        <v>2.63</v>
       </c>
       <c r="AI118">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AJ118">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AK118">
-        <v>1.64</v>
+        <v>2.83</v>
       </c>
       <c r="AL118">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="AM118">
-        <v>1.29</v>
+        <v>1.07</v>
       </c>
       <c r="AN118">
         <v>1.11</v>
       </c>
       <c r="AO118">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AP118">
-        <v>0.92</v>
+        <v>1.18</v>
       </c>
       <c r="AQ118">
-        <v>1.75</v>
+        <v>2.18</v>
       </c>
       <c r="AR118">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="AS118">
+        <v>2.24</v>
+      </c>
+      <c r="AT118">
+        <v>3.64</v>
+      </c>
+      <c r="AU118">
+        <v>5</v>
+      </c>
+      <c r="AV118">
+        <v>12</v>
+      </c>
+      <c r="AW118">
+        <v>3</v>
+      </c>
+      <c r="AX118">
+        <v>6</v>
+      </c>
+      <c r="AY118">
+        <v>11</v>
+      </c>
+      <c r="AZ118">
+        <v>23</v>
+      </c>
+      <c r="BA118">
+        <v>6</v>
+      </c>
+      <c r="BB118">
+        <v>6</v>
+      </c>
+      <c r="BC118">
+        <v>12</v>
+      </c>
+      <c r="BD118">
+        <v>6.5</v>
+      </c>
+      <c r="BE118">
+        <v>12.25</v>
+      </c>
+      <c r="BF118">
+        <v>1.13</v>
+      </c>
+      <c r="BG118">
+        <v>1.21</v>
+      </c>
+      <c r="BH118">
+        <v>4.15</v>
+      </c>
+      <c r="BI118">
         <v>1.33</v>
       </c>
-      <c r="AT118">
-        <v>3.01</v>
-      </c>
-      <c r="AU118">
-        <v>2</v>
-      </c>
-      <c r="AV118">
-        <v>6</v>
-      </c>
-      <c r="AW118">
-        <v>7</v>
-      </c>
-      <c r="AX118">
-        <v>4</v>
-      </c>
-      <c r="AY118">
-        <v>9</v>
-      </c>
-      <c r="AZ118">
-        <v>11</v>
-      </c>
-      <c r="BA118">
-        <v>4</v>
-      </c>
-      <c r="BB118">
-        <v>3</v>
-      </c>
-      <c r="BC118">
-        <v>7</v>
-      </c>
-      <c r="BD118">
-        <v>2.96</v>
-      </c>
-      <c r="BE118">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF118">
-        <v>1.52</v>
-      </c>
-      <c r="BG118">
+      <c r="BJ118">
+        <v>2.83</v>
+      </c>
+      <c r="BK118">
+        <v>1.59</v>
+      </c>
+      <c r="BL118">
+        <v>2.1</v>
+      </c>
+      <c r="BM118">
+        <v>2.05</v>
+      </c>
+      <c r="BN118">
+        <v>1.7</v>
+      </c>
+      <c r="BO118">
+        <v>2.56</v>
+      </c>
+      <c r="BP118">
         <v>1.4</v>
-      </c>
-      <c r="BH118">
-        <v>2.8</v>
-      </c>
-      <c r="BI118">
-        <v>1.68</v>
-      </c>
-      <c r="BJ118">
-        <v>2.11</v>
-      </c>
-      <c r="BK118">
-        <v>2.12</v>
-      </c>
-      <c r="BL118">
-        <v>1.67</v>
-      </c>
-      <c r="BM118">
-        <v>2.77</v>
-      </c>
-      <c r="BN118">
-        <v>1.41</v>
-      </c>
-      <c r="BO118">
-        <v>3.85</v>
-      </c>
-      <c r="BP118">
-        <v>1.24</v>
       </c>
     </row>
     <row r="119" spans="1:68">
@@ -26516,7 +26516,7 @@
         <v>123</v>
       </c>
       <c r="B124">
-        <v>7727606</v>
+        <v>7727607</v>
       </c>
       <c r="C124" t="s">
         <v>68</v>
@@ -26531,190 +26531,190 @@
         <v>19</v>
       </c>
       <c r="G124" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H124" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I124">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J124">
         <v>1</v>
       </c>
       <c r="K124">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L124">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M124">
         <v>1</v>
       </c>
       <c r="N124">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O124" t="s">
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>104</v>
+        <v>251</v>
       </c>
       <c r="Q124">
+        <v>1.44</v>
+      </c>
+      <c r="R124">
+        <v>3.1</v>
+      </c>
+      <c r="S124">
+        <v>11</v>
+      </c>
+      <c r="T124">
+        <v>1.2</v>
+      </c>
+      <c r="U124">
+        <v>4.33</v>
+      </c>
+      <c r="V124">
         <v>1.83</v>
       </c>
-      <c r="R124">
+      <c r="W124">
+        <v>1.83</v>
+      </c>
+      <c r="X124">
+        <v>3.75</v>
+      </c>
+      <c r="Y124">
+        <v>1.25</v>
+      </c>
+      <c r="Z124">
+        <v>1.13</v>
+      </c>
+      <c r="AA124">
+        <v>8.5</v>
+      </c>
+      <c r="AB124">
+        <v>13</v>
+      </c>
+      <c r="AC124">
+        <v>1</v>
+      </c>
+      <c r="AD124">
+        <v>23</v>
+      </c>
+      <c r="AE124">
+        <v>1.01</v>
+      </c>
+      <c r="AF124">
+        <v>7.7</v>
+      </c>
+      <c r="AG124">
+        <v>1.3</v>
+      </c>
+      <c r="AH124">
+        <v>3.4</v>
+      </c>
+      <c r="AI124">
+        <v>2.1</v>
+      </c>
+      <c r="AJ124">
+        <v>1.67</v>
+      </c>
+      <c r="AK124">
+        <v>1.01</v>
+      </c>
+      <c r="AL124">
+        <v>1.02</v>
+      </c>
+      <c r="AM124">
+        <v>4</v>
+      </c>
+      <c r="AN124">
         <v>2.4</v>
       </c>
-      <c r="S124">
-        <v>7</v>
-      </c>
-      <c r="T124">
-        <v>1.33</v>
-      </c>
-      <c r="U124">
-        <v>3.25</v>
-      </c>
-      <c r="V124">
+      <c r="AO124">
+        <v>0.9</v>
+      </c>
+      <c r="AP124">
         <v>2.5</v>
       </c>
-      <c r="W124">
-        <v>1.5</v>
-      </c>
-      <c r="X124">
-        <v>5.5</v>
-      </c>
-      <c r="Y124">
-        <v>1.13</v>
-      </c>
-      <c r="Z124">
-        <v>1.38</v>
-      </c>
-      <c r="AA124">
-        <v>4.33</v>
-      </c>
-      <c r="AB124">
-        <v>7</v>
-      </c>
-      <c r="AC124">
-        <v>1.01</v>
-      </c>
-      <c r="AD124">
-        <v>15</v>
-      </c>
-      <c r="AE124">
+      <c r="AQ124">
+        <v>0.75</v>
+      </c>
+      <c r="AR124">
+        <v>2.58</v>
+      </c>
+      <c r="AS124">
+        <v>1.32</v>
+      </c>
+      <c r="AT124">
+        <v>3.9</v>
+      </c>
+      <c r="AU124">
+        <v>11</v>
+      </c>
+      <c r="AV124">
+        <v>4</v>
+      </c>
+      <c r="AW124">
+        <v>11</v>
+      </c>
+      <c r="AX124">
+        <v>1</v>
+      </c>
+      <c r="AY124">
+        <v>35</v>
+      </c>
+      <c r="AZ124">
+        <v>5</v>
+      </c>
+      <c r="BA124">
+        <v>16</v>
+      </c>
+      <c r="BB124">
+        <v>0</v>
+      </c>
+      <c r="BC124">
+        <v>16</v>
+      </c>
+      <c r="BD124">
+        <v>1.02</v>
+      </c>
+      <c r="BE124">
+        <v>17.75</v>
+      </c>
+      <c r="BF124">
+        <v>12.75</v>
+      </c>
+      <c r="BG124">
+        <v>1.15</v>
+      </c>
+      <c r="BH124">
+        <v>5</v>
+      </c>
+      <c r="BI124">
         <v>1.21</v>
       </c>
-      <c r="AF124">
-        <v>4.1</v>
-      </c>
-      <c r="AG124">
-        <v>1.73</v>
-      </c>
-      <c r="AH124">
-        <v>2</v>
-      </c>
-      <c r="AI124">
-        <v>2</v>
-      </c>
-      <c r="AJ124">
-        <v>1.73</v>
-      </c>
-      <c r="AK124">
-        <v>1.06</v>
-      </c>
-      <c r="AL124">
-        <v>1.12</v>
-      </c>
-      <c r="AM124">
-        <v>2.55</v>
-      </c>
-      <c r="AN124">
-        <v>1.7</v>
-      </c>
-      <c r="AO124">
-        <v>0.67</v>
-      </c>
-      <c r="AP124">
-        <v>1.92</v>
-      </c>
-      <c r="AQ124">
-        <v>0.83</v>
-      </c>
-      <c r="AR124">
-        <v>1.41</v>
-      </c>
-      <c r="AS124">
-        <v>1.33</v>
-      </c>
-      <c r="AT124">
-        <v>2.74</v>
-      </c>
-      <c r="AU124">
-        <v>12</v>
-      </c>
-      <c r="AV124">
-        <v>5</v>
-      </c>
-      <c r="AW124">
-        <v>7</v>
-      </c>
-      <c r="AX124">
-        <v>3</v>
-      </c>
-      <c r="AY124">
-        <v>21</v>
-      </c>
-      <c r="AZ124">
-        <v>8</v>
-      </c>
-      <c r="BA124">
-        <v>6</v>
-      </c>
-      <c r="BB124">
-        <v>0</v>
-      </c>
-      <c r="BC124">
-        <v>6</v>
-      </c>
-      <c r="BD124">
-        <v>1.21</v>
-      </c>
-      <c r="BE124">
-        <v>10.25</v>
-      </c>
-      <c r="BF124">
-        <v>5.15</v>
-      </c>
-      <c r="BG124">
-        <v>1.24</v>
-      </c>
-      <c r="BH124">
-        <v>3.22</v>
-      </c>
-      <c r="BI124">
-        <v>1.47</v>
-      </c>
       <c r="BJ124">
-        <v>2.29</v>
+        <v>3.44</v>
       </c>
       <c r="BK124">
-        <v>1.91</v>
+        <v>1.4</v>
       </c>
       <c r="BL124">
-        <v>1.8</v>
+        <v>2.48</v>
       </c>
       <c r="BM124">
-        <v>2.35</v>
+        <v>1.77</v>
       </c>
       <c r="BN124">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="BO124">
-        <v>3.14</v>
+        <v>2.1</v>
       </c>
       <c r="BP124">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="125" spans="1:68">
@@ -26722,7 +26722,7 @@
         <v>124</v>
       </c>
       <c r="B125">
-        <v>7727611</v>
+        <v>7727606</v>
       </c>
       <c r="C125" t="s">
         <v>68</v>
@@ -26737,82 +26737,82 @@
         <v>19</v>
       </c>
       <c r="G125" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H125" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I125">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J125">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K125">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L125">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M125">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N125">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O125" t="s">
-        <v>142</v>
+        <v>175</v>
       </c>
       <c r="P125" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="Q125">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="R125">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="S125">
-        <v>4.75</v>
+        <v>7</v>
       </c>
       <c r="T125">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="U125">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="V125">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="W125">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="X125">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="Y125">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z125">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="AA125">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="AB125">
-        <v>3.8</v>
+        <v>7</v>
       </c>
       <c r="AC125">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AD125">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AE125">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AF125">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AG125">
         <v>1.73</v>
@@ -26821,106 +26821,106 @@
         <v>2</v>
       </c>
       <c r="AI125">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AJ125">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AK125">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AL125">
+        <v>1.12</v>
+      </c>
+      <c r="AM125">
+        <v>2.55</v>
+      </c>
+      <c r="AN125">
+        <v>1.7</v>
+      </c>
+      <c r="AO125">
+        <v>0.67</v>
+      </c>
+      <c r="AP125">
+        <v>1.92</v>
+      </c>
+      <c r="AQ125">
+        <v>0.83</v>
+      </c>
+      <c r="AR125">
+        <v>1.41</v>
+      </c>
+      <c r="AS125">
+        <v>1.33</v>
+      </c>
+      <c r="AT125">
+        <v>2.74</v>
+      </c>
+      <c r="AU125">
+        <v>12</v>
+      </c>
+      <c r="AV125">
+        <v>5</v>
+      </c>
+      <c r="AW125">
+        <v>7</v>
+      </c>
+      <c r="AX125">
+        <v>3</v>
+      </c>
+      <c r="AY125">
+        <v>21</v>
+      </c>
+      <c r="AZ125">
+        <v>8</v>
+      </c>
+      <c r="BA125">
+        <v>6</v>
+      </c>
+      <c r="BB125">
+        <v>0</v>
+      </c>
+      <c r="BC125">
+        <v>6</v>
+      </c>
+      <c r="BD125">
         <v>1.21</v>
       </c>
-      <c r="AM125">
-        <v>1.9</v>
-      </c>
-      <c r="AN125">
-        <v>2.1</v>
-      </c>
-      <c r="AO125">
-        <v>1.2</v>
-      </c>
-      <c r="AP125">
-        <v>2.08</v>
-      </c>
-      <c r="AQ125">
-        <v>1</v>
-      </c>
-      <c r="AR125">
-        <v>1.81</v>
-      </c>
-      <c r="AS125">
-        <v>1.46</v>
-      </c>
-      <c r="AT125">
-        <v>3.27</v>
-      </c>
-      <c r="AU125">
-        <v>4</v>
-      </c>
-      <c r="AV125">
-        <v>3</v>
-      </c>
-      <c r="AW125">
-        <v>5</v>
-      </c>
-      <c r="AX125">
-        <v>8</v>
-      </c>
-      <c r="AY125">
-        <v>11</v>
-      </c>
-      <c r="AZ125">
-        <v>15</v>
-      </c>
-      <c r="BA125">
-        <v>4</v>
-      </c>
-      <c r="BB125">
-        <v>5</v>
-      </c>
-      <c r="BC125">
-        <v>9</v>
-      </c>
-      <c r="BD125">
-        <v>0</v>
-      </c>
       <c r="BE125">
-        <v>0</v>
+        <v>10.25</v>
       </c>
       <c r="BF125">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="BG125">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BH125">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="BI125">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BJ125">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BK125">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BL125">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BM125">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="BN125">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BO125">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="BP125">
-        <v>0</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="126" spans="1:68">
@@ -26928,7 +26928,7 @@
         <v>125</v>
       </c>
       <c r="B126">
-        <v>7727607</v>
+        <v>7727611</v>
       </c>
       <c r="C126" t="s">
         <v>68</v>
@@ -26943,190 +26943,190 @@
         <v>19</v>
       </c>
       <c r="G126" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H126" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I126">
         <v>0</v>
       </c>
       <c r="J126">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K126">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L126">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M126">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N126">
+        <v>1</v>
+      </c>
+      <c r="O126" t="s">
+        <v>142</v>
+      </c>
+      <c r="P126" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q126">
+        <v>2.2</v>
+      </c>
+      <c r="R126">
+        <v>2.2</v>
+      </c>
+      <c r="S126">
+        <v>4.75</v>
+      </c>
+      <c r="T126">
+        <v>1.36</v>
+      </c>
+      <c r="U126">
         <v>3</v>
       </c>
-      <c r="O126" t="s">
-        <v>175</v>
-      </c>
-      <c r="P126" t="s">
-        <v>251</v>
-      </c>
-      <c r="Q126">
-        <v>1.44</v>
-      </c>
-      <c r="R126">
-        <v>3.1</v>
-      </c>
-      <c r="S126">
+      <c r="V126">
+        <v>2.75</v>
+      </c>
+      <c r="W126">
+        <v>1.4</v>
+      </c>
+      <c r="X126">
+        <v>6.5</v>
+      </c>
+      <c r="Y126">
+        <v>1.1</v>
+      </c>
+      <c r="Z126">
+        <v>1.75</v>
+      </c>
+      <c r="AA126">
+        <v>3.75</v>
+      </c>
+      <c r="AB126">
+        <v>3.8</v>
+      </c>
+      <c r="AC126">
+        <v>1.04</v>
+      </c>
+      <c r="AD126">
         <v>11</v>
       </c>
-      <c r="T126">
+      <c r="AE126">
+        <v>1.27</v>
+      </c>
+      <c r="AF126">
+        <v>3.5</v>
+      </c>
+      <c r="AG126">
+        <v>1.73</v>
+      </c>
+      <c r="AH126">
+        <v>2</v>
+      </c>
+      <c r="AI126">
+        <v>1.83</v>
+      </c>
+      <c r="AJ126">
+        <v>1.83</v>
+      </c>
+      <c r="AK126">
+        <v>1.15</v>
+      </c>
+      <c r="AL126">
+        <v>1.21</v>
+      </c>
+      <c r="AM126">
+        <v>1.9</v>
+      </c>
+      <c r="AN126">
+        <v>2.1</v>
+      </c>
+      <c r="AO126">
         <v>1.2</v>
       </c>
-      <c r="U126">
-        <v>4.33</v>
-      </c>
-      <c r="V126">
-        <v>1.83</v>
-      </c>
-      <c r="W126">
-        <v>1.83</v>
-      </c>
-      <c r="X126">
-        <v>3.75</v>
-      </c>
-      <c r="Y126">
-        <v>1.25</v>
-      </c>
-      <c r="Z126">
-        <v>1.13</v>
-      </c>
-      <c r="AA126">
-        <v>8.5</v>
-      </c>
-      <c r="AB126">
-        <v>13</v>
-      </c>
-      <c r="AC126">
-        <v>1</v>
-      </c>
-      <c r="AD126">
-        <v>23</v>
-      </c>
-      <c r="AE126">
-        <v>1.01</v>
-      </c>
-      <c r="AF126">
-        <v>7.7</v>
-      </c>
-      <c r="AG126">
-        <v>1.3</v>
-      </c>
-      <c r="AH126">
-        <v>3.4</v>
-      </c>
-      <c r="AI126">
-        <v>2.1</v>
-      </c>
-      <c r="AJ126">
-        <v>1.67</v>
-      </c>
-      <c r="AK126">
-        <v>1.01</v>
-      </c>
-      <c r="AL126">
-        <v>1.02</v>
-      </c>
-      <c r="AM126">
+      <c r="AP126">
+        <v>2.08</v>
+      </c>
+      <c r="AQ126">
+        <v>1</v>
+      </c>
+      <c r="AR126">
+        <v>1.81</v>
+      </c>
+      <c r="AS126">
+        <v>1.46</v>
+      </c>
+      <c r="AT126">
+        <v>3.27</v>
+      </c>
+      <c r="AU126">
         <v>4</v>
       </c>
-      <c r="AN126">
-        <v>2.4</v>
-      </c>
-      <c r="AO126">
-        <v>0.9</v>
-      </c>
-      <c r="AP126">
-        <v>2.5</v>
-      </c>
-      <c r="AQ126">
-        <v>0.75</v>
-      </c>
-      <c r="AR126">
-        <v>2.58</v>
-      </c>
-      <c r="AS126">
-        <v>1.32</v>
-      </c>
-      <c r="AT126">
-        <v>3.9</v>
-      </c>
-      <c r="AU126">
+      <c r="AV126">
+        <v>3</v>
+      </c>
+      <c r="AW126">
+        <v>5</v>
+      </c>
+      <c r="AX126">
+        <v>8</v>
+      </c>
+      <c r="AY126">
         <v>11</v>
       </c>
-      <c r="AV126">
+      <c r="AZ126">
+        <v>15</v>
+      </c>
+      <c r="BA126">
         <v>4</v>
       </c>
-      <c r="AW126">
-        <v>11</v>
-      </c>
-      <c r="AX126">
-        <v>1</v>
-      </c>
-      <c r="AY126">
-        <v>35</v>
-      </c>
-      <c r="AZ126">
+      <c r="BB126">
         <v>5</v>
       </c>
-      <c r="BA126">
-        <v>16</v>
-      </c>
-      <c r="BB126">
-        <v>0</v>
-      </c>
       <c r="BC126">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="BD126">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="BE126">
-        <v>17.75</v>
+        <v>0</v>
       </c>
       <c r="BF126">
-        <v>12.75</v>
+        <v>0</v>
       </c>
       <c r="BG126">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BH126">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BI126">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BJ126">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="BK126">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BL126">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="BM126">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="BN126">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BO126">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BP126">
-        <v>1.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:68">
@@ -27546,7 +27546,7 @@
         <v>128</v>
       </c>
       <c r="B129">
-        <v>7727634</v>
+        <v>7727625</v>
       </c>
       <c r="C129" t="s">
         <v>68</v>
@@ -27561,190 +27561,190 @@
         <v>22</v>
       </c>
       <c r="G129" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="H129" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="I129">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J129">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K129">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L129">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M129">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N129">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O129" t="s">
         <v>176</v>
       </c>
       <c r="P129" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="Q129">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="R129">
+        <v>2.38</v>
+      </c>
+      <c r="S129">
+        <v>3.25</v>
+      </c>
+      <c r="T129">
+        <v>1.29</v>
+      </c>
+      <c r="U129">
+        <v>3.5</v>
+      </c>
+      <c r="V129">
         <v>2.25</v>
       </c>
-      <c r="S129">
-        <v>2.4</v>
-      </c>
-      <c r="T129">
-        <v>1.33</v>
-      </c>
-      <c r="U129">
+      <c r="W129">
+        <v>1.57</v>
+      </c>
+      <c r="X129">
+        <v>5</v>
+      </c>
+      <c r="Y129">
+        <v>1.14</v>
+      </c>
+      <c r="Z129">
+        <v>1.98</v>
+      </c>
+      <c r="AA129">
         <v>3.25</v>
       </c>
-      <c r="V129">
-        <v>2.63</v>
-      </c>
-      <c r="W129">
-        <v>1.44</v>
-      </c>
-      <c r="X129">
-        <v>6</v>
-      </c>
-      <c r="Y129">
-        <v>1.11</v>
-      </c>
-      <c r="Z129">
-        <v>3.3</v>
-      </c>
-      <c r="AA129">
-        <v>3.6</v>
-      </c>
       <c r="AB129">
-        <v>1.83</v>
+        <v>3.25</v>
       </c>
       <c r="AC129">
         <v>1.01</v>
       </c>
       <c r="AD129">
-        <v>8.699999999999999</v>
+        <v>13</v>
       </c>
       <c r="AE129">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AF129">
-        <v>3.68</v>
+        <v>4.75</v>
       </c>
       <c r="AG129">
-        <v>1.8</v>
+        <v>1.45</v>
       </c>
       <c r="AH129">
-        <v>1.88</v>
+        <v>2.55</v>
       </c>
       <c r="AI129">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AJ129">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="AK129">
-        <v>1.73</v>
+        <v>1.31</v>
       </c>
       <c r="AL129">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AM129">
-        <v>1.27</v>
+        <v>1.58</v>
       </c>
       <c r="AN129">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="AO129">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="AP129">
-        <v>1.75</v>
+        <v>1.18</v>
       </c>
       <c r="AQ129">
-        <v>1.75</v>
+        <v>0.58</v>
       </c>
       <c r="AR129">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="AS129">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="AT129">
-        <v>2.81</v>
+        <v>2.89</v>
       </c>
       <c r="AU129">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="AV129">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AW129">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX129">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY129">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="AZ129">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA129">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB129">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BC129">
         <v>7</v>
       </c>
       <c r="BD129">
-        <v>2.55</v>
+        <v>1.61</v>
       </c>
       <c r="BE129">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
       <c r="BF129">
-        <v>1.68</v>
+        <v>2.62</v>
       </c>
       <c r="BG129">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="BH129">
-        <v>2.43</v>
+        <v>4.2</v>
       </c>
       <c r="BI129">
+        <v>1.32</v>
+      </c>
+      <c r="BJ129">
+        <v>2.88</v>
+      </c>
+      <c r="BK129">
+        <v>1.57</v>
+      </c>
+      <c r="BL129">
+        <v>2.14</v>
+      </c>
+      <c r="BM129">
+        <v>1.95</v>
+      </c>
+      <c r="BN129">
         <v>1.77</v>
       </c>
-      <c r="BJ129">
-        <v>1.95</v>
-      </c>
-      <c r="BK129">
-        <v>2.35</v>
-      </c>
-      <c r="BL129">
-        <v>1.47</v>
-      </c>
-      <c r="BM129">
-        <v>3.28</v>
-      </c>
-      <c r="BN129">
-        <v>1.25</v>
-      </c>
       <c r="BO129">
-        <v>4.33</v>
+        <v>2.56</v>
       </c>
       <c r="BP129">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="130" spans="1:68">
@@ -27752,7 +27752,7 @@
         <v>129</v>
       </c>
       <c r="B130">
-        <v>7727627</v>
+        <v>7727635</v>
       </c>
       <c r="C130" t="s">
         <v>68</v>
@@ -27767,10 +27767,10 @@
         <v>22</v>
       </c>
       <c r="G130" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H130" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="I130">
         <v>0</v>
@@ -27782,175 +27782,175 @@
         <v>1</v>
       </c>
       <c r="L130">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M130">
         <v>2</v>
       </c>
       <c r="N130">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O130" t="s">
-        <v>177</v>
+        <v>85</v>
       </c>
       <c r="P130" t="s">
         <v>254</v>
       </c>
       <c r="Q130">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="R130">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="S130">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="T130">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="U130">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="V130">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="W130">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="X130">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="Y130">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z130">
-        <v>4.75</v>
+        <v>6.5</v>
       </c>
       <c r="AA130">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AB130">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AC130">
         <v>1.01</v>
       </c>
       <c r="AD130">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE130">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AF130">
-        <v>4.05</v>
+        <v>5.4</v>
       </c>
       <c r="AG130">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AH130">
-        <v>1.95</v>
+        <v>2.63</v>
       </c>
       <c r="AI130">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AJ130">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AK130">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="AL130">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AM130">
         <v>1.1</v>
       </c>
       <c r="AN130">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="AO130">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AP130">
-        <v>0.92</v>
+        <v>1.58</v>
       </c>
       <c r="AQ130">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="AR130">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AS130">
-        <v>1.66</v>
+        <v>2.25</v>
       </c>
       <c r="AT130">
-        <v>3.29</v>
+        <v>3.75</v>
       </c>
       <c r="AU130">
+        <v>-1</v>
+      </c>
+      <c r="AV130">
+        <v>-1</v>
+      </c>
+      <c r="AW130">
+        <v>-1</v>
+      </c>
+      <c r="AX130">
+        <v>-1</v>
+      </c>
+      <c r="AY130">
+        <v>-1</v>
+      </c>
+      <c r="AZ130">
+        <v>-1</v>
+      </c>
+      <c r="BA130">
+        <v>1</v>
+      </c>
+      <c r="BB130">
         <v>4</v>
       </c>
-      <c r="AV130">
-        <v>4</v>
-      </c>
-      <c r="AW130">
-        <v>2</v>
-      </c>
-      <c r="AX130">
-        <v>2</v>
-      </c>
-      <c r="AY130">
-        <v>6</v>
-      </c>
-      <c r="AZ130">
-        <v>6</v>
-      </c>
-      <c r="BA130">
-        <v>4</v>
-      </c>
-      <c r="BB130">
-        <v>9</v>
-      </c>
       <c r="BC130">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="BD130">
-        <v>3.05</v>
+        <v>5.75</v>
       </c>
       <c r="BE130">
-        <v>8.699999999999999</v>
+        <v>11</v>
       </c>
       <c r="BF130">
+        <v>1.17</v>
+      </c>
+      <c r="BG130">
+        <v>1.25</v>
+      </c>
+      <c r="BH130">
+        <v>3.28</v>
+      </c>
+      <c r="BI130">
         <v>1.48</v>
       </c>
-      <c r="BG130">
-        <v>1.18</v>
-      </c>
-      <c r="BH130">
-        <v>3.84</v>
-      </c>
-      <c r="BI130">
-        <v>1.37</v>
-      </c>
       <c r="BJ130">
-        <v>2.66</v>
+        <v>2.33</v>
       </c>
       <c r="BK130">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="BL130">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="BM130">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="BN130">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="BO130">
-        <v>2.74</v>
+        <v>3.14</v>
       </c>
       <c r="BP130">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="131" spans="1:68">
@@ -27958,7 +27958,7 @@
         <v>130</v>
       </c>
       <c r="B131">
-        <v>7727635</v>
+        <v>7727627</v>
       </c>
       <c r="C131" t="s">
         <v>68</v>
@@ -27973,10 +27973,10 @@
         <v>22</v>
       </c>
       <c r="G131" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H131" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="I131">
         <v>0</v>
@@ -27988,175 +27988,175 @@
         <v>1</v>
       </c>
       <c r="L131">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M131">
         <v>2</v>
       </c>
       <c r="N131">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O131" t="s">
-        <v>85</v>
+        <v>177</v>
       </c>
       <c r="P131" t="s">
         <v>255</v>
       </c>
       <c r="Q131">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="R131">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="S131">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="T131">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="U131">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="V131">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="W131">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="X131">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="Y131">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z131">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="AA131">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="AB131">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AC131">
         <v>1.01</v>
       </c>
       <c r="AD131">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE131">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AF131">
-        <v>5.4</v>
+        <v>4.05</v>
       </c>
       <c r="AG131">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AH131">
-        <v>2.63</v>
+        <v>1.95</v>
       </c>
       <c r="AI131">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AJ131">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="AK131">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="AL131">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AM131">
         <v>1.1</v>
       </c>
       <c r="AN131">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="AO131">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AP131">
-        <v>1.58</v>
+        <v>0.92</v>
       </c>
       <c r="AQ131">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AR131">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AS131">
-        <v>2.25</v>
+        <v>1.66</v>
       </c>
       <c r="AT131">
-        <v>3.75</v>
+        <v>3.29</v>
       </c>
       <c r="AU131">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AV131">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AW131">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AX131">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AY131">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AZ131">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BA131">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BB131">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="BC131">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="BD131">
-        <v>5.75</v>
+        <v>3.05</v>
       </c>
       <c r="BE131">
-        <v>11</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BF131">
-        <v>1.17</v>
+        <v>1.48</v>
       </c>
       <c r="BG131">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="BH131">
-        <v>3.28</v>
+        <v>3.84</v>
       </c>
       <c r="BI131">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="BJ131">
-        <v>2.33</v>
+        <v>2.66</v>
       </c>
       <c r="BK131">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="BL131">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="BM131">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="BN131">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="BO131">
-        <v>3.14</v>
+        <v>2.74</v>
       </c>
       <c r="BP131">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="132" spans="1:68">
@@ -28164,7 +28164,7 @@
         <v>131</v>
       </c>
       <c r="B132">
-        <v>7727625</v>
+        <v>7727634</v>
       </c>
       <c r="C132" t="s">
         <v>68</v>
@@ -28179,190 +28179,190 @@
         <v>22</v>
       </c>
       <c r="G132" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="H132" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="I132">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J132">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K132">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L132">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M132">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N132">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O132" t="s">
         <v>178</v>
       </c>
       <c r="P132" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="Q132">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="R132">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S132">
+        <v>2.4</v>
+      </c>
+      <c r="T132">
+        <v>1.33</v>
+      </c>
+      <c r="U132">
         <v>3.25</v>
       </c>
-      <c r="T132">
-        <v>1.29</v>
-      </c>
-      <c r="U132">
-        <v>3.5</v>
-      </c>
       <c r="V132">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="W132">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="X132">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y132">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z132">
-        <v>1.98</v>
+        <v>3.3</v>
       </c>
       <c r="AA132">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="AB132">
-        <v>3.25</v>
+        <v>1.83</v>
       </c>
       <c r="AC132">
         <v>1.01</v>
       </c>
       <c r="AD132">
-        <v>13</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AE132">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AF132">
-        <v>4.75</v>
+        <v>3.68</v>
       </c>
       <c r="AG132">
-        <v>1.45</v>
+        <v>1.8</v>
       </c>
       <c r="AH132">
-        <v>2.55</v>
+        <v>1.88</v>
       </c>
       <c r="AI132">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AJ132">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="AK132">
-        <v>1.31</v>
+        <v>1.73</v>
       </c>
       <c r="AL132">
+        <v>1.22</v>
+      </c>
+      <c r="AM132">
         <v>1.27</v>
       </c>
-      <c r="AM132">
-        <v>1.58</v>
-      </c>
       <c r="AN132">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="AO132">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="AP132">
-        <v>1.18</v>
+        <v>1.75</v>
       </c>
       <c r="AQ132">
-        <v>0.58</v>
+        <v>1.75</v>
       </c>
       <c r="AR132">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="AS132">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="AT132">
-        <v>2.89</v>
+        <v>2.81</v>
       </c>
       <c r="AU132">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AV132">
+        <v>7</v>
+      </c>
+      <c r="AW132">
+        <v>8</v>
+      </c>
+      <c r="AX132">
         <v>4</v>
       </c>
-      <c r="AW132">
-        <v>9</v>
-      </c>
-      <c r="AX132">
-        <v>5</v>
-      </c>
       <c r="AY132">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="AZ132">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA132">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB132">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC132">
         <v>7</v>
       </c>
       <c r="BD132">
-        <v>1.61</v>
+        <v>2.55</v>
       </c>
       <c r="BE132">
-        <v>8.6</v>
+        <v>7.7</v>
       </c>
       <c r="BF132">
-        <v>2.62</v>
+        <v>1.68</v>
       </c>
       <c r="BG132">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="BH132">
-        <v>4.2</v>
+        <v>2.43</v>
       </c>
       <c r="BI132">
-        <v>1.32</v>
+        <v>1.77</v>
       </c>
       <c r="BJ132">
-        <v>2.88</v>
+        <v>1.95</v>
       </c>
       <c r="BK132">
-        <v>1.57</v>
+        <v>2.35</v>
       </c>
       <c r="BL132">
-        <v>2.14</v>
+        <v>1.47</v>
       </c>
       <c r="BM132">
-        <v>1.95</v>
+        <v>3.28</v>
       </c>
       <c r="BN132">
-        <v>1.77</v>
+        <v>1.25</v>
       </c>
       <c r="BO132">
-        <v>2.56</v>
+        <v>4.33</v>
       </c>
       <c r="BP132">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="133" spans="1:68">
@@ -30224,7 +30224,7 @@
         <v>141</v>
       </c>
       <c r="B142">
-        <v>7817179</v>
+        <v>7817178</v>
       </c>
       <c r="C142" t="s">
         <v>68</v>
@@ -30239,28 +30239,28 @@
         <v>2</v>
       </c>
       <c r="G142" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H142" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="I142">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J142">
         <v>1</v>
       </c>
       <c r="K142">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L142">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M142">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N142">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O142" t="s">
         <v>185</v>
@@ -30269,160 +30269,160 @@
         <v>262</v>
       </c>
       <c r="Q142">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="R142">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S142">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="T142">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="U142">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="V142">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="W142">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="X142">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="Y142">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z142">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AA142">
-        <v>4.2</v>
+        <v>3.91</v>
       </c>
       <c r="AB142">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AC142">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AD142">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE142">
         <v>1.18</v>
       </c>
       <c r="AF142">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AG142">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AH142">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AI142">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AJ142">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AK142">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AL142">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AM142">
-        <v>2.06</v>
+        <v>1.8</v>
       </c>
       <c r="AN142">
-        <v>1.09</v>
+        <v>1.64</v>
       </c>
       <c r="AO142">
-        <v>0.27</v>
+        <v>0.64</v>
       </c>
       <c r="AP142">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="AQ142">
-        <v>0.5</v>
+        <v>0.58</v>
       </c>
       <c r="AR142">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AS142">
-        <v>0.91</v>
+        <v>1.47</v>
       </c>
       <c r="AT142">
-        <v>2.3</v>
+        <v>2.91</v>
       </c>
       <c r="AU142">
         <v>5</v>
       </c>
       <c r="AV142">
+        <v>4</v>
+      </c>
+      <c r="AW142">
+        <v>3</v>
+      </c>
+      <c r="AX142">
+        <v>4</v>
+      </c>
+      <c r="AY142">
         <v>8</v>
       </c>
-      <c r="AW142">
-        <v>5</v>
-      </c>
-      <c r="AX142">
+      <c r="AZ142">
         <v>8</v>
       </c>
-      <c r="AY142">
-        <v>10</v>
-      </c>
-      <c r="AZ142">
-        <v>16</v>
-      </c>
       <c r="BA142">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BB142">
+        <v>1</v>
+      </c>
+      <c r="BC142">
         <v>7</v>
       </c>
-      <c r="BC142">
-        <v>11</v>
-      </c>
       <c r="BD142">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BE142">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BF142">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BG142">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BH142">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BI142">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BJ142">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BK142">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BL142">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BM142">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BN142">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BO142">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BP142">
-        <v>0</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="143" spans="1:68">
@@ -30430,7 +30430,7 @@
         <v>142</v>
       </c>
       <c r="B143">
-        <v>7817177</v>
+        <v>7817179</v>
       </c>
       <c r="C143" t="s">
         <v>68</v>
@@ -30445,28 +30445,28 @@
         <v>2</v>
       </c>
       <c r="G143" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H143" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I143">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J143">
         <v>1</v>
       </c>
       <c r="K143">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L143">
+        <v>2</v>
+      </c>
+      <c r="M143">
         <v>3</v>
       </c>
-      <c r="M143">
-        <v>1</v>
-      </c>
       <c r="N143">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O143" t="s">
         <v>186</v>
@@ -30475,121 +30475,121 @@
         <v>263</v>
       </c>
       <c r="Q143">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="R143">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="S143">
-        <v>9.5</v>
+        <v>4.5</v>
       </c>
       <c r="T143">
+        <v>1.29</v>
+      </c>
+      <c r="U143">
+        <v>3.5</v>
+      </c>
+      <c r="V143">
+        <v>2.25</v>
+      </c>
+      <c r="W143">
+        <v>1.57</v>
+      </c>
+      <c r="X143">
+        <v>5</v>
+      </c>
+      <c r="Y143">
+        <v>1.14</v>
+      </c>
+      <c r="Z143">
+        <v>1.65</v>
+      </c>
+      <c r="AA143">
+        <v>4.2</v>
+      </c>
+      <c r="AB143">
+        <v>4.5</v>
+      </c>
+      <c r="AC143">
+        <v>1</v>
+      </c>
+      <c r="AD143">
+        <v>17</v>
+      </c>
+      <c r="AE143">
+        <v>1.18</v>
+      </c>
+      <c r="AF143">
+        <v>4.4</v>
+      </c>
+      <c r="AG143">
+        <v>1.65</v>
+      </c>
+      <c r="AH143">
+        <v>2.05</v>
+      </c>
+      <c r="AI143">
+        <v>1.62</v>
+      </c>
+      <c r="AJ143">
+        <v>2.2</v>
+      </c>
+      <c r="AK143">
+        <v>1.19</v>
+      </c>
+      <c r="AL143">
         <v>1.22</v>
       </c>
-      <c r="U143">
+      <c r="AM143">
+        <v>2.06</v>
+      </c>
+      <c r="AN143">
+        <v>1.09</v>
+      </c>
+      <c r="AO143">
+        <v>0.27</v>
+      </c>
+      <c r="AP143">
+        <v>1</v>
+      </c>
+      <c r="AQ143">
+        <v>0.5</v>
+      </c>
+      <c r="AR143">
+        <v>1.39</v>
+      </c>
+      <c r="AS143">
+        <v>0.91</v>
+      </c>
+      <c r="AT143">
+        <v>2.3</v>
+      </c>
+      <c r="AU143">
+        <v>5</v>
+      </c>
+      <c r="AV143">
+        <v>8</v>
+      </c>
+      <c r="AW143">
+        <v>5</v>
+      </c>
+      <c r="AX143">
+        <v>8</v>
+      </c>
+      <c r="AY143">
+        <v>10</v>
+      </c>
+      <c r="AZ143">
+        <v>16</v>
+      </c>
+      <c r="BA143">
         <v>4</v>
       </c>
-      <c r="V143">
-        <v>2.1</v>
-      </c>
-      <c r="W143">
-        <v>1.67</v>
-      </c>
-      <c r="X143">
-        <v>4.33</v>
-      </c>
-      <c r="Y143">
-        <v>1.2</v>
-      </c>
-      <c r="Z143">
-        <v>1.17</v>
-      </c>
-      <c r="AA143">
-        <v>6.25</v>
-      </c>
-      <c r="AB143">
-        <v>12</v>
-      </c>
-      <c r="AC143">
-        <v>1</v>
-      </c>
-      <c r="AD143">
-        <v>19</v>
-      </c>
-      <c r="AE143">
-        <v>1.1</v>
-      </c>
-      <c r="AF143">
-        <v>6.2</v>
-      </c>
-      <c r="AG143">
-        <v>1.44</v>
-      </c>
-      <c r="AH143">
-        <v>2.63</v>
-      </c>
-      <c r="AI143">
-        <v>2.1</v>
-      </c>
-      <c r="AJ143">
-        <v>1.67</v>
-      </c>
-      <c r="AK143">
-        <v>1.03</v>
-      </c>
-      <c r="AL143">
-        <v>1.06</v>
-      </c>
-      <c r="AM143">
-        <v>4.6</v>
-      </c>
-      <c r="AN143">
-        <v>2.45</v>
-      </c>
-      <c r="AO143">
-        <v>1.45</v>
-      </c>
-      <c r="AP143">
-        <v>2.5</v>
-      </c>
-      <c r="AQ143">
-        <v>1.33</v>
-      </c>
-      <c r="AR143">
-        <v>2.6</v>
-      </c>
-      <c r="AS143">
-        <v>1.36</v>
-      </c>
-      <c r="AT143">
-        <v>3.96</v>
-      </c>
-      <c r="AU143">
-        <v>12</v>
-      </c>
-      <c r="AV143">
-        <v>3</v>
-      </c>
-      <c r="AW143">
-        <v>9</v>
-      </c>
-      <c r="AX143">
-        <v>2</v>
-      </c>
-      <c r="AY143">
-        <v>21</v>
-      </c>
-      <c r="AZ143">
-        <v>5</v>
-      </c>
-      <c r="BA143">
-        <v>6</v>
-      </c>
       <c r="BB143">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BC143">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="BD143">
         <v>0</v>
@@ -30636,7 +30636,7 @@
         <v>143</v>
       </c>
       <c r="B144">
-        <v>7817178</v>
+        <v>7817177</v>
       </c>
       <c r="C144" t="s">
         <v>68</v>
@@ -30651,19 +30651,19 @@
         <v>2</v>
       </c>
       <c r="G144" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="H144" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I144">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J144">
         <v>1</v>
       </c>
       <c r="K144">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L144">
         <v>3</v>
@@ -30681,160 +30681,160 @@
         <v>264</v>
       </c>
       <c r="Q144">
-        <v>2.4</v>
+        <v>1.53</v>
       </c>
       <c r="R144">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="S144">
-        <v>3.75</v>
+        <v>9.5</v>
       </c>
       <c r="T144">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="U144">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="V144">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="W144">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="X144">
-        <v>5.5</v>
+        <v>4.33</v>
       </c>
       <c r="Y144">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="Z144">
-        <v>1.71</v>
+        <v>1.17</v>
       </c>
       <c r="AA144">
-        <v>3.91</v>
+        <v>6.25</v>
       </c>
       <c r="AB144">
-        <v>4.4</v>
+        <v>12</v>
       </c>
       <c r="AC144">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AD144">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AE144">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AF144">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="AG144">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AH144">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="AI144">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="AJ144">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AK144">
-        <v>1.26</v>
+        <v>1.03</v>
       </c>
       <c r="AL144">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AM144">
-        <v>1.8</v>
+        <v>4.6</v>
       </c>
       <c r="AN144">
-        <v>1.64</v>
+        <v>2.45</v>
       </c>
       <c r="AO144">
-        <v>0.64</v>
+        <v>1.45</v>
       </c>
       <c r="AP144">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="AQ144">
-        <v>0.58</v>
+        <v>1.33</v>
       </c>
       <c r="AR144">
-        <v>1.44</v>
+        <v>2.6</v>
       </c>
       <c r="AS144">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AT144">
-        <v>2.91</v>
+        <v>3.96</v>
       </c>
       <c r="AU144">
+        <v>12</v>
+      </c>
+      <c r="AV144">
+        <v>3</v>
+      </c>
+      <c r="AW144">
+        <v>9</v>
+      </c>
+      <c r="AX144">
+        <v>2</v>
+      </c>
+      <c r="AY144">
+        <v>21</v>
+      </c>
+      <c r="AZ144">
         <v>5</v>
-      </c>
-      <c r="AV144">
-        <v>4</v>
-      </c>
-      <c r="AW144">
-        <v>3</v>
-      </c>
-      <c r="AX144">
-        <v>4</v>
-      </c>
-      <c r="AY144">
-        <v>8</v>
-      </c>
-      <c r="AZ144">
-        <v>8</v>
       </c>
       <c r="BA144">
         <v>6</v>
       </c>
       <c r="BB144">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC144">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD144">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BE144">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BF144">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BG144">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BH144">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BI144">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BJ144">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BK144">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BL144">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BM144">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="BN144">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="BO144">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BP144">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Wales Welsh Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Wales Welsh Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="926" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="266">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -578,6 +578,9 @@
   </si>
   <si>
     <t>['2', '53', '68']</t>
+  </si>
+  <si>
+    <t>['52', '76']</t>
   </si>
   <si>
     <t>['45+2']</t>
@@ -1170,7 +1173,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP144"/>
+  <dimension ref="A1:BP145"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1426,7 +1429,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q2">
         <v>1.83</v>
@@ -1507,7 +1510,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ2">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1632,7 +1635,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q3">
         <v>3.75</v>
@@ -1838,7 +1841,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -1916,7 +1919,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ4">
         <v>1.33</v>
@@ -2250,7 +2253,7 @@
         <v>85</v>
       </c>
       <c r="P6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q6">
         <v>4</v>
@@ -2456,7 +2459,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q7">
         <v>11</v>
@@ -2534,7 +2537,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ7">
         <v>2.18</v>
@@ -3280,7 +3283,7 @@
         <v>89</v>
       </c>
       <c r="P11" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q11">
         <v>3.6</v>
@@ -3486,7 +3489,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q12">
         <v>2.9</v>
@@ -3898,7 +3901,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q14">
         <v>4.33</v>
@@ -4310,7 +4313,7 @@
         <v>85</v>
       </c>
       <c r="P16" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q16">
         <v>2.63</v>
@@ -4722,7 +4725,7 @@
         <v>94</v>
       </c>
       <c r="P18" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q18">
         <v>3</v>
@@ -4928,7 +4931,7 @@
         <v>85</v>
       </c>
       <c r="P19" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q19">
         <v>4.75</v>
@@ -5006,7 +5009,7 @@
         <v>1</v>
       </c>
       <c r="AP19">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ19">
         <v>1</v>
@@ -5421,7 +5424,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ21">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR21">
         <v>1.58</v>
@@ -5958,7 +5961,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6164,7 +6167,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q25">
         <v>3.2</v>
@@ -6370,7 +6373,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -6576,7 +6579,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q27">
         <v>5.5</v>
@@ -6863,7 +6866,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ28">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR28">
         <v>0</v>
@@ -7400,7 +7403,7 @@
         <v>85</v>
       </c>
       <c r="P31" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q31">
         <v>13</v>
@@ -7606,7 +7609,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q32">
         <v>1.83</v>
@@ -8018,7 +8021,7 @@
         <v>85</v>
       </c>
       <c r="P34" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q34">
         <v>3</v>
@@ -8511,7 +8514,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ36">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR36">
         <v>1.37</v>
@@ -8714,7 +8717,7 @@
         <v>2.33</v>
       </c>
       <c r="AP37">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ37">
         <v>1.75</v>
@@ -9048,7 +9051,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q39">
         <v>1.83</v>
@@ -9460,7 +9463,7 @@
         <v>110</v>
       </c>
       <c r="P41" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q41">
         <v>7</v>
@@ -9666,7 +9669,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q42">
         <v>2.6</v>
@@ -9872,7 +9875,7 @@
         <v>85</v>
       </c>
       <c r="P43" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q43">
         <v>3.75</v>
@@ -10490,7 +10493,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q46">
         <v>3.4</v>
@@ -10696,7 +10699,7 @@
         <v>115</v>
       </c>
       <c r="P47" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q47">
         <v>2.25</v>
@@ -10902,7 +10905,7 @@
         <v>116</v>
       </c>
       <c r="P48" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q48">
         <v>2.5</v>
@@ -11314,7 +11317,7 @@
         <v>117</v>
       </c>
       <c r="P50" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q50">
         <v>1.67</v>
@@ -11520,7 +11523,7 @@
         <v>118</v>
       </c>
       <c r="P51" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q51">
         <v>6</v>
@@ -11726,7 +11729,7 @@
         <v>119</v>
       </c>
       <c r="P52" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -11804,7 +11807,7 @@
         <v>1.33</v>
       </c>
       <c r="AP52">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ52">
         <v>2</v>
@@ -12013,7 +12016,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ53">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR53">
         <v>1.67</v>
@@ -12138,7 +12141,7 @@
         <v>114</v>
       </c>
       <c r="P54" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q54">
         <v>9.5</v>
@@ -12550,7 +12553,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q56">
         <v>7</v>
@@ -12756,7 +12759,7 @@
         <v>85</v>
       </c>
       <c r="P57" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q57">
         <v>6.5</v>
@@ -12834,7 +12837,7 @@
         <v>2.5</v>
       </c>
       <c r="AP57">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ57">
         <v>2.17</v>
@@ -13374,7 +13377,7 @@
         <v>125</v>
       </c>
       <c r="P60" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q60">
         <v>2.3</v>
@@ -13580,7 +13583,7 @@
         <v>85</v>
       </c>
       <c r="P61" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q61">
         <v>2.88</v>
@@ -13867,7 +13870,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ62">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR62">
         <v>1.28</v>
@@ -13992,7 +13995,7 @@
         <v>87</v>
       </c>
       <c r="P63" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q63">
         <v>2.63</v>
@@ -14198,7 +14201,7 @@
         <v>127</v>
       </c>
       <c r="P64" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q64">
         <v>1.42</v>
@@ -14610,7 +14613,7 @@
         <v>128</v>
       </c>
       <c r="P66" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -14688,7 +14691,7 @@
         <v>1.5</v>
       </c>
       <c r="AP66">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ66">
         <v>1.25</v>
@@ -15228,7 +15231,7 @@
         <v>131</v>
       </c>
       <c r="P69" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15434,7 +15437,7 @@
         <v>85</v>
       </c>
       <c r="P70" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q70">
         <v>9</v>
@@ -15846,7 +15849,7 @@
         <v>132</v>
       </c>
       <c r="P72" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q72">
         <v>7</v>
@@ -16052,7 +16055,7 @@
         <v>133</v>
       </c>
       <c r="P73" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q73">
         <v>1.73</v>
@@ -16133,7 +16136,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ73">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR73">
         <v>1.35</v>
@@ -16464,7 +16467,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16876,7 +16879,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q77">
         <v>2.5</v>
@@ -17082,7 +17085,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17160,7 +17163,7 @@
         <v>1.14</v>
       </c>
       <c r="AP78">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ78">
         <v>1.25</v>
@@ -17288,7 +17291,7 @@
         <v>139</v>
       </c>
       <c r="P79" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q79">
         <v>2.75</v>
@@ -17700,7 +17703,7 @@
         <v>140</v>
       </c>
       <c r="P81" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q81">
         <v>19</v>
@@ -17906,7 +17909,7 @@
         <v>141</v>
       </c>
       <c r="P82" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q82">
         <v>1.5</v>
@@ -18112,7 +18115,7 @@
         <v>142</v>
       </c>
       <c r="P83" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18318,7 +18321,7 @@
         <v>143</v>
       </c>
       <c r="P84" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q84">
         <v>11</v>
@@ -18524,7 +18527,7 @@
         <v>144</v>
       </c>
       <c r="P85" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q85">
         <v>4.75</v>
@@ -19429,7 +19432,7 @@
         <v>1</v>
       </c>
       <c r="AQ89">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR89">
         <v>1.09</v>
@@ -19554,7 +19557,7 @@
         <v>148</v>
       </c>
       <c r="P90" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q90">
         <v>4.75</v>
@@ -19966,7 +19969,7 @@
         <v>150</v>
       </c>
       <c r="P92" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q92">
         <v>2.88</v>
@@ -20378,7 +20381,7 @@
         <v>151</v>
       </c>
       <c r="P94" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q94">
         <v>2.88</v>
@@ -20790,7 +20793,7 @@
         <v>153</v>
       </c>
       <c r="P96" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q96">
         <v>11</v>
@@ -21077,7 +21080,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ97">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR97">
         <v>1.22</v>
@@ -21280,7 +21283,7 @@
         <v>0.5</v>
       </c>
       <c r="AP98">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ98">
         <v>0.83</v>
@@ -21614,7 +21617,7 @@
         <v>156</v>
       </c>
       <c r="P100" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q100">
         <v>1.73</v>
@@ -21820,7 +21823,7 @@
         <v>85</v>
       </c>
       <c r="P101" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q101">
         <v>3.4</v>
@@ -22026,7 +22029,7 @@
         <v>157</v>
       </c>
       <c r="P102" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q102">
         <v>3</v>
@@ -22232,7 +22235,7 @@
         <v>158</v>
       </c>
       <c r="P103" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22928,10 +22931,10 @@
         <v>0.33</v>
       </c>
       <c r="AP106">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ106">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR106">
         <v>1.69</v>
@@ -23056,7 +23059,7 @@
         <v>162</v>
       </c>
       <c r="P107" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q107">
         <v>3</v>
@@ -23262,7 +23265,7 @@
         <v>163</v>
       </c>
       <c r="P108" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q108">
         <v>2.75</v>
@@ -23674,7 +23677,7 @@
         <v>165</v>
       </c>
       <c r="P110" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q110">
         <v>2.4</v>
@@ -24086,7 +24089,7 @@
         <v>167</v>
       </c>
       <c r="P112" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q112">
         <v>1.4</v>
@@ -24292,7 +24295,7 @@
         <v>168</v>
       </c>
       <c r="P113" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q113">
         <v>4.75</v>
@@ -24498,7 +24501,7 @@
         <v>98</v>
       </c>
       <c r="P114" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q114">
         <v>2</v>
@@ -24704,7 +24707,7 @@
         <v>85</v>
       </c>
       <c r="P115" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q115">
         <v>3.75</v>
@@ -25116,7 +25119,7 @@
         <v>169</v>
       </c>
       <c r="P117" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25322,7 +25325,7 @@
         <v>170</v>
       </c>
       <c r="P118" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q118">
         <v>6</v>
@@ -25940,7 +25943,7 @@
         <v>172</v>
       </c>
       <c r="P121" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q121">
         <v>2.1</v>
@@ -26224,7 +26227,7 @@
         <v>1</v>
       </c>
       <c r="AP122">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ122">
         <v>0.75</v>
@@ -26433,7 +26436,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ123">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR123">
         <v>1.34</v>
@@ -26558,7 +26561,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q124">
         <v>1.44</v>
@@ -27176,7 +27179,7 @@
         <v>85</v>
       </c>
       <c r="P127" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q127">
         <v>2.3</v>
@@ -27382,7 +27385,7 @@
         <v>139</v>
       </c>
       <c r="P128" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q128">
         <v>2.75</v>
@@ -27794,7 +27797,7 @@
         <v>85</v>
       </c>
       <c r="P130" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q130">
         <v>5.5</v>
@@ -28000,7 +28003,7 @@
         <v>177</v>
       </c>
       <c r="P131" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q131">
         <v>7</v>
@@ -28412,7 +28415,7 @@
         <v>85</v>
       </c>
       <c r="P133" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q133">
         <v>2.75</v>
@@ -28618,7 +28621,7 @@
         <v>179</v>
       </c>
       <c r="P134" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q134">
         <v>4.75</v>
@@ -28824,7 +28827,7 @@
         <v>180</v>
       </c>
       <c r="P135" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q135">
         <v>2.5</v>
@@ -29030,7 +29033,7 @@
         <v>120</v>
       </c>
       <c r="P136" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q136">
         <v>3.75</v>
@@ -29236,7 +29239,7 @@
         <v>181</v>
       </c>
       <c r="P137" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q137">
         <v>2.38</v>
@@ -29520,7 +29523,7 @@
         <v>1.09</v>
       </c>
       <c r="AP138">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ138">
         <v>1</v>
@@ -29648,7 +29651,7 @@
         <v>183</v>
       </c>
       <c r="P139" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q139">
         <v>2.7</v>
@@ -30266,7 +30269,7 @@
         <v>185</v>
       </c>
       <c r="P142" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q142">
         <v>2.4</v>
@@ -30472,7 +30475,7 @@
         <v>186</v>
       </c>
       <c r="P143" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q143">
         <v>2.1</v>
@@ -30553,7 +30556,7 @@
         <v>1</v>
       </c>
       <c r="AQ143">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR143">
         <v>1.39</v>
@@ -30678,7 +30681,7 @@
         <v>187</v>
       </c>
       <c r="P144" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q144">
         <v>1.53</v>
@@ -30835,6 +30838,212 @@
       </c>
       <c r="BP144">
         <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:68">
+      <c r="A145" s="1">
+        <v>144</v>
+      </c>
+      <c r="B145">
+        <v>7817181</v>
+      </c>
+      <c r="C145" t="s">
+        <v>68</v>
+      </c>
+      <c r="D145" t="s">
+        <v>69</v>
+      </c>
+      <c r="E145" s="2">
+        <v>45695.69791666666</v>
+      </c>
+      <c r="F145">
+        <v>3</v>
+      </c>
+      <c r="G145" t="s">
+        <v>72</v>
+      </c>
+      <c r="H145" t="s">
+        <v>78</v>
+      </c>
+      <c r="I145">
+        <v>0</v>
+      </c>
+      <c r="J145">
+        <v>0</v>
+      </c>
+      <c r="K145">
+        <v>0</v>
+      </c>
+      <c r="L145">
+        <v>2</v>
+      </c>
+      <c r="M145">
+        <v>0</v>
+      </c>
+      <c r="N145">
+        <v>2</v>
+      </c>
+      <c r="O145" t="s">
+        <v>188</v>
+      </c>
+      <c r="P145" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q145">
+        <v>2.01</v>
+      </c>
+      <c r="R145">
+        <v>2.33</v>
+      </c>
+      <c r="S145">
+        <v>5.25</v>
+      </c>
+      <c r="T145">
+        <v>1.29</v>
+      </c>
+      <c r="U145">
+        <v>3.4</v>
+      </c>
+      <c r="V145">
+        <v>2.45</v>
+      </c>
+      <c r="W145">
+        <v>1.51</v>
+      </c>
+      <c r="X145">
+        <v>5.3</v>
+      </c>
+      <c r="Y145">
+        <v>1.12</v>
+      </c>
+      <c r="Z145">
+        <v>1.58</v>
+      </c>
+      <c r="AA145">
+        <v>4.6</v>
+      </c>
+      <c r="AB145">
+        <v>4.6</v>
+      </c>
+      <c r="AC145">
+        <v>1.01</v>
+      </c>
+      <c r="AD145">
+        <v>11</v>
+      </c>
+      <c r="AE145">
+        <v>1.15</v>
+      </c>
+      <c r="AF145">
+        <v>4.3</v>
+      </c>
+      <c r="AG145">
+        <v>1.65</v>
+      </c>
+      <c r="AH145">
+        <v>2.2</v>
+      </c>
+      <c r="AI145">
+        <v>1.68</v>
+      </c>
+      <c r="AJ145">
+        <v>2.01</v>
+      </c>
+      <c r="AK145">
+        <v>1.11</v>
+      </c>
+      <c r="AL145">
+        <v>1.18</v>
+      </c>
+      <c r="AM145">
+        <v>2.35</v>
+      </c>
+      <c r="AN145">
+        <v>1.33</v>
+      </c>
+      <c r="AO145">
+        <v>0.5</v>
+      </c>
+      <c r="AP145">
+        <v>1.46</v>
+      </c>
+      <c r="AQ145">
+        <v>0.46</v>
+      </c>
+      <c r="AR145">
+        <v>1.76</v>
+      </c>
+      <c r="AS145">
+        <v>1.02</v>
+      </c>
+      <c r="AT145">
+        <v>2.78</v>
+      </c>
+      <c r="AU145">
+        <v>8</v>
+      </c>
+      <c r="AV145">
+        <v>5</v>
+      </c>
+      <c r="AW145">
+        <v>11</v>
+      </c>
+      <c r="AX145">
+        <v>5</v>
+      </c>
+      <c r="AY145">
+        <v>19</v>
+      </c>
+      <c r="AZ145">
+        <v>10</v>
+      </c>
+      <c r="BA145">
+        <v>6</v>
+      </c>
+      <c r="BB145">
+        <v>3</v>
+      </c>
+      <c r="BC145">
+        <v>9</v>
+      </c>
+      <c r="BD145">
+        <v>1.56</v>
+      </c>
+      <c r="BE145">
+        <v>8.4</v>
+      </c>
+      <c r="BF145">
+        <v>2.79</v>
+      </c>
+      <c r="BG145">
+        <v>1.29</v>
+      </c>
+      <c r="BH145">
+        <v>3.4</v>
+      </c>
+      <c r="BI145">
+        <v>1.42</v>
+      </c>
+      <c r="BJ145">
+        <v>2.65</v>
+      </c>
+      <c r="BK145">
+        <v>1.75</v>
+      </c>
+      <c r="BL145">
+        <v>1.96</v>
+      </c>
+      <c r="BM145">
+        <v>2.25</v>
+      </c>
+      <c r="BN145">
+        <v>1.57</v>
+      </c>
+      <c r="BO145">
+        <v>3</v>
+      </c>
+      <c r="BP145">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Wales Welsh Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Wales Welsh Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="267">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -581,6 +581,9 @@
   </si>
   <si>
     <t>['52', '76']</t>
+  </si>
+  <si>
+    <t>['11', '53', '63', '88']</t>
   </si>
   <si>
     <t>['45+2']</t>
@@ -1173,7 +1176,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP145"/>
+  <dimension ref="A1:BP146"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1429,7 +1432,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q2">
         <v>1.83</v>
@@ -1635,7 +1638,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q3">
         <v>3.75</v>
@@ -1841,7 +1844,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -2253,7 +2256,7 @@
         <v>85</v>
       </c>
       <c r="P6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q6">
         <v>4</v>
@@ -2334,7 +2337,7 @@
         <v>1</v>
       </c>
       <c r="AQ6">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2459,7 +2462,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q7">
         <v>11</v>
@@ -3283,7 +3286,7 @@
         <v>89</v>
       </c>
       <c r="P11" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q11">
         <v>3.6</v>
@@ -3489,7 +3492,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q12">
         <v>2.9</v>
@@ -3901,7 +3904,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q14">
         <v>4.33</v>
@@ -4188,7 +4191,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ15">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4313,7 +4316,7 @@
         <v>85</v>
       </c>
       <c r="P16" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q16">
         <v>2.63</v>
@@ -4725,7 +4728,7 @@
         <v>94</v>
       </c>
       <c r="P18" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q18">
         <v>3</v>
@@ -4931,7 +4934,7 @@
         <v>85</v>
       </c>
       <c r="P19" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q19">
         <v>4.75</v>
@@ -5961,7 +5964,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6167,7 +6170,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q25">
         <v>3.2</v>
@@ -6248,7 +6251,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ25">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR25">
         <v>1.81</v>
@@ -6373,7 +6376,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -6579,7 +6582,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q27">
         <v>5.5</v>
@@ -6863,7 +6866,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ28">
         <v>0.46</v>
@@ -7403,7 +7406,7 @@
         <v>85</v>
       </c>
       <c r="P31" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q31">
         <v>13</v>
@@ -7609,7 +7612,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q32">
         <v>1.83</v>
@@ -8021,7 +8024,7 @@
         <v>85</v>
       </c>
       <c r="P34" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q34">
         <v>3</v>
@@ -8923,7 +8926,7 @@
         <v>1.33</v>
       </c>
       <c r="AP38">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ38">
         <v>1.25</v>
@@ -9051,7 +9054,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q39">
         <v>1.83</v>
@@ -9338,7 +9341,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ40">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR40">
         <v>1.48</v>
@@ -9463,7 +9466,7 @@
         <v>110</v>
       </c>
       <c r="P41" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q41">
         <v>7</v>
@@ -9669,7 +9672,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q42">
         <v>2.6</v>
@@ -9875,7 +9878,7 @@
         <v>85</v>
       </c>
       <c r="P43" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q43">
         <v>3.75</v>
@@ -10493,7 +10496,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q46">
         <v>3.4</v>
@@ -10699,7 +10702,7 @@
         <v>115</v>
       </c>
       <c r="P47" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q47">
         <v>2.25</v>
@@ -10905,7 +10908,7 @@
         <v>116</v>
       </c>
       <c r="P48" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q48">
         <v>2.5</v>
@@ -11317,7 +11320,7 @@
         <v>117</v>
       </c>
       <c r="P50" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q50">
         <v>1.67</v>
@@ -11395,7 +11398,7 @@
         <v>1</v>
       </c>
       <c r="AP50">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ50">
         <v>1.25</v>
@@ -11523,7 +11526,7 @@
         <v>118</v>
       </c>
       <c r="P51" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q51">
         <v>6</v>
@@ -11729,7 +11732,7 @@
         <v>119</v>
       </c>
       <c r="P52" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -12141,7 +12144,7 @@
         <v>114</v>
       </c>
       <c r="P54" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q54">
         <v>9.5</v>
@@ -12553,7 +12556,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q56">
         <v>7</v>
@@ -12759,7 +12762,7 @@
         <v>85</v>
       </c>
       <c r="P57" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q57">
         <v>6.5</v>
@@ -12840,7 +12843,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ57">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR57">
         <v>1.7</v>
@@ -13377,7 +13380,7 @@
         <v>125</v>
       </c>
       <c r="P60" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q60">
         <v>2.3</v>
@@ -13583,7 +13586,7 @@
         <v>85</v>
       </c>
       <c r="P61" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q61">
         <v>2.88</v>
@@ -13995,7 +13998,7 @@
         <v>87</v>
       </c>
       <c r="P63" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q63">
         <v>2.63</v>
@@ -14201,7 +14204,7 @@
         <v>127</v>
       </c>
       <c r="P64" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q64">
         <v>1.42</v>
@@ -14279,7 +14282,7 @@
         <v>2</v>
       </c>
       <c r="AP64">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ64">
         <v>2</v>
@@ -14613,7 +14616,7 @@
         <v>128</v>
       </c>
       <c r="P66" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -14897,7 +14900,7 @@
         <v>2.14</v>
       </c>
       <c r="AP67">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ67">
         <v>1.33</v>
@@ -15231,7 +15234,7 @@
         <v>131</v>
       </c>
       <c r="P69" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15437,7 +15440,7 @@
         <v>85</v>
       </c>
       <c r="P70" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q70">
         <v>9</v>
@@ -15518,7 +15521,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ70">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR70">
         <v>0.96</v>
@@ -15849,7 +15852,7 @@
         <v>132</v>
       </c>
       <c r="P72" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q72">
         <v>7</v>
@@ -16055,7 +16058,7 @@
         <v>133</v>
       </c>
       <c r="P73" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q73">
         <v>1.73</v>
@@ -16342,7 +16345,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ74">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR74">
         <v>1.22</v>
@@ -16467,7 +16470,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16751,7 +16754,7 @@
         <v>1.4</v>
       </c>
       <c r="AP76">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ76">
         <v>0.58</v>
@@ -16879,7 +16882,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q77">
         <v>2.5</v>
@@ -17085,7 +17088,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17291,7 +17294,7 @@
         <v>139</v>
       </c>
       <c r="P79" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q79">
         <v>2.75</v>
@@ -17703,7 +17706,7 @@
         <v>140</v>
       </c>
       <c r="P81" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q81">
         <v>19</v>
@@ -17909,7 +17912,7 @@
         <v>141</v>
       </c>
       <c r="P82" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q82">
         <v>1.5</v>
@@ -18115,7 +18118,7 @@
         <v>142</v>
       </c>
       <c r="P83" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18321,7 +18324,7 @@
         <v>143</v>
       </c>
       <c r="P84" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q84">
         <v>11</v>
@@ -18527,7 +18530,7 @@
         <v>144</v>
       </c>
       <c r="P85" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q85">
         <v>4.75</v>
@@ -18608,7 +18611,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ85">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR85">
         <v>1.4</v>
@@ -19557,7 +19560,7 @@
         <v>148</v>
       </c>
       <c r="P90" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q90">
         <v>4.75</v>
@@ -19969,7 +19972,7 @@
         <v>150</v>
       </c>
       <c r="P92" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q92">
         <v>2.88</v>
@@ -20381,7 +20384,7 @@
         <v>151</v>
       </c>
       <c r="P94" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q94">
         <v>2.88</v>
@@ -20665,7 +20668,7 @@
         <v>2.29</v>
       </c>
       <c r="AP95">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ95">
         <v>1.75</v>
@@ -20793,7 +20796,7 @@
         <v>153</v>
       </c>
       <c r="P96" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q96">
         <v>11</v>
@@ -21617,7 +21620,7 @@
         <v>156</v>
       </c>
       <c r="P100" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q100">
         <v>1.73</v>
@@ -21695,10 +21698,10 @@
         <v>2.5</v>
       </c>
       <c r="AP100">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ100">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR100">
         <v>2.55</v>
@@ -21823,7 +21826,7 @@
         <v>85</v>
       </c>
       <c r="P101" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q101">
         <v>3.4</v>
@@ -22029,7 +22032,7 @@
         <v>157</v>
       </c>
       <c r="P102" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q102">
         <v>3</v>
@@ -22235,7 +22238,7 @@
         <v>158</v>
       </c>
       <c r="P103" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -23059,7 +23062,7 @@
         <v>162</v>
       </c>
       <c r="P107" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q107">
         <v>3</v>
@@ -23265,7 +23268,7 @@
         <v>163</v>
       </c>
       <c r="P108" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q108">
         <v>2.75</v>
@@ -23677,7 +23680,7 @@
         <v>165</v>
       </c>
       <c r="P110" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q110">
         <v>2.4</v>
@@ -24089,7 +24092,7 @@
         <v>167</v>
       </c>
       <c r="P112" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q112">
         <v>1.4</v>
@@ -24167,7 +24170,7 @@
         <v>0.43</v>
       </c>
       <c r="AP112">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ112">
         <v>0.83</v>
@@ -24295,7 +24298,7 @@
         <v>168</v>
       </c>
       <c r="P113" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q113">
         <v>4.75</v>
@@ -24376,7 +24379,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ113">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR113">
         <v>1.49</v>
@@ -24501,7 +24504,7 @@
         <v>98</v>
       </c>
       <c r="P114" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q114">
         <v>2</v>
@@ -24707,7 +24710,7 @@
         <v>85</v>
       </c>
       <c r="P115" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q115">
         <v>3.75</v>
@@ -25119,7 +25122,7 @@
         <v>169</v>
       </c>
       <c r="P117" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25325,7 +25328,7 @@
         <v>170</v>
       </c>
       <c r="P118" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q118">
         <v>6</v>
@@ -25815,7 +25818,7 @@
         <v>1.33</v>
       </c>
       <c r="AP120">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ120">
         <v>1</v>
@@ -25943,7 +25946,7 @@
         <v>172</v>
       </c>
       <c r="P121" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q121">
         <v>2.1</v>
@@ -26561,7 +26564,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q124">
         <v>1.44</v>
@@ -26639,7 +26642,7 @@
         <v>0.9</v>
       </c>
       <c r="AP124">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ124">
         <v>0.75</v>
@@ -27179,7 +27182,7 @@
         <v>85</v>
       </c>
       <c r="P127" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q127">
         <v>2.3</v>
@@ -27385,7 +27388,7 @@
         <v>139</v>
       </c>
       <c r="P128" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q128">
         <v>2.75</v>
@@ -27797,7 +27800,7 @@
         <v>85</v>
       </c>
       <c r="P130" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q130">
         <v>5.5</v>
@@ -28003,7 +28006,7 @@
         <v>177</v>
       </c>
       <c r="P131" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q131">
         <v>7</v>
@@ -28084,7 +28087,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ131">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR131">
         <v>1.63</v>
@@ -28415,7 +28418,7 @@
         <v>85</v>
       </c>
       <c r="P133" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q133">
         <v>2.75</v>
@@ -28621,7 +28624,7 @@
         <v>179</v>
       </c>
       <c r="P134" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q134">
         <v>4.75</v>
@@ -28702,7 +28705,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ134">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AR134">
         <v>1.5</v>
@@ -28827,7 +28830,7 @@
         <v>180</v>
       </c>
       <c r="P135" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q135">
         <v>2.5</v>
@@ -29033,7 +29036,7 @@
         <v>120</v>
       </c>
       <c r="P136" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q136">
         <v>3.75</v>
@@ -29239,7 +29242,7 @@
         <v>181</v>
       </c>
       <c r="P137" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q137">
         <v>2.38</v>
@@ -29651,7 +29654,7 @@
         <v>183</v>
       </c>
       <c r="P139" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q139">
         <v>2.7</v>
@@ -30269,7 +30272,7 @@
         <v>185</v>
       </c>
       <c r="P142" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q142">
         <v>2.4</v>
@@ -30475,7 +30478,7 @@
         <v>186</v>
       </c>
       <c r="P143" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q143">
         <v>2.1</v>
@@ -30681,7 +30684,7 @@
         <v>187</v>
       </c>
       <c r="P144" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q144">
         <v>1.53</v>
@@ -30759,7 +30762,7 @@
         <v>1.45</v>
       </c>
       <c r="AP144">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ144">
         <v>1.33</v>
@@ -31044,6 +31047,212 @@
       </c>
       <c r="BP145">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="146" spans="1:68">
+      <c r="A146" s="1">
+        <v>145</v>
+      </c>
+      <c r="B146">
+        <v>7817182</v>
+      </c>
+      <c r="C146" t="s">
+        <v>68</v>
+      </c>
+      <c r="D146" t="s">
+        <v>69</v>
+      </c>
+      <c r="E146" s="2">
+        <v>45696.38541666666</v>
+      </c>
+      <c r="F146">
+        <v>3</v>
+      </c>
+      <c r="G146" t="s">
+        <v>81</v>
+      </c>
+      <c r="H146" t="s">
+        <v>76</v>
+      </c>
+      <c r="I146">
+        <v>1</v>
+      </c>
+      <c r="J146">
+        <v>0</v>
+      </c>
+      <c r="K146">
+        <v>1</v>
+      </c>
+      <c r="L146">
+        <v>4</v>
+      </c>
+      <c r="M146">
+        <v>0</v>
+      </c>
+      <c r="N146">
+        <v>4</v>
+      </c>
+      <c r="O146" t="s">
+        <v>189</v>
+      </c>
+      <c r="P146" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q146">
+        <v>1.7</v>
+      </c>
+      <c r="R146">
+        <v>2.51</v>
+      </c>
+      <c r="S146">
+        <v>7.6</v>
+      </c>
+      <c r="T146">
+        <v>1.28</v>
+      </c>
+      <c r="U146">
+        <v>3.46</v>
+      </c>
+      <c r="V146">
+        <v>2.4</v>
+      </c>
+      <c r="W146">
+        <v>1.53</v>
+      </c>
+      <c r="X146">
+        <v>5.2</v>
+      </c>
+      <c r="Y146">
+        <v>1.12</v>
+      </c>
+      <c r="Z146">
+        <v>1.3</v>
+      </c>
+      <c r="AA146">
+        <v>4.5</v>
+      </c>
+      <c r="AB146">
+        <v>8</v>
+      </c>
+      <c r="AC146">
+        <v>1.01</v>
+      </c>
+      <c r="AD146">
+        <v>13</v>
+      </c>
+      <c r="AE146">
+        <v>1.14</v>
+      </c>
+      <c r="AF146">
+        <v>4.4</v>
+      </c>
+      <c r="AG146">
+        <v>1.62</v>
+      </c>
+      <c r="AH146">
+        <v>2.25</v>
+      </c>
+      <c r="AI146">
+        <v>1.95</v>
+      </c>
+      <c r="AJ146">
+        <v>1.72</v>
+      </c>
+      <c r="AK146">
+        <v>1.02</v>
+      </c>
+      <c r="AL146">
+        <v>1.12</v>
+      </c>
+      <c r="AM146">
+        <v>3.32</v>
+      </c>
+      <c r="AN146">
+        <v>2.5</v>
+      </c>
+      <c r="AO146">
+        <v>2.17</v>
+      </c>
+      <c r="AP146">
+        <v>2.54</v>
+      </c>
+      <c r="AQ146">
+        <v>2</v>
+      </c>
+      <c r="AR146">
+        <v>2.6</v>
+      </c>
+      <c r="AS146">
+        <v>1.55</v>
+      </c>
+      <c r="AT146">
+        <v>4.15</v>
+      </c>
+      <c r="AU146">
+        <v>7</v>
+      </c>
+      <c r="AV146">
+        <v>2</v>
+      </c>
+      <c r="AW146">
+        <v>7</v>
+      </c>
+      <c r="AX146">
+        <v>1</v>
+      </c>
+      <c r="AY146">
+        <v>14</v>
+      </c>
+      <c r="AZ146">
+        <v>3</v>
+      </c>
+      <c r="BA146">
+        <v>5</v>
+      </c>
+      <c r="BB146">
+        <v>2</v>
+      </c>
+      <c r="BC146">
+        <v>7</v>
+      </c>
+      <c r="BD146">
+        <v>1.24</v>
+      </c>
+      <c r="BE146">
+        <v>9.9</v>
+      </c>
+      <c r="BF146">
+        <v>4.75</v>
+      </c>
+      <c r="BG146">
+        <v>1.3</v>
+      </c>
+      <c r="BH146">
+        <v>3.2</v>
+      </c>
+      <c r="BI146">
+        <v>1.5</v>
+      </c>
+      <c r="BJ146">
+        <v>2.37</v>
+      </c>
+      <c r="BK146">
+        <v>1.89</v>
+      </c>
+      <c r="BL146">
+        <v>1.88</v>
+      </c>
+      <c r="BM146">
+        <v>2.38</v>
+      </c>
+      <c r="BN146">
+        <v>1.5</v>
+      </c>
+      <c r="BO146">
+        <v>3</v>
+      </c>
+      <c r="BP146">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Wales Welsh Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Wales Welsh Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="268">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -586,6 +586,15 @@
     <t>['11', '53', '63', '88']</t>
   </si>
   <si>
+    <t>['25']</t>
+  </si>
+  <si>
+    <t>['5', '49']</t>
+  </si>
+  <si>
+    <t>['70']</t>
+  </si>
+  <si>
     <t>['45+2']</t>
   </si>
   <si>
@@ -671,9 +680,6 @@
   </si>
   <si>
     <t>['3', '53']</t>
-  </si>
-  <si>
-    <t>['70']</t>
   </si>
   <si>
     <t>['9', '17', '58', '88']</t>
@@ -806,9 +812,6 @@
   </si>
   <si>
     <t>['6', '14', '90+2']</t>
-  </si>
-  <si>
-    <t>['25']</t>
   </si>
   <si>
     <t>['4', '58', '70']</t>
@@ -1176,7 +1179,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP146"/>
+  <dimension ref="A1:BP150"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1432,7 +1435,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q2">
         <v>1.83</v>
@@ -1638,7 +1641,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q3">
         <v>3.75</v>
@@ -1719,7 +1722,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ3">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1844,7 +1847,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -2128,10 +2131,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ5">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2256,7 +2259,7 @@
         <v>85</v>
       </c>
       <c r="P6" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q6">
         <v>4</v>
@@ -2462,7 +2465,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q7">
         <v>11</v>
@@ -2746,10 +2749,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ8">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3161,7 +3164,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ10">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3286,7 +3289,7 @@
         <v>89</v>
       </c>
       <c r="P11" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q11">
         <v>3.6</v>
@@ -3492,7 +3495,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q12">
         <v>2.9</v>
@@ -3570,10 +3573,10 @@
         <v>3</v>
       </c>
       <c r="AP12">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ12">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3904,7 +3907,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q14">
         <v>4.33</v>
@@ -4316,7 +4319,7 @@
         <v>85</v>
       </c>
       <c r="P16" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q16">
         <v>2.63</v>
@@ -4603,7 +4606,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ17">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR17">
         <v>0.68</v>
@@ -4728,7 +4731,7 @@
         <v>94</v>
       </c>
       <c r="P18" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q18">
         <v>3</v>
@@ -4934,7 +4937,7 @@
         <v>85</v>
       </c>
       <c r="P19" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q19">
         <v>4.75</v>
@@ -5218,10 +5221,10 @@
         <v>3</v>
       </c>
       <c r="AP20">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ20">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR20">
         <v>1.34</v>
@@ -5630,10 +5633,10 @@
         <v>1</v>
       </c>
       <c r="AP22">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ22">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR22">
         <v>1.22</v>
@@ -5964,7 +5967,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6042,7 +6045,7 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ24">
         <v>1.33</v>
@@ -6170,7 +6173,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q25">
         <v>3.2</v>
@@ -6376,7 +6379,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -6582,7 +6585,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q27">
         <v>5.5</v>
@@ -7281,7 +7284,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ30">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR30">
         <v>1.93</v>
@@ -7406,7 +7409,7 @@
         <v>85</v>
       </c>
       <c r="P31" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q31">
         <v>13</v>
@@ -7612,7 +7615,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q32">
         <v>1.83</v>
@@ -7690,10 +7693,10 @@
         <v>0.5</v>
       </c>
       <c r="AP32">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ32">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR32">
         <v>1.41</v>
@@ -8024,7 +8027,7 @@
         <v>85</v>
       </c>
       <c r="P34" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q34">
         <v>3</v>
@@ -8723,7 +8726,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ37">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR37">
         <v>1.69</v>
@@ -8929,7 +8932,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ38">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR38">
         <v>3.26</v>
@@ -9054,7 +9057,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q39">
         <v>1.83</v>
@@ -9132,10 +9135,10 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ39">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR39">
         <v>1.1</v>
@@ -9338,7 +9341,7 @@
         <v>2.33</v>
       </c>
       <c r="AP40">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ40">
         <v>2</v>
@@ -9466,7 +9469,7 @@
         <v>110</v>
       </c>
       <c r="P41" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q41">
         <v>7</v>
@@ -9672,7 +9675,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q42">
         <v>2.6</v>
@@ -9878,7 +9881,7 @@
         <v>85</v>
       </c>
       <c r="P43" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q43">
         <v>3.75</v>
@@ -9959,7 +9962,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ43">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR43">
         <v>0.99</v>
@@ -10162,7 +10165,7 @@
         <v>2.33</v>
       </c>
       <c r="AP44">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ44">
         <v>1</v>
@@ -10496,7 +10499,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q46">
         <v>3.4</v>
@@ -10702,7 +10705,7 @@
         <v>115</v>
       </c>
       <c r="P47" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q47">
         <v>2.25</v>
@@ -10780,7 +10783,7 @@
         <v>1.25</v>
       </c>
       <c r="AP47">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ47">
         <v>0.75</v>
@@ -10908,7 +10911,7 @@
         <v>116</v>
       </c>
       <c r="P48" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q48">
         <v>2.5</v>
@@ -10989,7 +10992,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ48">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR48">
         <v>1.21</v>
@@ -11195,7 +11198,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ49">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR49">
         <v>2.19</v>
@@ -11320,7 +11323,7 @@
         <v>117</v>
       </c>
       <c r="P50" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q50">
         <v>1.67</v>
@@ -11401,7 +11404,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ50">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR50">
         <v>3.27</v>
@@ -11526,7 +11529,7 @@
         <v>118</v>
       </c>
       <c r="P51" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q51">
         <v>6</v>
@@ -11732,7 +11735,7 @@
         <v>119</v>
       </c>
       <c r="P52" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -12144,7 +12147,7 @@
         <v>114</v>
       </c>
       <c r="P54" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q54">
         <v>9.5</v>
@@ -12556,7 +12559,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q56">
         <v>7</v>
@@ -12637,7 +12640,7 @@
         <v>1</v>
       </c>
       <c r="AQ56">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR56">
         <v>1.02</v>
@@ -12762,7 +12765,7 @@
         <v>85</v>
       </c>
       <c r="P57" t="s">
-        <v>219</v>
+        <v>192</v>
       </c>
       <c r="Q57">
         <v>6.5</v>
@@ -13046,7 +13049,7 @@
         <v>1.75</v>
       </c>
       <c r="AP58">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ58">
         <v>1</v>
@@ -13255,7 +13258,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ59">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR59">
         <v>2.07</v>
@@ -13380,7 +13383,7 @@
         <v>125</v>
       </c>
       <c r="P60" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q60">
         <v>2.3</v>
@@ -13586,7 +13589,7 @@
         <v>85</v>
       </c>
       <c r="P61" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q61">
         <v>2.88</v>
@@ -13667,7 +13670,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ61">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR61">
         <v>1.49</v>
@@ -13870,7 +13873,7 @@
         <v>0</v>
       </c>
       <c r="AP62">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ62">
         <v>0.46</v>
@@ -13998,7 +14001,7 @@
         <v>87</v>
       </c>
       <c r="P63" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q63">
         <v>2.63</v>
@@ -14076,7 +14079,7 @@
         <v>1.75</v>
       </c>
       <c r="AP63">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ63">
         <v>2</v>
@@ -14204,7 +14207,7 @@
         <v>127</v>
       </c>
       <c r="P64" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q64">
         <v>1.42</v>
@@ -14616,7 +14619,7 @@
         <v>128</v>
       </c>
       <c r="P66" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -14697,7 +14700,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ66">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR66">
         <v>1.56</v>
@@ -15109,7 +15112,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ68">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR68">
         <v>1.7</v>
@@ -15234,7 +15237,7 @@
         <v>131</v>
       </c>
       <c r="P69" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15312,7 +15315,7 @@
         <v>1.2</v>
       </c>
       <c r="AP69">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ69">
         <v>0.75</v>
@@ -15440,7 +15443,7 @@
         <v>85</v>
       </c>
       <c r="P70" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q70">
         <v>9</v>
@@ -15852,7 +15855,7 @@
         <v>132</v>
       </c>
       <c r="P72" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q72">
         <v>7</v>
@@ -15933,7 +15936,7 @@
         <v>1</v>
       </c>
       <c r="AQ72">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR72">
         <v>1.05</v>
@@ -16058,7 +16061,7 @@
         <v>133</v>
       </c>
       <c r="P73" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q73">
         <v>1.73</v>
@@ -16136,7 +16139,7 @@
         <v>0</v>
       </c>
       <c r="AP73">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ73">
         <v>0.46</v>
@@ -16342,7 +16345,7 @@
         <v>2.67</v>
       </c>
       <c r="AP74">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ74">
         <v>2</v>
@@ -16470,7 +16473,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16551,7 +16554,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ75">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR75">
         <v>1.8</v>
@@ -16882,7 +16885,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q77">
         <v>2.5</v>
@@ -16960,7 +16963,7 @@
         <v>1.5</v>
       </c>
       <c r="AP77">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ77">
         <v>0.75</v>
@@ -17088,7 +17091,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17169,7 +17172,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ78">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR78">
         <v>1.54</v>
@@ -17294,7 +17297,7 @@
         <v>139</v>
       </c>
       <c r="P79" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q79">
         <v>2.75</v>
@@ -17375,7 +17378,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ79">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR79">
         <v>1.99</v>
@@ -17706,7 +17709,7 @@
         <v>140</v>
       </c>
       <c r="P81" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q81">
         <v>19</v>
@@ -17912,7 +17915,7 @@
         <v>141</v>
       </c>
       <c r="P82" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q82">
         <v>1.5</v>
@@ -17990,10 +17993,10 @@
         <v>0.6</v>
       </c>
       <c r="AP82">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ82">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR82">
         <v>1.39</v>
@@ -18118,7 +18121,7 @@
         <v>142</v>
       </c>
       <c r="P83" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18196,7 +18199,7 @@
         <v>2.4</v>
       </c>
       <c r="AP83">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ83">
         <v>2.18</v>
@@ -18324,7 +18327,7 @@
         <v>143</v>
       </c>
       <c r="P84" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q84">
         <v>11</v>
@@ -18530,7 +18533,7 @@
         <v>144</v>
       </c>
       <c r="P85" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q85">
         <v>4.75</v>
@@ -18608,7 +18611,7 @@
         <v>2.43</v>
       </c>
       <c r="AP85">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ85">
         <v>2</v>
@@ -18814,7 +18817,7 @@
         <v>1.88</v>
       </c>
       <c r="AP86">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ86">
         <v>1.33</v>
@@ -19229,7 +19232,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ88">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR88">
         <v>1.83</v>
@@ -19560,7 +19563,7 @@
         <v>148</v>
       </c>
       <c r="P90" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q90">
         <v>4.75</v>
@@ -19972,7 +19975,7 @@
         <v>150</v>
       </c>
       <c r="P92" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q92">
         <v>2.88</v>
@@ -20384,7 +20387,7 @@
         <v>151</v>
       </c>
       <c r="P94" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q94">
         <v>2.88</v>
@@ -20462,10 +20465,10 @@
         <v>1.29</v>
       </c>
       <c r="AP94">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ94">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR94">
         <v>1.18</v>
@@ -20671,7 +20674,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ95">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR95">
         <v>2.71</v>
@@ -20796,7 +20799,7 @@
         <v>153</v>
       </c>
       <c r="P96" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q96">
         <v>11</v>
@@ -21080,7 +21083,7 @@
         <v>0.38</v>
       </c>
       <c r="AP97">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ97">
         <v>0.46</v>
@@ -21289,7 +21292,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ98">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR98">
         <v>1.69</v>
@@ -21495,7 +21498,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ99">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR99">
         <v>1.39</v>
@@ -21620,7 +21623,7 @@
         <v>156</v>
       </c>
       <c r="P100" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q100">
         <v>1.73</v>
@@ -21826,7 +21829,7 @@
         <v>85</v>
       </c>
       <c r="P101" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q101">
         <v>3.4</v>
@@ -22032,7 +22035,7 @@
         <v>157</v>
       </c>
       <c r="P102" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q102">
         <v>3</v>
@@ -22238,7 +22241,7 @@
         <v>158</v>
       </c>
       <c r="P103" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22316,7 +22319,7 @@
         <v>2.13</v>
       </c>
       <c r="AP103">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ103">
         <v>2</v>
@@ -22525,7 +22528,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ104">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR104">
         <v>1.93</v>
@@ -23062,7 +23065,7 @@
         <v>162</v>
       </c>
       <c r="P107" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q107">
         <v>3</v>
@@ -23268,7 +23271,7 @@
         <v>163</v>
       </c>
       <c r="P108" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q108">
         <v>2.75</v>
@@ -23346,10 +23349,10 @@
         <v>1.38</v>
       </c>
       <c r="AP108">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ108">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR108">
         <v>1.33</v>
@@ -23552,7 +23555,7 @@
         <v>0.88</v>
       </c>
       <c r="AP109">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ109">
         <v>0.58</v>
@@ -23680,7 +23683,7 @@
         <v>165</v>
       </c>
       <c r="P110" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q110">
         <v>2.4</v>
@@ -23761,7 +23764,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ110">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR110">
         <v>1.27</v>
@@ -24092,7 +24095,7 @@
         <v>167</v>
       </c>
       <c r="P112" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q112">
         <v>1.4</v>
@@ -24173,7 +24176,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ112">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR112">
         <v>2.55</v>
@@ -24298,7 +24301,7 @@
         <v>168</v>
       </c>
       <c r="P113" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q113">
         <v>4.75</v>
@@ -24504,7 +24507,7 @@
         <v>98</v>
       </c>
       <c r="P114" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q114">
         <v>2</v>
@@ -24582,10 +24585,10 @@
         <v>0.38</v>
       </c>
       <c r="AP114">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ114">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR114">
         <v>1.45</v>
@@ -24710,7 +24713,7 @@
         <v>85</v>
       </c>
       <c r="P115" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q115">
         <v>3.75</v>
@@ -24791,7 +24794,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ115">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR115">
         <v>1.68</v>
@@ -24997,7 +25000,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ116">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR116">
         <v>1.04</v>
@@ -25122,7 +25125,7 @@
         <v>169</v>
       </c>
       <c r="P117" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25200,7 +25203,7 @@
         <v>0.78</v>
       </c>
       <c r="AP117">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ117">
         <v>0.58</v>
@@ -25328,7 +25331,7 @@
         <v>170</v>
       </c>
       <c r="P118" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q118">
         <v>6</v>
@@ -25406,7 +25409,7 @@
         <v>2</v>
       </c>
       <c r="AP118">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ118">
         <v>2.18</v>
@@ -25615,7 +25618,7 @@
         <v>1</v>
       </c>
       <c r="AQ119">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR119">
         <v>1.37</v>
@@ -25946,7 +25949,7 @@
         <v>172</v>
       </c>
       <c r="P121" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q121">
         <v>2.1</v>
@@ -26564,7 +26567,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q124">
         <v>1.44</v>
@@ -26851,7 +26854,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ125">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR125">
         <v>1.41</v>
@@ -27182,7 +27185,7 @@
         <v>85</v>
       </c>
       <c r="P127" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q127">
         <v>2.3</v>
@@ -27388,7 +27391,7 @@
         <v>139</v>
       </c>
       <c r="P128" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q128">
         <v>2.75</v>
@@ -27469,7 +27472,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ128">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR128">
         <v>1.06</v>
@@ -27672,7 +27675,7 @@
         <v>0.7</v>
       </c>
       <c r="AP129">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ129">
         <v>0.58</v>
@@ -27800,7 +27803,7 @@
         <v>85</v>
       </c>
       <c r="P130" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q130">
         <v>5.5</v>
@@ -27878,7 +27881,7 @@
         <v>2.1</v>
       </c>
       <c r="AP130">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ130">
         <v>2.18</v>
@@ -28006,7 +28009,7 @@
         <v>177</v>
       </c>
       <c r="P131" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q131">
         <v>7</v>
@@ -28293,7 +28296,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ132">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR132">
         <v>1.46</v>
@@ -28418,7 +28421,7 @@
         <v>85</v>
       </c>
       <c r="P133" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q133">
         <v>2.75</v>
@@ -28496,10 +28499,10 @@
         <v>1.2</v>
       </c>
       <c r="AP133">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ133">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR133">
         <v>1.54</v>
@@ -28624,7 +28627,7 @@
         <v>179</v>
       </c>
       <c r="P134" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q134">
         <v>4.75</v>
@@ -28702,7 +28705,7 @@
         <v>2.36</v>
       </c>
       <c r="AP134">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ134">
         <v>2</v>
@@ -28830,7 +28833,7 @@
         <v>180</v>
       </c>
       <c r="P135" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q135">
         <v>2.5</v>
@@ -28911,7 +28914,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ135">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR135">
         <v>1.57</v>
@@ -29036,7 +29039,7 @@
         <v>120</v>
       </c>
       <c r="P136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q136">
         <v>3.75</v>
@@ -29117,7 +29120,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ136">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR136">
         <v>1.08</v>
@@ -29242,7 +29245,7 @@
         <v>181</v>
       </c>
       <c r="P137" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q137">
         <v>2.38</v>
@@ -29323,7 +29326,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ137">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR137">
         <v>1.51</v>
@@ -29654,7 +29657,7 @@
         <v>183</v>
       </c>
       <c r="P139" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q139">
         <v>2.7</v>
@@ -29941,7 +29944,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ140">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR140">
         <v>1.75</v>
@@ -30144,7 +30147,7 @@
         <v>0.82</v>
       </c>
       <c r="AP141">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ141">
         <v>0.75</v>
@@ -30272,7 +30275,7 @@
         <v>185</v>
       </c>
       <c r="P142" t="s">
-        <v>264</v>
+        <v>190</v>
       </c>
       <c r="Q142">
         <v>2.4</v>
@@ -30478,7 +30481,7 @@
         <v>186</v>
       </c>
       <c r="P143" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q143">
         <v>2.1</v>
@@ -30684,7 +30687,7 @@
         <v>187</v>
       </c>
       <c r="P144" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q144">
         <v>1.53</v>
@@ -31253,6 +31256,830 @@
       </c>
       <c r="BP146">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="147" spans="1:68">
+      <c r="A147" s="1">
+        <v>146</v>
+      </c>
+      <c r="B147">
+        <v>7817183</v>
+      </c>
+      <c r="C147" t="s">
+        <v>68</v>
+      </c>
+      <c r="D147" t="s">
+        <v>69</v>
+      </c>
+      <c r="E147" s="2">
+        <v>45696.47916666666</v>
+      </c>
+      <c r="F147">
+        <v>3</v>
+      </c>
+      <c r="G147" t="s">
+        <v>79</v>
+      </c>
+      <c r="H147" t="s">
+        <v>80</v>
+      </c>
+      <c r="I147">
+        <v>1</v>
+      </c>
+      <c r="J147">
+        <v>1</v>
+      </c>
+      <c r="K147">
+        <v>2</v>
+      </c>
+      <c r="L147">
+        <v>1</v>
+      </c>
+      <c r="M147">
+        <v>1</v>
+      </c>
+      <c r="N147">
+        <v>2</v>
+      </c>
+      <c r="O147" t="s">
+        <v>190</v>
+      </c>
+      <c r="P147" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q147">
+        <v>3.44</v>
+      </c>
+      <c r="R147">
+        <v>2.02</v>
+      </c>
+      <c r="S147">
+        <v>3.02</v>
+      </c>
+      <c r="T147">
+        <v>1.42</v>
+      </c>
+      <c r="U147">
+        <v>2.73</v>
+      </c>
+      <c r="V147">
+        <v>3.04</v>
+      </c>
+      <c r="W147">
+        <v>1.35</v>
+      </c>
+      <c r="X147">
+        <v>7.3</v>
+      </c>
+      <c r="Y147">
+        <v>1.06</v>
+      </c>
+      <c r="Z147">
+        <v>2.71</v>
+      </c>
+      <c r="AA147">
+        <v>3.56</v>
+      </c>
+      <c r="AB147">
+        <v>2.39</v>
+      </c>
+      <c r="AC147">
+        <v>1</v>
+      </c>
+      <c r="AD147">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AE147">
+        <v>1.28</v>
+      </c>
+      <c r="AF147">
+        <v>3.05</v>
+      </c>
+      <c r="AG147">
+        <v>2.08</v>
+      </c>
+      <c r="AH147">
+        <v>1.73</v>
+      </c>
+      <c r="AI147">
+        <v>1.77</v>
+      </c>
+      <c r="AJ147">
+        <v>1.89</v>
+      </c>
+      <c r="AK147">
+        <v>1.5</v>
+      </c>
+      <c r="AL147">
+        <v>1.28</v>
+      </c>
+      <c r="AM147">
+        <v>1.38</v>
+      </c>
+      <c r="AN147">
+        <v>1.18</v>
+      </c>
+      <c r="AO147">
+        <v>1.75</v>
+      </c>
+      <c r="AP147">
+        <v>1.17</v>
+      </c>
+      <c r="AQ147">
+        <v>1.69</v>
+      </c>
+      <c r="AR147">
+        <v>1.47</v>
+      </c>
+      <c r="AS147">
+        <v>1.33</v>
+      </c>
+      <c r="AT147">
+        <v>2.8</v>
+      </c>
+      <c r="AU147">
+        <v>2</v>
+      </c>
+      <c r="AV147">
+        <v>4</v>
+      </c>
+      <c r="AW147">
+        <v>3</v>
+      </c>
+      <c r="AX147">
+        <v>1</v>
+      </c>
+      <c r="AY147">
+        <v>5</v>
+      </c>
+      <c r="AZ147">
+        <v>5</v>
+      </c>
+      <c r="BA147">
+        <v>0</v>
+      </c>
+      <c r="BB147">
+        <v>3</v>
+      </c>
+      <c r="BC147">
+        <v>3</v>
+      </c>
+      <c r="BD147">
+        <v>0</v>
+      </c>
+      <c r="BE147">
+        <v>0</v>
+      </c>
+      <c r="BF147">
+        <v>0</v>
+      </c>
+      <c r="BG147">
+        <v>0</v>
+      </c>
+      <c r="BH147">
+        <v>0</v>
+      </c>
+      <c r="BI147">
+        <v>0</v>
+      </c>
+      <c r="BJ147">
+        <v>0</v>
+      </c>
+      <c r="BK147">
+        <v>0</v>
+      </c>
+      <c r="BL147">
+        <v>0</v>
+      </c>
+      <c r="BM147">
+        <v>0</v>
+      </c>
+      <c r="BN147">
+        <v>0</v>
+      </c>
+      <c r="BO147">
+        <v>0</v>
+      </c>
+      <c r="BP147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:68">
+      <c r="A148" s="1">
+        <v>147</v>
+      </c>
+      <c r="B148">
+        <v>7817184</v>
+      </c>
+      <c r="C148" t="s">
+        <v>68</v>
+      </c>
+      <c r="D148" t="s">
+        <v>69</v>
+      </c>
+      <c r="E148" s="2">
+        <v>45696.47916666666</v>
+      </c>
+      <c r="F148">
+        <v>3</v>
+      </c>
+      <c r="G148" t="s">
+        <v>75</v>
+      </c>
+      <c r="H148" t="s">
+        <v>77</v>
+      </c>
+      <c r="I148">
+        <v>1</v>
+      </c>
+      <c r="J148">
+        <v>0</v>
+      </c>
+      <c r="K148">
+        <v>1</v>
+      </c>
+      <c r="L148">
+        <v>2</v>
+      </c>
+      <c r="M148">
+        <v>1</v>
+      </c>
+      <c r="N148">
+        <v>3</v>
+      </c>
+      <c r="O148" t="s">
+        <v>191</v>
+      </c>
+      <c r="P148" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q148">
+        <v>3.24</v>
+      </c>
+      <c r="R148">
+        <v>2.05</v>
+      </c>
+      <c r="S148">
+        <v>3.12</v>
+      </c>
+      <c r="T148">
+        <v>1.41</v>
+      </c>
+      <c r="U148">
+        <v>2.77</v>
+      </c>
+      <c r="V148">
+        <v>2.9</v>
+      </c>
+      <c r="W148">
+        <v>1.38</v>
+      </c>
+      <c r="X148">
+        <v>7</v>
+      </c>
+      <c r="Y148">
+        <v>1.06</v>
+      </c>
+      <c r="Z148">
+        <v>2.55</v>
+      </c>
+      <c r="AA148">
+        <v>3.41</v>
+      </c>
+      <c r="AB148">
+        <v>2.6</v>
+      </c>
+      <c r="AC148">
+        <v>1.01</v>
+      </c>
+      <c r="AD148">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AE148">
+        <v>1.28</v>
+      </c>
+      <c r="AF148">
+        <v>3.08</v>
+      </c>
+      <c r="AG148">
+        <v>1.98</v>
+      </c>
+      <c r="AH148">
+        <v>1.77</v>
+      </c>
+      <c r="AI148">
+        <v>1.74</v>
+      </c>
+      <c r="AJ148">
+        <v>1.93</v>
+      </c>
+      <c r="AK148">
+        <v>1.44</v>
+      </c>
+      <c r="AL148">
+        <v>1.28</v>
+      </c>
+      <c r="AM148">
+        <v>1.44</v>
+      </c>
+      <c r="AN148">
+        <v>1.58</v>
+      </c>
+      <c r="AO148">
+        <v>1.25</v>
+      </c>
+      <c r="AP148">
+        <v>1.69</v>
+      </c>
+      <c r="AQ148">
+        <v>1.15</v>
+      </c>
+      <c r="AR148">
+        <v>1.47</v>
+      </c>
+      <c r="AS148">
+        <v>1.37</v>
+      </c>
+      <c r="AT148">
+        <v>2.84</v>
+      </c>
+      <c r="AU148">
+        <v>4</v>
+      </c>
+      <c r="AV148">
+        <v>2</v>
+      </c>
+      <c r="AW148">
+        <v>7</v>
+      </c>
+      <c r="AX148">
+        <v>2</v>
+      </c>
+      <c r="AY148">
+        <v>11</v>
+      </c>
+      <c r="AZ148">
+        <v>4</v>
+      </c>
+      <c r="BA148">
+        <v>4</v>
+      </c>
+      <c r="BB148">
+        <v>3</v>
+      </c>
+      <c r="BC148">
+        <v>7</v>
+      </c>
+      <c r="BD148">
+        <v>1.89</v>
+      </c>
+      <c r="BE148">
+        <v>6.15</v>
+      </c>
+      <c r="BF148">
+        <v>2.35</v>
+      </c>
+      <c r="BG148">
+        <v>1.36</v>
+      </c>
+      <c r="BH148">
+        <v>2.7</v>
+      </c>
+      <c r="BI148">
+        <v>1.68</v>
+      </c>
+      <c r="BJ148">
+        <v>2.01</v>
+      </c>
+      <c r="BK148">
+        <v>2.13</v>
+      </c>
+      <c r="BL148">
+        <v>1.57</v>
+      </c>
+      <c r="BM148">
+        <v>2.88</v>
+      </c>
+      <c r="BN148">
+        <v>1.32</v>
+      </c>
+      <c r="BO148">
+        <v>3.6</v>
+      </c>
+      <c r="BP148">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="149" spans="1:68">
+      <c r="A149" s="1">
+        <v>148</v>
+      </c>
+      <c r="B149">
+        <v>7817185</v>
+      </c>
+      <c r="C149" t="s">
+        <v>68</v>
+      </c>
+      <c r="D149" t="s">
+        <v>69</v>
+      </c>
+      <c r="E149" s="2">
+        <v>45696.47916666666</v>
+      </c>
+      <c r="F149">
+        <v>3</v>
+      </c>
+      <c r="G149" t="s">
+        <v>73</v>
+      </c>
+      <c r="H149" t="s">
+        <v>74</v>
+      </c>
+      <c r="I149">
+        <v>0</v>
+      </c>
+      <c r="J149">
+        <v>0</v>
+      </c>
+      <c r="K149">
+        <v>0</v>
+      </c>
+      <c r="L149">
+        <v>0</v>
+      </c>
+      <c r="M149">
+        <v>1</v>
+      </c>
+      <c r="N149">
+        <v>1</v>
+      </c>
+      <c r="O149" t="s">
+        <v>85</v>
+      </c>
+      <c r="P149" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q149">
+        <v>2.07</v>
+      </c>
+      <c r="R149">
+        <v>2.36</v>
+      </c>
+      <c r="S149">
+        <v>4.75</v>
+      </c>
+      <c r="T149">
+        <v>1.25</v>
+      </c>
+      <c r="U149">
+        <v>3.6</v>
+      </c>
+      <c r="V149">
+        <v>2.33</v>
+      </c>
+      <c r="W149">
+        <v>1.56</v>
+      </c>
+      <c r="X149">
+        <v>4.9</v>
+      </c>
+      <c r="Y149">
+        <v>1.14</v>
+      </c>
+      <c r="Z149">
+        <v>1.7</v>
+      </c>
+      <c r="AA149">
+        <v>4</v>
+      </c>
+      <c r="AB149">
+        <v>4.33</v>
+      </c>
+      <c r="AC149">
+        <v>1.01</v>
+      </c>
+      <c r="AD149">
+        <v>13</v>
+      </c>
+      <c r="AE149">
+        <v>1.12</v>
+      </c>
+      <c r="AF149">
+        <v>4.65</v>
+      </c>
+      <c r="AG149">
+        <v>1.57</v>
+      </c>
+      <c r="AH149">
+        <v>2.35</v>
+      </c>
+      <c r="AI149">
+        <v>1.58</v>
+      </c>
+      <c r="AJ149">
+        <v>2.17</v>
+      </c>
+      <c r="AK149">
+        <v>1.14</v>
+      </c>
+      <c r="AL149">
+        <v>1.18</v>
+      </c>
+      <c r="AM149">
+        <v>2.2</v>
+      </c>
+      <c r="AN149">
+        <v>1.42</v>
+      </c>
+      <c r="AO149">
+        <v>0.83</v>
+      </c>
+      <c r="AP149">
+        <v>1.31</v>
+      </c>
+      <c r="AQ149">
+        <v>1</v>
+      </c>
+      <c r="AR149">
+        <v>1.53</v>
+      </c>
+      <c r="AS149">
+        <v>1.41</v>
+      </c>
+      <c r="AT149">
+        <v>2.94</v>
+      </c>
+      <c r="AU149">
+        <v>8</v>
+      </c>
+      <c r="AV149">
+        <v>6</v>
+      </c>
+      <c r="AW149">
+        <v>18</v>
+      </c>
+      <c r="AX149">
+        <v>8</v>
+      </c>
+      <c r="AY149">
+        <v>26</v>
+      </c>
+      <c r="AZ149">
+        <v>14</v>
+      </c>
+      <c r="BA149">
+        <v>12</v>
+      </c>
+      <c r="BB149">
+        <v>1</v>
+      </c>
+      <c r="BC149">
+        <v>13</v>
+      </c>
+      <c r="BD149">
+        <v>1.26</v>
+      </c>
+      <c r="BE149">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF149">
+        <v>4.5</v>
+      </c>
+      <c r="BG149">
+        <v>1.29</v>
+      </c>
+      <c r="BH149">
+        <v>3.42</v>
+      </c>
+      <c r="BI149">
+        <v>1.44</v>
+      </c>
+      <c r="BJ149">
+        <v>2.51</v>
+      </c>
+      <c r="BK149">
+        <v>1.86</v>
+      </c>
+      <c r="BL149">
+        <v>1.91</v>
+      </c>
+      <c r="BM149">
+        <v>2.23</v>
+      </c>
+      <c r="BN149">
+        <v>1.56</v>
+      </c>
+      <c r="BO149">
+        <v>3.15</v>
+      </c>
+      <c r="BP149">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="150" spans="1:68">
+      <c r="A150" s="1">
+        <v>149</v>
+      </c>
+      <c r="B150">
+        <v>7817186</v>
+      </c>
+      <c r="C150" t="s">
+        <v>68</v>
+      </c>
+      <c r="D150" t="s">
+        <v>69</v>
+      </c>
+      <c r="E150" s="2">
+        <v>45696.47916666666</v>
+      </c>
+      <c r="F150">
+        <v>3</v>
+      </c>
+      <c r="G150" t="s">
+        <v>70</v>
+      </c>
+      <c r="H150" t="s">
+        <v>71</v>
+      </c>
+      <c r="I150">
+        <v>0</v>
+      </c>
+      <c r="J150">
+        <v>1</v>
+      </c>
+      <c r="K150">
+        <v>1</v>
+      </c>
+      <c r="L150">
+        <v>1</v>
+      </c>
+      <c r="M150">
+        <v>1</v>
+      </c>
+      <c r="N150">
+        <v>2</v>
+      </c>
+      <c r="O150" t="s">
+        <v>192</v>
+      </c>
+      <c r="P150" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q150">
+        <v>3.64</v>
+      </c>
+      <c r="R150">
+        <v>2.27</v>
+      </c>
+      <c r="S150">
+        <v>2.49</v>
+      </c>
+      <c r="T150">
+        <v>1.29</v>
+      </c>
+      <c r="U150">
+        <v>3.4</v>
+      </c>
+      <c r="V150">
+        <v>2.4</v>
+      </c>
+      <c r="W150">
+        <v>1.53</v>
+      </c>
+      <c r="X150">
+        <v>5.2</v>
+      </c>
+      <c r="Y150">
+        <v>1.12</v>
+      </c>
+      <c r="Z150">
+        <v>3.34</v>
+      </c>
+      <c r="AA150">
+        <v>3.66</v>
+      </c>
+      <c r="AB150">
+        <v>2.01</v>
+      </c>
+      <c r="AC150">
+        <v>1.01</v>
+      </c>
+      <c r="AD150">
+        <v>13</v>
+      </c>
+      <c r="AE150">
+        <v>1.15</v>
+      </c>
+      <c r="AF150">
+        <v>4.3</v>
+      </c>
+      <c r="AG150">
+        <v>1.62</v>
+      </c>
+      <c r="AH150">
+        <v>2.25</v>
+      </c>
+      <c r="AI150">
+        <v>1.52</v>
+      </c>
+      <c r="AJ150">
+        <v>2.3</v>
+      </c>
+      <c r="AK150">
+        <v>1.71</v>
+      </c>
+      <c r="AL150">
+        <v>1.23</v>
+      </c>
+      <c r="AM150">
+        <v>1.29</v>
+      </c>
+      <c r="AN150">
+        <v>0.92</v>
+      </c>
+      <c r="AO150">
+        <v>1.25</v>
+      </c>
+      <c r="AP150">
+        <v>0.92</v>
+      </c>
+      <c r="AQ150">
+        <v>1.23</v>
+      </c>
+      <c r="AR150">
+        <v>1.56</v>
+      </c>
+      <c r="AS150">
+        <v>1.46</v>
+      </c>
+      <c r="AT150">
+        <v>3.02</v>
+      </c>
+      <c r="AU150">
+        <v>3</v>
+      </c>
+      <c r="AV150">
+        <v>4</v>
+      </c>
+      <c r="AW150">
+        <v>4</v>
+      </c>
+      <c r="AX150">
+        <v>7</v>
+      </c>
+      <c r="AY150">
+        <v>7</v>
+      </c>
+      <c r="AZ150">
+        <v>11</v>
+      </c>
+      <c r="BA150">
+        <v>4</v>
+      </c>
+      <c r="BB150">
+        <v>4</v>
+      </c>
+      <c r="BC150">
+        <v>8</v>
+      </c>
+      <c r="BD150">
+        <v>2.02</v>
+      </c>
+      <c r="BE150">
+        <v>6.5</v>
+      </c>
+      <c r="BF150">
+        <v>2.13</v>
+      </c>
+      <c r="BG150">
+        <v>1.18</v>
+      </c>
+      <c r="BH150">
+        <v>3.84</v>
+      </c>
+      <c r="BI150">
+        <v>1.27</v>
+      </c>
+      <c r="BJ150">
+        <v>3.14</v>
+      </c>
+      <c r="BK150">
+        <v>1.5</v>
+      </c>
+      <c r="BL150">
+        <v>2.28</v>
+      </c>
+      <c r="BM150">
+        <v>1.86</v>
+      </c>
+      <c r="BN150">
+        <v>1.8</v>
+      </c>
+      <c r="BO150">
+        <v>2.35</v>
+      </c>
+      <c r="BP150">
+        <v>1.47</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Wales Welsh Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Wales Welsh Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="268">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1179,7 +1179,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP150"/>
+  <dimension ref="A1:BP151"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2546,7 +2546,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ7">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AR7">
         <v>1.59</v>
@@ -3573,7 +3573,7 @@
         <v>3</v>
       </c>
       <c r="AP12">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ12">
         <v>1.69</v>
@@ -5633,7 +5633,7 @@
         <v>1</v>
       </c>
       <c r="AP22">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ22">
         <v>1.15</v>
@@ -6045,7 +6045,7 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ24">
         <v>1.33</v>
@@ -7490,7 +7490,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ31">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AR31">
         <v>1.46</v>
@@ -9135,7 +9135,7 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ39">
         <v>1</v>
@@ -9550,7 +9550,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ41">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AR41">
         <v>2.47</v>
@@ -12228,7 +12228,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ54">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AR54">
         <v>1.83</v>
@@ -13049,7 +13049,7 @@
         <v>1.75</v>
       </c>
       <c r="AP58">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ58">
         <v>1</v>
@@ -15315,7 +15315,7 @@
         <v>1.2</v>
       </c>
       <c r="AP69">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ69">
         <v>0.75</v>
@@ -16139,7 +16139,7 @@
         <v>0</v>
       </c>
       <c r="AP73">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ73">
         <v>0.46</v>
@@ -17790,7 +17790,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ81">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AR81">
         <v>0.87</v>
@@ -18202,7 +18202,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ83">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AR83">
         <v>1.47</v>
@@ -18408,7 +18408,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ84">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AR84">
         <v>1.66</v>
@@ -18611,7 +18611,7 @@
         <v>2.43</v>
       </c>
       <c r="AP85">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ85">
         <v>2</v>
@@ -20880,7 +20880,7 @@
         <v>1</v>
       </c>
       <c r="AQ96">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AR96">
         <v>1.34</v>
@@ -22734,7 +22734,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ105">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AR105">
         <v>1.31</v>
@@ -23349,7 +23349,7 @@
         <v>1.38</v>
       </c>
       <c r="AP108">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ108">
         <v>1.23</v>
@@ -25409,10 +25409,10 @@
         <v>2</v>
       </c>
       <c r="AP118">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ118">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AR118">
         <v>1.4</v>
@@ -27675,7 +27675,7 @@
         <v>0.7</v>
       </c>
       <c r="AP129">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ129">
         <v>0.58</v>
@@ -27884,7 +27884,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ130">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AR130">
         <v>1.5</v>
@@ -31383,7 +31383,7 @@
         <v>1.75</v>
       </c>
       <c r="AP147">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ147">
         <v>1.69</v>
@@ -32080,6 +32080,212 @@
       </c>
       <c r="BP150">
         <v>1.47</v>
+      </c>
+    </row>
+    <row r="151" spans="1:68">
+      <c r="A151" s="1">
+        <v>150</v>
+      </c>
+      <c r="B151">
+        <v>7817169</v>
+      </c>
+      <c r="C151" t="s">
+        <v>68</v>
+      </c>
+      <c r="D151" t="s">
+        <v>69</v>
+      </c>
+      <c r="E151" s="2">
+        <v>45699.69791666666</v>
+      </c>
+      <c r="F151">
+        <v>1</v>
+      </c>
+      <c r="G151" t="s">
+        <v>79</v>
+      </c>
+      <c r="H151" t="s">
+        <v>81</v>
+      </c>
+      <c r="I151">
+        <v>0</v>
+      </c>
+      <c r="J151">
+        <v>1</v>
+      </c>
+      <c r="K151">
+        <v>1</v>
+      </c>
+      <c r="L151">
+        <v>0</v>
+      </c>
+      <c r="M151">
+        <v>1</v>
+      </c>
+      <c r="N151">
+        <v>1</v>
+      </c>
+      <c r="O151" t="s">
+        <v>85</v>
+      </c>
+      <c r="P151" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q151">
+        <v>8</v>
+      </c>
+      <c r="R151">
+        <v>2.88</v>
+      </c>
+      <c r="S151">
+        <v>1.57</v>
+      </c>
+      <c r="T151">
+        <v>1.2</v>
+      </c>
+      <c r="U151">
+        <v>4.33</v>
+      </c>
+      <c r="V151">
+        <v>1.91</v>
+      </c>
+      <c r="W151">
+        <v>1.8</v>
+      </c>
+      <c r="X151">
+        <v>4</v>
+      </c>
+      <c r="Y151">
+        <v>1.22</v>
+      </c>
+      <c r="Z151">
+        <v>8.5</v>
+      </c>
+      <c r="AA151">
+        <v>7</v>
+      </c>
+      <c r="AB151">
+        <v>1.2</v>
+      </c>
+      <c r="AC151">
+        <v>1.01</v>
+      </c>
+      <c r="AD151">
+        <v>18.5</v>
+      </c>
+      <c r="AE151">
+        <v>1.07</v>
+      </c>
+      <c r="AF151">
+        <v>8</v>
+      </c>
+      <c r="AG151">
+        <v>1.33</v>
+      </c>
+      <c r="AH151">
+        <v>3.25</v>
+      </c>
+      <c r="AI151">
+        <v>1.83</v>
+      </c>
+      <c r="AJ151">
+        <v>1.83</v>
+      </c>
+      <c r="AK151">
+        <v>3.25</v>
+      </c>
+      <c r="AL151">
+        <v>1.08</v>
+      </c>
+      <c r="AM151">
+        <v>1.05</v>
+      </c>
+      <c r="AN151">
+        <v>1.17</v>
+      </c>
+      <c r="AO151">
+        <v>2.18</v>
+      </c>
+      <c r="AP151">
+        <v>1.08</v>
+      </c>
+      <c r="AQ151">
+        <v>2.25</v>
+      </c>
+      <c r="AR151">
+        <v>1.4</v>
+      </c>
+      <c r="AS151">
+        <v>2.25</v>
+      </c>
+      <c r="AT151">
+        <v>3.65</v>
+      </c>
+      <c r="AU151">
+        <v>2</v>
+      </c>
+      <c r="AV151">
+        <v>7</v>
+      </c>
+      <c r="AW151">
+        <v>4</v>
+      </c>
+      <c r="AX151">
+        <v>12</v>
+      </c>
+      <c r="AY151">
+        <v>6</v>
+      </c>
+      <c r="AZ151">
+        <v>19</v>
+      </c>
+      <c r="BA151">
+        <v>4</v>
+      </c>
+      <c r="BB151">
+        <v>7</v>
+      </c>
+      <c r="BC151">
+        <v>11</v>
+      </c>
+      <c r="BD151">
+        <v>7.8</v>
+      </c>
+      <c r="BE151">
+        <v>13</v>
+      </c>
+      <c r="BF151">
+        <v>1.12</v>
+      </c>
+      <c r="BG151">
+        <v>1.2</v>
+      </c>
+      <c r="BH151">
+        <v>4</v>
+      </c>
+      <c r="BI151">
+        <v>1.28</v>
+      </c>
+      <c r="BJ151">
+        <v>3.35</v>
+      </c>
+      <c r="BK151">
+        <v>1.56</v>
+      </c>
+      <c r="BL151">
+        <v>2.22</v>
+      </c>
+      <c r="BM151">
+        <v>1.94</v>
+      </c>
+      <c r="BN151">
+        <v>1.82</v>
+      </c>
+      <c r="BO151">
+        <v>2.37</v>
+      </c>
+      <c r="BP151">
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Wales Welsh Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Wales Welsh Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="269">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -819,6 +819,9 @@
   <si>
     <t>['16']</t>
   </si>
+  <si>
+    <t>['1', '75']</t>
+  </si>
 </sst>
 </file>
 
@@ -1179,7 +1182,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP151"/>
+  <dimension ref="A1:BP153"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1928,7 +1931,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ4">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2546,7 +2549,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ7">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AR7">
         <v>1.59</v>
@@ -3161,7 +3164,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ10">
         <v>1</v>
@@ -3779,7 +3782,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ13">
         <v>0.58</v>
@@ -3988,7 +3991,7 @@
         <v>1</v>
       </c>
       <c r="AQ14">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR14">
         <v>0.82</v>
@@ -4191,7 +4194,7 @@
         <v>3</v>
       </c>
       <c r="AP15">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ15">
         <v>2</v>
@@ -5839,7 +5842,7 @@
         <v>2</v>
       </c>
       <c r="AP23">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ23">
         <v>0.75</v>
@@ -6048,7 +6051,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ24">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR24">
         <v>1.08</v>
@@ -6251,7 +6254,7 @@
         <v>2</v>
       </c>
       <c r="AP25">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ25">
         <v>2</v>
@@ -7487,10 +7490,10 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ31">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AR31">
         <v>1.46</v>
@@ -7899,10 +7902,10 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ33">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR33">
         <v>1.47</v>
@@ -8314,7 +8317,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ35">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR35">
         <v>1.94</v>
@@ -8517,7 +8520,7 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ36">
         <v>0.46</v>
@@ -9550,7 +9553,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ41">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AR41">
         <v>2.47</v>
@@ -9753,7 +9756,7 @@
         <v>1.33</v>
       </c>
       <c r="AP42">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ42">
         <v>0.75</v>
@@ -10989,7 +10992,7 @@
         <v>1</v>
       </c>
       <c r="AP48">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ48">
         <v>1.23</v>
@@ -11610,7 +11613,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ51">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR51">
         <v>0.9399999999999999</v>
@@ -12228,7 +12231,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ54">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AR54">
         <v>1.83</v>
@@ -12431,10 +12434,10 @@
         <v>2.5</v>
       </c>
       <c r="AP55">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ55">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR55">
         <v>1.17</v>
@@ -13667,7 +13670,7 @@
         <v>2</v>
       </c>
       <c r="AP61">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ61">
         <v>1.69</v>
@@ -14491,7 +14494,7 @@
         <v>1.4</v>
       </c>
       <c r="AP65">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ65">
         <v>1</v>
@@ -14906,7 +14909,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ67">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR67">
         <v>2.85</v>
@@ -15727,7 +15730,7 @@
         <v>1.33</v>
       </c>
       <c r="AP71">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ71">
         <v>1</v>
@@ -17581,7 +17584,7 @@
         <v>2.17</v>
       </c>
       <c r="AP80">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ80">
         <v>2</v>
@@ -17790,7 +17793,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ81">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AR81">
         <v>0.87</v>
@@ -18202,7 +18205,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ83">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AR83">
         <v>1.47</v>
@@ -18408,7 +18411,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ84">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AR84">
         <v>1.66</v>
@@ -18820,7 +18823,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ86">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR86">
         <v>1.39</v>
@@ -19023,7 +19026,7 @@
         <v>1.17</v>
       </c>
       <c r="AP87">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ87">
         <v>0.58</v>
@@ -20880,7 +20883,7 @@
         <v>1</v>
       </c>
       <c r="AQ96">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AR96">
         <v>1.34</v>
@@ -21495,7 +21498,7 @@
         <v>1.25</v>
       </c>
       <c r="AP99">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ99">
         <v>1.15</v>
@@ -22731,10 +22734,10 @@
         <v>2.25</v>
       </c>
       <c r="AP105">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ105">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AR105">
         <v>1.31</v>
@@ -23146,7 +23149,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ107">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR107">
         <v>1.55</v>
@@ -23761,7 +23764,7 @@
         <v>1.22</v>
       </c>
       <c r="AP110">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ110">
         <v>1.23</v>
@@ -25412,7 +25415,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ118">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AR118">
         <v>1.4</v>
@@ -26030,7 +26033,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ121">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR121">
         <v>1.88</v>
@@ -26439,7 +26442,7 @@
         <v>0.3</v>
       </c>
       <c r="AP123">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ123">
         <v>0.46</v>
@@ -26851,7 +26854,7 @@
         <v>0.67</v>
       </c>
       <c r="AP125">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ125">
         <v>1</v>
@@ -27263,7 +27266,7 @@
         <v>1.8</v>
       </c>
       <c r="AP127">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ127">
         <v>2</v>
@@ -27884,7 +27887,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ130">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AR130">
         <v>1.5</v>
@@ -29323,7 +29326,7 @@
         <v>1.36</v>
       </c>
       <c r="AP137">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ137">
         <v>1.15</v>
@@ -29735,7 +29738,7 @@
         <v>1.91</v>
       </c>
       <c r="AP139">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ139">
         <v>2</v>
@@ -30768,7 +30771,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ144">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR144">
         <v>2.6</v>
@@ -32210,7 +32213,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ151">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AR151">
         <v>1.4</v>
@@ -32286,6 +32289,418 @@
       </c>
       <c r="BP151">
         <v>1.49</v>
+      </c>
+    </row>
+    <row r="152" spans="1:68">
+      <c r="A152" s="1">
+        <v>151</v>
+      </c>
+      <c r="B152">
+        <v>7817187</v>
+      </c>
+      <c r="C152" t="s">
+        <v>68</v>
+      </c>
+      <c r="D152" t="s">
+        <v>69</v>
+      </c>
+      <c r="E152" s="2">
+        <v>45709.69791666666</v>
+      </c>
+      <c r="F152">
+        <v>4</v>
+      </c>
+      <c r="G152" t="s">
+        <v>77</v>
+      </c>
+      <c r="H152" t="s">
+        <v>81</v>
+      </c>
+      <c r="I152">
+        <v>0</v>
+      </c>
+      <c r="J152">
+        <v>1</v>
+      </c>
+      <c r="K152">
+        <v>1</v>
+      </c>
+      <c r="L152">
+        <v>0</v>
+      </c>
+      <c r="M152">
+        <v>2</v>
+      </c>
+      <c r="N152">
+        <v>2</v>
+      </c>
+      <c r="O152" t="s">
+        <v>85</v>
+      </c>
+      <c r="P152" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q152">
+        <v>6</v>
+      </c>
+      <c r="R152">
+        <v>2.75</v>
+      </c>
+      <c r="S152">
+        <v>1.73</v>
+      </c>
+      <c r="T152">
+        <v>1.2</v>
+      </c>
+      <c r="U152">
+        <v>4.33</v>
+      </c>
+      <c r="V152">
+        <v>1.91</v>
+      </c>
+      <c r="W152">
+        <v>1.8</v>
+      </c>
+      <c r="X152">
+        <v>4</v>
+      </c>
+      <c r="Y152">
+        <v>1.22</v>
+      </c>
+      <c r="Z152">
+        <v>5.75</v>
+      </c>
+      <c r="AA152">
+        <v>5.75</v>
+      </c>
+      <c r="AB152">
+        <v>1.3</v>
+      </c>
+      <c r="AC152">
+        <v>1.01</v>
+      </c>
+      <c r="AD152">
+        <v>18.5</v>
+      </c>
+      <c r="AE152">
+        <v>1.03</v>
+      </c>
+      <c r="AF152">
+        <v>7.4</v>
+      </c>
+      <c r="AG152">
+        <v>1.33</v>
+      </c>
+      <c r="AH152">
+        <v>3.25</v>
+      </c>
+      <c r="AI152">
+        <v>1.62</v>
+      </c>
+      <c r="AJ152">
+        <v>2.2</v>
+      </c>
+      <c r="AK152">
+        <v>3</v>
+      </c>
+      <c r="AL152">
+        <v>1.12</v>
+      </c>
+      <c r="AM152">
+        <v>1.09</v>
+      </c>
+      <c r="AN152">
+        <v>1.42</v>
+      </c>
+      <c r="AO152">
+        <v>2.25</v>
+      </c>
+      <c r="AP152">
+        <v>1.31</v>
+      </c>
+      <c r="AQ152">
+        <v>2.31</v>
+      </c>
+      <c r="AR152">
+        <v>1.39</v>
+      </c>
+      <c r="AS152">
+        <v>2.24</v>
+      </c>
+      <c r="AT152">
+        <v>3.63</v>
+      </c>
+      <c r="AU152">
+        <v>0</v>
+      </c>
+      <c r="AV152">
+        <v>8</v>
+      </c>
+      <c r="AW152">
+        <v>3</v>
+      </c>
+      <c r="AX152">
+        <v>6</v>
+      </c>
+      <c r="AY152">
+        <v>3</v>
+      </c>
+      <c r="AZ152">
+        <v>14</v>
+      </c>
+      <c r="BA152">
+        <v>3</v>
+      </c>
+      <c r="BB152">
+        <v>3</v>
+      </c>
+      <c r="BC152">
+        <v>6</v>
+      </c>
+      <c r="BD152">
+        <v>7.3</v>
+      </c>
+      <c r="BE152">
+        <v>12.25</v>
+      </c>
+      <c r="BF152">
+        <v>1.11</v>
+      </c>
+      <c r="BG152">
+        <v>1.27</v>
+      </c>
+      <c r="BH152">
+        <v>3.14</v>
+      </c>
+      <c r="BI152">
+        <v>1.53</v>
+      </c>
+      <c r="BJ152">
+        <v>2.3</v>
+      </c>
+      <c r="BK152">
+        <v>1.9</v>
+      </c>
+      <c r="BL152">
+        <v>1.86</v>
+      </c>
+      <c r="BM152">
+        <v>2.33</v>
+      </c>
+      <c r="BN152">
+        <v>1.52</v>
+      </c>
+      <c r="BO152">
+        <v>3.28</v>
+      </c>
+      <c r="BP152">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="153" spans="1:68">
+      <c r="A153" s="1">
+        <v>152</v>
+      </c>
+      <c r="B153">
+        <v>7817188</v>
+      </c>
+      <c r="C153" t="s">
+        <v>68</v>
+      </c>
+      <c r="D153" t="s">
+        <v>69</v>
+      </c>
+      <c r="E153" s="2">
+        <v>45709.69791666666</v>
+      </c>
+      <c r="F153">
+        <v>4</v>
+      </c>
+      <c r="G153" t="s">
+        <v>80</v>
+      </c>
+      <c r="H153" t="s">
+        <v>75</v>
+      </c>
+      <c r="I153">
+        <v>0</v>
+      </c>
+      <c r="J153">
+        <v>0</v>
+      </c>
+      <c r="K153">
+        <v>0</v>
+      </c>
+      <c r="L153">
+        <v>1</v>
+      </c>
+      <c r="M153">
+        <v>0</v>
+      </c>
+      <c r="N153">
+        <v>1</v>
+      </c>
+      <c r="O153" t="s">
+        <v>144</v>
+      </c>
+      <c r="P153" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q153">
+        <v>2.3</v>
+      </c>
+      <c r="R153">
+        <v>2.1</v>
+      </c>
+      <c r="S153">
+        <v>5</v>
+      </c>
+      <c r="T153">
+        <v>1.44</v>
+      </c>
+      <c r="U153">
+        <v>2.63</v>
+      </c>
+      <c r="V153">
+        <v>3.25</v>
+      </c>
+      <c r="W153">
+        <v>1.33</v>
+      </c>
+      <c r="X153">
+        <v>7.5</v>
+      </c>
+      <c r="Y153">
+        <v>1.07</v>
+      </c>
+      <c r="Z153">
+        <v>1.72</v>
+      </c>
+      <c r="AA153">
+        <v>3.59</v>
+      </c>
+      <c r="AB153">
+        <v>4.8</v>
+      </c>
+      <c r="AC153">
+        <v>1.02</v>
+      </c>
+      <c r="AD153">
+        <v>8.1</v>
+      </c>
+      <c r="AE153">
+        <v>1.3</v>
+      </c>
+      <c r="AF153">
+        <v>2.97</v>
+      </c>
+      <c r="AG153">
+        <v>1.98</v>
+      </c>
+      <c r="AH153">
+        <v>1.77</v>
+      </c>
+      <c r="AI153">
+        <v>2</v>
+      </c>
+      <c r="AJ153">
+        <v>1.73</v>
+      </c>
+      <c r="AK153">
+        <v>1.14</v>
+      </c>
+      <c r="AL153">
+        <v>1.24</v>
+      </c>
+      <c r="AM153">
+        <v>2.04</v>
+      </c>
+      <c r="AN153">
+        <v>1.92</v>
+      </c>
+      <c r="AO153">
+        <v>1.33</v>
+      </c>
+      <c r="AP153">
+        <v>2</v>
+      </c>
+      <c r="AQ153">
+        <v>1.23</v>
+      </c>
+      <c r="AR153">
+        <v>1.55</v>
+      </c>
+      <c r="AS153">
+        <v>1.3</v>
+      </c>
+      <c r="AT153">
+        <v>2.85</v>
+      </c>
+      <c r="AU153">
+        <v>5</v>
+      </c>
+      <c r="AV153">
+        <v>2</v>
+      </c>
+      <c r="AW153">
+        <v>7</v>
+      </c>
+      <c r="AX153">
+        <v>2</v>
+      </c>
+      <c r="AY153">
+        <v>12</v>
+      </c>
+      <c r="AZ153">
+        <v>4</v>
+      </c>
+      <c r="BA153">
+        <v>2</v>
+      </c>
+      <c r="BB153">
+        <v>1</v>
+      </c>
+      <c r="BC153">
+        <v>3</v>
+      </c>
+      <c r="BD153">
+        <v>0</v>
+      </c>
+      <c r="BE153">
+        <v>0</v>
+      </c>
+      <c r="BF153">
+        <v>0</v>
+      </c>
+      <c r="BG153">
+        <v>0</v>
+      </c>
+      <c r="BH153">
+        <v>0</v>
+      </c>
+      <c r="BI153">
+        <v>0</v>
+      </c>
+      <c r="BJ153">
+        <v>0</v>
+      </c>
+      <c r="BK153">
+        <v>0</v>
+      </c>
+      <c r="BL153">
+        <v>0</v>
+      </c>
+      <c r="BM153">
+        <v>0</v>
+      </c>
+      <c r="BN153">
+        <v>0</v>
+      </c>
+      <c r="BO153">
+        <v>0</v>
+      </c>
+      <c r="BP153">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Wales Welsh Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Wales Welsh Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="273">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -595,6 +595,12 @@
     <t>['70']</t>
   </si>
   <si>
+    <t>['7', '51', '72']</t>
+  </si>
+  <si>
+    <t>['9', '37', '83']</t>
+  </si>
+  <si>
     <t>['45+2']</t>
   </si>
   <si>
@@ -821,6 +827,12 @@
   </si>
   <si>
     <t>['1', '75']</t>
+  </si>
+  <si>
+    <t>['57', '63']</t>
+  </si>
+  <si>
+    <t>['43', '90+1']</t>
   </si>
 </sst>
 </file>
@@ -1182,7 +1194,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP153"/>
+  <dimension ref="A1:BP157"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1438,7 +1450,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q2">
         <v>1.83</v>
@@ -1644,7 +1656,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q3">
         <v>3.75</v>
@@ -1722,7 +1734,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ3">
         <v>1.15</v>
@@ -1850,7 +1862,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -1928,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ4">
         <v>1.23</v>
@@ -2262,7 +2274,7 @@
         <v>85</v>
       </c>
       <c r="P6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q6">
         <v>4</v>
@@ -2343,7 +2355,7 @@
         <v>1</v>
       </c>
       <c r="AQ6">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2468,7 +2480,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q7">
         <v>11</v>
@@ -2546,7 +2558,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ7">
         <v>2.31</v>
@@ -2961,7 +2973,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ9">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3167,7 +3179,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ10">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3292,7 +3304,7 @@
         <v>89</v>
       </c>
       <c r="P11" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q11">
         <v>3.6</v>
@@ -3370,10 +3382,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ11">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3498,7 +3510,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q12">
         <v>2.9</v>
@@ -3576,7 +3588,7 @@
         <v>3</v>
       </c>
       <c r="AP12">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ12">
         <v>1.69</v>
@@ -3910,7 +3922,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q14">
         <v>4.33</v>
@@ -4197,7 +4209,7 @@
         <v>2</v>
       </c>
       <c r="AQ15">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4322,7 +4334,7 @@
         <v>85</v>
       </c>
       <c r="P16" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q16">
         <v>2.63</v>
@@ -4606,7 +4618,7 @@
         <v>1</v>
       </c>
       <c r="AP17">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ17">
         <v>1.23</v>
@@ -4734,7 +4746,7 @@
         <v>94</v>
       </c>
       <c r="P18" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q18">
         <v>3</v>
@@ -4812,10 +4824,10 @@
         <v>1</v>
       </c>
       <c r="AP18">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ18">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR18">
         <v>1.28</v>
@@ -4940,7 +4952,7 @@
         <v>85</v>
       </c>
       <c r="P19" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q19">
         <v>4.75</v>
@@ -5018,10 +5030,10 @@
         <v>1</v>
       </c>
       <c r="AP19">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ19">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR19">
         <v>1.46</v>
@@ -5636,7 +5648,7 @@
         <v>1</v>
       </c>
       <c r="AP22">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ22">
         <v>1.15</v>
@@ -5845,7 +5857,7 @@
         <v>2</v>
       </c>
       <c r="AQ23">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR23">
         <v>1.19</v>
@@ -5970,7 +5982,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6048,7 +6060,7 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ24">
         <v>1.23</v>
@@ -6176,7 +6188,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q25">
         <v>3.2</v>
@@ -6257,7 +6269,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ25">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AR25">
         <v>1.81</v>
@@ -6382,7 +6394,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -6460,7 +6472,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ26">
         <v>0.58</v>
@@ -6588,7 +6600,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q27">
         <v>5.5</v>
@@ -6669,7 +6681,7 @@
         <v>1</v>
       </c>
       <c r="AQ27">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR27">
         <v>0.89</v>
@@ -7287,7 +7299,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ30">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR30">
         <v>1.93</v>
@@ -7412,7 +7424,7 @@
         <v>85</v>
       </c>
       <c r="P31" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q31">
         <v>13</v>
@@ -7618,7 +7630,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q32">
         <v>1.83</v>
@@ -8030,7 +8042,7 @@
         <v>85</v>
       </c>
       <c r="P34" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q34">
         <v>3</v>
@@ -8108,7 +8120,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ34">
         <v>0.58</v>
@@ -8726,7 +8738,7 @@
         <v>2.33</v>
       </c>
       <c r="AP37">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ37">
         <v>1.69</v>
@@ -9060,7 +9072,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q39">
         <v>1.83</v>
@@ -9138,10 +9150,10 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ39">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR39">
         <v>1.1</v>
@@ -9347,7 +9359,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ40">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AR40">
         <v>1.48</v>
@@ -9472,7 +9484,7 @@
         <v>110</v>
       </c>
       <c r="P41" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q41">
         <v>7</v>
@@ -9678,7 +9690,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q42">
         <v>2.6</v>
@@ -9759,7 +9771,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ42">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR42">
         <v>1.52</v>
@@ -9884,7 +9896,7 @@
         <v>85</v>
       </c>
       <c r="P43" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q43">
         <v>3.75</v>
@@ -9962,7 +9974,7 @@
         <v>1.75</v>
       </c>
       <c r="AP43">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ43">
         <v>1.69</v>
@@ -10171,7 +10183,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ44">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR44">
         <v>1.05</v>
@@ -10374,7 +10386,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ45">
         <v>2</v>
@@ -10502,7 +10514,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q46">
         <v>3.4</v>
@@ -10708,7 +10720,7 @@
         <v>115</v>
       </c>
       <c r="P47" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q47">
         <v>2.25</v>
@@ -10789,7 +10801,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ47">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR47">
         <v>1.34</v>
@@ -10914,7 +10926,7 @@
         <v>116</v>
       </c>
       <c r="P48" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q48">
         <v>2.5</v>
@@ -11201,7 +11213,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ49">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR49">
         <v>2.19</v>
@@ -11326,7 +11338,7 @@
         <v>117</v>
       </c>
       <c r="P50" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q50">
         <v>1.67</v>
@@ -11532,7 +11544,7 @@
         <v>118</v>
       </c>
       <c r="P51" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q51">
         <v>6</v>
@@ -11610,7 +11622,7 @@
         <v>2.4</v>
       </c>
       <c r="AP51">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ51">
         <v>1.23</v>
@@ -11738,7 +11750,7 @@
         <v>119</v>
       </c>
       <c r="P52" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -11816,7 +11828,7 @@
         <v>1.33</v>
       </c>
       <c r="AP52">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ52">
         <v>2</v>
@@ -12022,7 +12034,7 @@
         <v>0</v>
       </c>
       <c r="AP53">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ53">
         <v>0.46</v>
@@ -12150,7 +12162,7 @@
         <v>114</v>
       </c>
       <c r="P54" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q54">
         <v>9.5</v>
@@ -12562,7 +12574,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q56">
         <v>7</v>
@@ -12846,10 +12858,10 @@
         <v>2.5</v>
       </c>
       <c r="AP57">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ57">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AR57">
         <v>1.7</v>
@@ -13052,10 +13064,10 @@
         <v>1.75</v>
       </c>
       <c r="AP58">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ58">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR58">
         <v>1.13</v>
@@ -13386,7 +13398,7 @@
         <v>125</v>
       </c>
       <c r="P60" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q60">
         <v>2.3</v>
@@ -13592,7 +13604,7 @@
         <v>85</v>
       </c>
       <c r="P61" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q61">
         <v>2.88</v>
@@ -14004,7 +14016,7 @@
         <v>87</v>
       </c>
       <c r="P63" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q63">
         <v>2.63</v>
@@ -14210,7 +14222,7 @@
         <v>127</v>
       </c>
       <c r="P64" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q64">
         <v>1.42</v>
@@ -14497,7 +14509,7 @@
         <v>2</v>
       </c>
       <c r="AQ65">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR65">
         <v>1.25</v>
@@ -14622,7 +14634,7 @@
         <v>128</v>
       </c>
       <c r="P66" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -14700,7 +14712,7 @@
         <v>1.5</v>
       </c>
       <c r="AP66">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ66">
         <v>1.15</v>
@@ -15112,10 +15124,10 @@
         <v>0.75</v>
       </c>
       <c r="AP68">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ68">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR68">
         <v>1.7</v>
@@ -15240,7 +15252,7 @@
         <v>131</v>
       </c>
       <c r="P69" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15318,10 +15330,10 @@
         <v>1.2</v>
       </c>
       <c r="AP69">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ69">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR69">
         <v>1.2</v>
@@ -15446,7 +15458,7 @@
         <v>85</v>
       </c>
       <c r="P70" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q70">
         <v>9</v>
@@ -15524,10 +15536,10 @@
         <v>2.6</v>
       </c>
       <c r="AP70">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ70">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AR70">
         <v>0.96</v>
@@ -15733,7 +15745,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ71">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR71">
         <v>1.39</v>
@@ -15858,7 +15870,7 @@
         <v>132</v>
       </c>
       <c r="P72" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q72">
         <v>7</v>
@@ -16064,7 +16076,7 @@
         <v>133</v>
       </c>
       <c r="P73" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q73">
         <v>1.73</v>
@@ -16142,7 +16154,7 @@
         <v>0</v>
       </c>
       <c r="AP73">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ73">
         <v>0.46</v>
@@ -16351,7 +16363,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ74">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AR74">
         <v>1.22</v>
@@ -16476,7 +16488,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16888,7 +16900,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q77">
         <v>2.5</v>
@@ -16969,7 +16981,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ77">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR77">
         <v>1.29</v>
@@ -17094,7 +17106,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17172,7 +17184,7 @@
         <v>1.14</v>
       </c>
       <c r="AP78">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ78">
         <v>1.23</v>
@@ -17300,7 +17312,7 @@
         <v>139</v>
       </c>
       <c r="P79" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q79">
         <v>2.75</v>
@@ -17712,7 +17724,7 @@
         <v>140</v>
       </c>
       <c r="P81" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q81">
         <v>19</v>
@@ -17790,7 +17802,7 @@
         <v>2.25</v>
       </c>
       <c r="AP81">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ81">
         <v>2.31</v>
@@ -17918,7 +17930,7 @@
         <v>141</v>
       </c>
       <c r="P82" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q82">
         <v>1.5</v>
@@ -17999,7 +18011,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ82">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR82">
         <v>1.39</v>
@@ -18124,7 +18136,7 @@
         <v>142</v>
       </c>
       <c r="P83" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18330,7 +18342,7 @@
         <v>143</v>
       </c>
       <c r="P84" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q84">
         <v>11</v>
@@ -18408,7 +18420,7 @@
         <v>2.5</v>
       </c>
       <c r="AP84">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ84">
         <v>2.31</v>
@@ -18536,7 +18548,7 @@
         <v>144</v>
       </c>
       <c r="P85" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q85">
         <v>4.75</v>
@@ -18614,10 +18626,10 @@
         <v>2.43</v>
       </c>
       <c r="AP85">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ85">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AR85">
         <v>1.4</v>
@@ -19566,7 +19578,7 @@
         <v>148</v>
       </c>
       <c r="P90" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q90">
         <v>4.75</v>
@@ -19644,10 +19656,10 @@
         <v>1.29</v>
       </c>
       <c r="AP90">
+        <v>0.85</v>
+      </c>
+      <c r="AQ90">
         <v>0.92</v>
-      </c>
-      <c r="AQ90">
-        <v>0.75</v>
       </c>
       <c r="AR90">
         <v>0.87</v>
@@ -19978,7 +19990,7 @@
         <v>150</v>
       </c>
       <c r="P92" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q92">
         <v>2.88</v>
@@ -20056,10 +20068,10 @@
         <v>1.29</v>
       </c>
       <c r="AP92">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ92">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR92">
         <v>1.58</v>
@@ -20390,7 +20402,7 @@
         <v>151</v>
       </c>
       <c r="P94" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q94">
         <v>2.88</v>
@@ -20802,7 +20814,7 @@
         <v>153</v>
       </c>
       <c r="P96" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q96">
         <v>11</v>
@@ -21292,10 +21304,10 @@
         <v>0.5</v>
       </c>
       <c r="AP98">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ98">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR98">
         <v>1.69</v>
@@ -21626,7 +21638,7 @@
         <v>156</v>
       </c>
       <c r="P100" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q100">
         <v>1.73</v>
@@ -21707,7 +21719,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ100">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AR100">
         <v>2.55</v>
@@ -21832,7 +21844,7 @@
         <v>85</v>
       </c>
       <c r="P101" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q101">
         <v>3.4</v>
@@ -21913,7 +21925,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ101">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR101">
         <v>1.77</v>
@@ -22038,7 +22050,7 @@
         <v>157</v>
       </c>
       <c r="P102" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q102">
         <v>3</v>
@@ -22119,7 +22131,7 @@
         <v>1</v>
       </c>
       <c r="AQ102">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR102">
         <v>1.32</v>
@@ -22244,7 +22256,7 @@
         <v>158</v>
       </c>
       <c r="P103" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22940,7 +22952,7 @@
         <v>0.33</v>
       </c>
       <c r="AP106">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ106">
         <v>0.46</v>
@@ -23068,7 +23080,7 @@
         <v>162</v>
       </c>
       <c r="P107" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q107">
         <v>3</v>
@@ -23146,7 +23158,7 @@
         <v>1.67</v>
       </c>
       <c r="AP107">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ107">
         <v>1.23</v>
@@ -23274,7 +23286,7 @@
         <v>163</v>
       </c>
       <c r="P108" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q108">
         <v>2.75</v>
@@ -23352,7 +23364,7 @@
         <v>1.38</v>
       </c>
       <c r="AP108">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ108">
         <v>1.23</v>
@@ -23686,7 +23698,7 @@
         <v>165</v>
       </c>
       <c r="P110" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q110">
         <v>2.4</v>
@@ -23970,7 +23982,7 @@
         <v>2</v>
       </c>
       <c r="AP111">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ111">
         <v>2</v>
@@ -24098,7 +24110,7 @@
         <v>167</v>
       </c>
       <c r="P112" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q112">
         <v>1.4</v>
@@ -24179,7 +24191,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ112">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR112">
         <v>2.55</v>
@@ -24304,7 +24316,7 @@
         <v>168</v>
       </c>
       <c r="P113" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q113">
         <v>4.75</v>
@@ -24382,10 +24394,10 @@
         <v>2.22</v>
       </c>
       <c r="AP113">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ113">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AR113">
         <v>1.49</v>
@@ -24510,7 +24522,7 @@
         <v>98</v>
       </c>
       <c r="P114" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q114">
         <v>2</v>
@@ -24591,7 +24603,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ114">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR114">
         <v>1.45</v>
@@ -24716,7 +24728,7 @@
         <v>85</v>
       </c>
       <c r="P115" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q115">
         <v>3.75</v>
@@ -25000,7 +25012,7 @@
         <v>1.22</v>
       </c>
       <c r="AP116">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ116">
         <v>1.15</v>
@@ -25128,7 +25140,7 @@
         <v>169</v>
       </c>
       <c r="P117" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25334,7 +25346,7 @@
         <v>170</v>
       </c>
       <c r="P118" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q118">
         <v>6</v>
@@ -25412,7 +25424,7 @@
         <v>2</v>
       </c>
       <c r="AP118">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ118">
         <v>2.31</v>
@@ -25827,7 +25839,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ120">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR120">
         <v>2.7</v>
@@ -25952,7 +25964,7 @@
         <v>172</v>
       </c>
       <c r="P121" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q121">
         <v>2.1</v>
@@ -26236,10 +26248,10 @@
         <v>1</v>
       </c>
       <c r="AP122">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ122">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR122">
         <v>1.73</v>
@@ -26570,7 +26582,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q124">
         <v>1.44</v>
@@ -26651,7 +26663,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ124">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR124">
         <v>2.58</v>
@@ -26857,7 +26869,7 @@
         <v>2</v>
       </c>
       <c r="AQ125">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR125">
         <v>1.41</v>
@@ -27063,7 +27075,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ126">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR126">
         <v>1.81</v>
@@ -27188,7 +27200,7 @@
         <v>85</v>
       </c>
       <c r="P127" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q127">
         <v>2.3</v>
@@ -27394,7 +27406,7 @@
         <v>139</v>
       </c>
       <c r="P128" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q128">
         <v>2.75</v>
@@ -27472,10 +27484,10 @@
         <v>0.6</v>
       </c>
       <c r="AP128">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ128">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR128">
         <v>1.06</v>
@@ -27678,7 +27690,7 @@
         <v>0.7</v>
       </c>
       <c r="AP129">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ129">
         <v>0.58</v>
@@ -27806,7 +27818,7 @@
         <v>85</v>
       </c>
       <c r="P130" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q130">
         <v>5.5</v>
@@ -28012,7 +28024,7 @@
         <v>177</v>
       </c>
       <c r="P131" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q131">
         <v>7</v>
@@ -28093,7 +28105,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ131">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AR131">
         <v>1.63</v>
@@ -28296,7 +28308,7 @@
         <v>1.9</v>
       </c>
       <c r="AP132">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ132">
         <v>1.69</v>
@@ -28424,7 +28436,7 @@
         <v>85</v>
       </c>
       <c r="P133" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q133">
         <v>2.75</v>
@@ -28630,7 +28642,7 @@
         <v>179</v>
       </c>
       <c r="P134" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q134">
         <v>4.75</v>
@@ -28711,7 +28723,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ134">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AR134">
         <v>1.5</v>
@@ -28836,7 +28848,7 @@
         <v>180</v>
       </c>
       <c r="P135" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q135">
         <v>2.5</v>
@@ -28917,7 +28929,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ135">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR135">
         <v>1.57</v>
@@ -29042,7 +29054,7 @@
         <v>120</v>
       </c>
       <c r="P136" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q136">
         <v>3.75</v>
@@ -29120,7 +29132,7 @@
         <v>1.09</v>
       </c>
       <c r="AP136">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AQ136">
         <v>1.23</v>
@@ -29248,7 +29260,7 @@
         <v>181</v>
       </c>
       <c r="P137" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q137">
         <v>2.38</v>
@@ -29532,10 +29544,10 @@
         <v>1.09</v>
       </c>
       <c r="AP138">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ138">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AR138">
         <v>1.74</v>
@@ -29660,7 +29672,7 @@
         <v>183</v>
       </c>
       <c r="P139" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q139">
         <v>2.7</v>
@@ -30153,7 +30165,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ141">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="AR141">
         <v>1.54</v>
@@ -30356,7 +30368,7 @@
         <v>0.64</v>
       </c>
       <c r="AP142">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ142">
         <v>0.58</v>
@@ -30484,7 +30496,7 @@
         <v>186</v>
       </c>
       <c r="P143" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q143">
         <v>2.1</v>
@@ -30690,7 +30702,7 @@
         <v>187</v>
       </c>
       <c r="P144" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q144">
         <v>1.53</v>
@@ -30974,7 +30986,7 @@
         <v>0.5</v>
       </c>
       <c r="AP145">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AQ145">
         <v>0.46</v>
@@ -31183,7 +31195,7 @@
         <v>2.54</v>
       </c>
       <c r="AQ146">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AR146">
         <v>2.6</v>
@@ -31386,7 +31398,7 @@
         <v>1.75</v>
       </c>
       <c r="AP147">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ147">
         <v>1.69</v>
@@ -31801,7 +31813,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ149">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR149">
         <v>1.53</v>
@@ -32132,7 +32144,7 @@
         <v>85</v>
       </c>
       <c r="P151" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q151">
         <v>8</v>
@@ -32210,7 +32222,7 @@
         <v>2.18</v>
       </c>
       <c r="AP151">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AQ151">
         <v>2.31</v>
@@ -32338,7 +32350,7 @@
         <v>85</v>
       </c>
       <c r="P152" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q152">
         <v>6</v>
@@ -32701,6 +32713,830 @@
       </c>
       <c r="BP153">
         <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:68">
+      <c r="A154" s="1">
+        <v>153</v>
+      </c>
+      <c r="B154">
+        <v>7817189</v>
+      </c>
+      <c r="C154" t="s">
+        <v>68</v>
+      </c>
+      <c r="D154" t="s">
+        <v>69</v>
+      </c>
+      <c r="E154" s="2">
+        <v>45710.38541666666</v>
+      </c>
+      <c r="F154">
+        <v>4</v>
+      </c>
+      <c r="G154" t="s">
+        <v>78</v>
+      </c>
+      <c r="H154" t="s">
+        <v>70</v>
+      </c>
+      <c r="I154">
+        <v>0</v>
+      </c>
+      <c r="J154">
+        <v>0</v>
+      </c>
+      <c r="K154">
+        <v>0</v>
+      </c>
+      <c r="L154">
+        <v>0</v>
+      </c>
+      <c r="M154">
+        <v>1</v>
+      </c>
+      <c r="N154">
+        <v>1</v>
+      </c>
+      <c r="O154" t="s">
+        <v>85</v>
+      </c>
+      <c r="P154" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q154">
+        <v>3.5</v>
+      </c>
+      <c r="R154">
+        <v>2.3</v>
+      </c>
+      <c r="S154">
+        <v>2.6</v>
+      </c>
+      <c r="T154">
+        <v>1.3</v>
+      </c>
+      <c r="U154">
+        <v>3.4</v>
+      </c>
+      <c r="V154">
+        <v>2.5</v>
+      </c>
+      <c r="W154">
+        <v>1.5</v>
+      </c>
+      <c r="X154">
+        <v>5.5</v>
+      </c>
+      <c r="Y154">
+        <v>1.13</v>
+      </c>
+      <c r="Z154">
+        <v>2.6</v>
+      </c>
+      <c r="AA154">
+        <v>3.77</v>
+      </c>
+      <c r="AB154">
+        <v>2.38</v>
+      </c>
+      <c r="AC154">
+        <v>1.01</v>
+      </c>
+      <c r="AD154">
+        <v>11</v>
+      </c>
+      <c r="AE154">
+        <v>1.16</v>
+      </c>
+      <c r="AF154">
+        <v>4.15</v>
+      </c>
+      <c r="AG154">
+        <v>1.83</v>
+      </c>
+      <c r="AH154">
+        <v>1.91</v>
+      </c>
+      <c r="AI154">
+        <v>1.62</v>
+      </c>
+      <c r="AJ154">
+        <v>2.2</v>
+      </c>
+      <c r="AK154">
+        <v>1.66</v>
+      </c>
+      <c r="AL154">
+        <v>1.24</v>
+      </c>
+      <c r="AM154">
+        <v>1.32</v>
+      </c>
+      <c r="AN154">
+        <v>0.92</v>
+      </c>
+      <c r="AO154">
+        <v>0.75</v>
+      </c>
+      <c r="AP154">
+        <v>0.85</v>
+      </c>
+      <c r="AQ154">
+        <v>0.92</v>
+      </c>
+      <c r="AR154">
+        <v>1.1</v>
+      </c>
+      <c r="AS154">
+        <v>1.24</v>
+      </c>
+      <c r="AT154">
+        <v>2.34</v>
+      </c>
+      <c r="AU154">
+        <v>0</v>
+      </c>
+      <c r="AV154">
+        <v>10</v>
+      </c>
+      <c r="AW154">
+        <v>3</v>
+      </c>
+      <c r="AX154">
+        <v>8</v>
+      </c>
+      <c r="AY154">
+        <v>3</v>
+      </c>
+      <c r="AZ154">
+        <v>18</v>
+      </c>
+      <c r="BA154">
+        <v>1</v>
+      </c>
+      <c r="BB154">
+        <v>8</v>
+      </c>
+      <c r="BC154">
+        <v>9</v>
+      </c>
+      <c r="BD154">
+        <v>2.26</v>
+      </c>
+      <c r="BE154">
+        <v>6.25</v>
+      </c>
+      <c r="BF154">
+        <v>1.94</v>
+      </c>
+      <c r="BG154">
+        <v>1.25</v>
+      </c>
+      <c r="BH154">
+        <v>3.28</v>
+      </c>
+      <c r="BI154">
+        <v>1.48</v>
+      </c>
+      <c r="BJ154">
+        <v>2.33</v>
+      </c>
+      <c r="BK154">
+        <v>1.86</v>
+      </c>
+      <c r="BL154">
+        <v>1.8</v>
+      </c>
+      <c r="BM154">
+        <v>2.38</v>
+      </c>
+      <c r="BN154">
+        <v>1.46</v>
+      </c>
+      <c r="BO154">
+        <v>3.28</v>
+      </c>
+      <c r="BP154">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="155" spans="1:68">
+      <c r="A155" s="1">
+        <v>154</v>
+      </c>
+      <c r="B155">
+        <v>7817190</v>
+      </c>
+      <c r="C155" t="s">
+        <v>68</v>
+      </c>
+      <c r="D155" t="s">
+        <v>69</v>
+      </c>
+      <c r="E155" s="2">
+        <v>45710.47916666666</v>
+      </c>
+      <c r="F155">
+        <v>4</v>
+      </c>
+      <c r="G155" t="s">
+        <v>79</v>
+      </c>
+      <c r="H155" t="s">
+        <v>76</v>
+      </c>
+      <c r="I155">
+        <v>1</v>
+      </c>
+      <c r="J155">
+        <v>0</v>
+      </c>
+      <c r="K155">
+        <v>1</v>
+      </c>
+      <c r="L155">
+        <v>3</v>
+      </c>
+      <c r="M155">
+        <v>2</v>
+      </c>
+      <c r="N155">
+        <v>5</v>
+      </c>
+      <c r="O155" t="s">
+        <v>193</v>
+      </c>
+      <c r="P155" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q155">
+        <v>3.25</v>
+      </c>
+      <c r="R155">
+        <v>2.25</v>
+      </c>
+      <c r="S155">
+        <v>2.88</v>
+      </c>
+      <c r="T155">
+        <v>1.33</v>
+      </c>
+      <c r="U155">
+        <v>3.25</v>
+      </c>
+      <c r="V155">
+        <v>2.5</v>
+      </c>
+      <c r="W155">
+        <v>1.5</v>
+      </c>
+      <c r="X155">
+        <v>6</v>
+      </c>
+      <c r="Y155">
+        <v>1.11</v>
+      </c>
+      <c r="Z155">
+        <v>2.75</v>
+      </c>
+      <c r="AA155">
+        <v>3.7</v>
+      </c>
+      <c r="AB155">
+        <v>2.29</v>
+      </c>
+      <c r="AC155">
+        <v>1.01</v>
+      </c>
+      <c r="AD155">
+        <v>11</v>
+      </c>
+      <c r="AE155">
+        <v>1.16</v>
+      </c>
+      <c r="AF155">
+        <v>4.1</v>
+      </c>
+      <c r="AG155">
+        <v>1.67</v>
+      </c>
+      <c r="AH155">
+        <v>2.1</v>
+      </c>
+      <c r="AI155">
+        <v>1.62</v>
+      </c>
+      <c r="AJ155">
+        <v>2.2</v>
+      </c>
+      <c r="AK155">
+        <v>1.55</v>
+      </c>
+      <c r="AL155">
+        <v>1.24</v>
+      </c>
+      <c r="AM155">
+        <v>1.39</v>
+      </c>
+      <c r="AN155">
+        <v>1.08</v>
+      </c>
+      <c r="AO155">
+        <v>2</v>
+      </c>
+      <c r="AP155">
+        <v>1.21</v>
+      </c>
+      <c r="AQ155">
+        <v>1.86</v>
+      </c>
+      <c r="AR155">
+        <v>1.35</v>
+      </c>
+      <c r="AS155">
+        <v>1.47</v>
+      </c>
+      <c r="AT155">
+        <v>2.82</v>
+      </c>
+      <c r="AU155">
+        <v>5</v>
+      </c>
+      <c r="AV155">
+        <v>7</v>
+      </c>
+      <c r="AW155">
+        <v>5</v>
+      </c>
+      <c r="AX155">
+        <v>6</v>
+      </c>
+      <c r="AY155">
+        <v>10</v>
+      </c>
+      <c r="AZ155">
+        <v>13</v>
+      </c>
+      <c r="BA155">
+        <v>4</v>
+      </c>
+      <c r="BB155">
+        <v>8</v>
+      </c>
+      <c r="BC155">
+        <v>12</v>
+      </c>
+      <c r="BD155">
+        <v>0</v>
+      </c>
+      <c r="BE155">
+        <v>0</v>
+      </c>
+      <c r="BF155">
+        <v>0</v>
+      </c>
+      <c r="BG155">
+        <v>0</v>
+      </c>
+      <c r="BH155">
+        <v>0</v>
+      </c>
+      <c r="BI155">
+        <v>0</v>
+      </c>
+      <c r="BJ155">
+        <v>0</v>
+      </c>
+      <c r="BK155">
+        <v>0</v>
+      </c>
+      <c r="BL155">
+        <v>0</v>
+      </c>
+      <c r="BM155">
+        <v>0</v>
+      </c>
+      <c r="BN155">
+        <v>0</v>
+      </c>
+      <c r="BO155">
+        <v>0</v>
+      </c>
+      <c r="BP155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:68">
+      <c r="A156" s="1">
+        <v>155</v>
+      </c>
+      <c r="B156">
+        <v>7817191</v>
+      </c>
+      <c r="C156" t="s">
+        <v>68</v>
+      </c>
+      <c r="D156" t="s">
+        <v>69</v>
+      </c>
+      <c r="E156" s="2">
+        <v>45710.47916666666</v>
+      </c>
+      <c r="F156">
+        <v>4</v>
+      </c>
+      <c r="G156" t="s">
+        <v>71</v>
+      </c>
+      <c r="H156" t="s">
+        <v>73</v>
+      </c>
+      <c r="I156">
+        <v>0</v>
+      </c>
+      <c r="J156">
+        <v>1</v>
+      </c>
+      <c r="K156">
+        <v>1</v>
+      </c>
+      <c r="L156">
+        <v>0</v>
+      </c>
+      <c r="M156">
+        <v>2</v>
+      </c>
+      <c r="N156">
+        <v>2</v>
+      </c>
+      <c r="O156" t="s">
+        <v>85</v>
+      </c>
+      <c r="P156" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q156">
+        <v>2.88</v>
+      </c>
+      <c r="R156">
+        <v>2.2</v>
+      </c>
+      <c r="S156">
+        <v>3.1</v>
+      </c>
+      <c r="T156">
+        <v>1.33</v>
+      </c>
+      <c r="U156">
+        <v>3.25</v>
+      </c>
+      <c r="V156">
+        <v>2.63</v>
+      </c>
+      <c r="W156">
+        <v>1.44</v>
+      </c>
+      <c r="X156">
+        <v>6</v>
+      </c>
+      <c r="Y156">
+        <v>1.11</v>
+      </c>
+      <c r="Z156">
+        <v>2.38</v>
+      </c>
+      <c r="AA156">
+        <v>3.77</v>
+      </c>
+      <c r="AB156">
+        <v>2.6</v>
+      </c>
+      <c r="AC156">
+        <v>1.01</v>
+      </c>
+      <c r="AD156">
+        <v>11</v>
+      </c>
+      <c r="AE156">
+        <v>1.18</v>
+      </c>
+      <c r="AF156">
+        <v>3.84</v>
+      </c>
+      <c r="AG156">
+        <v>1.67</v>
+      </c>
+      <c r="AH156">
+        <v>2</v>
+      </c>
+      <c r="AI156">
+        <v>1.62</v>
+      </c>
+      <c r="AJ156">
+        <v>2.2</v>
+      </c>
+      <c r="AK156">
+        <v>1.43</v>
+      </c>
+      <c r="AL156">
+        <v>1.25</v>
+      </c>
+      <c r="AM156">
+        <v>1.48</v>
+      </c>
+      <c r="AN156">
+        <v>1.75</v>
+      </c>
+      <c r="AO156">
+        <v>1</v>
+      </c>
+      <c r="AP156">
+        <v>1.62</v>
+      </c>
+      <c r="AQ156">
+        <v>1.15</v>
+      </c>
+      <c r="AR156">
+        <v>1.42</v>
+      </c>
+      <c r="AS156">
+        <v>1.47</v>
+      </c>
+      <c r="AT156">
+        <v>2.89</v>
+      </c>
+      <c r="AU156">
+        <v>5</v>
+      </c>
+      <c r="AV156">
+        <v>3</v>
+      </c>
+      <c r="AW156">
+        <v>3</v>
+      </c>
+      <c r="AX156">
+        <v>4</v>
+      </c>
+      <c r="AY156">
+        <v>8</v>
+      </c>
+      <c r="AZ156">
+        <v>7</v>
+      </c>
+      <c r="BA156">
+        <v>5</v>
+      </c>
+      <c r="BB156">
+        <v>3</v>
+      </c>
+      <c r="BC156">
+        <v>8</v>
+      </c>
+      <c r="BD156">
+        <v>2.4</v>
+      </c>
+      <c r="BE156">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF156">
+        <v>1.73</v>
+      </c>
+      <c r="BG156">
+        <v>1.23</v>
+      </c>
+      <c r="BH156">
+        <v>3.42</v>
+      </c>
+      <c r="BI156">
+        <v>1.44</v>
+      </c>
+      <c r="BJ156">
+        <v>2.43</v>
+      </c>
+      <c r="BK156">
+        <v>1.79</v>
+      </c>
+      <c r="BL156">
+        <v>1.87</v>
+      </c>
+      <c r="BM156">
+        <v>2.26</v>
+      </c>
+      <c r="BN156">
+        <v>1.51</v>
+      </c>
+      <c r="BO156">
+        <v>3.05</v>
+      </c>
+      <c r="BP156">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="157" spans="1:68">
+      <c r="A157" s="1">
+        <v>156</v>
+      </c>
+      <c r="B157">
+        <v>7817192</v>
+      </c>
+      <c r="C157" t="s">
+        <v>68</v>
+      </c>
+      <c r="D157" t="s">
+        <v>69</v>
+      </c>
+      <c r="E157" s="2">
+        <v>45710.47916666666</v>
+      </c>
+      <c r="F157">
+        <v>4</v>
+      </c>
+      <c r="G157" t="s">
+        <v>72</v>
+      </c>
+      <c r="H157" t="s">
+        <v>74</v>
+      </c>
+      <c r="I157">
+        <v>2</v>
+      </c>
+      <c r="J157">
+        <v>0</v>
+      </c>
+      <c r="K157">
+        <v>2</v>
+      </c>
+      <c r="L157">
+        <v>3</v>
+      </c>
+      <c r="M157">
+        <v>1</v>
+      </c>
+      <c r="N157">
+        <v>4</v>
+      </c>
+      <c r="O157" t="s">
+        <v>194</v>
+      </c>
+      <c r="P157" t="s">
+        <v>247</v>
+      </c>
+      <c r="Q157">
+        <v>2.63</v>
+      </c>
+      <c r="R157">
+        <v>2.3</v>
+      </c>
+      <c r="S157">
+        <v>3.4</v>
+      </c>
+      <c r="T157">
+        <v>1.3</v>
+      </c>
+      <c r="U157">
+        <v>3.4</v>
+      </c>
+      <c r="V157">
+        <v>2.38</v>
+      </c>
+      <c r="W157">
+        <v>1.53</v>
+      </c>
+      <c r="X157">
+        <v>5</v>
+      </c>
+      <c r="Y157">
+        <v>1.14</v>
+      </c>
+      <c r="Z157">
+        <v>2.12</v>
+      </c>
+      <c r="AA157">
+        <v>3.93</v>
+      </c>
+      <c r="AB157">
+        <v>2.92</v>
+      </c>
+      <c r="AC157">
+        <v>1</v>
+      </c>
+      <c r="AD157">
+        <v>12</v>
+      </c>
+      <c r="AE157">
+        <v>1.12</v>
+      </c>
+      <c r="AF157">
+        <v>4.8</v>
+      </c>
+      <c r="AG157">
+        <v>1.44</v>
+      </c>
+      <c r="AH157">
+        <v>2.59</v>
+      </c>
+      <c r="AI157">
+        <v>1.53</v>
+      </c>
+      <c r="AJ157">
+        <v>2.38</v>
+      </c>
+      <c r="AK157">
+        <v>1.35</v>
+      </c>
+      <c r="AL157">
+        <v>1.23</v>
+      </c>
+      <c r="AM157">
+        <v>1.62</v>
+      </c>
+      <c r="AN157">
+        <v>1.46</v>
+      </c>
+      <c r="AO157">
+        <v>1</v>
+      </c>
+      <c r="AP157">
+        <v>1.57</v>
+      </c>
+      <c r="AQ157">
+        <v>0.93</v>
+      </c>
+      <c r="AR157">
+        <v>1.81</v>
+      </c>
+      <c r="AS157">
+        <v>1.42</v>
+      </c>
+      <c r="AT157">
+        <v>3.23</v>
+      </c>
+      <c r="AU157">
+        <v>10</v>
+      </c>
+      <c r="AV157">
+        <v>7</v>
+      </c>
+      <c r="AW157">
+        <v>7</v>
+      </c>
+      <c r="AX157">
+        <v>4</v>
+      </c>
+      <c r="AY157">
+        <v>17</v>
+      </c>
+      <c r="AZ157">
+        <v>11</v>
+      </c>
+      <c r="BA157">
+        <v>5</v>
+      </c>
+      <c r="BB157">
+        <v>4</v>
+      </c>
+      <c r="BC157">
+        <v>9</v>
+      </c>
+      <c r="BD157">
+        <v>1.47</v>
+      </c>
+      <c r="BE157">
+        <v>8.9</v>
+      </c>
+      <c r="BF157">
+        <v>3.08</v>
+      </c>
+      <c r="BG157">
+        <v>1.18</v>
+      </c>
+      <c r="BH157">
+        <v>3.92</v>
+      </c>
+      <c r="BI157">
+        <v>1.36</v>
+      </c>
+      <c r="BJ157">
+        <v>2.7</v>
+      </c>
+      <c r="BK157">
+        <v>1.69</v>
+      </c>
+      <c r="BL157">
+        <v>2.07</v>
+      </c>
+      <c r="BM157">
+        <v>2.11</v>
+      </c>
+      <c r="BN157">
+        <v>1.67</v>
+      </c>
+      <c r="BO157">
+        <v>2.7</v>
+      </c>
+      <c r="BP157">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Wales Welsh Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Wales Welsh Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="283">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -601,6 +601,24 @@
     <t>['9', '37', '83']</t>
   </si>
   <si>
+    <t>['29', '77', '90']</t>
+  </si>
+  <si>
+    <t>['14', '63', '90+3']</t>
+  </si>
+  <si>
+    <t>['30', '51']</t>
+  </si>
+  <si>
+    <t>['18', '21', '29', '60', '76']</t>
+  </si>
+  <si>
+    <t>['24', '55', '71', '79']</t>
+  </si>
+  <si>
+    <t>['13', '61', '90+6']</t>
+  </si>
+  <si>
     <t>['45+2']</t>
   </si>
   <si>
@@ -833,6 +851,18 @@
   </si>
   <si>
     <t>['43', '90+1']</t>
+  </si>
+  <si>
+    <t>['6', '21', '53', '90+3']</t>
+  </si>
+  <si>
+    <t>['42', '87']</t>
+  </si>
+  <si>
+    <t>['33', '46']</t>
+  </si>
+  <si>
+    <t>['51', '75']</t>
   </si>
 </sst>
 </file>
@@ -1194,7 +1224,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP157"/>
+  <dimension ref="A1:BP163"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1450,7 +1480,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="Q2">
         <v>1.83</v>
@@ -1528,10 +1558,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ2">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1656,7 +1686,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="Q3">
         <v>3.75</v>
@@ -1737,7 +1767,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ3">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1862,7 +1892,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -2146,10 +2176,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ5">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2274,7 +2304,7 @@
         <v>85</v>
       </c>
       <c r="P6" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="Q6">
         <v>4</v>
@@ -2352,7 +2382,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ6">
         <v>1.86</v>
@@ -2480,7 +2510,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="Q7">
         <v>11</v>
@@ -2764,10 +2794,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ8">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2970,7 +3000,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ9">
         <v>0.92</v>
@@ -3304,7 +3334,7 @@
         <v>89</v>
       </c>
       <c r="P11" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="Q11">
         <v>3.6</v>
@@ -3510,7 +3540,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="Q12">
         <v>2.9</v>
@@ -3591,7 +3621,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ12">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3797,7 +3827,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ13">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR13">
         <v>1.91</v>
@@ -3922,7 +3952,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="Q14">
         <v>4.33</v>
@@ -4000,7 +4030,7 @@
         <v>3</v>
       </c>
       <c r="AP14">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ14">
         <v>1.23</v>
@@ -4334,7 +4364,7 @@
         <v>85</v>
       </c>
       <c r="P16" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="Q16">
         <v>2.63</v>
@@ -4412,10 +4442,10 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ16">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AR16">
         <v>2.12</v>
@@ -4621,7 +4651,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ17">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR17">
         <v>0.68</v>
@@ -4746,7 +4776,7 @@
         <v>94</v>
       </c>
       <c r="P18" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="Q18">
         <v>3</v>
@@ -4952,7 +4982,7 @@
         <v>85</v>
       </c>
       <c r="P19" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="Q19">
         <v>4.75</v>
@@ -5236,10 +5266,10 @@
         <v>3</v>
       </c>
       <c r="AP20">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ20">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR20">
         <v>1.34</v>
@@ -5442,10 +5472,10 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ21">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR21">
         <v>1.58</v>
@@ -5651,7 +5681,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ22">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR22">
         <v>1.22</v>
@@ -5982,7 +6012,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6188,7 +6218,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="Q25">
         <v>3.2</v>
@@ -6394,7 +6424,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -6475,7 +6505,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ26">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR26">
         <v>1.77</v>
@@ -6600,7 +6630,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="Q27">
         <v>5.5</v>
@@ -6678,7 +6708,7 @@
         <v>2</v>
       </c>
       <c r="AP27">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ27">
         <v>1.15</v>
@@ -6884,10 +6914,10 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ28">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR28">
         <v>0</v>
@@ -7090,10 +7120,10 @@
         <v>3</v>
       </c>
       <c r="AP29">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ29">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AR29">
         <v>2.16</v>
@@ -7296,7 +7326,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ30">
         <v>0.93</v>
@@ -7424,7 +7454,7 @@
         <v>85</v>
       </c>
       <c r="P31" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="Q31">
         <v>13</v>
@@ -7630,7 +7660,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="Q32">
         <v>1.83</v>
@@ -7708,10 +7738,10 @@
         <v>0.5</v>
       </c>
       <c r="AP32">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ32">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR32">
         <v>1.41</v>
@@ -8042,7 +8072,7 @@
         <v>85</v>
       </c>
       <c r="P34" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="Q34">
         <v>3</v>
@@ -8123,7 +8153,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ34">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR34">
         <v>0.86</v>
@@ -8326,7 +8356,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ35">
         <v>1.23</v>
@@ -8535,7 +8565,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ36">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR36">
         <v>1.37</v>
@@ -8741,7 +8771,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ37">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR37">
         <v>1.69</v>
@@ -8944,10 +8974,10 @@
         <v>1.33</v>
       </c>
       <c r="AP38">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ38">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR38">
         <v>3.26</v>
@@ -9072,7 +9102,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="Q39">
         <v>1.83</v>
@@ -9356,7 +9386,7 @@
         <v>2.33</v>
       </c>
       <c r="AP40">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ40">
         <v>1.86</v>
@@ -9484,7 +9514,7 @@
         <v>110</v>
       </c>
       <c r="P41" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="Q41">
         <v>7</v>
@@ -9562,7 +9592,7 @@
         <v>3</v>
       </c>
       <c r="AP41">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ41">
         <v>2.31</v>
@@ -9690,7 +9720,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="Q42">
         <v>2.6</v>
@@ -9896,7 +9926,7 @@
         <v>85</v>
       </c>
       <c r="P43" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="Q43">
         <v>3.75</v>
@@ -9977,7 +10007,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ43">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR43">
         <v>0.99</v>
@@ -10180,7 +10210,7 @@
         <v>2.33</v>
       </c>
       <c r="AP44">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ44">
         <v>1.15</v>
@@ -10389,7 +10419,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ45">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AR45">
         <v>1.74</v>
@@ -10514,7 +10544,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="Q46">
         <v>3.4</v>
@@ -10592,10 +10622,10 @@
         <v>1</v>
       </c>
       <c r="AP46">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ46">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR46">
         <v>0.8100000000000001</v>
@@ -10720,7 +10750,7 @@
         <v>115</v>
       </c>
       <c r="P47" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="Q47">
         <v>2.25</v>
@@ -10798,7 +10828,7 @@
         <v>1.25</v>
       </c>
       <c r="AP47">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ47">
         <v>0.92</v>
@@ -10926,7 +10956,7 @@
         <v>116</v>
       </c>
       <c r="P48" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="Q48">
         <v>2.5</v>
@@ -11007,7 +11037,7 @@
         <v>2</v>
       </c>
       <c r="AQ48">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR48">
         <v>1.21</v>
@@ -11210,7 +11240,7 @@
         <v>0</v>
       </c>
       <c r="AP49">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ49">
         <v>0.93</v>
@@ -11338,7 +11368,7 @@
         <v>117</v>
       </c>
       <c r="P50" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="Q50">
         <v>1.67</v>
@@ -11416,10 +11446,10 @@
         <v>1</v>
       </c>
       <c r="AP50">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ50">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR50">
         <v>3.27</v>
@@ -11544,7 +11574,7 @@
         <v>118</v>
       </c>
       <c r="P51" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="Q51">
         <v>6</v>
@@ -11750,7 +11780,7 @@
         <v>119</v>
       </c>
       <c r="P52" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -11831,7 +11861,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ52">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AR52">
         <v>1.62</v>
@@ -12037,7 +12067,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ53">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR53">
         <v>1.67</v>
@@ -12162,7 +12192,7 @@
         <v>114</v>
       </c>
       <c r="P54" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="Q54">
         <v>9.5</v>
@@ -12240,7 +12270,7 @@
         <v>2</v>
       </c>
       <c r="AP54">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ54">
         <v>2.31</v>
@@ -12574,7 +12604,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="Q56">
         <v>7</v>
@@ -12652,10 +12682,10 @@
         <v>1.67</v>
       </c>
       <c r="AP56">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ56">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR56">
         <v>1.02</v>
@@ -13270,10 +13300,10 @@
         <v>1</v>
       </c>
       <c r="AP59">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ59">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR59">
         <v>2.07</v>
@@ -13398,7 +13428,7 @@
         <v>125</v>
       </c>
       <c r="P60" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="Q60">
         <v>2.3</v>
@@ -13476,10 +13506,10 @@
         <v>1</v>
       </c>
       <c r="AP60">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ60">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR60">
         <v>1.7</v>
@@ -13604,7 +13634,7 @@
         <v>85</v>
       </c>
       <c r="P61" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="Q61">
         <v>2.88</v>
@@ -13685,7 +13715,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ61">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR61">
         <v>1.49</v>
@@ -13888,10 +13918,10 @@
         <v>0</v>
       </c>
       <c r="AP62">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ62">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR62">
         <v>1.28</v>
@@ -14016,7 +14046,7 @@
         <v>87</v>
       </c>
       <c r="P63" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="Q63">
         <v>2.63</v>
@@ -14094,10 +14124,10 @@
         <v>1.75</v>
       </c>
       <c r="AP63">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ63">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AR63">
         <v>1.21</v>
@@ -14222,7 +14252,7 @@
         <v>127</v>
       </c>
       <c r="P64" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="Q64">
         <v>1.42</v>
@@ -14300,10 +14330,10 @@
         <v>2</v>
       </c>
       <c r="AP64">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ64">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AR64">
         <v>3.13</v>
@@ -14634,7 +14664,7 @@
         <v>128</v>
       </c>
       <c r="P66" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -14715,7 +14745,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ66">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR66">
         <v>1.56</v>
@@ -14918,7 +14948,7 @@
         <v>2.14</v>
       </c>
       <c r="AP67">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ67">
         <v>1.23</v>
@@ -15252,7 +15282,7 @@
         <v>131</v>
       </c>
       <c r="P69" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15458,7 +15488,7 @@
         <v>85</v>
       </c>
       <c r="P70" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="Q70">
         <v>9</v>
@@ -15870,7 +15900,7 @@
         <v>132</v>
       </c>
       <c r="P72" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="Q72">
         <v>7</v>
@@ -15948,10 +15978,10 @@
         <v>2.17</v>
       </c>
       <c r="AP72">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ72">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR72">
         <v>1.05</v>
@@ -16076,7 +16106,7 @@
         <v>133</v>
       </c>
       <c r="P73" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="Q73">
         <v>1.73</v>
@@ -16157,7 +16187,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ73">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR73">
         <v>1.35</v>
@@ -16360,7 +16390,7 @@
         <v>2.67</v>
       </c>
       <c r="AP74">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ74">
         <v>1.86</v>
@@ -16488,7 +16518,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16566,10 +16596,10 @@
         <v>0.83</v>
       </c>
       <c r="AP75">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ75">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR75">
         <v>1.8</v>
@@ -16772,10 +16802,10 @@
         <v>1.4</v>
       </c>
       <c r="AP76">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ76">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR76">
         <v>2.71</v>
@@ -16900,7 +16930,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="Q77">
         <v>2.5</v>
@@ -16978,7 +17008,7 @@
         <v>1.5</v>
       </c>
       <c r="AP77">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ77">
         <v>0.92</v>
@@ -17106,7 +17136,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17187,7 +17217,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ78">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR78">
         <v>1.54</v>
@@ -17312,7 +17342,7 @@
         <v>139</v>
       </c>
       <c r="P79" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="Q79">
         <v>2.75</v>
@@ -17390,10 +17420,10 @@
         <v>1.4</v>
       </c>
       <c r="AP79">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ79">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR79">
         <v>1.99</v>
@@ -17599,7 +17629,7 @@
         <v>2</v>
       </c>
       <c r="AQ80">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AR80">
         <v>1.28</v>
@@ -17724,7 +17754,7 @@
         <v>140</v>
       </c>
       <c r="P81" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="Q81">
         <v>19</v>
@@ -17930,7 +17960,7 @@
         <v>141</v>
       </c>
       <c r="P82" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="Q82">
         <v>1.5</v>
@@ -18008,7 +18038,7 @@
         <v>0.6</v>
       </c>
       <c r="AP82">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ82">
         <v>0.93</v>
@@ -18136,7 +18166,7 @@
         <v>142</v>
       </c>
       <c r="P83" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18214,7 +18244,7 @@
         <v>2.4</v>
       </c>
       <c r="AP83">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ83">
         <v>2.31</v>
@@ -18342,7 +18372,7 @@
         <v>143</v>
       </c>
       <c r="P84" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="Q84">
         <v>11</v>
@@ -18548,7 +18578,7 @@
         <v>144</v>
       </c>
       <c r="P85" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="Q85">
         <v>4.75</v>
@@ -18832,7 +18862,7 @@
         <v>1.88</v>
       </c>
       <c r="AP86">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ86">
         <v>1.23</v>
@@ -19041,7 +19071,7 @@
         <v>2</v>
       </c>
       <c r="AQ87">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR87">
         <v>1.32</v>
@@ -19244,10 +19274,10 @@
         <v>1.33</v>
       </c>
       <c r="AP88">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ88">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR88">
         <v>1.83</v>
@@ -19450,10 +19480,10 @@
         <v>0.43</v>
       </c>
       <c r="AP89">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ89">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR89">
         <v>1.09</v>
@@ -19578,7 +19608,7 @@
         <v>148</v>
       </c>
       <c r="P90" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="Q90">
         <v>4.75</v>
@@ -19862,10 +19892,10 @@
         <v>1</v>
       </c>
       <c r="AP91">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ91">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR91">
         <v>1.97</v>
@@ -19990,7 +20020,7 @@
         <v>150</v>
       </c>
       <c r="P92" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="Q92">
         <v>2.88</v>
@@ -20274,10 +20304,10 @@
         <v>2</v>
       </c>
       <c r="AP93">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ93">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AR93">
         <v>1.26</v>
@@ -20402,7 +20432,7 @@
         <v>151</v>
       </c>
       <c r="P94" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="Q94">
         <v>2.88</v>
@@ -20480,10 +20510,10 @@
         <v>1.29</v>
       </c>
       <c r="AP94">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ94">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR94">
         <v>1.18</v>
@@ -20686,10 +20716,10 @@
         <v>2.29</v>
       </c>
       <c r="AP95">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ95">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR95">
         <v>2.71</v>
@@ -20814,7 +20844,7 @@
         <v>153</v>
       </c>
       <c r="P96" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="Q96">
         <v>11</v>
@@ -20892,7 +20922,7 @@
         <v>2.57</v>
       </c>
       <c r="AP96">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ96">
         <v>2.31</v>
@@ -21098,10 +21128,10 @@
         <v>0.38</v>
       </c>
       <c r="AP97">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ97">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR97">
         <v>1.22</v>
@@ -21513,7 +21543,7 @@
         <v>2</v>
       </c>
       <c r="AQ99">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR99">
         <v>1.39</v>
@@ -21638,7 +21668,7 @@
         <v>156</v>
       </c>
       <c r="P100" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="Q100">
         <v>1.73</v>
@@ -21716,7 +21746,7 @@
         <v>2.5</v>
       </c>
       <c r="AP100">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ100">
         <v>1.86</v>
@@ -21844,7 +21874,7 @@
         <v>85</v>
       </c>
       <c r="P101" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="Q101">
         <v>3.4</v>
@@ -21922,7 +21952,7 @@
         <v>1.13</v>
       </c>
       <c r="AP101">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ101">
         <v>1.15</v>
@@ -22050,7 +22080,7 @@
         <v>157</v>
       </c>
       <c r="P102" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="Q102">
         <v>3</v>
@@ -22128,7 +22158,7 @@
         <v>1.13</v>
       </c>
       <c r="AP102">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ102">
         <v>0.92</v>
@@ -22256,7 +22286,7 @@
         <v>158</v>
       </c>
       <c r="P103" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22334,10 +22364,10 @@
         <v>2.13</v>
       </c>
       <c r="AP103">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ103">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AR103">
         <v>1.45</v>
@@ -22540,10 +22570,10 @@
         <v>2</v>
       </c>
       <c r="AP104">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ104">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR104">
         <v>1.93</v>
@@ -22955,7 +22985,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ106">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR106">
         <v>1.69</v>
@@ -23080,7 +23110,7 @@
         <v>162</v>
       </c>
       <c r="P107" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="Q107">
         <v>3</v>
@@ -23286,7 +23316,7 @@
         <v>163</v>
       </c>
       <c r="P108" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="Q108">
         <v>2.75</v>
@@ -23367,7 +23397,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ108">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR108">
         <v>1.33</v>
@@ -23570,10 +23600,10 @@
         <v>0.88</v>
       </c>
       <c r="AP109">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ109">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR109">
         <v>1.26</v>
@@ -23698,7 +23728,7 @@
         <v>165</v>
       </c>
       <c r="P110" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="Q110">
         <v>2.4</v>
@@ -23779,7 +23809,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ110">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR110">
         <v>1.27</v>
@@ -23985,7 +24015,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ111">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AR111">
         <v>0.97</v>
@@ -24110,7 +24140,7 @@
         <v>167</v>
       </c>
       <c r="P112" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="Q112">
         <v>1.4</v>
@@ -24188,7 +24218,7 @@
         <v>0.43</v>
       </c>
       <c r="AP112">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ112">
         <v>0.93</v>
@@ -24316,7 +24346,7 @@
         <v>168</v>
       </c>
       <c r="P113" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="Q113">
         <v>4.75</v>
@@ -24522,7 +24552,7 @@
         <v>98</v>
       </c>
       <c r="P114" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="Q114">
         <v>2</v>
@@ -24600,7 +24630,7 @@
         <v>0.38</v>
       </c>
       <c r="AP114">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ114">
         <v>0.93</v>
@@ -24728,7 +24758,7 @@
         <v>85</v>
       </c>
       <c r="P115" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="Q115">
         <v>3.75</v>
@@ -24806,10 +24836,10 @@
         <v>1.78</v>
       </c>
       <c r="AP115">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ115">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR115">
         <v>1.68</v>
@@ -25015,7 +25045,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ116">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR116">
         <v>1.04</v>
@@ -25140,7 +25170,7 @@
         <v>169</v>
       </c>
       <c r="P117" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25218,10 +25248,10 @@
         <v>0.78</v>
       </c>
       <c r="AP117">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ117">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR117">
         <v>1.49</v>
@@ -25346,7 +25376,7 @@
         <v>170</v>
       </c>
       <c r="P118" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="Q118">
         <v>6</v>
@@ -25630,10 +25660,10 @@
         <v>1.1</v>
       </c>
       <c r="AP119">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ119">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR119">
         <v>1.37</v>
@@ -25836,7 +25866,7 @@
         <v>1.33</v>
       </c>
       <c r="AP120">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ120">
         <v>1.15</v>
@@ -25964,7 +25994,7 @@
         <v>172</v>
       </c>
       <c r="P121" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="Q121">
         <v>2.1</v>
@@ -26042,7 +26072,7 @@
         <v>1.5</v>
       </c>
       <c r="AP121">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ121">
         <v>1.23</v>
@@ -26457,7 +26487,7 @@
         <v>2</v>
       </c>
       <c r="AQ123">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR123">
         <v>1.34</v>
@@ -26582,7 +26612,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="Q124">
         <v>1.44</v>
@@ -26660,7 +26690,7 @@
         <v>0.9</v>
       </c>
       <c r="AP124">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ124">
         <v>0.92</v>
@@ -27072,7 +27102,7 @@
         <v>1.2</v>
       </c>
       <c r="AP126">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ126">
         <v>1.15</v>
@@ -27200,7 +27230,7 @@
         <v>85</v>
       </c>
       <c r="P127" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="Q127">
         <v>2.3</v>
@@ -27281,7 +27311,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ127">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AR127">
         <v>1.34</v>
@@ -27406,7 +27436,7 @@
         <v>139</v>
       </c>
       <c r="P128" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="Q128">
         <v>2.75</v>
@@ -27693,7 +27723,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ129">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR129">
         <v>1.37</v>
@@ -27818,7 +27848,7 @@
         <v>85</v>
       </c>
       <c r="P130" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="Q130">
         <v>5.5</v>
@@ -27896,7 +27926,7 @@
         <v>2.1</v>
       </c>
       <c r="AP130">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ130">
         <v>2.31</v>
@@ -28024,7 +28054,7 @@
         <v>177</v>
       </c>
       <c r="P131" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="Q131">
         <v>7</v>
@@ -28102,7 +28132,7 @@
         <v>2.3</v>
       </c>
       <c r="AP131">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ131">
         <v>1.86</v>
@@ -28311,7 +28341,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ132">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR132">
         <v>1.46</v>
@@ -28436,7 +28466,7 @@
         <v>85</v>
       </c>
       <c r="P133" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="Q133">
         <v>2.75</v>
@@ -28514,10 +28544,10 @@
         <v>1.2</v>
       </c>
       <c r="AP133">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ133">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR133">
         <v>1.54</v>
@@ -28642,7 +28672,7 @@
         <v>179</v>
       </c>
       <c r="P134" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="Q134">
         <v>4.75</v>
@@ -28720,7 +28750,7 @@
         <v>2.36</v>
       </c>
       <c r="AP134">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ134">
         <v>1.86</v>
@@ -28848,7 +28878,7 @@
         <v>180</v>
       </c>
       <c r="P135" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="Q135">
         <v>2.5</v>
@@ -28926,7 +28956,7 @@
         <v>0.82</v>
       </c>
       <c r="AP135">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ135">
         <v>0.93</v>
@@ -29054,7 +29084,7 @@
         <v>120</v>
       </c>
       <c r="P136" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="Q136">
         <v>3.75</v>
@@ -29135,7 +29165,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ136">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR136">
         <v>1.08</v>
@@ -29260,7 +29290,7 @@
         <v>181</v>
       </c>
       <c r="P137" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="Q137">
         <v>2.38</v>
@@ -29341,7 +29371,7 @@
         <v>2</v>
       </c>
       <c r="AQ137">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR137">
         <v>1.51</v>
@@ -29672,7 +29702,7 @@
         <v>183</v>
       </c>
       <c r="P139" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="Q139">
         <v>2.7</v>
@@ -29753,7 +29783,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ139">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AR139">
         <v>1.37</v>
@@ -29956,10 +29986,10 @@
         <v>1.82</v>
       </c>
       <c r="AP140">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ140">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR140">
         <v>1.75</v>
@@ -30162,7 +30192,7 @@
         <v>0.82</v>
       </c>
       <c r="AP141">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ141">
         <v>0.92</v>
@@ -30371,7 +30401,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ142">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AR142">
         <v>1.44</v>
@@ -30496,7 +30526,7 @@
         <v>186</v>
       </c>
       <c r="P143" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="Q143">
         <v>2.1</v>
@@ -30574,10 +30604,10 @@
         <v>0.27</v>
       </c>
       <c r="AP143">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AQ143">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR143">
         <v>1.39</v>
@@ -30702,7 +30732,7 @@
         <v>187</v>
       </c>
       <c r="P144" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="Q144">
         <v>1.53</v>
@@ -30780,7 +30810,7 @@
         <v>1.45</v>
       </c>
       <c r="AP144">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ144">
         <v>1.23</v>
@@ -30989,7 +31019,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ145">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AR145">
         <v>1.76</v>
@@ -31192,7 +31222,7 @@
         <v>2.17</v>
       </c>
       <c r="AP146">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AQ146">
         <v>1.86</v>
@@ -31401,7 +31431,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ147">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AR147">
         <v>1.47</v>
@@ -31604,10 +31634,10 @@
         <v>1.25</v>
       </c>
       <c r="AP148">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ148">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AR148">
         <v>1.47</v>
@@ -31810,7 +31840,7 @@
         <v>0.83</v>
       </c>
       <c r="AP149">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ149">
         <v>0.93</v>
@@ -32016,10 +32046,10 @@
         <v>1.25</v>
       </c>
       <c r="AP150">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ150">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AR150">
         <v>1.56</v>
@@ -32144,7 +32174,7 @@
         <v>85</v>
       </c>
       <c r="P151" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="Q151">
         <v>8</v>
@@ -32350,7 +32380,7 @@
         <v>85</v>
       </c>
       <c r="P152" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="Q152">
         <v>6</v>
@@ -32968,7 +32998,7 @@
         <v>193</v>
       </c>
       <c r="P155" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="Q155">
         <v>3.25</v>
@@ -33174,7 +33204,7 @@
         <v>85</v>
       </c>
       <c r="P156" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="Q156">
         <v>2.88</v>
@@ -33380,7 +33410,7 @@
         <v>194</v>
       </c>
       <c r="P157" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="Q157">
         <v>2.63</v>
@@ -33537,6 +33567,1242 @@
       </c>
       <c r="BP157">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="158" spans="1:68">
+      <c r="A158" s="1">
+        <v>157</v>
+      </c>
+      <c r="B158">
+        <v>7817193</v>
+      </c>
+      <c r="C158" t="s">
+        <v>68</v>
+      </c>
+      <c r="D158" t="s">
+        <v>69</v>
+      </c>
+      <c r="E158" s="2">
+        <v>45723.69791666666</v>
+      </c>
+      <c r="F158">
+        <v>5</v>
+      </c>
+      <c r="G158" t="s">
+        <v>74</v>
+      </c>
+      <c r="H158" t="s">
+        <v>71</v>
+      </c>
+      <c r="I158">
+        <v>1</v>
+      </c>
+      <c r="J158">
+        <v>2</v>
+      </c>
+      <c r="K158">
+        <v>3</v>
+      </c>
+      <c r="L158">
+        <v>3</v>
+      </c>
+      <c r="M158">
+        <v>4</v>
+      </c>
+      <c r="N158">
+        <v>7</v>
+      </c>
+      <c r="O158" t="s">
+        <v>195</v>
+      </c>
+      <c r="P158" t="s">
+        <v>279</v>
+      </c>
+      <c r="Q158">
+        <v>3</v>
+      </c>
+      <c r="R158">
+        <v>2.25</v>
+      </c>
+      <c r="S158">
+        <v>3</v>
+      </c>
+      <c r="T158">
+        <v>1.33</v>
+      </c>
+      <c r="U158">
+        <v>3.25</v>
+      </c>
+      <c r="V158">
+        <v>2.5</v>
+      </c>
+      <c r="W158">
+        <v>1.5</v>
+      </c>
+      <c r="X158">
+        <v>6</v>
+      </c>
+      <c r="Y158">
+        <v>1.11</v>
+      </c>
+      <c r="Z158">
+        <v>2.49</v>
+      </c>
+      <c r="AA158">
+        <v>3.76</v>
+      </c>
+      <c r="AB158">
+        <v>2.49</v>
+      </c>
+      <c r="AC158">
+        <v>1.01</v>
+      </c>
+      <c r="AD158">
+        <v>11</v>
+      </c>
+      <c r="AE158">
+        <v>1.16</v>
+      </c>
+      <c r="AF158">
+        <v>4.05</v>
+      </c>
+      <c r="AG158">
+        <v>1.61</v>
+      </c>
+      <c r="AH158">
+        <v>2.05</v>
+      </c>
+      <c r="AI158">
+        <v>1.62</v>
+      </c>
+      <c r="AJ158">
+        <v>2.2</v>
+      </c>
+      <c r="AK158">
+        <v>1.47</v>
+      </c>
+      <c r="AL158">
+        <v>1.25</v>
+      </c>
+      <c r="AM158">
+        <v>1.45</v>
+      </c>
+      <c r="AN158">
+        <v>1</v>
+      </c>
+      <c r="AO158">
+        <v>1.23</v>
+      </c>
+      <c r="AP158">
+        <v>0.92</v>
+      </c>
+      <c r="AQ158">
+        <v>1.36</v>
+      </c>
+      <c r="AR158">
+        <v>1.4</v>
+      </c>
+      <c r="AS158">
+        <v>1.46</v>
+      </c>
+      <c r="AT158">
+        <v>2.86</v>
+      </c>
+      <c r="AU158">
+        <v>10</v>
+      </c>
+      <c r="AV158">
+        <v>11</v>
+      </c>
+      <c r="AW158">
+        <v>8</v>
+      </c>
+      <c r="AX158">
+        <v>12</v>
+      </c>
+      <c r="AY158">
+        <v>18</v>
+      </c>
+      <c r="AZ158">
+        <v>23</v>
+      </c>
+      <c r="BA158">
+        <v>9</v>
+      </c>
+      <c r="BB158">
+        <v>7</v>
+      </c>
+      <c r="BC158">
+        <v>16</v>
+      </c>
+      <c r="BD158">
+        <v>2.43</v>
+      </c>
+      <c r="BE158">
+        <v>7.2</v>
+      </c>
+      <c r="BF158">
+        <v>1.82</v>
+      </c>
+      <c r="BG158">
+        <v>1.23</v>
+      </c>
+      <c r="BH158">
+        <v>3.58</v>
+      </c>
+      <c r="BI158">
+        <v>1.44</v>
+      </c>
+      <c r="BJ158">
+        <v>2.57</v>
+      </c>
+      <c r="BK158">
+        <v>1.77</v>
+      </c>
+      <c r="BL158">
+        <v>1.95</v>
+      </c>
+      <c r="BM158">
+        <v>2.17</v>
+      </c>
+      <c r="BN158">
+        <v>1.61</v>
+      </c>
+      <c r="BO158">
+        <v>2.78</v>
+      </c>
+      <c r="BP158">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="159" spans="1:68">
+      <c r="A159" s="1">
+        <v>158</v>
+      </c>
+      <c r="B159">
+        <v>7817194</v>
+      </c>
+      <c r="C159" t="s">
+        <v>68</v>
+      </c>
+      <c r="D159" t="s">
+        <v>69</v>
+      </c>
+      <c r="E159" s="2">
+        <v>45723.69791666666</v>
+      </c>
+      <c r="F159">
+        <v>5</v>
+      </c>
+      <c r="G159" t="s">
+        <v>73</v>
+      </c>
+      <c r="H159" t="s">
+        <v>78</v>
+      </c>
+      <c r="I159">
+        <v>1</v>
+      </c>
+      <c r="J159">
+        <v>0</v>
+      </c>
+      <c r="K159">
+        <v>1</v>
+      </c>
+      <c r="L159">
+        <v>3</v>
+      </c>
+      <c r="M159">
+        <v>0</v>
+      </c>
+      <c r="N159">
+        <v>3</v>
+      </c>
+      <c r="O159" t="s">
+        <v>196</v>
+      </c>
+      <c r="P159" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q159">
+        <v>1.73</v>
+      </c>
+      <c r="R159">
+        <v>2.6</v>
+      </c>
+      <c r="S159">
+        <v>6.5</v>
+      </c>
+      <c r="T159">
+        <v>1.25</v>
+      </c>
+      <c r="U159">
+        <v>3.75</v>
+      </c>
+      <c r="V159">
+        <v>2.2</v>
+      </c>
+      <c r="W159">
+        <v>1.62</v>
+      </c>
+      <c r="X159">
+        <v>4.5</v>
+      </c>
+      <c r="Y159">
+        <v>1.17</v>
+      </c>
+      <c r="Z159">
+        <v>1.36</v>
+      </c>
+      <c r="AA159">
+        <v>5.9</v>
+      </c>
+      <c r="AB159">
+        <v>6.2</v>
+      </c>
+      <c r="AC159">
+        <v>1.01</v>
+      </c>
+      <c r="AD159">
+        <v>17</v>
+      </c>
+      <c r="AE159">
+        <v>1.09</v>
+      </c>
+      <c r="AF159">
+        <v>5.3</v>
+      </c>
+      <c r="AG159">
+        <v>1.48</v>
+      </c>
+      <c r="AH159">
+        <v>2.47</v>
+      </c>
+      <c r="AI159">
+        <v>1.8</v>
+      </c>
+      <c r="AJ159">
+        <v>1.91</v>
+      </c>
+      <c r="AK159">
+        <v>1.04</v>
+      </c>
+      <c r="AL159">
+        <v>1.11</v>
+      </c>
+      <c r="AM159">
+        <v>3.2</v>
+      </c>
+      <c r="AN159">
+        <v>1.31</v>
+      </c>
+      <c r="AO159">
+        <v>0.46</v>
+      </c>
+      <c r="AP159">
+        <v>1.43</v>
+      </c>
+      <c r="AQ159">
+        <v>0.43</v>
+      </c>
+      <c r="AR159">
+        <v>1.62</v>
+      </c>
+      <c r="AS159">
+        <v>1.04</v>
+      </c>
+      <c r="AT159">
+        <v>2.66</v>
+      </c>
+      <c r="AU159">
+        <v>6</v>
+      </c>
+      <c r="AV159">
+        <v>3</v>
+      </c>
+      <c r="AW159">
+        <v>8</v>
+      </c>
+      <c r="AX159">
+        <v>3</v>
+      </c>
+      <c r="AY159">
+        <v>14</v>
+      </c>
+      <c r="AZ159">
+        <v>6</v>
+      </c>
+      <c r="BA159">
+        <v>4</v>
+      </c>
+      <c r="BB159">
+        <v>0</v>
+      </c>
+      <c r="BC159">
+        <v>4</v>
+      </c>
+      <c r="BD159">
+        <v>1.13</v>
+      </c>
+      <c r="BE159">
+        <v>12.25</v>
+      </c>
+      <c r="BF159">
+        <v>6.75</v>
+      </c>
+      <c r="BG159">
+        <v>1.2</v>
+      </c>
+      <c r="BH159">
+        <v>3.72</v>
+      </c>
+      <c r="BI159">
+        <v>1.41</v>
+      </c>
+      <c r="BJ159">
+        <v>2.58</v>
+      </c>
+      <c r="BK159">
+        <v>1.8</v>
+      </c>
+      <c r="BL159">
+        <v>1.96</v>
+      </c>
+      <c r="BM159">
+        <v>2.19</v>
+      </c>
+      <c r="BN159">
+        <v>1.58</v>
+      </c>
+      <c r="BO159">
+        <v>2.45</v>
+      </c>
+      <c r="BP159">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="160" spans="1:68">
+      <c r="A160" s="1">
+        <v>159</v>
+      </c>
+      <c r="B160">
+        <v>7817195</v>
+      </c>
+      <c r="C160" t="s">
+        <v>68</v>
+      </c>
+      <c r="D160" t="s">
+        <v>69</v>
+      </c>
+      <c r="E160" s="2">
+        <v>45723.69791666666</v>
+      </c>
+      <c r="F160">
+        <v>5</v>
+      </c>
+      <c r="G160" t="s">
+        <v>70</v>
+      </c>
+      <c r="H160" t="s">
+        <v>72</v>
+      </c>
+      <c r="I160">
+        <v>1</v>
+      </c>
+      <c r="J160">
+        <v>1</v>
+      </c>
+      <c r="K160">
+        <v>2</v>
+      </c>
+      <c r="L160">
+        <v>2</v>
+      </c>
+      <c r="M160">
+        <v>2</v>
+      </c>
+      <c r="N160">
+        <v>4</v>
+      </c>
+      <c r="O160" t="s">
+        <v>197</v>
+      </c>
+      <c r="P160" t="s">
+        <v>280</v>
+      </c>
+      <c r="Q160">
+        <v>2.88</v>
+      </c>
+      <c r="R160">
+        <v>2.3</v>
+      </c>
+      <c r="S160">
+        <v>3.1</v>
+      </c>
+      <c r="T160">
+        <v>1.3</v>
+      </c>
+      <c r="U160">
+        <v>3.4</v>
+      </c>
+      <c r="V160">
+        <v>2.38</v>
+      </c>
+      <c r="W160">
+        <v>1.53</v>
+      </c>
+      <c r="X160">
+        <v>5</v>
+      </c>
+      <c r="Y160">
+        <v>1.14</v>
+      </c>
+      <c r="Z160">
+        <v>2.33</v>
+      </c>
+      <c r="AA160">
+        <v>3.92</v>
+      </c>
+      <c r="AB160">
+        <v>2.59</v>
+      </c>
+      <c r="AC160">
+        <v>1.01</v>
+      </c>
+      <c r="AD160">
+        <v>11</v>
+      </c>
+      <c r="AE160">
+        <v>1.12</v>
+      </c>
+      <c r="AF160">
+        <v>4.7</v>
+      </c>
+      <c r="AG160">
+        <v>1.53</v>
+      </c>
+      <c r="AH160">
+        <v>2.25</v>
+      </c>
+      <c r="AI160">
+        <v>1.53</v>
+      </c>
+      <c r="AJ160">
+        <v>2.38</v>
+      </c>
+      <c r="AK160">
+        <v>1.44</v>
+      </c>
+      <c r="AL160">
+        <v>1.23</v>
+      </c>
+      <c r="AM160">
+        <v>1.5</v>
+      </c>
+      <c r="AN160">
+        <v>0.92</v>
+      </c>
+      <c r="AO160">
+        <v>0.58</v>
+      </c>
+      <c r="AP160">
+        <v>0.93</v>
+      </c>
+      <c r="AQ160">
+        <v>0.62</v>
+      </c>
+      <c r="AR160">
+        <v>1.52</v>
+      </c>
+      <c r="AS160">
+        <v>1.44</v>
+      </c>
+      <c r="AT160">
+        <v>2.96</v>
+      </c>
+      <c r="AU160">
+        <v>5</v>
+      </c>
+      <c r="AV160">
+        <v>3</v>
+      </c>
+      <c r="AW160">
+        <v>5</v>
+      </c>
+      <c r="AX160">
+        <v>8</v>
+      </c>
+      <c r="AY160">
+        <v>10</v>
+      </c>
+      <c r="AZ160">
+        <v>11</v>
+      </c>
+      <c r="BA160">
+        <v>6</v>
+      </c>
+      <c r="BB160">
+        <v>4</v>
+      </c>
+      <c r="BC160">
+        <v>10</v>
+      </c>
+      <c r="BD160">
+        <v>1.9</v>
+      </c>
+      <c r="BE160">
+        <v>6.8</v>
+      </c>
+      <c r="BF160">
+        <v>2.28</v>
+      </c>
+      <c r="BG160">
+        <v>1.34</v>
+      </c>
+      <c r="BH160">
+        <v>2.98</v>
+      </c>
+      <c r="BI160">
+        <v>1.52</v>
+      </c>
+      <c r="BJ160">
+        <v>2.3</v>
+      </c>
+      <c r="BK160">
+        <v>1.95</v>
+      </c>
+      <c r="BL160">
+        <v>1.77</v>
+      </c>
+      <c r="BM160">
+        <v>2.39</v>
+      </c>
+      <c r="BN160">
+        <v>1.48</v>
+      </c>
+      <c r="BO160">
+        <v>3.32</v>
+      </c>
+      <c r="BP160">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="161" spans="1:68">
+      <c r="A161" s="1">
+        <v>160</v>
+      </c>
+      <c r="B161">
+        <v>7817198</v>
+      </c>
+      <c r="C161" t="s">
+        <v>68</v>
+      </c>
+      <c r="D161" t="s">
+        <v>69</v>
+      </c>
+      <c r="E161" s="2">
+        <v>45724.38541666666</v>
+      </c>
+      <c r="F161">
+        <v>5</v>
+      </c>
+      <c r="G161" t="s">
+        <v>81</v>
+      </c>
+      <c r="H161" t="s">
+        <v>80</v>
+      </c>
+      <c r="I161">
+        <v>3</v>
+      </c>
+      <c r="J161">
+        <v>1</v>
+      </c>
+      <c r="K161">
+        <v>4</v>
+      </c>
+      <c r="L161">
+        <v>5</v>
+      </c>
+      <c r="M161">
+        <v>1</v>
+      </c>
+      <c r="N161">
+        <v>6</v>
+      </c>
+      <c r="O161" t="s">
+        <v>198</v>
+      </c>
+      <c r="P161" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q161">
+        <v>1.73</v>
+      </c>
+      <c r="R161">
+        <v>2.4</v>
+      </c>
+      <c r="S161">
+        <v>8.5</v>
+      </c>
+      <c r="T161">
+        <v>1.33</v>
+      </c>
+      <c r="U161">
+        <v>3.25</v>
+      </c>
+      <c r="V161">
+        <v>2.5</v>
+      </c>
+      <c r="W161">
+        <v>1.5</v>
+      </c>
+      <c r="X161">
+        <v>6</v>
+      </c>
+      <c r="Y161">
+        <v>1.11</v>
+      </c>
+      <c r="Z161">
+        <v>1.27</v>
+      </c>
+      <c r="AA161">
+        <v>4.75</v>
+      </c>
+      <c r="AB161">
+        <v>9</v>
+      </c>
+      <c r="AC161">
+        <v>1.01</v>
+      </c>
+      <c r="AD161">
+        <v>11</v>
+      </c>
+      <c r="AE161">
+        <v>1.2</v>
+      </c>
+      <c r="AF161">
+        <v>4</v>
+      </c>
+      <c r="AG161">
+        <v>1.7</v>
+      </c>
+      <c r="AH161">
+        <v>2.1</v>
+      </c>
+      <c r="AI161">
+        <v>2.2</v>
+      </c>
+      <c r="AJ161">
+        <v>1.62</v>
+      </c>
+      <c r="AK161">
+        <v>1.04</v>
+      </c>
+      <c r="AL161">
+        <v>1.12</v>
+      </c>
+      <c r="AM161">
+        <v>3.4</v>
+      </c>
+      <c r="AN161">
+        <v>2.54</v>
+      </c>
+      <c r="AO161">
+        <v>1.69</v>
+      </c>
+      <c r="AP161">
+        <v>2.57</v>
+      </c>
+      <c r="AQ161">
+        <v>1.57</v>
+      </c>
+      <c r="AR161">
+        <v>2.54</v>
+      </c>
+      <c r="AS161">
+        <v>1.29</v>
+      </c>
+      <c r="AT161">
+        <v>3.83</v>
+      </c>
+      <c r="AU161">
+        <v>10</v>
+      </c>
+      <c r="AV161">
+        <v>2</v>
+      </c>
+      <c r="AW161">
+        <v>8</v>
+      </c>
+      <c r="AX161">
+        <v>4</v>
+      </c>
+      <c r="AY161">
+        <v>18</v>
+      </c>
+      <c r="AZ161">
+        <v>6</v>
+      </c>
+      <c r="BA161">
+        <v>7</v>
+      </c>
+      <c r="BB161">
+        <v>1</v>
+      </c>
+      <c r="BC161">
+        <v>8</v>
+      </c>
+      <c r="BD161">
+        <v>1.15</v>
+      </c>
+      <c r="BE161">
+        <v>11.75</v>
+      </c>
+      <c r="BF161">
+        <v>6.2</v>
+      </c>
+      <c r="BG161">
+        <v>1.48</v>
+      </c>
+      <c r="BH161">
+        <v>2.33</v>
+      </c>
+      <c r="BI161">
+        <v>1.87</v>
+      </c>
+      <c r="BJ161">
+        <v>1.79</v>
+      </c>
+      <c r="BK161">
+        <v>2.43</v>
+      </c>
+      <c r="BL161">
+        <v>1.44</v>
+      </c>
+      <c r="BM161">
+        <v>3.34</v>
+      </c>
+      <c r="BN161">
+        <v>1.24</v>
+      </c>
+      <c r="BO161">
+        <v>3.8</v>
+      </c>
+      <c r="BP161">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="162" spans="1:68">
+      <c r="A162" s="1">
+        <v>161</v>
+      </c>
+      <c r="B162">
+        <v>7817196</v>
+      </c>
+      <c r="C162" t="s">
+        <v>68</v>
+      </c>
+      <c r="D162" t="s">
+        <v>69</v>
+      </c>
+      <c r="E162" s="2">
+        <v>45724.47916666666</v>
+      </c>
+      <c r="F162">
+        <v>5</v>
+      </c>
+      <c r="G162" t="s">
+        <v>75</v>
+      </c>
+      <c r="H162" t="s">
+        <v>79</v>
+      </c>
+      <c r="I162">
+        <v>1</v>
+      </c>
+      <c r="J162">
+        <v>1</v>
+      </c>
+      <c r="K162">
+        <v>2</v>
+      </c>
+      <c r="L162">
+        <v>4</v>
+      </c>
+      <c r="M162">
+        <v>2</v>
+      </c>
+      <c r="N162">
+        <v>6</v>
+      </c>
+      <c r="O162" t="s">
+        <v>199</v>
+      </c>
+      <c r="P162" t="s">
+        <v>281</v>
+      </c>
+      <c r="Q162">
+        <v>3</v>
+      </c>
+      <c r="R162">
+        <v>2.2</v>
+      </c>
+      <c r="S162">
+        <v>3.1</v>
+      </c>
+      <c r="T162">
+        <v>1.33</v>
+      </c>
+      <c r="U162">
+        <v>3.25</v>
+      </c>
+      <c r="V162">
+        <v>2.63</v>
+      </c>
+      <c r="W162">
+        <v>1.44</v>
+      </c>
+      <c r="X162">
+        <v>6</v>
+      </c>
+      <c r="Y162">
+        <v>1.11</v>
+      </c>
+      <c r="Z162">
+        <v>2.49</v>
+      </c>
+      <c r="AA162">
+        <v>3.55</v>
+      </c>
+      <c r="AB162">
+        <v>2.59</v>
+      </c>
+      <c r="AC162">
+        <v>1.01</v>
+      </c>
+      <c r="AD162">
+        <v>11</v>
+      </c>
+      <c r="AE162">
+        <v>1.19</v>
+      </c>
+      <c r="AF162">
+        <v>3.78</v>
+      </c>
+      <c r="AG162">
+        <v>1.7</v>
+      </c>
+      <c r="AH162">
+        <v>2.05</v>
+      </c>
+      <c r="AI162">
+        <v>1.62</v>
+      </c>
+      <c r="AJ162">
+        <v>2.2</v>
+      </c>
+      <c r="AK162">
+        <v>1.45</v>
+      </c>
+      <c r="AL162">
+        <v>1.25</v>
+      </c>
+      <c r="AM162">
+        <v>1.46</v>
+      </c>
+      <c r="AN162">
+        <v>1.69</v>
+      </c>
+      <c r="AO162">
+        <v>2</v>
+      </c>
+      <c r="AP162">
+        <v>1.79</v>
+      </c>
+      <c r="AQ162">
+        <v>1.85</v>
+      </c>
+      <c r="AR162">
+        <v>1.46</v>
+      </c>
+      <c r="AS162">
+        <v>1.51</v>
+      </c>
+      <c r="AT162">
+        <v>2.97</v>
+      </c>
+      <c r="AU162">
+        <v>7</v>
+      </c>
+      <c r="AV162">
+        <v>3</v>
+      </c>
+      <c r="AW162">
+        <v>9</v>
+      </c>
+      <c r="AX162">
+        <v>5</v>
+      </c>
+      <c r="AY162">
+        <v>16</v>
+      </c>
+      <c r="AZ162">
+        <v>8</v>
+      </c>
+      <c r="BA162">
+        <v>4</v>
+      </c>
+      <c r="BB162">
+        <v>2</v>
+      </c>
+      <c r="BC162">
+        <v>6</v>
+      </c>
+      <c r="BD162">
+        <v>1.85</v>
+      </c>
+      <c r="BE162">
+        <v>6.3</v>
+      </c>
+      <c r="BF162">
+        <v>2.39</v>
+      </c>
+      <c r="BG162">
+        <v>1.22</v>
+      </c>
+      <c r="BH162">
+        <v>3.5</v>
+      </c>
+      <c r="BI162">
+        <v>1.45</v>
+      </c>
+      <c r="BJ162">
+        <v>2.49</v>
+      </c>
+      <c r="BK162">
+        <v>1.8</v>
+      </c>
+      <c r="BL162">
+        <v>1.96</v>
+      </c>
+      <c r="BM162">
+        <v>2.23</v>
+      </c>
+      <c r="BN162">
+        <v>1.57</v>
+      </c>
+      <c r="BO162">
+        <v>2.97</v>
+      </c>
+      <c r="BP162">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="163" spans="1:68">
+      <c r="A163" s="1">
+        <v>162</v>
+      </c>
+      <c r="B163">
+        <v>7817197</v>
+      </c>
+      <c r="C163" t="s">
+        <v>68</v>
+      </c>
+      <c r="D163" t="s">
+        <v>69</v>
+      </c>
+      <c r="E163" s="2">
+        <v>45724.47916666666</v>
+      </c>
+      <c r="F163">
+        <v>5</v>
+      </c>
+      <c r="G163" t="s">
+        <v>76</v>
+      </c>
+      <c r="H163" t="s">
+        <v>77</v>
+      </c>
+      <c r="I163">
+        <v>1</v>
+      </c>
+      <c r="J163">
+        <v>0</v>
+      </c>
+      <c r="K163">
+        <v>1</v>
+      </c>
+      <c r="L163">
+        <v>3</v>
+      </c>
+      <c r="M163">
+        <v>2</v>
+      </c>
+      <c r="N163">
+        <v>5</v>
+      </c>
+      <c r="O163" t="s">
+        <v>200</v>
+      </c>
+      <c r="P163" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q163">
+        <v>2.2</v>
+      </c>
+      <c r="R163">
+        <v>2.05</v>
+      </c>
+      <c r="S163">
+        <v>5.5</v>
+      </c>
+      <c r="T163">
+        <v>1.44</v>
+      </c>
+      <c r="U163">
+        <v>2.63</v>
+      </c>
+      <c r="V163">
+        <v>3.25</v>
+      </c>
+      <c r="W163">
+        <v>1.33</v>
+      </c>
+      <c r="X163">
+        <v>8</v>
+      </c>
+      <c r="Y163">
+        <v>1.06</v>
+      </c>
+      <c r="Z163">
+        <v>1.64</v>
+      </c>
+      <c r="AA163">
+        <v>4</v>
+      </c>
+      <c r="AB163">
+        <v>4.75</v>
+      </c>
+      <c r="AC163">
+        <v>1.01</v>
+      </c>
+      <c r="AD163">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AE163">
+        <v>1.32</v>
+      </c>
+      <c r="AF163">
+        <v>2.88</v>
+      </c>
+      <c r="AG163">
+        <v>1.77</v>
+      </c>
+      <c r="AH163">
+        <v>1.98</v>
+      </c>
+      <c r="AI163">
+        <v>2.2</v>
+      </c>
+      <c r="AJ163">
+        <v>1.62</v>
+      </c>
+      <c r="AK163">
+        <v>1.1</v>
+      </c>
+      <c r="AL163">
+        <v>1.23</v>
+      </c>
+      <c r="AM163">
+        <v>2.2</v>
+      </c>
+      <c r="AN163">
+        <v>2.08</v>
+      </c>
+      <c r="AO163">
+        <v>1.15</v>
+      </c>
+      <c r="AP163">
+        <v>2.15</v>
+      </c>
+      <c r="AQ163">
+        <v>1.07</v>
+      </c>
+      <c r="AR163">
+        <v>1.65</v>
+      </c>
+      <c r="AS163">
+        <v>1.32</v>
+      </c>
+      <c r="AT163">
+        <v>2.97</v>
+      </c>
+      <c r="AU163">
+        <v>-1</v>
+      </c>
+      <c r="AV163">
+        <v>-1</v>
+      </c>
+      <c r="AW163">
+        <v>-1</v>
+      </c>
+      <c r="AX163">
+        <v>-1</v>
+      </c>
+      <c r="AY163">
+        <v>-1</v>
+      </c>
+      <c r="AZ163">
+        <v>-1</v>
+      </c>
+      <c r="BA163">
+        <v>-1</v>
+      </c>
+      <c r="BB163">
+        <v>-1</v>
+      </c>
+      <c r="BC163">
+        <v>-1</v>
+      </c>
+      <c r="BD163">
+        <v>0</v>
+      </c>
+      <c r="BE163">
+        <v>0</v>
+      </c>
+      <c r="BF163">
+        <v>0</v>
+      </c>
+      <c r="BG163">
+        <v>0</v>
+      </c>
+      <c r="BH163">
+        <v>0</v>
+      </c>
+      <c r="BI163">
+        <v>0</v>
+      </c>
+      <c r="BJ163">
+        <v>0</v>
+      </c>
+      <c r="BK163">
+        <v>0</v>
+      </c>
+      <c r="BL163">
+        <v>0</v>
+      </c>
+      <c r="BM163">
+        <v>0</v>
+      </c>
+      <c r="BN163">
+        <v>0</v>
+      </c>
+      <c r="BO163">
+        <v>0</v>
+      </c>
+      <c r="BP163">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Wales Welsh Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Wales Welsh Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="286">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -619,10 +619,19 @@
     <t>['13', '61', '90+6']</t>
   </si>
   <si>
-    <t>['45+2']</t>
+    <t>['67']</t>
   </si>
   <si>
-    <t>['67']</t>
+    <t>['7', '90+2']</t>
+  </si>
+  <si>
+    <t>['22', '38', '54', '81']</t>
+  </si>
+  <si>
+    <t>['45+1', '90+4']</t>
+  </si>
+  <si>
+    <t>['45+2']</t>
   </si>
   <si>
     <t>['21', '56']</t>
@@ -1224,7 +1233,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP163"/>
+  <dimension ref="A1:BP167"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1480,7 +1489,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="Q2">
         <v>1.83</v>
@@ -1561,7 +1570,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ2">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1686,7 +1695,7 @@
         <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Q3">
         <v>3.75</v>
@@ -1764,7 +1773,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ3">
         <v>1.07</v>
@@ -1892,7 +1901,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -2176,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ5">
         <v>1.57</v>
@@ -2304,7 +2313,7 @@
         <v>85</v>
       </c>
       <c r="P6" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q6">
         <v>4</v>
@@ -2382,7 +2391,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ6">
         <v>1.86</v>
@@ -2510,7 +2519,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q7">
         <v>11</v>
@@ -3003,7 +3012,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ9">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3334,7 +3343,7 @@
         <v>89</v>
       </c>
       <c r="P11" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q11">
         <v>3.6</v>
@@ -3540,7 +3549,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q12">
         <v>2.9</v>
@@ -3827,7 +3836,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ13">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR13">
         <v>1.91</v>
@@ -3952,7 +3961,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q14">
         <v>4.33</v>
@@ -4030,7 +4039,7 @@
         <v>3</v>
       </c>
       <c r="AP14">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ14">
         <v>1.23</v>
@@ -4364,7 +4373,7 @@
         <v>85</v>
       </c>
       <c r="P16" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q16">
         <v>2.63</v>
@@ -4445,7 +4454,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ16">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR16">
         <v>2.12</v>
@@ -4776,7 +4785,7 @@
         <v>94</v>
       </c>
       <c r="P18" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q18">
         <v>3</v>
@@ -4854,10 +4863,10 @@
         <v>1</v>
       </c>
       <c r="AP18">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ18">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR18">
         <v>1.28</v>
@@ -4982,7 +4991,7 @@
         <v>85</v>
       </c>
       <c r="P19" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q19">
         <v>4.75</v>
@@ -5475,7 +5484,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ21">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="AR21">
         <v>1.58</v>
@@ -5887,7 +5896,7 @@
         <v>2</v>
       </c>
       <c r="AQ23">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR23">
         <v>1.19</v>
@@ -6012,7 +6021,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6218,7 +6227,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q25">
         <v>3.2</v>
@@ -6424,7 +6433,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -6502,10 +6511,10 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ26">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR26">
         <v>1.77</v>
@@ -6630,7 +6639,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q27">
         <v>5.5</v>
@@ -6708,7 +6717,7 @@
         <v>2</v>
       </c>
       <c r="AP27">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ27">
         <v>1.15</v>
@@ -6914,10 +6923,10 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="AQ28">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="AR28">
         <v>0</v>
@@ -7123,7 +7132,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ29">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR29">
         <v>2.16</v>
@@ -7454,7 +7463,7 @@
         <v>85</v>
       </c>
       <c r="P31" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q31">
         <v>13</v>
@@ -7660,7 +7669,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q32">
         <v>1.83</v>
@@ -7738,7 +7747,7 @@
         <v>0.5</v>
       </c>
       <c r="AP32">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ32">
         <v>1.36</v>
@@ -8072,7 +8081,7 @@
         <v>85</v>
       </c>
       <c r="P34" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q34">
         <v>3</v>
@@ -8153,7 +8162,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ34">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR34">
         <v>0.86</v>
@@ -8565,7 +8574,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ36">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="AR36">
         <v>1.37</v>
@@ -8974,7 +8983,7 @@
         <v>1.33</v>
       </c>
       <c r="AP38">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="AQ38">
         <v>1.36</v>
@@ -9102,7 +9111,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q39">
         <v>1.83</v>
@@ -9386,7 +9395,7 @@
         <v>2.33</v>
       </c>
       <c r="AP40">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ40">
         <v>1.86</v>
@@ -9514,7 +9523,7 @@
         <v>110</v>
       </c>
       <c r="P41" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q41">
         <v>7</v>
@@ -9720,7 +9729,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q42">
         <v>2.6</v>
@@ -9801,7 +9810,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ42">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR42">
         <v>1.52</v>
@@ -9926,7 +9935,7 @@
         <v>85</v>
       </c>
       <c r="P43" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q43">
         <v>3.75</v>
@@ -10416,10 +10425,10 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ45">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR45">
         <v>1.74</v>
@@ -10544,7 +10553,7 @@
         <v>114</v>
       </c>
       <c r="P46" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Q46">
         <v>3.4</v>
@@ -10622,10 +10631,10 @@
         <v>1</v>
       </c>
       <c r="AP46">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ46">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR46">
         <v>0.8100000000000001</v>
@@ -10750,7 +10759,7 @@
         <v>115</v>
       </c>
       <c r="P47" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q47">
         <v>2.25</v>
@@ -10828,10 +10837,10 @@
         <v>1.25</v>
       </c>
       <c r="AP47">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ47">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR47">
         <v>1.34</v>
@@ -10956,7 +10965,7 @@
         <v>116</v>
       </c>
       <c r="P48" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q48">
         <v>2.5</v>
@@ -11368,7 +11377,7 @@
         <v>117</v>
       </c>
       <c r="P50" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q50">
         <v>1.67</v>
@@ -11446,7 +11455,7 @@
         <v>1</v>
       </c>
       <c r="AP50">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="AQ50">
         <v>1.07</v>
@@ -11574,7 +11583,7 @@
         <v>118</v>
       </c>
       <c r="P51" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q51">
         <v>6</v>
@@ -11780,7 +11789,7 @@
         <v>119</v>
       </c>
       <c r="P52" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -11861,7 +11870,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ52">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR52">
         <v>1.62</v>
@@ -12064,10 +12073,10 @@
         <v>0</v>
       </c>
       <c r="AP53">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ53">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="AR53">
         <v>1.67</v>
@@ -12192,7 +12201,7 @@
         <v>114</v>
       </c>
       <c r="P54" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q54">
         <v>9.5</v>
@@ -12604,7 +12613,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q56">
         <v>7</v>
@@ -12682,7 +12691,7 @@
         <v>1.67</v>
       </c>
       <c r="AP56">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ56">
         <v>1.07</v>
@@ -13428,7 +13437,7 @@
         <v>125</v>
       </c>
       <c r="P60" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q60">
         <v>2.3</v>
@@ -13509,7 +13518,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ60">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR60">
         <v>1.7</v>
@@ -13634,7 +13643,7 @@
         <v>85</v>
       </c>
       <c r="P61" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q61">
         <v>2.88</v>
@@ -13918,10 +13927,10 @@
         <v>0</v>
       </c>
       <c r="AP62">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ62">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="AR62">
         <v>1.28</v>
@@ -14046,7 +14055,7 @@
         <v>87</v>
       </c>
       <c r="P63" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q63">
         <v>2.63</v>
@@ -14127,7 +14136,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ63">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR63">
         <v>1.21</v>
@@ -14252,7 +14261,7 @@
         <v>127</v>
       </c>
       <c r="P64" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q64">
         <v>1.42</v>
@@ -14330,10 +14339,10 @@
         <v>2</v>
       </c>
       <c r="AP64">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="AQ64">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR64">
         <v>3.13</v>
@@ -14664,7 +14673,7 @@
         <v>128</v>
       </c>
       <c r="P66" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -14948,7 +14957,7 @@
         <v>2.14</v>
       </c>
       <c r="AP67">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="AQ67">
         <v>1.23</v>
@@ -15154,7 +15163,7 @@
         <v>0.75</v>
       </c>
       <c r="AP68">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ68">
         <v>0.93</v>
@@ -15282,7 +15291,7 @@
         <v>131</v>
       </c>
       <c r="P69" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15363,7 +15372,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ69">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR69">
         <v>1.2</v>
@@ -15488,7 +15497,7 @@
         <v>85</v>
       </c>
       <c r="P70" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q70">
         <v>9</v>
@@ -15900,7 +15909,7 @@
         <v>132</v>
       </c>
       <c r="P72" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q72">
         <v>7</v>
@@ -15978,7 +15987,7 @@
         <v>2.17</v>
       </c>
       <c r="AP72">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ72">
         <v>1.57</v>
@@ -16106,7 +16115,7 @@
         <v>133</v>
       </c>
       <c r="P73" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q73">
         <v>1.73</v>
@@ -16187,7 +16196,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ73">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="AR73">
         <v>1.35</v>
@@ -16518,7 +16527,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16802,10 +16811,10 @@
         <v>1.4</v>
       </c>
       <c r="AP76">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="AQ76">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR76">
         <v>2.71</v>
@@ -16930,7 +16939,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q77">
         <v>2.5</v>
@@ -17011,7 +17020,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ77">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR77">
         <v>1.29</v>
@@ -17136,7 +17145,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17342,7 +17351,7 @@
         <v>139</v>
       </c>
       <c r="P79" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q79">
         <v>2.75</v>
@@ -17629,7 +17638,7 @@
         <v>2</v>
       </c>
       <c r="AQ80">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR80">
         <v>1.28</v>
@@ -17754,7 +17763,7 @@
         <v>140</v>
       </c>
       <c r="P81" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q81">
         <v>19</v>
@@ -17960,7 +17969,7 @@
         <v>141</v>
       </c>
       <c r="P82" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Q82">
         <v>1.5</v>
@@ -18038,7 +18047,7 @@
         <v>0.6</v>
       </c>
       <c r="AP82">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ82">
         <v>0.93</v>
@@ -18166,7 +18175,7 @@
         <v>142</v>
       </c>
       <c r="P83" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18244,7 +18253,7 @@
         <v>2.4</v>
       </c>
       <c r="AP83">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ83">
         <v>2.31</v>
@@ -18372,7 +18381,7 @@
         <v>143</v>
       </c>
       <c r="P84" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q84">
         <v>11</v>
@@ -18450,7 +18459,7 @@
         <v>2.5</v>
       </c>
       <c r="AP84">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ84">
         <v>2.31</v>
@@ -18578,7 +18587,7 @@
         <v>144</v>
       </c>
       <c r="P85" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q85">
         <v>4.75</v>
@@ -18862,7 +18871,7 @@
         <v>1.88</v>
       </c>
       <c r="AP86">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ86">
         <v>1.23</v>
@@ -19071,7 +19080,7 @@
         <v>2</v>
       </c>
       <c r="AQ87">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR87">
         <v>1.32</v>
@@ -19480,10 +19489,10 @@
         <v>0.43</v>
       </c>
       <c r="AP89">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ89">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="AR89">
         <v>1.09</v>
@@ -19608,7 +19617,7 @@
         <v>148</v>
       </c>
       <c r="P90" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q90">
         <v>4.75</v>
@@ -19689,7 +19698,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ90">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR90">
         <v>0.87</v>
@@ -19895,7 +19904,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ91">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR91">
         <v>1.97</v>
@@ -20020,7 +20029,7 @@
         <v>150</v>
       </c>
       <c r="P92" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q92">
         <v>2.88</v>
@@ -20098,7 +20107,7 @@
         <v>1.29</v>
       </c>
       <c r="AP92">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ92">
         <v>1.15</v>
@@ -20304,10 +20313,10 @@
         <v>2</v>
       </c>
       <c r="AP93">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ93">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR93">
         <v>1.26</v>
@@ -20432,7 +20441,7 @@
         <v>151</v>
       </c>
       <c r="P94" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q94">
         <v>2.88</v>
@@ -20716,7 +20725,7 @@
         <v>2.29</v>
       </c>
       <c r="AP95">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="AQ95">
         <v>1.57</v>
@@ -20844,7 +20853,7 @@
         <v>153</v>
       </c>
       <c r="P96" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q96">
         <v>11</v>
@@ -20922,7 +20931,7 @@
         <v>2.57</v>
       </c>
       <c r="AP96">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ96">
         <v>2.31</v>
@@ -21131,7 +21140,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ97">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="AR97">
         <v>1.22</v>
@@ -21668,7 +21677,7 @@
         <v>156</v>
       </c>
       <c r="P100" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q100">
         <v>1.73</v>
@@ -21746,7 +21755,7 @@
         <v>2.5</v>
       </c>
       <c r="AP100">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="AQ100">
         <v>1.86</v>
@@ -21874,7 +21883,7 @@
         <v>85</v>
       </c>
       <c r="P101" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q101">
         <v>3.4</v>
@@ -22080,7 +22089,7 @@
         <v>157</v>
       </c>
       <c r="P102" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q102">
         <v>3</v>
@@ -22158,10 +22167,10 @@
         <v>1.13</v>
       </c>
       <c r="AP102">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ102">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR102">
         <v>1.32</v>
@@ -22286,7 +22295,7 @@
         <v>158</v>
       </c>
       <c r="P103" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22364,10 +22373,10 @@
         <v>2.13</v>
       </c>
       <c r="AP103">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ103">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR103">
         <v>1.45</v>
@@ -22985,7 +22994,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ106">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="AR106">
         <v>1.69</v>
@@ -23110,7 +23119,7 @@
         <v>162</v>
       </c>
       <c r="P107" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q107">
         <v>3</v>
@@ -23188,7 +23197,7 @@
         <v>1.67</v>
       </c>
       <c r="AP107">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ107">
         <v>1.23</v>
@@ -23316,7 +23325,7 @@
         <v>163</v>
       </c>
       <c r="P108" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q108">
         <v>2.75</v>
@@ -23603,7 +23612,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ109">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR109">
         <v>1.26</v>
@@ -23728,7 +23737,7 @@
         <v>165</v>
       </c>
       <c r="P110" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q110">
         <v>2.4</v>
@@ -24015,7 +24024,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ111">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR111">
         <v>0.97</v>
@@ -24140,7 +24149,7 @@
         <v>167</v>
       </c>
       <c r="P112" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q112">
         <v>1.4</v>
@@ -24218,7 +24227,7 @@
         <v>0.43</v>
       </c>
       <c r="AP112">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="AQ112">
         <v>0.93</v>
@@ -24346,7 +24355,7 @@
         <v>168</v>
       </c>
       <c r="P113" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q113">
         <v>4.75</v>
@@ -24424,7 +24433,7 @@
         <v>2.22</v>
       </c>
       <c r="AP113">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ113">
         <v>1.86</v>
@@ -24552,7 +24561,7 @@
         <v>98</v>
       </c>
       <c r="P114" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q114">
         <v>2</v>
@@ -24758,7 +24767,7 @@
         <v>85</v>
       </c>
       <c r="P115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q115">
         <v>3.75</v>
@@ -25170,7 +25179,7 @@
         <v>169</v>
       </c>
       <c r="P117" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25248,10 +25257,10 @@
         <v>0.78</v>
       </c>
       <c r="AP117">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ117">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR117">
         <v>1.49</v>
@@ -25376,7 +25385,7 @@
         <v>170</v>
       </c>
       <c r="P118" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q118">
         <v>6</v>
@@ -25660,7 +25669,7 @@
         <v>1.1</v>
       </c>
       <c r="AP119">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ119">
         <v>1.36</v>
@@ -25866,7 +25875,7 @@
         <v>1.33</v>
       </c>
       <c r="AP120">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="AQ120">
         <v>1.15</v>
@@ -25994,7 +26003,7 @@
         <v>172</v>
       </c>
       <c r="P121" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q121">
         <v>2.1</v>
@@ -26281,7 +26290,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ122">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR122">
         <v>1.73</v>
@@ -26487,7 +26496,7 @@
         <v>2</v>
       </c>
       <c r="AQ123">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="AR123">
         <v>1.34</v>
@@ -26612,7 +26621,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q124">
         <v>1.44</v>
@@ -26690,10 +26699,10 @@
         <v>0.9</v>
       </c>
       <c r="AP124">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="AQ124">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR124">
         <v>2.58</v>
@@ -27230,7 +27239,7 @@
         <v>85</v>
       </c>
       <c r="P127" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q127">
         <v>2.3</v>
@@ -27311,7 +27320,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ127">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR127">
         <v>1.34</v>
@@ -27436,7 +27445,7 @@
         <v>139</v>
       </c>
       <c r="P128" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q128">
         <v>2.75</v>
@@ -27723,7 +27732,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ129">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR129">
         <v>1.37</v>
@@ -27848,7 +27857,7 @@
         <v>85</v>
       </c>
       <c r="P130" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q130">
         <v>5.5</v>
@@ -28054,7 +28063,7 @@
         <v>177</v>
       </c>
       <c r="P131" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q131">
         <v>7</v>
@@ -28338,7 +28347,7 @@
         <v>1.9</v>
       </c>
       <c r="AP132">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ132">
         <v>1.57</v>
@@ -28466,7 +28475,7 @@
         <v>85</v>
       </c>
       <c r="P133" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q133">
         <v>2.75</v>
@@ -28544,7 +28553,7 @@
         <v>1.2</v>
       </c>
       <c r="AP133">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ133">
         <v>1.07</v>
@@ -28672,7 +28681,7 @@
         <v>179</v>
       </c>
       <c r="P134" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q134">
         <v>4.75</v>
@@ -28878,7 +28887,7 @@
         <v>180</v>
       </c>
       <c r="P135" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q135">
         <v>2.5</v>
@@ -29084,7 +29093,7 @@
         <v>120</v>
       </c>
       <c r="P136" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q136">
         <v>3.75</v>
@@ -29290,7 +29299,7 @@
         <v>181</v>
       </c>
       <c r="P137" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q137">
         <v>2.38</v>
@@ -29702,7 +29711,7 @@
         <v>183</v>
       </c>
       <c r="P139" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q139">
         <v>2.7</v>
@@ -29783,7 +29792,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ139">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR139">
         <v>1.37</v>
@@ -30192,10 +30201,10 @@
         <v>0.82</v>
       </c>
       <c r="AP141">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ141">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR141">
         <v>1.54</v>
@@ -30398,10 +30407,10 @@
         <v>0.64</v>
       </c>
       <c r="AP142">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ142">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR142">
         <v>1.44</v>
@@ -30526,7 +30535,7 @@
         <v>186</v>
       </c>
       <c r="P143" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q143">
         <v>2.1</v>
@@ -30604,10 +30613,10 @@
         <v>0.27</v>
       </c>
       <c r="AP143">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ143">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="AR143">
         <v>1.39</v>
@@ -30732,7 +30741,7 @@
         <v>187</v>
       </c>
       <c r="P144" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q144">
         <v>1.53</v>
@@ -30810,7 +30819,7 @@
         <v>1.45</v>
       </c>
       <c r="AP144">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="AQ144">
         <v>1.23</v>
@@ -31019,7 +31028,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ145">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="AR145">
         <v>1.76</v>
@@ -31222,7 +31231,7 @@
         <v>2.17</v>
       </c>
       <c r="AP146">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="AQ146">
         <v>1.86</v>
@@ -31840,7 +31849,7 @@
         <v>0.83</v>
       </c>
       <c r="AP149">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ149">
         <v>0.93</v>
@@ -32174,7 +32183,7 @@
         <v>85</v>
       </c>
       <c r="P151" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q151">
         <v>8</v>
@@ -32380,7 +32389,7 @@
         <v>85</v>
       </c>
       <c r="P152" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q152">
         <v>6</v>
@@ -32873,7 +32882,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ154">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AR154">
         <v>1.1</v>
@@ -32998,7 +33007,7 @@
         <v>193</v>
       </c>
       <c r="P155" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q155">
         <v>3.25</v>
@@ -33204,7 +33213,7 @@
         <v>85</v>
       </c>
       <c r="P156" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q156">
         <v>2.88</v>
@@ -33282,7 +33291,7 @@
         <v>1</v>
       </c>
       <c r="AP156">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AQ156">
         <v>1.15</v>
@@ -33410,7 +33419,7 @@
         <v>194</v>
       </c>
       <c r="P157" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q157">
         <v>2.63</v>
@@ -33616,7 +33625,7 @@
         <v>195</v>
       </c>
       <c r="P158" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q158">
         <v>3</v>
@@ -33694,7 +33703,7 @@
         <v>1.23</v>
       </c>
       <c r="AP158">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ158">
         <v>1.36</v>
@@ -33900,10 +33909,10 @@
         <v>0.46</v>
       </c>
       <c r="AP159">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ159">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="AR159">
         <v>1.62</v>
@@ -34028,7 +34037,7 @@
         <v>197</v>
       </c>
       <c r="P160" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q160">
         <v>2.88</v>
@@ -34109,7 +34118,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ160">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AR160">
         <v>1.52</v>
@@ -34312,7 +34321,7 @@
         <v>1.69</v>
       </c>
       <c r="AP161">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="AQ161">
         <v>1.57</v>
@@ -34440,7 +34449,7 @@
         <v>199</v>
       </c>
       <c r="P162" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q162">
         <v>3</v>
@@ -34521,7 +34530,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ162">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AR162">
         <v>1.46</v>
@@ -34646,7 +34655,7 @@
         <v>200</v>
       </c>
       <c r="P163" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q163">
         <v>2.2</v>
@@ -34803,6 +34812,830 @@
       </c>
       <c r="BP163">
         <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:68">
+      <c r="A164" s="1">
+        <v>163</v>
+      </c>
+      <c r="B164">
+        <v>7817202</v>
+      </c>
+      <c r="C164" t="s">
+        <v>68</v>
+      </c>
+      <c r="D164" t="s">
+        <v>69</v>
+      </c>
+      <c r="E164" s="2">
+        <v>45727.69791666666</v>
+      </c>
+      <c r="F164">
+        <v>6</v>
+      </c>
+      <c r="G164" t="s">
+        <v>74</v>
+      </c>
+      <c r="H164" t="s">
+        <v>70</v>
+      </c>
+      <c r="I164">
+        <v>0</v>
+      </c>
+      <c r="J164">
+        <v>0</v>
+      </c>
+      <c r="K164">
+        <v>0</v>
+      </c>
+      <c r="L164">
+        <v>1</v>
+      </c>
+      <c r="M164">
+        <v>1</v>
+      </c>
+      <c r="N164">
+        <v>2</v>
+      </c>
+      <c r="O164" t="s">
+        <v>201</v>
+      </c>
+      <c r="P164" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q164">
+        <v>3.1</v>
+      </c>
+      <c r="R164">
+        <v>2.2</v>
+      </c>
+      <c r="S164">
+        <v>2.87</v>
+      </c>
+      <c r="T164">
+        <v>1.3</v>
+      </c>
+      <c r="U164">
+        <v>3.2</v>
+      </c>
+      <c r="V164">
+        <v>2.3</v>
+      </c>
+      <c r="W164">
+        <v>1.53</v>
+      </c>
+      <c r="X164">
+        <v>5.25</v>
+      </c>
+      <c r="Y164">
+        <v>1.13</v>
+      </c>
+      <c r="Z164">
+        <v>2.68</v>
+      </c>
+      <c r="AA164">
+        <v>3.63</v>
+      </c>
+      <c r="AB164">
+        <v>2.37</v>
+      </c>
+      <c r="AC164">
+        <v>1.02</v>
+      </c>
+      <c r="AD164">
+        <v>13</v>
+      </c>
+      <c r="AE164">
+        <v>1.22</v>
+      </c>
+      <c r="AF164">
+        <v>4</v>
+      </c>
+      <c r="AG164">
+        <v>1.6</v>
+      </c>
+      <c r="AH164">
+        <v>2.1</v>
+      </c>
+      <c r="AI164">
+        <v>1.53</v>
+      </c>
+      <c r="AJ164">
+        <v>2.3</v>
+      </c>
+      <c r="AK164">
+        <v>1.53</v>
+      </c>
+      <c r="AL164">
+        <v>1.29</v>
+      </c>
+      <c r="AM164">
+        <v>1.43</v>
+      </c>
+      <c r="AN164">
+        <v>0.92</v>
+      </c>
+      <c r="AO164">
+        <v>0.92</v>
+      </c>
+      <c r="AP164">
+        <v>0.93</v>
+      </c>
+      <c r="AQ164">
+        <v>0.93</v>
+      </c>
+      <c r="AR164">
+        <v>1.48</v>
+      </c>
+      <c r="AS164">
+        <v>1.34</v>
+      </c>
+      <c r="AT164">
+        <v>2.82</v>
+      </c>
+      <c r="AU164">
+        <v>8</v>
+      </c>
+      <c r="AV164">
+        <v>12</v>
+      </c>
+      <c r="AW164">
+        <v>2</v>
+      </c>
+      <c r="AX164">
+        <v>7</v>
+      </c>
+      <c r="AY164">
+        <v>10</v>
+      </c>
+      <c r="AZ164">
+        <v>19</v>
+      </c>
+      <c r="BA164">
+        <v>2</v>
+      </c>
+      <c r="BB164">
+        <v>13</v>
+      </c>
+      <c r="BC164">
+        <v>15</v>
+      </c>
+      <c r="BD164">
+        <v>2.17</v>
+      </c>
+      <c r="BE164">
+        <v>6.9</v>
+      </c>
+      <c r="BF164">
+        <v>1.98</v>
+      </c>
+      <c r="BG164">
+        <v>1.19</v>
+      </c>
+      <c r="BH164">
+        <v>3.98</v>
+      </c>
+      <c r="BI164">
+        <v>1.38</v>
+      </c>
+      <c r="BJ164">
+        <v>2.82</v>
+      </c>
+      <c r="BK164">
+        <v>1.63</v>
+      </c>
+      <c r="BL164">
+        <v>2.17</v>
+      </c>
+      <c r="BM164">
+        <v>2.01</v>
+      </c>
+      <c r="BN164">
+        <v>1.74</v>
+      </c>
+      <c r="BO164">
+        <v>2.53</v>
+      </c>
+      <c r="BP164">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="165" spans="1:68">
+      <c r="A165" s="1">
+        <v>164</v>
+      </c>
+      <c r="B165">
+        <v>7817201</v>
+      </c>
+      <c r="C165" t="s">
+        <v>68</v>
+      </c>
+      <c r="D165" t="s">
+        <v>69</v>
+      </c>
+      <c r="E165" s="2">
+        <v>45727.69791666666</v>
+      </c>
+      <c r="F165">
+        <v>6</v>
+      </c>
+      <c r="G165" t="s">
+        <v>71</v>
+      </c>
+      <c r="H165" t="s">
+        <v>78</v>
+      </c>
+      <c r="I165">
+        <v>1</v>
+      </c>
+      <c r="J165">
+        <v>0</v>
+      </c>
+      <c r="K165">
+        <v>1</v>
+      </c>
+      <c r="L165">
+        <v>2</v>
+      </c>
+      <c r="M165">
+        <v>1</v>
+      </c>
+      <c r="N165">
+        <v>3</v>
+      </c>
+      <c r="O165" t="s">
+        <v>202</v>
+      </c>
+      <c r="P165" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q165">
+        <v>1.83</v>
+      </c>
+      <c r="R165">
+        <v>2.4</v>
+      </c>
+      <c r="S165">
+        <v>6.5</v>
+      </c>
+      <c r="T165">
+        <v>1.33</v>
+      </c>
+      <c r="U165">
+        <v>3.25</v>
+      </c>
+      <c r="V165">
+        <v>2.5</v>
+      </c>
+      <c r="W165">
+        <v>1.5</v>
+      </c>
+      <c r="X165">
+        <v>5.5</v>
+      </c>
+      <c r="Y165">
+        <v>1.13</v>
+      </c>
+      <c r="Z165">
+        <v>1.34</v>
+      </c>
+      <c r="AA165">
+        <v>5.5</v>
+      </c>
+      <c r="AB165">
+        <v>7.2</v>
+      </c>
+      <c r="AC165">
+        <v>1.01</v>
+      </c>
+      <c r="AD165">
+        <v>13</v>
+      </c>
+      <c r="AE165">
+        <v>1.13</v>
+      </c>
+      <c r="AF165">
+        <v>4.55</v>
+      </c>
+      <c r="AG165">
+        <v>1.65</v>
+      </c>
+      <c r="AH165">
+        <v>2</v>
+      </c>
+      <c r="AI165">
+        <v>2</v>
+      </c>
+      <c r="AJ165">
+        <v>1.73</v>
+      </c>
+      <c r="AK165">
+        <v>1.09</v>
+      </c>
+      <c r="AL165">
+        <v>1.17</v>
+      </c>
+      <c r="AM165">
+        <v>3</v>
+      </c>
+      <c r="AN165">
+        <v>1.62</v>
+      </c>
+      <c r="AO165">
+        <v>0.43</v>
+      </c>
+      <c r="AP165">
+        <v>1.71</v>
+      </c>
+      <c r="AQ165">
+        <v>0.4</v>
+      </c>
+      <c r="AR165">
+        <v>1.41</v>
+      </c>
+      <c r="AS165">
+        <v>1.03</v>
+      </c>
+      <c r="AT165">
+        <v>2.44</v>
+      </c>
+      <c r="AU165">
+        <v>8</v>
+      </c>
+      <c r="AV165">
+        <v>2</v>
+      </c>
+      <c r="AW165">
+        <v>16</v>
+      </c>
+      <c r="AX165">
+        <v>3</v>
+      </c>
+      <c r="AY165">
+        <v>24</v>
+      </c>
+      <c r="AZ165">
+        <v>5</v>
+      </c>
+      <c r="BA165">
+        <v>8</v>
+      </c>
+      <c r="BB165">
+        <v>3</v>
+      </c>
+      <c r="BC165">
+        <v>11</v>
+      </c>
+      <c r="BD165">
+        <v>1.3</v>
+      </c>
+      <c r="BE165">
+        <v>9.5</v>
+      </c>
+      <c r="BF165">
+        <v>4.1</v>
+      </c>
+      <c r="BG165">
+        <v>1.21</v>
+      </c>
+      <c r="BH165">
+        <v>3.58</v>
+      </c>
+      <c r="BI165">
+        <v>1.41</v>
+      </c>
+      <c r="BJ165">
+        <v>2.52</v>
+      </c>
+      <c r="BK165">
+        <v>1.75</v>
+      </c>
+      <c r="BL165">
+        <v>1.92</v>
+      </c>
+      <c r="BM165">
+        <v>2.21</v>
+      </c>
+      <c r="BN165">
+        <v>1.53</v>
+      </c>
+      <c r="BO165">
+        <v>2.92</v>
+      </c>
+      <c r="BP165">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="166" spans="1:68">
+      <c r="A166" s="1">
+        <v>165</v>
+      </c>
+      <c r="B166">
+        <v>7817203</v>
+      </c>
+      <c r="C166" t="s">
+        <v>68</v>
+      </c>
+      <c r="D166" t="s">
+        <v>69</v>
+      </c>
+      <c r="E166" s="2">
+        <v>45727.69791666666</v>
+      </c>
+      <c r="F166">
+        <v>6</v>
+      </c>
+      <c r="G166" t="s">
+        <v>73</v>
+      </c>
+      <c r="H166" t="s">
+        <v>72</v>
+      </c>
+      <c r="I166">
+        <v>2</v>
+      </c>
+      <c r="J166">
+        <v>0</v>
+      </c>
+      <c r="K166">
+        <v>2</v>
+      </c>
+      <c r="L166">
+        <v>4</v>
+      </c>
+      <c r="M166">
+        <v>0</v>
+      </c>
+      <c r="N166">
+        <v>4</v>
+      </c>
+      <c r="O166" t="s">
+        <v>203</v>
+      </c>
+      <c r="P166" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q166">
+        <v>2</v>
+      </c>
+      <c r="R166">
+        <v>2.37</v>
+      </c>
+      <c r="S166">
+        <v>5</v>
+      </c>
+      <c r="T166">
+        <v>1.28</v>
+      </c>
+      <c r="U166">
+        <v>3.4</v>
+      </c>
+      <c r="V166">
+        <v>2.25</v>
+      </c>
+      <c r="W166">
+        <v>1.55</v>
+      </c>
+      <c r="X166">
+        <v>5.25</v>
+      </c>
+      <c r="Y166">
+        <v>1.14</v>
+      </c>
+      <c r="Z166">
+        <v>1.55</v>
+      </c>
+      <c r="AA166">
+        <v>4.33</v>
+      </c>
+      <c r="AB166">
+        <v>5.1</v>
+      </c>
+      <c r="AC166">
+        <v>1.02</v>
+      </c>
+      <c r="AD166">
+        <v>13</v>
+      </c>
+      <c r="AE166">
+        <v>1.2</v>
+      </c>
+      <c r="AF166">
+        <v>4.33</v>
+      </c>
+      <c r="AG166">
+        <v>1.57</v>
+      </c>
+      <c r="AH166">
+        <v>2.15</v>
+      </c>
+      <c r="AI166">
+        <v>1.71</v>
+      </c>
+      <c r="AJ166">
+        <v>2</v>
+      </c>
+      <c r="AK166">
+        <v>1.15</v>
+      </c>
+      <c r="AL166">
+        <v>1.21</v>
+      </c>
+      <c r="AM166">
+        <v>2.37</v>
+      </c>
+      <c r="AN166">
+        <v>1.43</v>
+      </c>
+      <c r="AO166">
+        <v>0.62</v>
+      </c>
+      <c r="AP166">
+        <v>1.53</v>
+      </c>
+      <c r="AQ166">
+        <v>0.57</v>
+      </c>
+      <c r="AR166">
+        <v>1.64</v>
+      </c>
+      <c r="AS166">
+        <v>1.43</v>
+      </c>
+      <c r="AT166">
+        <v>3.07</v>
+      </c>
+      <c r="AU166">
+        <v>7</v>
+      </c>
+      <c r="AV166">
+        <v>2</v>
+      </c>
+      <c r="AW166">
+        <v>1</v>
+      </c>
+      <c r="AX166">
+        <v>5</v>
+      </c>
+      <c r="AY166">
+        <v>8</v>
+      </c>
+      <c r="AZ166">
+        <v>7</v>
+      </c>
+      <c r="BA166">
+        <v>2</v>
+      </c>
+      <c r="BB166">
+        <v>6</v>
+      </c>
+      <c r="BC166">
+        <v>8</v>
+      </c>
+      <c r="BD166">
+        <v>1.36</v>
+      </c>
+      <c r="BE166">
+        <v>7.6</v>
+      </c>
+      <c r="BF166">
+        <v>4.3</v>
+      </c>
+      <c r="BG166">
+        <v>1.31</v>
+      </c>
+      <c r="BH166">
+        <v>3.2</v>
+      </c>
+      <c r="BI166">
+        <v>1.48</v>
+      </c>
+      <c r="BJ166">
+        <v>2.38</v>
+      </c>
+      <c r="BK166">
+        <v>1.93</v>
+      </c>
+      <c r="BL166">
+        <v>1.83</v>
+      </c>
+      <c r="BM166">
+        <v>2.34</v>
+      </c>
+      <c r="BN166">
+        <v>1.5</v>
+      </c>
+      <c r="BO166">
+        <v>3.2</v>
+      </c>
+      <c r="BP166">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="167" spans="1:68">
+      <c r="A167" s="1">
+        <v>166</v>
+      </c>
+      <c r="B167">
+        <v>7817200</v>
+      </c>
+      <c r="C167" t="s">
+        <v>68</v>
+      </c>
+      <c r="D167" t="s">
+        <v>69</v>
+      </c>
+      <c r="E167" s="2">
+        <v>45727.69791666666</v>
+      </c>
+      <c r="F167">
+        <v>6</v>
+      </c>
+      <c r="G167" t="s">
+        <v>81</v>
+      </c>
+      <c r="H167" t="s">
+        <v>79</v>
+      </c>
+      <c r="I167">
+        <v>1</v>
+      </c>
+      <c r="J167">
+        <v>0</v>
+      </c>
+      <c r="K167">
+        <v>1</v>
+      </c>
+      <c r="L167">
+        <v>2</v>
+      </c>
+      <c r="M167">
+        <v>0</v>
+      </c>
+      <c r="N167">
+        <v>2</v>
+      </c>
+      <c r="O167" t="s">
+        <v>204</v>
+      </c>
+      <c r="P167" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q167">
+        <v>1.46</v>
+      </c>
+      <c r="R167">
+        <v>3.1</v>
+      </c>
+      <c r="S167">
+        <v>9.25</v>
+      </c>
+      <c r="T167">
+        <v>1.18</v>
+      </c>
+      <c r="U167">
+        <v>4.4</v>
+      </c>
+      <c r="V167">
+        <v>1.82</v>
+      </c>
+      <c r="W167">
+        <v>1.85</v>
+      </c>
+      <c r="X167">
+        <v>3.6</v>
+      </c>
+      <c r="Y167">
+        <v>1.25</v>
+      </c>
+      <c r="Z167">
+        <v>1.1</v>
+      </c>
+      <c r="AA167">
+        <v>7</v>
+      </c>
+      <c r="AB167">
+        <v>19</v>
+      </c>
+      <c r="AC167">
+        <v>1.01</v>
+      </c>
+      <c r="AD167">
+        <v>16.5</v>
+      </c>
+      <c r="AE167">
+        <v>1.03</v>
+      </c>
+      <c r="AF167">
+        <v>7.4</v>
+      </c>
+      <c r="AG167">
+        <v>1.33</v>
+      </c>
+      <c r="AH167">
+        <v>3.1</v>
+      </c>
+      <c r="AI167">
+        <v>1.95</v>
+      </c>
+      <c r="AJ167">
+        <v>1.75</v>
+      </c>
+      <c r="AK167">
+        <v>1.02</v>
+      </c>
+      <c r="AL167">
+        <v>1.08</v>
+      </c>
+      <c r="AM167">
+        <v>5.25</v>
+      </c>
+      <c r="AN167">
+        <v>2.57</v>
+      </c>
+      <c r="AO167">
+        <v>1.85</v>
+      </c>
+      <c r="AP167">
+        <v>2.6</v>
+      </c>
+      <c r="AQ167">
+        <v>1.71</v>
+      </c>
+      <c r="AR167">
+        <v>2.54</v>
+      </c>
+      <c r="AS167">
+        <v>1.47</v>
+      </c>
+      <c r="AT167">
+        <v>4.01</v>
+      </c>
+      <c r="AU167">
+        <v>6</v>
+      </c>
+      <c r="AV167">
+        <v>2</v>
+      </c>
+      <c r="AW167">
+        <v>8</v>
+      </c>
+      <c r="AX167">
+        <v>5</v>
+      </c>
+      <c r="AY167">
+        <v>14</v>
+      </c>
+      <c r="AZ167">
+        <v>7</v>
+      </c>
+      <c r="BA167">
+        <v>7</v>
+      </c>
+      <c r="BB167">
+        <v>1</v>
+      </c>
+      <c r="BC167">
+        <v>8</v>
+      </c>
+      <c r="BD167">
+        <v>1.04</v>
+      </c>
+      <c r="BE167">
+        <v>15.5</v>
+      </c>
+      <c r="BF167">
+        <v>12</v>
+      </c>
+      <c r="BG167">
+        <v>1.16</v>
+      </c>
+      <c r="BH167">
+        <v>4.25</v>
+      </c>
+      <c r="BI167">
+        <v>1.33</v>
+      </c>
+      <c r="BJ167">
+        <v>3.07</v>
+      </c>
+      <c r="BK167">
+        <v>1.52</v>
+      </c>
+      <c r="BL167">
+        <v>2.31</v>
+      </c>
+      <c r="BM167">
+        <v>1.93</v>
+      </c>
+      <c r="BN167">
+        <v>1.83</v>
+      </c>
+      <c r="BO167">
+        <v>2.44</v>
+      </c>
+      <c r="BP167">
+        <v>1.46</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Wales Welsh Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Wales Welsh Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="286">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1233,7 +1233,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP167"/>
+  <dimension ref="A1:BP169"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1982,7 +1982,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ4">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2188,7 +2188,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ5">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -3009,7 +3009,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AQ9">
         <v>0.93</v>
@@ -3215,7 +3215,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ10">
         <v>0.93</v>
@@ -3630,7 +3630,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ12">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3833,7 +3833,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ13">
         <v>0.57</v>
@@ -4042,7 +4042,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ14">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR14">
         <v>0.82</v>
@@ -5278,7 +5278,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ20">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR20">
         <v>1.34</v>
@@ -5481,7 +5481,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AQ21">
         <v>0.4</v>
@@ -6102,7 +6102,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ24">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR24">
         <v>1.08</v>
@@ -6305,7 +6305,7 @@
         <v>2</v>
       </c>
       <c r="AP25">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ25">
         <v>1.86</v>
@@ -7129,7 +7129,7 @@
         <v>3</v>
       </c>
       <c r="AP29">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AQ29">
         <v>1.71</v>
@@ -7953,10 +7953,10 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ33">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR33">
         <v>1.47</v>
@@ -8368,7 +8368,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ35">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR35">
         <v>1.94</v>
@@ -8571,7 +8571,7 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ36">
         <v>0.4</v>
@@ -8780,7 +8780,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ37">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR37">
         <v>1.69</v>
@@ -9601,7 +9601,7 @@
         <v>3</v>
       </c>
       <c r="AP41">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AQ41">
         <v>2.31</v>
@@ -9807,7 +9807,7 @@
         <v>1.33</v>
       </c>
       <c r="AP42">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ42">
         <v>0.93</v>
@@ -10016,7 +10016,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ43">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR43">
         <v>0.99</v>
@@ -11249,7 +11249,7 @@
         <v>0</v>
       </c>
       <c r="AP49">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AQ49">
         <v>0.93</v>
@@ -11664,7 +11664,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ51">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR51">
         <v>0.9399999999999999</v>
@@ -12488,7 +12488,7 @@
         <v>2</v>
       </c>
       <c r="AQ55">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR55">
         <v>1.17</v>
@@ -13309,7 +13309,7 @@
         <v>1</v>
       </c>
       <c r="AP59">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AQ59">
         <v>1.36</v>
@@ -13721,10 +13721,10 @@
         <v>2</v>
       </c>
       <c r="AP61">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ61">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR61">
         <v>1.49</v>
@@ -14960,7 +14960,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ67">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR67">
         <v>2.85</v>
@@ -15781,7 +15781,7 @@
         <v>1.33</v>
       </c>
       <c r="AP71">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ71">
         <v>1.15</v>
@@ -15990,7 +15990,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ72">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR72">
         <v>1.05</v>
@@ -17429,7 +17429,7 @@
         <v>1.4</v>
       </c>
       <c r="AP79">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AQ79">
         <v>1.07</v>
@@ -18874,7 +18874,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ86">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR86">
         <v>1.39</v>
@@ -19901,7 +19901,7 @@
         <v>1</v>
       </c>
       <c r="AP91">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AQ91">
         <v>0.57</v>
@@ -20728,7 +20728,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ95">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR95">
         <v>2.71</v>
@@ -22579,10 +22579,10 @@
         <v>2</v>
       </c>
       <c r="AP104">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AQ104">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR104">
         <v>1.93</v>
@@ -22785,7 +22785,7 @@
         <v>2.25</v>
       </c>
       <c r="AP105">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ105">
         <v>2.31</v>
@@ -23200,7 +23200,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ107">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR107">
         <v>1.55</v>
@@ -23815,7 +23815,7 @@
         <v>1.22</v>
       </c>
       <c r="AP110">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ110">
         <v>1.36</v>
@@ -24848,7 +24848,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ115">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR115">
         <v>1.68</v>
@@ -26081,10 +26081,10 @@
         <v>1.5</v>
       </c>
       <c r="AP121">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AQ121">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR121">
         <v>1.88</v>
@@ -27111,7 +27111,7 @@
         <v>1.2</v>
       </c>
       <c r="AP126">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AQ126">
         <v>1.15</v>
@@ -27317,7 +27317,7 @@
         <v>1.8</v>
       </c>
       <c r="AP127">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ127">
         <v>1.71</v>
@@ -28350,7 +28350,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ132">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR132">
         <v>1.46</v>
@@ -29789,7 +29789,7 @@
         <v>1.91</v>
       </c>
       <c r="AP139">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ139">
         <v>1.71</v>
@@ -29995,10 +29995,10 @@
         <v>1.82</v>
       </c>
       <c r="AP140">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AQ140">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR140">
         <v>1.75</v>
@@ -30822,7 +30822,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ144">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR144">
         <v>2.6</v>
@@ -31440,7 +31440,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ147">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR147">
         <v>1.47</v>
@@ -32467,7 +32467,7 @@
         <v>2.25</v>
       </c>
       <c r="AP152">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ152">
         <v>2.31</v>
@@ -32676,7 +32676,7 @@
         <v>2</v>
       </c>
       <c r="AQ153">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR153">
         <v>1.55</v>
@@ -34324,7 +34324,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ161">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AR161">
         <v>2.54</v>
@@ -34733,7 +34733,7 @@
         <v>1.15</v>
       </c>
       <c r="AP163">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AQ163">
         <v>1.07</v>
@@ -35636,6 +35636,418 @@
       </c>
       <c r="BP167">
         <v>1.46</v>
+      </c>
+    </row>
+    <row r="168" spans="1:68">
+      <c r="A168" s="1">
+        <v>167</v>
+      </c>
+      <c r="B168">
+        <v>7817199</v>
+      </c>
+      <c r="C168" t="s">
+        <v>68</v>
+      </c>
+      <c r="D168" t="s">
+        <v>69</v>
+      </c>
+      <c r="E168" s="2">
+        <v>45730.69791666666</v>
+      </c>
+      <c r="F168">
+        <v>6</v>
+      </c>
+      <c r="G168" t="s">
+        <v>76</v>
+      </c>
+      <c r="H168" t="s">
+        <v>75</v>
+      </c>
+      <c r="I168">
+        <v>0</v>
+      </c>
+      <c r="J168">
+        <v>0</v>
+      </c>
+      <c r="K168">
+        <v>0</v>
+      </c>
+      <c r="L168">
+        <v>0</v>
+      </c>
+      <c r="M168">
+        <v>0</v>
+      </c>
+      <c r="N168">
+        <v>0</v>
+      </c>
+      <c r="O168" t="s">
+        <v>85</v>
+      </c>
+      <c r="P168" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q168">
+        <v>2.2</v>
+      </c>
+      <c r="R168">
+        <v>2.3</v>
+      </c>
+      <c r="S168">
+        <v>4.5</v>
+      </c>
+      <c r="T168">
+        <v>1.33</v>
+      </c>
+      <c r="U168">
+        <v>3.25</v>
+      </c>
+      <c r="V168">
+        <v>2.5</v>
+      </c>
+      <c r="W168">
+        <v>1.5</v>
+      </c>
+      <c r="X168">
+        <v>5.5</v>
+      </c>
+      <c r="Y168">
+        <v>1.13</v>
+      </c>
+      <c r="Z168">
+        <v>1.71</v>
+      </c>
+      <c r="AA168">
+        <v>4</v>
+      </c>
+      <c r="AB168">
+        <v>4.2</v>
+      </c>
+      <c r="AC168">
+        <v>1.01</v>
+      </c>
+      <c r="AD168">
+        <v>11</v>
+      </c>
+      <c r="AE168">
+        <v>1.14</v>
+      </c>
+      <c r="AF168">
+        <v>4.8</v>
+      </c>
+      <c r="AG168">
+        <v>1.82</v>
+      </c>
+      <c r="AH168">
+        <v>1.92</v>
+      </c>
+      <c r="AI168">
+        <v>1.67</v>
+      </c>
+      <c r="AJ168">
+        <v>2.1</v>
+      </c>
+      <c r="AK168">
+        <v>1.15</v>
+      </c>
+      <c r="AL168">
+        <v>1.2</v>
+      </c>
+      <c r="AM168">
+        <v>2.12</v>
+      </c>
+      <c r="AN168">
+        <v>2.15</v>
+      </c>
+      <c r="AO168">
+        <v>1.23</v>
+      </c>
+      <c r="AP168">
+        <v>2.07</v>
+      </c>
+      <c r="AQ168">
+        <v>1.21</v>
+      </c>
+      <c r="AR168">
+        <v>1.65</v>
+      </c>
+      <c r="AS168">
+        <v>1.25</v>
+      </c>
+      <c r="AT168">
+        <v>2.9</v>
+      </c>
+      <c r="AU168">
+        <v>6</v>
+      </c>
+      <c r="AV168">
+        <v>2</v>
+      </c>
+      <c r="AW168">
+        <v>2</v>
+      </c>
+      <c r="AX168">
+        <v>7</v>
+      </c>
+      <c r="AY168">
+        <v>8</v>
+      </c>
+      <c r="AZ168">
+        <v>9</v>
+      </c>
+      <c r="BA168">
+        <v>2</v>
+      </c>
+      <c r="BB168">
+        <v>2</v>
+      </c>
+      <c r="BC168">
+        <v>4</v>
+      </c>
+      <c r="BD168">
+        <v>1.5</v>
+      </c>
+      <c r="BE168">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF168">
+        <v>3.04</v>
+      </c>
+      <c r="BG168">
+        <v>1.37</v>
+      </c>
+      <c r="BH168">
+        <v>2.66</v>
+      </c>
+      <c r="BI168">
+        <v>1.7</v>
+      </c>
+      <c r="BJ168">
+        <v>1.98</v>
+      </c>
+      <c r="BK168">
+        <v>2.15</v>
+      </c>
+      <c r="BL168">
+        <v>1.56</v>
+      </c>
+      <c r="BM168">
+        <v>2.92</v>
+      </c>
+      <c r="BN168">
+        <v>1.31</v>
+      </c>
+      <c r="BO168">
+        <v>3.8</v>
+      </c>
+      <c r="BP168">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="169" spans="1:68">
+      <c r="A169" s="1">
+        <v>168</v>
+      </c>
+      <c r="B169">
+        <v>7817204</v>
+      </c>
+      <c r="C169" t="s">
+        <v>68</v>
+      </c>
+      <c r="D169" t="s">
+        <v>69</v>
+      </c>
+      <c r="E169" s="2">
+        <v>45731.47916666666</v>
+      </c>
+      <c r="F169">
+        <v>6</v>
+      </c>
+      <c r="G169" t="s">
+        <v>77</v>
+      </c>
+      <c r="H169" t="s">
+        <v>80</v>
+      </c>
+      <c r="I169">
+        <v>0</v>
+      </c>
+      <c r="J169">
+        <v>0</v>
+      </c>
+      <c r="K169">
+        <v>0</v>
+      </c>
+      <c r="L169">
+        <v>0</v>
+      </c>
+      <c r="M169">
+        <v>0</v>
+      </c>
+      <c r="N169">
+        <v>0</v>
+      </c>
+      <c r="O169" t="s">
+        <v>85</v>
+      </c>
+      <c r="P169" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q169">
+        <v>4.33</v>
+      </c>
+      <c r="R169">
+        <v>1.83</v>
+      </c>
+      <c r="S169">
+        <v>3</v>
+      </c>
+      <c r="T169">
+        <v>1.57</v>
+      </c>
+      <c r="U169">
+        <v>2.25</v>
+      </c>
+      <c r="V169">
+        <v>3.75</v>
+      </c>
+      <c r="W169">
+        <v>1.25</v>
+      </c>
+      <c r="X169">
+        <v>9</v>
+      </c>
+      <c r="Y169">
+        <v>1.04</v>
+      </c>
+      <c r="Z169">
+        <v>3.17</v>
+      </c>
+      <c r="AA169">
+        <v>3.47</v>
+      </c>
+      <c r="AB169">
+        <v>2.14</v>
+      </c>
+      <c r="AC169">
+        <v>1.07</v>
+      </c>
+      <c r="AD169">
+        <v>5.95</v>
+      </c>
+      <c r="AE169">
+        <v>1.5</v>
+      </c>
+      <c r="AF169">
+        <v>2.3</v>
+      </c>
+      <c r="AG169">
+        <v>2.65</v>
+      </c>
+      <c r="AH169">
+        <v>1.42</v>
+      </c>
+      <c r="AI169">
+        <v>2.25</v>
+      </c>
+      <c r="AJ169">
+        <v>1.57</v>
+      </c>
+      <c r="AK169">
+        <v>1.65</v>
+      </c>
+      <c r="AL169">
+        <v>1.34</v>
+      </c>
+      <c r="AM169">
+        <v>1.3</v>
+      </c>
+      <c r="AN169">
+        <v>1.31</v>
+      </c>
+      <c r="AO169">
+        <v>1.57</v>
+      </c>
+      <c r="AP169">
+        <v>1.29</v>
+      </c>
+      <c r="AQ169">
+        <v>1.53</v>
+      </c>
+      <c r="AR169">
+        <v>1.32</v>
+      </c>
+      <c r="AS169">
+        <v>1.25</v>
+      </c>
+      <c r="AT169">
+        <v>2.57</v>
+      </c>
+      <c r="AU169">
+        <v>6</v>
+      </c>
+      <c r="AV169">
+        <v>4</v>
+      </c>
+      <c r="AW169">
+        <v>4</v>
+      </c>
+      <c r="AX169">
+        <v>5</v>
+      </c>
+      <c r="AY169">
+        <v>10</v>
+      </c>
+      <c r="AZ169">
+        <v>9</v>
+      </c>
+      <c r="BA169">
+        <v>6</v>
+      </c>
+      <c r="BB169">
+        <v>1</v>
+      </c>
+      <c r="BC169">
+        <v>7</v>
+      </c>
+      <c r="BD169">
+        <v>2.45</v>
+      </c>
+      <c r="BE169">
+        <v>6.1</v>
+      </c>
+      <c r="BF169">
+        <v>1.83</v>
+      </c>
+      <c r="BG169">
+        <v>1.43</v>
+      </c>
+      <c r="BH169">
+        <v>2.62</v>
+      </c>
+      <c r="BI169">
+        <v>1.74</v>
+      </c>
+      <c r="BJ169">
+        <v>2.01</v>
+      </c>
+      <c r="BK169">
+        <v>2.19</v>
+      </c>
+      <c r="BL169">
+        <v>1.62</v>
+      </c>
+      <c r="BM169">
+        <v>2.87</v>
+      </c>
+      <c r="BN169">
+        <v>1.37</v>
+      </c>
+      <c r="BO169">
+        <v>3.92</v>
+      </c>
+      <c r="BP169">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Wales Welsh Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Wales Welsh Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="293">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -631,6 +631,15 @@
     <t>['45+1', '90+4']</t>
   </si>
   <si>
+    <t>['33', '50', '57', '63', '74']</t>
+  </si>
+  <si>
+    <t>['57', '72']</t>
+  </si>
+  <si>
+    <t>['17', '40', '89']</t>
+  </si>
+  <si>
     <t>['45+2']</t>
   </si>
   <si>
@@ -872,6 +881,18 @@
   </si>
   <si>
     <t>['51', '75']</t>
+  </si>
+  <si>
+    <t>['22', '70']</t>
+  </si>
+  <si>
+    <t>['20', '43', '67']</t>
+  </si>
+  <si>
+    <t>['4', '33', '50', '52', '66', '78']</t>
+  </si>
+  <si>
+    <t>['7', '81']</t>
   </si>
 </sst>
 </file>
@@ -1233,7 +1254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP169"/>
+  <dimension ref="A1:BP175"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1489,7 +1510,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q2">
         <v>1.83</v>
@@ -1567,7 +1588,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ2">
         <v>0.4</v>
@@ -1776,7 +1797,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ3">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1901,7 +1922,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -1979,7 +2000,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ4">
         <v>1.21</v>
@@ -2313,7 +2334,7 @@
         <v>85</v>
       </c>
       <c r="P6" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q6">
         <v>4</v>
@@ -2394,7 +2415,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ6">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2519,7 +2540,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q7">
         <v>11</v>
@@ -2597,10 +2618,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ7">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AR7">
         <v>1.59</v>
@@ -2803,10 +2824,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ8">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3218,7 +3239,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ10">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3343,7 +3364,7 @@
         <v>89</v>
       </c>
       <c r="P11" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q11">
         <v>3.6</v>
@@ -3421,10 +3442,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ11">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3549,7 +3570,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q12">
         <v>2.9</v>
@@ -3627,7 +3648,7 @@
         <v>3</v>
       </c>
       <c r="AP12">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AQ12">
         <v>1.53</v>
@@ -3961,7 +3982,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q14">
         <v>4.33</v>
@@ -4245,10 +4266,10 @@
         <v>3</v>
       </c>
       <c r="AP15">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ15">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4373,7 +4394,7 @@
         <v>85</v>
       </c>
       <c r="P16" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q16">
         <v>2.63</v>
@@ -4451,7 +4472,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ16">
         <v>1.71</v>
@@ -4657,10 +4678,10 @@
         <v>1</v>
       </c>
       <c r="AP17">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ17">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR17">
         <v>0.68</v>
@@ -4785,7 +4806,7 @@
         <v>94</v>
       </c>
       <c r="P18" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q18">
         <v>3</v>
@@ -4991,7 +5012,7 @@
         <v>85</v>
       </c>
       <c r="P19" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q19">
         <v>4.75</v>
@@ -5069,10 +5090,10 @@
         <v>1</v>
       </c>
       <c r="AP19">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ19">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR19">
         <v>1.46</v>
@@ -5275,7 +5296,7 @@
         <v>3</v>
       </c>
       <c r="AP20">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ20">
         <v>1.53</v>
@@ -5687,10 +5708,10 @@
         <v>1</v>
       </c>
       <c r="AP22">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AQ22">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR22">
         <v>1.22</v>
@@ -5893,7 +5914,7 @@
         <v>2</v>
       </c>
       <c r="AP23">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ23">
         <v>0.93</v>
@@ -6021,7 +6042,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6099,7 +6120,7 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AQ24">
         <v>1.21</v>
@@ -6227,7 +6248,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q25">
         <v>3.2</v>
@@ -6308,7 +6329,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ25">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AR25">
         <v>1.81</v>
@@ -6433,7 +6454,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -6639,7 +6660,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q27">
         <v>5.5</v>
@@ -6720,7 +6741,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ27">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR27">
         <v>0.89</v>
@@ -7335,10 +7356,10 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ30">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR30">
         <v>1.93</v>
@@ -7463,7 +7484,7 @@
         <v>85</v>
       </c>
       <c r="P31" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q31">
         <v>13</v>
@@ -7541,10 +7562,10 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ31">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AR31">
         <v>1.46</v>
@@ -7669,7 +7690,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q32">
         <v>1.83</v>
@@ -7750,7 +7771,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ32">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR32">
         <v>1.41</v>
@@ -8081,7 +8102,7 @@
         <v>85</v>
       </c>
       <c r="P34" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q34">
         <v>3</v>
@@ -8159,7 +8180,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ34">
         <v>0.57</v>
@@ -8365,7 +8386,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ35">
         <v>1.21</v>
@@ -8777,7 +8798,7 @@
         <v>2.33</v>
       </c>
       <c r="AP37">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ37">
         <v>1.53</v>
@@ -8986,7 +9007,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ38">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR38">
         <v>3.26</v>
@@ -9111,7 +9132,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q39">
         <v>1.83</v>
@@ -9189,10 +9210,10 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AQ39">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR39">
         <v>1.1</v>
@@ -9398,7 +9419,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ40">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AR40">
         <v>1.48</v>
@@ -9523,7 +9544,7 @@
         <v>110</v>
       </c>
       <c r="P41" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q41">
         <v>7</v>
@@ -9604,7 +9625,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ41">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AR41">
         <v>2.47</v>
@@ -9729,7 +9750,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q42">
         <v>2.6</v>
@@ -9935,7 +9956,7 @@
         <v>85</v>
       </c>
       <c r="P43" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q43">
         <v>3.75</v>
@@ -10013,7 +10034,7 @@
         <v>1.75</v>
       </c>
       <c r="AP43">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ43">
         <v>1.53</v>
@@ -10219,10 +10240,10 @@
         <v>2.33</v>
       </c>
       <c r="AP44">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ44">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR44">
         <v>1.05</v>
@@ -10759,7 +10780,7 @@
         <v>115</v>
       </c>
       <c r="P47" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q47">
         <v>2.25</v>
@@ -10965,7 +10986,7 @@
         <v>116</v>
       </c>
       <c r="P48" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q48">
         <v>2.5</v>
@@ -11043,10 +11064,10 @@
         <v>1</v>
       </c>
       <c r="AP48">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ48">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR48">
         <v>1.21</v>
@@ -11252,7 +11273,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ49">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR49">
         <v>2.19</v>
@@ -11377,7 +11398,7 @@
         <v>117</v>
       </c>
       <c r="P50" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q50">
         <v>1.67</v>
@@ -11458,7 +11479,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ50">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR50">
         <v>3.27</v>
@@ -11583,7 +11604,7 @@
         <v>118</v>
       </c>
       <c r="P51" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q51">
         <v>6</v>
@@ -11661,7 +11682,7 @@
         <v>2.4</v>
       </c>
       <c r="AP51">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ51">
         <v>1.21</v>
@@ -11789,7 +11810,7 @@
         <v>119</v>
       </c>
       <c r="P52" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -11867,7 +11888,7 @@
         <v>1.33</v>
       </c>
       <c r="AP52">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ52">
         <v>1.71</v>
@@ -12201,7 +12222,7 @@
         <v>114</v>
       </c>
       <c r="P54" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q54">
         <v>9.5</v>
@@ -12279,10 +12300,10 @@
         <v>2</v>
       </c>
       <c r="AP54">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ54">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AR54">
         <v>1.83</v>
@@ -12485,7 +12506,7 @@
         <v>2.5</v>
       </c>
       <c r="AP55">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ55">
         <v>1.21</v>
@@ -12613,7 +12634,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q56">
         <v>7</v>
@@ -12694,7 +12715,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ56">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR56">
         <v>1.02</v>
@@ -12897,10 +12918,10 @@
         <v>2.5</v>
       </c>
       <c r="AP57">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ57">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AR57">
         <v>1.7</v>
@@ -13103,10 +13124,10 @@
         <v>1.75</v>
       </c>
       <c r="AP58">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AQ58">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR58">
         <v>1.13</v>
@@ -13312,7 +13333,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ59">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR59">
         <v>2.07</v>
@@ -13437,7 +13458,7 @@
         <v>125</v>
       </c>
       <c r="P60" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q60">
         <v>2.3</v>
@@ -13515,7 +13536,7 @@
         <v>1</v>
       </c>
       <c r="AP60">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ60">
         <v>0.57</v>
@@ -13643,7 +13664,7 @@
         <v>85</v>
       </c>
       <c r="P61" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q61">
         <v>2.88</v>
@@ -14055,7 +14076,7 @@
         <v>87</v>
       </c>
       <c r="P63" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q63">
         <v>2.63</v>
@@ -14133,7 +14154,7 @@
         <v>1.75</v>
       </c>
       <c r="AP63">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ63">
         <v>1.71</v>
@@ -14261,7 +14282,7 @@
         <v>127</v>
       </c>
       <c r="P64" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q64">
         <v>1.42</v>
@@ -14545,10 +14566,10 @@
         <v>1.4</v>
       </c>
       <c r="AP65">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ65">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR65">
         <v>1.25</v>
@@ -14673,7 +14694,7 @@
         <v>128</v>
       </c>
       <c r="P66" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -14751,10 +14772,10 @@
         <v>1.5</v>
       </c>
       <c r="AP66">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ66">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR66">
         <v>1.56</v>
@@ -15166,7 +15187,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ68">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR68">
         <v>1.7</v>
@@ -15291,7 +15312,7 @@
         <v>131</v>
       </c>
       <c r="P69" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15369,7 +15390,7 @@
         <v>1.2</v>
       </c>
       <c r="AP69">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AQ69">
         <v>0.93</v>
@@ -15497,7 +15518,7 @@
         <v>85</v>
       </c>
       <c r="P70" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q70">
         <v>9</v>
@@ -15575,10 +15596,10 @@
         <v>2.6</v>
       </c>
       <c r="AP70">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ70">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AR70">
         <v>0.96</v>
@@ -15784,7 +15805,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ71">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR71">
         <v>1.39</v>
@@ -15909,7 +15930,7 @@
         <v>132</v>
       </c>
       <c r="P72" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q72">
         <v>7</v>
@@ -16115,7 +16136,7 @@
         <v>133</v>
       </c>
       <c r="P73" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q73">
         <v>1.73</v>
@@ -16193,7 +16214,7 @@
         <v>0</v>
       </c>
       <c r="AP73">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AQ73">
         <v>0.4</v>
@@ -16399,10 +16420,10 @@
         <v>2.67</v>
       </c>
       <c r="AP74">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ74">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AR74">
         <v>1.22</v>
@@ -16527,7 +16548,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16605,10 +16626,10 @@
         <v>0.83</v>
       </c>
       <c r="AP75">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ75">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR75">
         <v>1.8</v>
@@ -16939,7 +16960,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q77">
         <v>2.5</v>
@@ -17017,7 +17038,7 @@
         <v>1.5</v>
       </c>
       <c r="AP77">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ77">
         <v>0.93</v>
@@ -17145,7 +17166,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17223,10 +17244,10 @@
         <v>1.14</v>
       </c>
       <c r="AP78">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ78">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR78">
         <v>1.54</v>
@@ -17351,7 +17372,7 @@
         <v>139</v>
       </c>
       <c r="P79" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q79">
         <v>2.75</v>
@@ -17432,7 +17453,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ79">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR79">
         <v>1.99</v>
@@ -17635,7 +17656,7 @@
         <v>2.17</v>
       </c>
       <c r="AP80">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ80">
         <v>1.71</v>
@@ -17763,7 +17784,7 @@
         <v>140</v>
       </c>
       <c r="P81" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q81">
         <v>19</v>
@@ -17841,10 +17862,10 @@
         <v>2.25</v>
       </c>
       <c r="AP81">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ81">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AR81">
         <v>0.87</v>
@@ -18050,7 +18071,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ82">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR82">
         <v>1.39</v>
@@ -18175,7 +18196,7 @@
         <v>142</v>
       </c>
       <c r="P83" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18256,7 +18277,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ83">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AR83">
         <v>1.47</v>
@@ -18381,7 +18402,7 @@
         <v>143</v>
       </c>
       <c r="P84" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q84">
         <v>11</v>
@@ -18462,7 +18483,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ84">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AR84">
         <v>1.66</v>
@@ -18587,7 +18608,7 @@
         <v>144</v>
       </c>
       <c r="P85" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q85">
         <v>4.75</v>
@@ -18665,10 +18686,10 @@
         <v>2.43</v>
       </c>
       <c r="AP85">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AQ85">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AR85">
         <v>1.4</v>
@@ -19077,7 +19098,7 @@
         <v>1.17</v>
       </c>
       <c r="AP87">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ87">
         <v>0.57</v>
@@ -19283,10 +19304,10 @@
         <v>1.33</v>
       </c>
       <c r="AP88">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ88">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR88">
         <v>1.83</v>
@@ -19617,7 +19638,7 @@
         <v>148</v>
       </c>
       <c r="P90" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q90">
         <v>4.75</v>
@@ -19695,7 +19716,7 @@
         <v>1.29</v>
       </c>
       <c r="AP90">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ90">
         <v>0.93</v>
@@ -20029,7 +20050,7 @@
         <v>150</v>
       </c>
       <c r="P92" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q92">
         <v>2.88</v>
@@ -20110,7 +20131,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ92">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR92">
         <v>1.58</v>
@@ -20441,7 +20462,7 @@
         <v>151</v>
       </c>
       <c r="P94" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q94">
         <v>2.88</v>
@@ -20519,10 +20540,10 @@
         <v>1.29</v>
       </c>
       <c r="AP94">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ94">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR94">
         <v>1.18</v>
@@ -20853,7 +20874,7 @@
         <v>153</v>
       </c>
       <c r="P96" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q96">
         <v>11</v>
@@ -20934,7 +20955,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ96">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AR96">
         <v>1.34</v>
@@ -21137,7 +21158,7 @@
         <v>0.38</v>
       </c>
       <c r="AP97">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ97">
         <v>0.4</v>
@@ -21343,10 +21364,10 @@
         <v>0.5</v>
       </c>
       <c r="AP98">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ98">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR98">
         <v>1.69</v>
@@ -21549,10 +21570,10 @@
         <v>1.25</v>
       </c>
       <c r="AP99">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ99">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR99">
         <v>1.39</v>
@@ -21677,7 +21698,7 @@
         <v>156</v>
       </c>
       <c r="P100" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q100">
         <v>1.73</v>
@@ -21758,7 +21779,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ100">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AR100">
         <v>2.55</v>
@@ -21883,7 +21904,7 @@
         <v>85</v>
       </c>
       <c r="P101" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q101">
         <v>3.4</v>
@@ -21961,10 +21982,10 @@
         <v>1.13</v>
       </c>
       <c r="AP101">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ101">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR101">
         <v>1.77</v>
@@ -22089,7 +22110,7 @@
         <v>157</v>
       </c>
       <c r="P102" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q102">
         <v>3</v>
@@ -22295,7 +22316,7 @@
         <v>158</v>
       </c>
       <c r="P103" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22788,7 +22809,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ105">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AR105">
         <v>1.31</v>
@@ -22991,7 +23012,7 @@
         <v>0.33</v>
       </c>
       <c r="AP106">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ106">
         <v>0.4</v>
@@ -23119,7 +23140,7 @@
         <v>162</v>
       </c>
       <c r="P107" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q107">
         <v>3</v>
@@ -23325,7 +23346,7 @@
         <v>163</v>
       </c>
       <c r="P108" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q108">
         <v>2.75</v>
@@ -23403,10 +23424,10 @@
         <v>1.38</v>
       </c>
       <c r="AP108">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AQ108">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR108">
         <v>1.33</v>
@@ -23609,7 +23630,7 @@
         <v>0.88</v>
       </c>
       <c r="AP109">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ109">
         <v>0.57</v>
@@ -23737,7 +23758,7 @@
         <v>165</v>
       </c>
       <c r="P110" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q110">
         <v>2.4</v>
@@ -23818,7 +23839,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ110">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR110">
         <v>1.27</v>
@@ -24021,7 +24042,7 @@
         <v>2</v>
       </c>
       <c r="AP111">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ111">
         <v>1.71</v>
@@ -24149,7 +24170,7 @@
         <v>167</v>
       </c>
       <c r="P112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q112">
         <v>1.4</v>
@@ -24230,7 +24251,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ112">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR112">
         <v>2.55</v>
@@ -24355,7 +24376,7 @@
         <v>168</v>
       </c>
       <c r="P113" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q113">
         <v>4.75</v>
@@ -24436,7 +24457,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ113">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AR113">
         <v>1.49</v>
@@ -24561,7 +24582,7 @@
         <v>98</v>
       </c>
       <c r="P114" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q114">
         <v>2</v>
@@ -24639,10 +24660,10 @@
         <v>0.38</v>
       </c>
       <c r="AP114">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ114">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR114">
         <v>1.45</v>
@@ -24767,7 +24788,7 @@
         <v>85</v>
       </c>
       <c r="P115" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q115">
         <v>3.75</v>
@@ -24845,7 +24866,7 @@
         <v>1.78</v>
       </c>
       <c r="AP115">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ115">
         <v>1.53</v>
@@ -25051,10 +25072,10 @@
         <v>1.22</v>
       </c>
       <c r="AP116">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ116">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR116">
         <v>1.04</v>
@@ -25179,7 +25200,7 @@
         <v>169</v>
       </c>
       <c r="P117" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25385,7 +25406,7 @@
         <v>170</v>
       </c>
       <c r="P118" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q118">
         <v>6</v>
@@ -25463,10 +25484,10 @@
         <v>2</v>
       </c>
       <c r="AP118">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AQ118">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AR118">
         <v>1.4</v>
@@ -25672,7 +25693,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ119">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR119">
         <v>1.37</v>
@@ -25878,7 +25899,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ120">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR120">
         <v>2.7</v>
@@ -26003,7 +26024,7 @@
         <v>172</v>
       </c>
       <c r="P121" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q121">
         <v>2.1</v>
@@ -26287,7 +26308,7 @@
         <v>1</v>
       </c>
       <c r="AP122">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ122">
         <v>0.93</v>
@@ -26493,7 +26514,7 @@
         <v>0.3</v>
       </c>
       <c r="AP123">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ123">
         <v>0.4</v>
@@ -26621,7 +26642,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q124">
         <v>1.44</v>
@@ -26905,10 +26926,10 @@
         <v>0.67</v>
       </c>
       <c r="AP125">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ125">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR125">
         <v>1.41</v>
@@ -27114,7 +27135,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ126">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR126">
         <v>1.81</v>
@@ -27239,7 +27260,7 @@
         <v>85</v>
       </c>
       <c r="P127" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q127">
         <v>2.3</v>
@@ -27445,7 +27466,7 @@
         <v>139</v>
       </c>
       <c r="P128" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q128">
         <v>2.75</v>
@@ -27523,10 +27544,10 @@
         <v>0.6</v>
       </c>
       <c r="AP128">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ128">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR128">
         <v>1.06</v>
@@ -27729,7 +27750,7 @@
         <v>0.7</v>
       </c>
       <c r="AP129">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AQ129">
         <v>0.57</v>
@@ -27857,7 +27878,7 @@
         <v>85</v>
       </c>
       <c r="P130" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q130">
         <v>5.5</v>
@@ -27935,10 +27956,10 @@
         <v>2.1</v>
       </c>
       <c r="AP130">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ130">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AR130">
         <v>1.5</v>
@@ -28063,7 +28084,7 @@
         <v>177</v>
       </c>
       <c r="P131" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q131">
         <v>7</v>
@@ -28141,10 +28162,10 @@
         <v>2.3</v>
       </c>
       <c r="AP131">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ131">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AR131">
         <v>1.63</v>
@@ -28475,7 +28496,7 @@
         <v>85</v>
       </c>
       <c r="P133" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q133">
         <v>2.75</v>
@@ -28556,7 +28577,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ133">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR133">
         <v>1.54</v>
@@ -28681,7 +28702,7 @@
         <v>179</v>
       </c>
       <c r="P134" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q134">
         <v>4.75</v>
@@ -28759,10 +28780,10 @@
         <v>2.36</v>
       </c>
       <c r="AP134">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ134">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AR134">
         <v>1.5</v>
@@ -28887,7 +28908,7 @@
         <v>180</v>
       </c>
       <c r="P135" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q135">
         <v>2.5</v>
@@ -28965,10 +28986,10 @@
         <v>0.82</v>
       </c>
       <c r="AP135">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ135">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR135">
         <v>1.57</v>
@@ -29093,7 +29114,7 @@
         <v>120</v>
       </c>
       <c r="P136" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q136">
         <v>3.75</v>
@@ -29171,10 +29192,10 @@
         <v>1.09</v>
       </c>
       <c r="AP136">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ136">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR136">
         <v>1.08</v>
@@ -29299,7 +29320,7 @@
         <v>181</v>
       </c>
       <c r="P137" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q137">
         <v>2.38</v>
@@ -29377,10 +29398,10 @@
         <v>1.36</v>
       </c>
       <c r="AP137">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ137">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR137">
         <v>1.51</v>
@@ -29583,10 +29604,10 @@
         <v>1.09</v>
       </c>
       <c r="AP138">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ138">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR138">
         <v>1.74</v>
@@ -29711,7 +29732,7 @@
         <v>183</v>
       </c>
       <c r="P139" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q139">
         <v>2.7</v>
@@ -30535,7 +30556,7 @@
         <v>186</v>
       </c>
       <c r="P143" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q143">
         <v>2.1</v>
@@ -30741,7 +30762,7 @@
         <v>187</v>
       </c>
       <c r="P144" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q144">
         <v>1.53</v>
@@ -31025,7 +31046,7 @@
         <v>0.5</v>
       </c>
       <c r="AP145">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ145">
         <v>0.4</v>
@@ -31234,7 +31255,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ146">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AR146">
         <v>2.6</v>
@@ -31437,7 +31458,7 @@
         <v>1.75</v>
       </c>
       <c r="AP147">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AQ147">
         <v>1.53</v>
@@ -31643,10 +31664,10 @@
         <v>1.25</v>
       </c>
       <c r="AP148">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ148">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR148">
         <v>1.47</v>
@@ -31852,7 +31873,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ149">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR149">
         <v>1.53</v>
@@ -32055,10 +32076,10 @@
         <v>1.25</v>
       </c>
       <c r="AP150">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ150">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR150">
         <v>1.56</v>
@@ -32183,7 +32204,7 @@
         <v>85</v>
       </c>
       <c r="P151" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q151">
         <v>8</v>
@@ -32261,10 +32282,10 @@
         <v>2.18</v>
       </c>
       <c r="AP151">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AQ151">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AR151">
         <v>1.4</v>
@@ -32389,7 +32410,7 @@
         <v>85</v>
       </c>
       <c r="P152" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q152">
         <v>6</v>
@@ -32470,7 +32491,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ152">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AR152">
         <v>1.39</v>
@@ -32673,7 +32694,7 @@
         <v>1.33</v>
       </c>
       <c r="AP153">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ153">
         <v>1.21</v>
@@ -32879,7 +32900,7 @@
         <v>0.75</v>
       </c>
       <c r="AP154">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AQ154">
         <v>0.93</v>
@@ -33007,7 +33028,7 @@
         <v>193</v>
       </c>
       <c r="P155" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q155">
         <v>3.25</v>
@@ -33085,10 +33106,10 @@
         <v>2</v>
       </c>
       <c r="AP155">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AQ155">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AR155">
         <v>1.35</v>
@@ -33213,7 +33234,7 @@
         <v>85</v>
       </c>
       <c r="P156" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q156">
         <v>2.88</v>
@@ -33294,7 +33315,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ156">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AR156">
         <v>1.42</v>
@@ -33419,7 +33440,7 @@
         <v>194</v>
       </c>
       <c r="P157" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q157">
         <v>2.63</v>
@@ -33497,10 +33518,10 @@
         <v>1</v>
       </c>
       <c r="AP157">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AQ157">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AR157">
         <v>1.81</v>
@@ -33625,7 +33646,7 @@
         <v>195</v>
       </c>
       <c r="P158" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q158">
         <v>3</v>
@@ -33706,7 +33727,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ158">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AR158">
         <v>1.4</v>
@@ -34037,7 +34058,7 @@
         <v>197</v>
       </c>
       <c r="P160" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q160">
         <v>2.88</v>
@@ -34115,7 +34136,7 @@
         <v>0.58</v>
       </c>
       <c r="AP160">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AQ160">
         <v>0.57</v>
@@ -34449,7 +34470,7 @@
         <v>199</v>
       </c>
       <c r="P162" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q162">
         <v>3</v>
@@ -34527,7 +34548,7 @@
         <v>2</v>
       </c>
       <c r="AP162">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ162">
         <v>1.71</v>
@@ -34655,7 +34676,7 @@
         <v>200</v>
       </c>
       <c r="P163" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q163">
         <v>2.2</v>
@@ -34736,7 +34757,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ163">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR163">
         <v>1.65</v>
@@ -35067,7 +35088,7 @@
         <v>202</v>
       </c>
       <c r="P165" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q165">
         <v>1.83</v>
@@ -36048,6 +36069,1242 @@
       </c>
       <c r="BP169">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="170" spans="1:68">
+      <c r="A170" s="1">
+        <v>169</v>
+      </c>
+      <c r="B170">
+        <v>7817205</v>
+      </c>
+      <c r="C170" t="s">
+        <v>68</v>
+      </c>
+      <c r="D170" t="s">
+        <v>69</v>
+      </c>
+      <c r="E170" s="2">
+        <v>45737.69791666666</v>
+      </c>
+      <c r="F170">
+        <v>7</v>
+      </c>
+      <c r="G170" t="s">
+        <v>79</v>
+      </c>
+      <c r="H170" t="s">
+        <v>77</v>
+      </c>
+      <c r="I170">
+        <v>1</v>
+      </c>
+      <c r="J170">
+        <v>0</v>
+      </c>
+      <c r="K170">
+        <v>1</v>
+      </c>
+      <c r="L170">
+        <v>5</v>
+      </c>
+      <c r="M170">
+        <v>0</v>
+      </c>
+      <c r="N170">
+        <v>5</v>
+      </c>
+      <c r="O170" t="s">
+        <v>205</v>
+      </c>
+      <c r="P170" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q170">
+        <v>2.75</v>
+      </c>
+      <c r="R170">
+        <v>2.05</v>
+      </c>
+      <c r="S170">
+        <v>3.6</v>
+      </c>
+      <c r="T170">
+        <v>1.37</v>
+      </c>
+      <c r="U170">
+        <v>2.8</v>
+      </c>
+      <c r="V170">
+        <v>2.6</v>
+      </c>
+      <c r="W170">
+        <v>1.44</v>
+      </c>
+      <c r="X170">
+        <v>6.5</v>
+      </c>
+      <c r="Y170">
+        <v>1.1</v>
+      </c>
+      <c r="Z170">
+        <v>2.51</v>
+      </c>
+      <c r="AA170">
+        <v>3.6</v>
+      </c>
+      <c r="AB170">
+        <v>2.54</v>
+      </c>
+      <c r="AC170">
+        <v>1.06</v>
+      </c>
+      <c r="AD170">
+        <v>8.75</v>
+      </c>
+      <c r="AE170">
+        <v>1.27</v>
+      </c>
+      <c r="AF170">
+        <v>3.4</v>
+      </c>
+      <c r="AG170">
+        <v>1.82</v>
+      </c>
+      <c r="AH170">
+        <v>1.92</v>
+      </c>
+      <c r="AI170">
+        <v>1.68</v>
+      </c>
+      <c r="AJ170">
+        <v>2.05</v>
+      </c>
+      <c r="AK170">
+        <v>1.32</v>
+      </c>
+      <c r="AL170">
+        <v>1.32</v>
+      </c>
+      <c r="AM170">
+        <v>1.63</v>
+      </c>
+      <c r="AN170">
+        <v>1.21</v>
+      </c>
+      <c r="AO170">
+        <v>1.07</v>
+      </c>
+      <c r="AP170">
+        <v>1.33</v>
+      </c>
+      <c r="AQ170">
+        <v>1</v>
+      </c>
+      <c r="AR170">
+        <v>1.34</v>
+      </c>
+      <c r="AS170">
+        <v>1.32</v>
+      </c>
+      <c r="AT170">
+        <v>2.66</v>
+      </c>
+      <c r="AU170">
+        <v>7</v>
+      </c>
+      <c r="AV170">
+        <v>0</v>
+      </c>
+      <c r="AW170">
+        <v>5</v>
+      </c>
+      <c r="AX170">
+        <v>5</v>
+      </c>
+      <c r="AY170">
+        <v>12</v>
+      </c>
+      <c r="AZ170">
+        <v>5</v>
+      </c>
+      <c r="BA170">
+        <v>4</v>
+      </c>
+      <c r="BB170">
+        <v>2</v>
+      </c>
+      <c r="BC170">
+        <v>6</v>
+      </c>
+      <c r="BD170">
+        <v>2.2</v>
+      </c>
+      <c r="BE170">
+        <v>7</v>
+      </c>
+      <c r="BF170">
+        <v>1.95</v>
+      </c>
+      <c r="BG170">
+        <v>1.36</v>
+      </c>
+      <c r="BH170">
+        <v>2.9</v>
+      </c>
+      <c r="BI170">
+        <v>1.57</v>
+      </c>
+      <c r="BJ170">
+        <v>2.2</v>
+      </c>
+      <c r="BK170">
+        <v>1.98</v>
+      </c>
+      <c r="BL170">
+        <v>1.78</v>
+      </c>
+      <c r="BM170">
+        <v>2.48</v>
+      </c>
+      <c r="BN170">
+        <v>1.45</v>
+      </c>
+      <c r="BO170">
+        <v>3.3</v>
+      </c>
+      <c r="BP170">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="171" spans="1:68">
+      <c r="A171" s="1">
+        <v>170</v>
+      </c>
+      <c r="B171">
+        <v>7817206</v>
+      </c>
+      <c r="C171" t="s">
+        <v>68</v>
+      </c>
+      <c r="D171" t="s">
+        <v>69</v>
+      </c>
+      <c r="E171" s="2">
+        <v>45737.69791666666</v>
+      </c>
+      <c r="F171">
+        <v>7</v>
+      </c>
+      <c r="G171" t="s">
+        <v>80</v>
+      </c>
+      <c r="H171" t="s">
+        <v>76</v>
+      </c>
+      <c r="I171">
+        <v>1</v>
+      </c>
+      <c r="J171">
+        <v>1</v>
+      </c>
+      <c r="K171">
+        <v>2</v>
+      </c>
+      <c r="L171">
+        <v>1</v>
+      </c>
+      <c r="M171">
+        <v>2</v>
+      </c>
+      <c r="N171">
+        <v>3</v>
+      </c>
+      <c r="O171" t="s">
+        <v>97</v>
+      </c>
+      <c r="P171" t="s">
+        <v>289</v>
+      </c>
+      <c r="Q171">
+        <v>3</v>
+      </c>
+      <c r="R171">
+        <v>1.93</v>
+      </c>
+      <c r="S171">
+        <v>3.7</v>
+      </c>
+      <c r="T171">
+        <v>1.49</v>
+      </c>
+      <c r="U171">
+        <v>2.4</v>
+      </c>
+      <c r="V171">
+        <v>3.2</v>
+      </c>
+      <c r="W171">
+        <v>1.31</v>
+      </c>
+      <c r="X171">
+        <v>8.75</v>
+      </c>
+      <c r="Y171">
+        <v>1.06</v>
+      </c>
+      <c r="Z171">
+        <v>2.38</v>
+      </c>
+      <c r="AA171">
+        <v>3</v>
+      </c>
+      <c r="AB171">
+        <v>3.17</v>
+      </c>
+      <c r="AC171">
+        <v>1.09</v>
+      </c>
+      <c r="AD171">
+        <v>6.75</v>
+      </c>
+      <c r="AE171">
+        <v>1.42</v>
+      </c>
+      <c r="AF171">
+        <v>2.65</v>
+      </c>
+      <c r="AG171">
+        <v>2.2</v>
+      </c>
+      <c r="AH171">
+        <v>1.55</v>
+      </c>
+      <c r="AI171">
+        <v>1.95</v>
+      </c>
+      <c r="AJ171">
+        <v>1.75</v>
+      </c>
+      <c r="AK171">
+        <v>1.34</v>
+      </c>
+      <c r="AL171">
+        <v>1.36</v>
+      </c>
+      <c r="AM171">
+        <v>1.55</v>
+      </c>
+      <c r="AN171">
+        <v>2</v>
+      </c>
+      <c r="AO171">
+        <v>1.86</v>
+      </c>
+      <c r="AP171">
+        <v>1.86</v>
+      </c>
+      <c r="AQ171">
+        <v>1.93</v>
+      </c>
+      <c r="AR171">
+        <v>1.54</v>
+      </c>
+      <c r="AS171">
+        <v>1.48</v>
+      </c>
+      <c r="AT171">
+        <v>3.02</v>
+      </c>
+      <c r="AU171">
+        <v>5</v>
+      </c>
+      <c r="AV171">
+        <v>3</v>
+      </c>
+      <c r="AW171">
+        <v>5</v>
+      </c>
+      <c r="AX171">
+        <v>2</v>
+      </c>
+      <c r="AY171">
+        <v>10</v>
+      </c>
+      <c r="AZ171">
+        <v>5</v>
+      </c>
+      <c r="BA171">
+        <v>5</v>
+      </c>
+      <c r="BB171">
+        <v>4</v>
+      </c>
+      <c r="BC171">
+        <v>9</v>
+      </c>
+      <c r="BD171">
+        <v>1.73</v>
+      </c>
+      <c r="BE171">
+        <v>7.5</v>
+      </c>
+      <c r="BF171">
+        <v>2.47</v>
+      </c>
+      <c r="BG171">
+        <v>1.54</v>
+      </c>
+      <c r="BH171">
+        <v>2.19</v>
+      </c>
+      <c r="BI171">
+        <v>1.98</v>
+      </c>
+      <c r="BJ171">
+        <v>1.7</v>
+      </c>
+      <c r="BK171">
+        <v>2.62</v>
+      </c>
+      <c r="BL171">
+        <v>1.38</v>
+      </c>
+      <c r="BM171">
+        <v>3.74</v>
+      </c>
+      <c r="BN171">
+        <v>1.19</v>
+      </c>
+      <c r="BO171">
+        <v>4.75</v>
+      </c>
+      <c r="BP171">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="172" spans="1:68">
+      <c r="A172" s="1">
+        <v>171</v>
+      </c>
+      <c r="B172">
+        <v>7817207</v>
+      </c>
+      <c r="C172" t="s">
+        <v>68</v>
+      </c>
+      <c r="D172" t="s">
+        <v>69</v>
+      </c>
+      <c r="E172" s="2">
+        <v>45737.69791666666</v>
+      </c>
+      <c r="F172">
+        <v>7</v>
+      </c>
+      <c r="G172" t="s">
+        <v>70</v>
+      </c>
+      <c r="H172" t="s">
+        <v>73</v>
+      </c>
+      <c r="I172">
+        <v>0</v>
+      </c>
+      <c r="J172">
+        <v>2</v>
+      </c>
+      <c r="K172">
+        <v>2</v>
+      </c>
+      <c r="L172">
+        <v>2</v>
+      </c>
+      <c r="M172">
+        <v>3</v>
+      </c>
+      <c r="N172">
+        <v>5</v>
+      </c>
+      <c r="O172" t="s">
+        <v>206</v>
+      </c>
+      <c r="P172" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q172">
+        <v>4</v>
+      </c>
+      <c r="R172">
+        <v>2.1</v>
+      </c>
+      <c r="S172">
+        <v>2.55</v>
+      </c>
+      <c r="T172">
+        <v>1.37</v>
+      </c>
+      <c r="U172">
+        <v>2.85</v>
+      </c>
+      <c r="V172">
+        <v>2.6</v>
+      </c>
+      <c r="W172">
+        <v>1.44</v>
+      </c>
+      <c r="X172">
+        <v>6.5</v>
+      </c>
+      <c r="Y172">
+        <v>1.1</v>
+      </c>
+      <c r="Z172">
+        <v>3.63</v>
+      </c>
+      <c r="AA172">
+        <v>3.53</v>
+      </c>
+      <c r="AB172">
+        <v>1.96</v>
+      </c>
+      <c r="AC172">
+        <v>1.06</v>
+      </c>
+      <c r="AD172">
+        <v>9</v>
+      </c>
+      <c r="AE172">
+        <v>1.27</v>
+      </c>
+      <c r="AF172">
+        <v>3.4</v>
+      </c>
+      <c r="AG172">
+        <v>1.8</v>
+      </c>
+      <c r="AH172">
+        <v>1.83</v>
+      </c>
+      <c r="AI172">
+        <v>1.7</v>
+      </c>
+      <c r="AJ172">
+        <v>2</v>
+      </c>
+      <c r="AK172">
+        <v>1.75</v>
+      </c>
+      <c r="AL172">
+        <v>1.31</v>
+      </c>
+      <c r="AM172">
+        <v>1.26</v>
+      </c>
+      <c r="AN172">
+        <v>0.93</v>
+      </c>
+      <c r="AO172">
+        <v>1.15</v>
+      </c>
+      <c r="AP172">
+        <v>0.87</v>
+      </c>
+      <c r="AQ172">
+        <v>1.29</v>
+      </c>
+      <c r="AR172">
+        <v>1.51</v>
+      </c>
+      <c r="AS172">
+        <v>1.43</v>
+      </c>
+      <c r="AT172">
+        <v>2.94</v>
+      </c>
+      <c r="AU172">
+        <v>5</v>
+      </c>
+      <c r="AV172">
+        <v>7</v>
+      </c>
+      <c r="AW172">
+        <v>2</v>
+      </c>
+      <c r="AX172">
+        <v>6</v>
+      </c>
+      <c r="AY172">
+        <v>7</v>
+      </c>
+      <c r="AZ172">
+        <v>13</v>
+      </c>
+      <c r="BA172">
+        <v>4</v>
+      </c>
+      <c r="BB172">
+        <v>7</v>
+      </c>
+      <c r="BC172">
+        <v>11</v>
+      </c>
+      <c r="BD172">
+        <v>2.4</v>
+      </c>
+      <c r="BE172">
+        <v>7.5</v>
+      </c>
+      <c r="BF172">
+        <v>1.82</v>
+      </c>
+      <c r="BG172">
+        <v>1.33</v>
+      </c>
+      <c r="BH172">
+        <v>3</v>
+      </c>
+      <c r="BI172">
+        <v>1.49</v>
+      </c>
+      <c r="BJ172">
+        <v>2.37</v>
+      </c>
+      <c r="BK172">
+        <v>1.92</v>
+      </c>
+      <c r="BL172">
+        <v>1.84</v>
+      </c>
+      <c r="BM172">
+        <v>2.3</v>
+      </c>
+      <c r="BN172">
+        <v>1.52</v>
+      </c>
+      <c r="BO172">
+        <v>3.2</v>
+      </c>
+      <c r="BP172">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="173" spans="1:68">
+      <c r="A173" s="1">
+        <v>172</v>
+      </c>
+      <c r="B173">
+        <v>7817208</v>
+      </c>
+      <c r="C173" t="s">
+        <v>68</v>
+      </c>
+      <c r="D173" t="s">
+        <v>69</v>
+      </c>
+      <c r="E173" s="2">
+        <v>45737.70833333334</v>
+      </c>
+      <c r="F173">
+        <v>7</v>
+      </c>
+      <c r="G173" t="s">
+        <v>78</v>
+      </c>
+      <c r="H173" t="s">
+        <v>74</v>
+      </c>
+      <c r="I173">
+        <v>0</v>
+      </c>
+      <c r="J173">
+        <v>0</v>
+      </c>
+      <c r="K173">
+        <v>0</v>
+      </c>
+      <c r="L173">
+        <v>0</v>
+      </c>
+      <c r="M173">
+        <v>1</v>
+      </c>
+      <c r="N173">
+        <v>1</v>
+      </c>
+      <c r="O173" t="s">
+        <v>85</v>
+      </c>
+      <c r="P173" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q173">
+        <v>3.3</v>
+      </c>
+      <c r="R173">
+        <v>2.15</v>
+      </c>
+      <c r="S173">
+        <v>2.8</v>
+      </c>
+      <c r="T173">
+        <v>1.34</v>
+      </c>
+      <c r="U173">
+        <v>3</v>
+      </c>
+      <c r="V173">
+        <v>2.5</v>
+      </c>
+      <c r="W173">
+        <v>1.47</v>
+      </c>
+      <c r="X173">
+        <v>6</v>
+      </c>
+      <c r="Y173">
+        <v>1.11</v>
+      </c>
+      <c r="Z173">
+        <v>3.31</v>
+      </c>
+      <c r="AA173">
+        <v>3.7</v>
+      </c>
+      <c r="AB173">
+        <v>2.01</v>
+      </c>
+      <c r="AC173">
+        <v>1.04</v>
+      </c>
+      <c r="AD173">
+        <v>10.5</v>
+      </c>
+      <c r="AE173">
+        <v>1.23</v>
+      </c>
+      <c r="AF173">
+        <v>3.8</v>
+      </c>
+      <c r="AG173">
+        <v>1.67</v>
+      </c>
+      <c r="AH173">
+        <v>2</v>
+      </c>
+      <c r="AI173">
+        <v>1.6</v>
+      </c>
+      <c r="AJ173">
+        <v>2.15</v>
+      </c>
+      <c r="AK173">
+        <v>1.58</v>
+      </c>
+      <c r="AL173">
+        <v>1.29</v>
+      </c>
+      <c r="AM173">
+        <v>1.39</v>
+      </c>
+      <c r="AN173">
+        <v>0.85</v>
+      </c>
+      <c r="AO173">
+        <v>0.93</v>
+      </c>
+      <c r="AP173">
+        <v>0.79</v>
+      </c>
+      <c r="AQ173">
+        <v>1.07</v>
+      </c>
+      <c r="AR173">
+        <v>1.05</v>
+      </c>
+      <c r="AS173">
+        <v>1.45</v>
+      </c>
+      <c r="AT173">
+        <v>2.5</v>
+      </c>
+      <c r="AU173">
+        <v>5</v>
+      </c>
+      <c r="AV173">
+        <v>7</v>
+      </c>
+      <c r="AW173">
+        <v>2</v>
+      </c>
+      <c r="AX173">
+        <v>16</v>
+      </c>
+      <c r="AY173">
+        <v>7</v>
+      </c>
+      <c r="AZ173">
+        <v>23</v>
+      </c>
+      <c r="BA173">
+        <v>4</v>
+      </c>
+      <c r="BB173">
+        <v>8</v>
+      </c>
+      <c r="BC173">
+        <v>12</v>
+      </c>
+      <c r="BD173">
+        <v>2.36</v>
+      </c>
+      <c r="BE173">
+        <v>7.4</v>
+      </c>
+      <c r="BF173">
+        <v>1.85</v>
+      </c>
+      <c r="BG173">
+        <v>1.25</v>
+      </c>
+      <c r="BH173">
+        <v>3.6</v>
+      </c>
+      <c r="BI173">
+        <v>1.43</v>
+      </c>
+      <c r="BJ173">
+        <v>2.51</v>
+      </c>
+      <c r="BK173">
+        <v>1.73</v>
+      </c>
+      <c r="BL173">
+        <v>2.01</v>
+      </c>
+      <c r="BM173">
+        <v>2.14</v>
+      </c>
+      <c r="BN173">
+        <v>1.63</v>
+      </c>
+      <c r="BO173">
+        <v>2.7</v>
+      </c>
+      <c r="BP173">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="174" spans="1:68">
+      <c r="A174" s="1">
+        <v>173</v>
+      </c>
+      <c r="B174">
+        <v>7817209</v>
+      </c>
+      <c r="C174" t="s">
+        <v>68</v>
+      </c>
+      <c r="D174" t="s">
+        <v>69</v>
+      </c>
+      <c r="E174" s="2">
+        <v>45738.47916666666</v>
+      </c>
+      <c r="F174">
+        <v>7</v>
+      </c>
+      <c r="G174" t="s">
+        <v>75</v>
+      </c>
+      <c r="H174" t="s">
+        <v>81</v>
+      </c>
+      <c r="I174">
+        <v>0</v>
+      </c>
+      <c r="J174">
+        <v>2</v>
+      </c>
+      <c r="K174">
+        <v>2</v>
+      </c>
+      <c r="L174">
+        <v>0</v>
+      </c>
+      <c r="M174">
+        <v>6</v>
+      </c>
+      <c r="N174">
+        <v>6</v>
+      </c>
+      <c r="O174" t="s">
+        <v>85</v>
+      </c>
+      <c r="P174" t="s">
+        <v>291</v>
+      </c>
+      <c r="Q174">
+        <v>6.75</v>
+      </c>
+      <c r="R174">
+        <v>2.75</v>
+      </c>
+      <c r="S174">
+        <v>1.65</v>
+      </c>
+      <c r="T174">
+        <v>1.2</v>
+      </c>
+      <c r="U174">
+        <v>4.1</v>
+      </c>
+      <c r="V174">
+        <v>1.87</v>
+      </c>
+      <c r="W174">
+        <v>1.82</v>
+      </c>
+      <c r="X174">
+        <v>3.75</v>
+      </c>
+      <c r="Y174">
+        <v>1.23</v>
+      </c>
+      <c r="Z174">
+        <v>6.8</v>
+      </c>
+      <c r="AA174">
+        <v>5.06</v>
+      </c>
+      <c r="AB174">
+        <v>1.24</v>
+      </c>
+      <c r="AC174">
+        <v>1.01</v>
+      </c>
+      <c r="AD174">
+        <v>16.5</v>
+      </c>
+      <c r="AE174">
+        <v>1.08</v>
+      </c>
+      <c r="AF174">
+        <v>7.5</v>
+      </c>
+      <c r="AG174">
+        <v>1.36</v>
+      </c>
+      <c r="AH174">
+        <v>3</v>
+      </c>
+      <c r="AI174">
+        <v>1.66</v>
+      </c>
+      <c r="AJ174">
+        <v>2.05</v>
+      </c>
+      <c r="AK174">
+        <v>3.6</v>
+      </c>
+      <c r="AL174">
+        <v>1.13</v>
+      </c>
+      <c r="AM174">
+        <v>1.06</v>
+      </c>
+      <c r="AN174">
+        <v>1.79</v>
+      </c>
+      <c r="AO174">
+        <v>2.31</v>
+      </c>
+      <c r="AP174">
+        <v>1.67</v>
+      </c>
+      <c r="AQ174">
+        <v>2.36</v>
+      </c>
+      <c r="AR174">
+        <v>1.5</v>
+      </c>
+      <c r="AS174">
+        <v>2.21</v>
+      </c>
+      <c r="AT174">
+        <v>3.71</v>
+      </c>
+      <c r="AU174">
+        <v>3</v>
+      </c>
+      <c r="AV174">
+        <v>8</v>
+      </c>
+      <c r="AW174">
+        <v>3</v>
+      </c>
+      <c r="AX174">
+        <v>8</v>
+      </c>
+      <c r="AY174">
+        <v>6</v>
+      </c>
+      <c r="AZ174">
+        <v>16</v>
+      </c>
+      <c r="BA174">
+        <v>4</v>
+      </c>
+      <c r="BB174">
+        <v>3</v>
+      </c>
+      <c r="BC174">
+        <v>7</v>
+      </c>
+      <c r="BD174">
+        <v>5.95</v>
+      </c>
+      <c r="BE174">
+        <v>11</v>
+      </c>
+      <c r="BF174">
+        <v>1.16</v>
+      </c>
+      <c r="BG174">
+        <v>1.33</v>
+      </c>
+      <c r="BH174">
+        <v>3</v>
+      </c>
+      <c r="BI174">
+        <v>1.69</v>
+      </c>
+      <c r="BJ174">
+        <v>2.06</v>
+      </c>
+      <c r="BK174">
+        <v>2.1</v>
+      </c>
+      <c r="BL174">
+        <v>1.66</v>
+      </c>
+      <c r="BM174">
+        <v>2.44</v>
+      </c>
+      <c r="BN174">
+        <v>1.47</v>
+      </c>
+      <c r="BO174">
+        <v>3.2</v>
+      </c>
+      <c r="BP174">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="175" spans="1:68">
+      <c r="A175" s="1">
+        <v>174</v>
+      </c>
+      <c r="B175">
+        <v>7817210</v>
+      </c>
+      <c r="C175" t="s">
+        <v>68</v>
+      </c>
+      <c r="D175" t="s">
+        <v>69</v>
+      </c>
+      <c r="E175" s="2">
+        <v>45738.47916666666</v>
+      </c>
+      <c r="F175">
+        <v>7</v>
+      </c>
+      <c r="G175" t="s">
+        <v>72</v>
+      </c>
+      <c r="H175" t="s">
+        <v>71</v>
+      </c>
+      <c r="I175">
+        <v>2</v>
+      </c>
+      <c r="J175">
+        <v>1</v>
+      </c>
+      <c r="K175">
+        <v>3</v>
+      </c>
+      <c r="L175">
+        <v>3</v>
+      </c>
+      <c r="M175">
+        <v>2</v>
+      </c>
+      <c r="N175">
+        <v>5</v>
+      </c>
+      <c r="O175" t="s">
+        <v>207</v>
+      </c>
+      <c r="P175" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q175">
+        <v>3.4</v>
+      </c>
+      <c r="R175">
+        <v>2.15</v>
+      </c>
+      <c r="S175">
+        <v>2.75</v>
+      </c>
+      <c r="T175">
+        <v>1.31</v>
+      </c>
+      <c r="U175">
+        <v>3.1</v>
+      </c>
+      <c r="V175">
+        <v>2.3</v>
+      </c>
+      <c r="W175">
+        <v>1.53</v>
+      </c>
+      <c r="X175">
+        <v>5.5</v>
+      </c>
+      <c r="Y175">
+        <v>1.13</v>
+      </c>
+      <c r="Z175">
+        <v>2.41</v>
+      </c>
+      <c r="AA175">
+        <v>3.66</v>
+      </c>
+      <c r="AB175">
+        <v>2.63</v>
+      </c>
+      <c r="AC175">
+        <v>1.03</v>
+      </c>
+      <c r="AD175">
+        <v>12</v>
+      </c>
+      <c r="AE175">
+        <v>1.22</v>
+      </c>
+      <c r="AF175">
+        <v>4</v>
+      </c>
+      <c r="AG175">
+        <v>1.6</v>
+      </c>
+      <c r="AH175">
+        <v>2.1</v>
+      </c>
+      <c r="AI175">
+        <v>1.53</v>
+      </c>
+      <c r="AJ175">
+        <v>2.3</v>
+      </c>
+      <c r="AK175">
+        <v>1.61</v>
+      </c>
+      <c r="AL175">
+        <v>1.3</v>
+      </c>
+      <c r="AM175">
+        <v>1.36</v>
+      </c>
+      <c r="AN175">
+        <v>1.57</v>
+      </c>
+      <c r="AO175">
+        <v>1.36</v>
+      </c>
+      <c r="AP175">
+        <v>1.67</v>
+      </c>
+      <c r="AQ175">
+        <v>1.27</v>
+      </c>
+      <c r="AR175">
+        <v>1.86</v>
+      </c>
+      <c r="AS175">
+        <v>1.55</v>
+      </c>
+      <c r="AT175">
+        <v>3.41</v>
+      </c>
+      <c r="AU175">
+        <v>4</v>
+      </c>
+      <c r="AV175">
+        <v>4</v>
+      </c>
+      <c r="AW175">
+        <v>7</v>
+      </c>
+      <c r="AX175">
+        <v>6</v>
+      </c>
+      <c r="AY175">
+        <v>11</v>
+      </c>
+      <c r="AZ175">
+        <v>10</v>
+      </c>
+      <c r="BA175">
+        <v>3</v>
+      </c>
+      <c r="BB175">
+        <v>9</v>
+      </c>
+      <c r="BC175">
+        <v>12</v>
+      </c>
+      <c r="BD175">
+        <v>1.92</v>
+      </c>
+      <c r="BE175">
+        <v>6.3</v>
+      </c>
+      <c r="BF175">
+        <v>2.28</v>
+      </c>
+      <c r="BG175">
+        <v>1.29</v>
+      </c>
+      <c r="BH175">
+        <v>3.4</v>
+      </c>
+      <c r="BI175">
+        <v>1.44</v>
+      </c>
+      <c r="BJ175">
+        <v>2.52</v>
+      </c>
+      <c r="BK175">
+        <v>1.78</v>
+      </c>
+      <c r="BL175">
+        <v>1.98</v>
+      </c>
+      <c r="BM175">
+        <v>2.2</v>
+      </c>
+      <c r="BN175">
+        <v>1.59</v>
+      </c>
+      <c r="BO175">
+        <v>2.8</v>
+      </c>
+      <c r="BP175">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Wales Welsh Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Wales Welsh Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="295">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -640,6 +640,9 @@
     <t>['17', '40', '89']</t>
   </si>
   <si>
+    <t>['19', '57']</t>
+  </si>
+  <si>
     <t>['45+2']</t>
   </si>
   <si>
@@ -893,6 +896,9 @@
   </si>
   <si>
     <t>['7', '81']</t>
+  </si>
+  <si>
+    <t>['36', '65']</t>
   </si>
 </sst>
 </file>
@@ -1254,7 +1260,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP175"/>
+  <dimension ref="A1:BP177"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1510,7 +1516,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q2">
         <v>1.83</v>
@@ -1794,7 +1800,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ3">
         <v>1</v>
@@ -1922,7 +1928,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -2334,7 +2340,7 @@
         <v>85</v>
       </c>
       <c r="P6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q6">
         <v>4</v>
@@ -2540,7 +2546,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q7">
         <v>11</v>
@@ -3033,7 +3039,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ9">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3364,7 +3370,7 @@
         <v>89</v>
       </c>
       <c r="P11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q11">
         <v>3.6</v>
@@ -3442,7 +3448,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AQ11">
         <v>1.29</v>
@@ -3570,7 +3576,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q12">
         <v>2.9</v>
@@ -3857,7 +3863,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ13">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="AR13">
         <v>1.91</v>
@@ -3982,7 +3988,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q14">
         <v>4.33</v>
@@ -4394,7 +4400,7 @@
         <v>85</v>
       </c>
       <c r="P16" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q16">
         <v>2.63</v>
@@ -4678,7 +4684,7 @@
         <v>1</v>
       </c>
       <c r="AP17">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AQ17">
         <v>1.27</v>
@@ -4806,7 +4812,7 @@
         <v>94</v>
       </c>
       <c r="P18" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q18">
         <v>3</v>
@@ -4884,10 +4890,10 @@
         <v>1</v>
       </c>
       <c r="AP18">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ18">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR18">
         <v>1.28</v>
@@ -5012,7 +5018,7 @@
         <v>85</v>
       </c>
       <c r="P19" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q19">
         <v>4.75</v>
@@ -5917,7 +5923,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ23">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR23">
         <v>1.19</v>
@@ -6042,7 +6048,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6248,7 +6254,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q25">
         <v>3.2</v>
@@ -6454,7 +6460,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -6532,10 +6538,10 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ26">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="AR26">
         <v>1.77</v>
@@ -6660,7 +6666,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q27">
         <v>5.5</v>
@@ -7484,7 +7490,7 @@
         <v>85</v>
       </c>
       <c r="P31" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q31">
         <v>13</v>
@@ -7690,7 +7696,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q32">
         <v>1.83</v>
@@ -8102,7 +8108,7 @@
         <v>85</v>
       </c>
       <c r="P34" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q34">
         <v>3</v>
@@ -8180,10 +8186,10 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AQ34">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="AR34">
         <v>0.86</v>
@@ -9132,7 +9138,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q39">
         <v>1.83</v>
@@ -9544,7 +9550,7 @@
         <v>110</v>
       </c>
       <c r="P41" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q41">
         <v>7</v>
@@ -9750,7 +9756,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q42">
         <v>2.6</v>
@@ -9831,7 +9837,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ42">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR42">
         <v>1.52</v>
@@ -9956,7 +9962,7 @@
         <v>85</v>
       </c>
       <c r="P43" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q43">
         <v>3.75</v>
@@ -10034,7 +10040,7 @@
         <v>1.75</v>
       </c>
       <c r="AP43">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AQ43">
         <v>1.53</v>
@@ -10446,7 +10452,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ45">
         <v>1.71</v>
@@ -10655,7 +10661,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ46">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="AR46">
         <v>0.8100000000000001</v>
@@ -10780,7 +10786,7 @@
         <v>115</v>
       </c>
       <c r="P47" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q47">
         <v>2.25</v>
@@ -10861,7 +10867,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ47">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR47">
         <v>1.34</v>
@@ -10986,7 +10992,7 @@
         <v>116</v>
       </c>
       <c r="P48" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q48">
         <v>2.5</v>
@@ -11398,7 +11404,7 @@
         <v>117</v>
       </c>
       <c r="P50" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q50">
         <v>1.67</v>
@@ -11604,7 +11610,7 @@
         <v>118</v>
       </c>
       <c r="P51" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q51">
         <v>6</v>
@@ -11682,7 +11688,7 @@
         <v>2.4</v>
       </c>
       <c r="AP51">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AQ51">
         <v>1.21</v>
@@ -11810,7 +11816,7 @@
         <v>119</v>
       </c>
       <c r="P52" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -12094,7 +12100,7 @@
         <v>0</v>
       </c>
       <c r="AP53">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ53">
         <v>0.4</v>
@@ -12222,7 +12228,7 @@
         <v>114</v>
       </c>
       <c r="P54" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q54">
         <v>9.5</v>
@@ -12634,7 +12640,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q56">
         <v>7</v>
@@ -13458,7 +13464,7 @@
         <v>125</v>
       </c>
       <c r="P60" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q60">
         <v>2.3</v>
@@ -13539,7 +13545,7 @@
         <v>0.87</v>
       </c>
       <c r="AQ60">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="AR60">
         <v>1.7</v>
@@ -13664,7 +13670,7 @@
         <v>85</v>
       </c>
       <c r="P61" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q61">
         <v>2.88</v>
@@ -14076,7 +14082,7 @@
         <v>87</v>
       </c>
       <c r="P63" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q63">
         <v>2.63</v>
@@ -14282,7 +14288,7 @@
         <v>127</v>
       </c>
       <c r="P64" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q64">
         <v>1.42</v>
@@ -14694,7 +14700,7 @@
         <v>128</v>
       </c>
       <c r="P66" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -15184,7 +15190,7 @@
         <v>0.75</v>
       </c>
       <c r="AP68">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ68">
         <v>1.07</v>
@@ -15312,7 +15318,7 @@
         <v>131</v>
       </c>
       <c r="P69" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15393,7 +15399,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ69">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR69">
         <v>1.2</v>
@@ -15518,7 +15524,7 @@
         <v>85</v>
       </c>
       <c r="P70" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q70">
         <v>9</v>
@@ -15596,7 +15602,7 @@
         <v>2.6</v>
       </c>
       <c r="AP70">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AQ70">
         <v>1.93</v>
@@ -15930,7 +15936,7 @@
         <v>132</v>
       </c>
       <c r="P72" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q72">
         <v>7</v>
@@ -16136,7 +16142,7 @@
         <v>133</v>
       </c>
       <c r="P73" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q73">
         <v>1.73</v>
@@ -16548,7 +16554,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16835,7 +16841,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ76">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="AR76">
         <v>2.71</v>
@@ -16960,7 +16966,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q77">
         <v>2.5</v>
@@ -17041,7 +17047,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ77">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR77">
         <v>1.29</v>
@@ -17166,7 +17172,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17372,7 +17378,7 @@
         <v>139</v>
       </c>
       <c r="P79" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q79">
         <v>2.75</v>
@@ -17784,7 +17790,7 @@
         <v>140</v>
       </c>
       <c r="P81" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q81">
         <v>19</v>
@@ -17862,7 +17868,7 @@
         <v>2.25</v>
       </c>
       <c r="AP81">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AQ81">
         <v>2.36</v>
@@ -18196,7 +18202,7 @@
         <v>142</v>
       </c>
       <c r="P83" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18402,7 +18408,7 @@
         <v>143</v>
       </c>
       <c r="P84" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q84">
         <v>11</v>
@@ -18480,7 +18486,7 @@
         <v>2.5</v>
       </c>
       <c r="AP84">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ84">
         <v>2.36</v>
@@ -18608,7 +18614,7 @@
         <v>144</v>
       </c>
       <c r="P85" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q85">
         <v>4.75</v>
@@ -19101,7 +19107,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ87">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="AR87">
         <v>1.32</v>
@@ -19638,7 +19644,7 @@
         <v>148</v>
       </c>
       <c r="P90" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q90">
         <v>4.75</v>
@@ -19716,10 +19722,10 @@
         <v>1.29</v>
       </c>
       <c r="AP90">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AQ90">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR90">
         <v>0.87</v>
@@ -19925,7 +19931,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ91">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="AR91">
         <v>1.97</v>
@@ -20050,7 +20056,7 @@
         <v>150</v>
       </c>
       <c r="P92" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q92">
         <v>2.88</v>
@@ -20128,7 +20134,7 @@
         <v>1.29</v>
       </c>
       <c r="AP92">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ92">
         <v>1.29</v>
@@ -20462,7 +20468,7 @@
         <v>151</v>
       </c>
       <c r="P94" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q94">
         <v>2.88</v>
@@ -20874,7 +20880,7 @@
         <v>153</v>
       </c>
       <c r="P96" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q96">
         <v>11</v>
@@ -21698,7 +21704,7 @@
         <v>156</v>
       </c>
       <c r="P100" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q100">
         <v>1.73</v>
@@ -21904,7 +21910,7 @@
         <v>85</v>
       </c>
       <c r="P101" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q101">
         <v>3.4</v>
@@ -22110,7 +22116,7 @@
         <v>157</v>
       </c>
       <c r="P102" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q102">
         <v>3</v>
@@ -22191,7 +22197,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ102">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR102">
         <v>1.32</v>
@@ -22316,7 +22322,7 @@
         <v>158</v>
       </c>
       <c r="P103" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -23140,7 +23146,7 @@
         <v>162</v>
       </c>
       <c r="P107" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q107">
         <v>3</v>
@@ -23218,7 +23224,7 @@
         <v>1.67</v>
       </c>
       <c r="AP107">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ107">
         <v>1.21</v>
@@ -23346,7 +23352,7 @@
         <v>163</v>
       </c>
       <c r="P108" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q108">
         <v>2.75</v>
@@ -23633,7 +23639,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ109">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="AR109">
         <v>1.26</v>
@@ -23758,7 +23764,7 @@
         <v>165</v>
       </c>
       <c r="P110" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q110">
         <v>2.4</v>
@@ -24042,7 +24048,7 @@
         <v>2</v>
       </c>
       <c r="AP111">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AQ111">
         <v>1.71</v>
@@ -24170,7 +24176,7 @@
         <v>167</v>
       </c>
       <c r="P112" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q112">
         <v>1.4</v>
@@ -24376,7 +24382,7 @@
         <v>168</v>
       </c>
       <c r="P113" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q113">
         <v>4.75</v>
@@ -24454,7 +24460,7 @@
         <v>2.22</v>
       </c>
       <c r="AP113">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ113">
         <v>1.93</v>
@@ -24582,7 +24588,7 @@
         <v>98</v>
       </c>
       <c r="P114" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q114">
         <v>2</v>
@@ -24788,7 +24794,7 @@
         <v>85</v>
       </c>
       <c r="P115" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q115">
         <v>3.75</v>
@@ -25072,7 +25078,7 @@
         <v>1.22</v>
       </c>
       <c r="AP116">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AQ116">
         <v>1</v>
@@ -25200,7 +25206,7 @@
         <v>169</v>
       </c>
       <c r="P117" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25281,7 +25287,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ117">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="AR117">
         <v>1.49</v>
@@ -25406,7 +25412,7 @@
         <v>170</v>
       </c>
       <c r="P118" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q118">
         <v>6</v>
@@ -26024,7 +26030,7 @@
         <v>172</v>
       </c>
       <c r="P121" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q121">
         <v>2.1</v>
@@ -26311,7 +26317,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ122">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR122">
         <v>1.73</v>
@@ -26642,7 +26648,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q124">
         <v>1.44</v>
@@ -26723,7 +26729,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ124">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR124">
         <v>2.58</v>
@@ -27260,7 +27266,7 @@
         <v>85</v>
       </c>
       <c r="P127" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q127">
         <v>2.3</v>
@@ -27466,7 +27472,7 @@
         <v>139</v>
       </c>
       <c r="P128" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q128">
         <v>2.75</v>
@@ -27544,7 +27550,7 @@
         <v>0.6</v>
       </c>
       <c r="AP128">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AQ128">
         <v>1.07</v>
@@ -27753,7 +27759,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ129">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="AR129">
         <v>1.37</v>
@@ -27878,7 +27884,7 @@
         <v>85</v>
       </c>
       <c r="P130" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q130">
         <v>5.5</v>
@@ -28084,7 +28090,7 @@
         <v>177</v>
       </c>
       <c r="P131" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q131">
         <v>7</v>
@@ -28368,7 +28374,7 @@
         <v>1.9</v>
       </c>
       <c r="AP132">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ132">
         <v>1.53</v>
@@ -28496,7 +28502,7 @@
         <v>85</v>
       </c>
       <c r="P133" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q133">
         <v>2.75</v>
@@ -28702,7 +28708,7 @@
         <v>179</v>
       </c>
       <c r="P134" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q134">
         <v>4.75</v>
@@ -28908,7 +28914,7 @@
         <v>180</v>
       </c>
       <c r="P135" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q135">
         <v>2.5</v>
@@ -29114,7 +29120,7 @@
         <v>120</v>
       </c>
       <c r="P136" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q136">
         <v>3.75</v>
@@ -29192,7 +29198,7 @@
         <v>1.09</v>
       </c>
       <c r="AP136">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AQ136">
         <v>1.27</v>
@@ -29320,7 +29326,7 @@
         <v>181</v>
       </c>
       <c r="P137" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q137">
         <v>2.38</v>
@@ -29732,7 +29738,7 @@
         <v>183</v>
       </c>
       <c r="P139" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q139">
         <v>2.7</v>
@@ -30225,7 +30231,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ141">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR141">
         <v>1.54</v>
@@ -30428,10 +30434,10 @@
         <v>0.64</v>
       </c>
       <c r="AP142">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ142">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="AR142">
         <v>1.44</v>
@@ -30556,7 +30562,7 @@
         <v>186</v>
       </c>
       <c r="P143" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q143">
         <v>2.1</v>
@@ -30762,7 +30768,7 @@
         <v>187</v>
       </c>
       <c r="P144" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q144">
         <v>1.53</v>
@@ -32204,7 +32210,7 @@
         <v>85</v>
       </c>
       <c r="P151" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q151">
         <v>8</v>
@@ -32410,7 +32416,7 @@
         <v>85</v>
       </c>
       <c r="P152" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q152">
         <v>6</v>
@@ -32900,10 +32906,10 @@
         <v>0.75</v>
       </c>
       <c r="AP154">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AQ154">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR154">
         <v>1.1</v>
@@ -33028,7 +33034,7 @@
         <v>193</v>
       </c>
       <c r="P155" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q155">
         <v>3.25</v>
@@ -33234,7 +33240,7 @@
         <v>85</v>
       </c>
       <c r="P156" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q156">
         <v>2.88</v>
@@ -33312,7 +33318,7 @@
         <v>1</v>
       </c>
       <c r="AP156">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ156">
         <v>1.29</v>
@@ -33440,7 +33446,7 @@
         <v>194</v>
       </c>
       <c r="P157" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q157">
         <v>2.63</v>
@@ -33646,7 +33652,7 @@
         <v>195</v>
       </c>
       <c r="P158" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q158">
         <v>3</v>
@@ -34058,7 +34064,7 @@
         <v>197</v>
       </c>
       <c r="P160" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q160">
         <v>2.88</v>
@@ -34139,7 +34145,7 @@
         <v>0.87</v>
       </c>
       <c r="AQ160">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="AR160">
         <v>1.52</v>
@@ -34470,7 +34476,7 @@
         <v>199</v>
       </c>
       <c r="P162" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q162">
         <v>3</v>
@@ -34676,7 +34682,7 @@
         <v>200</v>
       </c>
       <c r="P163" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q163">
         <v>2.2</v>
@@ -34963,7 +34969,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ164">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AR164">
         <v>1.48</v>
@@ -35088,7 +35094,7 @@
         <v>202</v>
       </c>
       <c r="P165" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q165">
         <v>1.83</v>
@@ -35166,7 +35172,7 @@
         <v>0.43</v>
       </c>
       <c r="AP165">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ165">
         <v>0.4</v>
@@ -35375,7 +35381,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ166">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="AR166">
         <v>1.64</v>
@@ -36324,7 +36330,7 @@
         <v>97</v>
       </c>
       <c r="P171" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q171">
         <v>3</v>
@@ -36530,7 +36536,7 @@
         <v>206</v>
       </c>
       <c r="P172" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q172">
         <v>4</v>
@@ -36814,7 +36820,7 @@
         <v>0.93</v>
       </c>
       <c r="AP173">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AQ173">
         <v>1.07</v>
@@ -36942,7 +36948,7 @@
         <v>85</v>
       </c>
       <c r="P174" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q174">
         <v>6.75</v>
@@ -37148,7 +37154,7 @@
         <v>207</v>
       </c>
       <c r="P175" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q175">
         <v>3.4</v>
@@ -37305,6 +37311,418 @@
       </c>
       <c r="BP175">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="176" spans="1:68">
+      <c r="A176" s="1">
+        <v>175</v>
+      </c>
+      <c r="B176">
+        <v>7817211</v>
+      </c>
+      <c r="C176" t="s">
+        <v>68</v>
+      </c>
+      <c r="D176" t="s">
+        <v>69</v>
+      </c>
+      <c r="E176" s="2">
+        <v>45744.69791666666</v>
+      </c>
+      <c r="F176">
+        <v>8</v>
+      </c>
+      <c r="G176" t="s">
+        <v>71</v>
+      </c>
+      <c r="H176" t="s">
+        <v>70</v>
+      </c>
+      <c r="I176">
+        <v>1</v>
+      </c>
+      <c r="J176">
+        <v>0</v>
+      </c>
+      <c r="K176">
+        <v>1</v>
+      </c>
+      <c r="L176">
+        <v>2</v>
+      </c>
+      <c r="M176">
+        <v>1</v>
+      </c>
+      <c r="N176">
+        <v>3</v>
+      </c>
+      <c r="O176" t="s">
+        <v>208</v>
+      </c>
+      <c r="P176" t="s">
+        <v>262</v>
+      </c>
+      <c r="Q176">
+        <v>2.05</v>
+      </c>
+      <c r="R176">
+        <v>2.41</v>
+      </c>
+      <c r="S176">
+        <v>4.65</v>
+      </c>
+      <c r="T176">
+        <v>1.24</v>
+      </c>
+      <c r="U176">
+        <v>3.6</v>
+      </c>
+      <c r="V176">
+        <v>2.25</v>
+      </c>
+      <c r="W176">
+        <v>1.6</v>
+      </c>
+      <c r="X176">
+        <v>4.8</v>
+      </c>
+      <c r="Y176">
+        <v>1.15</v>
+      </c>
+      <c r="Z176">
+        <v>1.63</v>
+      </c>
+      <c r="AA176">
+        <v>4.3</v>
+      </c>
+      <c r="AB176">
+        <v>4.5</v>
+      </c>
+      <c r="AC176">
+        <v>1.01</v>
+      </c>
+      <c r="AD176">
+        <v>13</v>
+      </c>
+      <c r="AE176">
+        <v>1.13</v>
+      </c>
+      <c r="AF176">
+        <v>4.6</v>
+      </c>
+      <c r="AG176">
+        <v>1.57</v>
+      </c>
+      <c r="AH176">
+        <v>2.25</v>
+      </c>
+      <c r="AI176">
+        <v>1.56</v>
+      </c>
+      <c r="AJ176">
+        <v>2.21</v>
+      </c>
+      <c r="AK176">
+        <v>1.14</v>
+      </c>
+      <c r="AL176">
+        <v>1.18</v>
+      </c>
+      <c r="AM176">
+        <v>2.22</v>
+      </c>
+      <c r="AN176">
+        <v>1.71</v>
+      </c>
+      <c r="AO176">
+        <v>0.93</v>
+      </c>
+      <c r="AP176">
+        <v>1.8</v>
+      </c>
+      <c r="AQ176">
+        <v>0.87</v>
+      </c>
+      <c r="AR176">
+        <v>1.49</v>
+      </c>
+      <c r="AS176">
+        <v>1.43</v>
+      </c>
+      <c r="AT176">
+        <v>2.92</v>
+      </c>
+      <c r="AU176">
+        <v>5</v>
+      </c>
+      <c r="AV176">
+        <v>2</v>
+      </c>
+      <c r="AW176">
+        <v>7</v>
+      </c>
+      <c r="AX176">
+        <v>6</v>
+      </c>
+      <c r="AY176">
+        <v>12</v>
+      </c>
+      <c r="AZ176">
+        <v>8</v>
+      </c>
+      <c r="BA176">
+        <v>1</v>
+      </c>
+      <c r="BB176">
+        <v>3</v>
+      </c>
+      <c r="BC176">
+        <v>4</v>
+      </c>
+      <c r="BD176">
+        <v>1.6</v>
+      </c>
+      <c r="BE176">
+        <v>8.5</v>
+      </c>
+      <c r="BF176">
+        <v>2.67</v>
+      </c>
+      <c r="BG176">
+        <v>1.25</v>
+      </c>
+      <c r="BH176">
+        <v>3.6</v>
+      </c>
+      <c r="BI176">
+        <v>1.44</v>
+      </c>
+      <c r="BJ176">
+        <v>2.51</v>
+      </c>
+      <c r="BK176">
+        <v>1.71</v>
+      </c>
+      <c r="BL176">
+        <v>2.03</v>
+      </c>
+      <c r="BM176">
+        <v>2.14</v>
+      </c>
+      <c r="BN176">
+        <v>1.63</v>
+      </c>
+      <c r="BO176">
+        <v>2.44</v>
+      </c>
+      <c r="BP176">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="177" spans="1:68">
+      <c r="A177" s="1">
+        <v>176</v>
+      </c>
+      <c r="B177">
+        <v>7817212</v>
+      </c>
+      <c r="C177" t="s">
+        <v>68</v>
+      </c>
+      <c r="D177" t="s">
+        <v>69</v>
+      </c>
+      <c r="E177" s="2">
+        <v>45744.70833333334</v>
+      </c>
+      <c r="F177">
+        <v>8</v>
+      </c>
+      <c r="G177" t="s">
+        <v>78</v>
+      </c>
+      <c r="H177" t="s">
+        <v>72</v>
+      </c>
+      <c r="I177">
+        <v>0</v>
+      </c>
+      <c r="J177">
+        <v>1</v>
+      </c>
+      <c r="K177">
+        <v>1</v>
+      </c>
+      <c r="L177">
+        <v>1</v>
+      </c>
+      <c r="M177">
+        <v>2</v>
+      </c>
+      <c r="N177">
+        <v>3</v>
+      </c>
+      <c r="O177" t="s">
+        <v>134</v>
+      </c>
+      <c r="P177" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q177">
+        <v>3.64</v>
+      </c>
+      <c r="R177">
+        <v>2.35</v>
+      </c>
+      <c r="S177">
+        <v>2.4</v>
+      </c>
+      <c r="T177">
+        <v>1.22</v>
+      </c>
+      <c r="U177">
+        <v>3.8</v>
+      </c>
+      <c r="V177">
+        <v>2.23</v>
+      </c>
+      <c r="W177">
+        <v>1.61</v>
+      </c>
+      <c r="X177">
+        <v>4.7</v>
+      </c>
+      <c r="Y177">
+        <v>1.15</v>
+      </c>
+      <c r="Z177">
+        <v>3.35</v>
+      </c>
+      <c r="AA177">
+        <v>3.78</v>
+      </c>
+      <c r="AB177">
+        <v>1.97</v>
+      </c>
+      <c r="AC177">
+        <v>1.01</v>
+      </c>
+      <c r="AD177">
+        <v>13</v>
+      </c>
+      <c r="AE177">
+        <v>1.12</v>
+      </c>
+      <c r="AF177">
+        <v>4.7</v>
+      </c>
+      <c r="AG177">
+        <v>1.6</v>
+      </c>
+      <c r="AH177">
+        <v>2.19</v>
+      </c>
+      <c r="AI177">
+        <v>1.46</v>
+      </c>
+      <c r="AJ177">
+        <v>2.45</v>
+      </c>
+      <c r="AK177">
+        <v>1.76</v>
+      </c>
+      <c r="AL177">
+        <v>1.22</v>
+      </c>
+      <c r="AM177">
+        <v>1.28</v>
+      </c>
+      <c r="AN177">
+        <v>0.79</v>
+      </c>
+      <c r="AO177">
+        <v>0.57</v>
+      </c>
+      <c r="AP177">
+        <v>0.73</v>
+      </c>
+      <c r="AQ177">
+        <v>0.73</v>
+      </c>
+      <c r="AR177">
+        <v>1.05</v>
+      </c>
+      <c r="AS177">
+        <v>1.42</v>
+      </c>
+      <c r="AT177">
+        <v>2.47</v>
+      </c>
+      <c r="AU177">
+        <v>7</v>
+      </c>
+      <c r="AV177">
+        <v>7</v>
+      </c>
+      <c r="AW177">
+        <v>7</v>
+      </c>
+      <c r="AX177">
+        <v>9</v>
+      </c>
+      <c r="AY177">
+        <v>14</v>
+      </c>
+      <c r="AZ177">
+        <v>16</v>
+      </c>
+      <c r="BA177">
+        <v>2</v>
+      </c>
+      <c r="BB177">
+        <v>7</v>
+      </c>
+      <c r="BC177">
+        <v>9</v>
+      </c>
+      <c r="BD177">
+        <v>3.1</v>
+      </c>
+      <c r="BE177">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF177">
+        <v>1.47</v>
+      </c>
+      <c r="BG177">
+        <v>1.25</v>
+      </c>
+      <c r="BH177">
+        <v>3.6</v>
+      </c>
+      <c r="BI177">
+        <v>1.44</v>
+      </c>
+      <c r="BJ177">
+        <v>2.6</v>
+      </c>
+      <c r="BK177">
+        <v>1.72</v>
+      </c>
+      <c r="BL177">
+        <v>2.02</v>
+      </c>
+      <c r="BM177">
+        <v>2.14</v>
+      </c>
+      <c r="BN177">
+        <v>1.63</v>
+      </c>
+      <c r="BO177">
+        <v>2.7</v>
+      </c>
+      <c r="BP177">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Wales Welsh Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Wales Welsh Premier League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="298">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -643,6 +643,15 @@
     <t>['19', '57']</t>
   </si>
   <si>
+    <t>['72']</t>
+  </si>
+  <si>
+    <t>['73']</t>
+  </si>
+  <si>
+    <t>['52']</t>
+  </si>
+  <si>
     <t>['45+2']</t>
   </si>
   <si>
@@ -1260,7 +1269,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP177"/>
+  <dimension ref="A1:BP181"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1516,7 +1525,7 @@
         <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q2">
         <v>1.83</v>
@@ -1928,7 +1937,7 @@
         <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -2009,7 +2018,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ4">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2340,7 +2349,7 @@
         <v>85</v>
       </c>
       <c r="P6" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q6">
         <v>4</v>
@@ -2418,7 +2427,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AQ6">
         <v>1.93</v>
@@ -2546,7 +2555,7 @@
         <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q7">
         <v>11</v>
@@ -2627,7 +2636,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ7">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AR7">
         <v>1.59</v>
@@ -3036,7 +3045,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ9">
         <v>0.87</v>
@@ -3242,7 +3251,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ10">
         <v>1.07</v>
@@ -3370,7 +3379,7 @@
         <v>89</v>
       </c>
       <c r="P11" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q11">
         <v>3.6</v>
@@ -3451,7 +3460,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ11">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3576,7 +3585,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q12">
         <v>2.9</v>
@@ -3860,7 +3869,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ13">
         <v>0.73</v>
@@ -3988,7 +3997,7 @@
         <v>92</v>
       </c>
       <c r="P14" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q14">
         <v>4.33</v>
@@ -4066,10 +4075,10 @@
         <v>3</v>
       </c>
       <c r="AP14">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AQ14">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR14">
         <v>0.82</v>
@@ -4272,7 +4281,7 @@
         <v>3</v>
       </c>
       <c r="AP15">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ15">
         <v>1.93</v>
@@ -4400,7 +4409,7 @@
         <v>85</v>
       </c>
       <c r="P16" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q16">
         <v>2.63</v>
@@ -4481,7 +4490,7 @@
         <v>0.87</v>
       </c>
       <c r="AQ16">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AR16">
         <v>2.12</v>
@@ -4812,7 +4821,7 @@
         <v>94</v>
       </c>
       <c r="P18" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q18">
         <v>3</v>
@@ -5018,7 +5027,7 @@
         <v>85</v>
       </c>
       <c r="P19" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q19">
         <v>4.75</v>
@@ -5099,7 +5108,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ19">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR19">
         <v>1.46</v>
@@ -5508,7 +5517,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ21">
         <v>0.4</v>
@@ -5920,7 +5929,7 @@
         <v>2</v>
       </c>
       <c r="AP23">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ23">
         <v>0.87</v>
@@ -6048,7 +6057,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6129,7 +6138,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ24">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR24">
         <v>1.08</v>
@@ -6254,7 +6263,7 @@
         <v>98</v>
       </c>
       <c r="P25" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q25">
         <v>3.2</v>
@@ -6332,7 +6341,7 @@
         <v>2</v>
       </c>
       <c r="AP25">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ25">
         <v>1.93</v>
@@ -6460,7 +6469,7 @@
         <v>99</v>
       </c>
       <c r="P26" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q26">
         <v>2.38</v>
@@ -6666,7 +6675,7 @@
         <v>100</v>
       </c>
       <c r="P27" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q27">
         <v>5.5</v>
@@ -6744,10 +6753,10 @@
         <v>2</v>
       </c>
       <c r="AP27">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AQ27">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR27">
         <v>0.89</v>
@@ -7156,10 +7165,10 @@
         <v>3</v>
       </c>
       <c r="AP29">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ29">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AR29">
         <v>2.16</v>
@@ -7490,7 +7499,7 @@
         <v>85</v>
       </c>
       <c r="P31" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q31">
         <v>13</v>
@@ -7568,10 +7577,10 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ31">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AR31">
         <v>1.46</v>
@@ -7696,7 +7705,7 @@
         <v>104</v>
       </c>
       <c r="P32" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q32">
         <v>1.83</v>
@@ -7980,10 +7989,10 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ33">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR33">
         <v>1.47</v>
@@ -8108,7 +8117,7 @@
         <v>85</v>
       </c>
       <c r="P34" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q34">
         <v>3</v>
@@ -8395,7 +8404,7 @@
         <v>0.87</v>
       </c>
       <c r="AQ35">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR35">
         <v>1.94</v>
@@ -8598,7 +8607,7 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ36">
         <v>0.4</v>
@@ -9138,7 +9147,7 @@
         <v>109</v>
       </c>
       <c r="P39" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q39">
         <v>1.83</v>
@@ -9550,7 +9559,7 @@
         <v>110</v>
       </c>
       <c r="P41" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q41">
         <v>7</v>
@@ -9628,10 +9637,10 @@
         <v>3</v>
       </c>
       <c r="AP41">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ41">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AR41">
         <v>2.47</v>
@@ -9756,7 +9765,7 @@
         <v>111</v>
       </c>
       <c r="P42" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q42">
         <v>2.6</v>
@@ -9834,7 +9843,7 @@
         <v>1.33</v>
       </c>
       <c r="AP42">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ42">
         <v>0.87</v>
@@ -9962,7 +9971,7 @@
         <v>85</v>
       </c>
       <c r="P43" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q43">
         <v>3.75</v>
@@ -10249,7 +10258,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ44">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR44">
         <v>1.05</v>
@@ -10455,7 +10464,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ45">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AR45">
         <v>1.74</v>
@@ -10658,7 +10667,7 @@
         <v>1</v>
       </c>
       <c r="AP46">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AQ46">
         <v>0.73</v>
@@ -10786,7 +10795,7 @@
         <v>115</v>
       </c>
       <c r="P47" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q47">
         <v>2.25</v>
@@ -10992,7 +11001,7 @@
         <v>116</v>
       </c>
       <c r="P48" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q48">
         <v>2.5</v>
@@ -11070,7 +11079,7 @@
         <v>1</v>
       </c>
       <c r="AP48">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ48">
         <v>1.27</v>
@@ -11276,7 +11285,7 @@
         <v>0</v>
       </c>
       <c r="AP49">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ49">
         <v>1.07</v>
@@ -11404,7 +11413,7 @@
         <v>117</v>
       </c>
       <c r="P50" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q50">
         <v>1.67</v>
@@ -11610,7 +11619,7 @@
         <v>118</v>
       </c>
       <c r="P51" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q51">
         <v>6</v>
@@ -11691,7 +11700,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ51">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR51">
         <v>0.9399999999999999</v>
@@ -11816,7 +11825,7 @@
         <v>119</v>
       </c>
       <c r="P52" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q52">
         <v>3</v>
@@ -11897,7 +11906,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ52">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AR52">
         <v>1.62</v>
@@ -12228,7 +12237,7 @@
         <v>114</v>
       </c>
       <c r="P54" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q54">
         <v>9.5</v>
@@ -12309,7 +12318,7 @@
         <v>0.87</v>
       </c>
       <c r="AQ54">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AR54">
         <v>1.83</v>
@@ -12512,10 +12521,10 @@
         <v>2.5</v>
       </c>
       <c r="AP55">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ55">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR55">
         <v>1.17</v>
@@ -12640,7 +12649,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q56">
         <v>7</v>
@@ -12718,7 +12727,7 @@
         <v>1.67</v>
       </c>
       <c r="AP56">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AQ56">
         <v>1</v>
@@ -13133,7 +13142,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ58">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR58">
         <v>1.13</v>
@@ -13336,7 +13345,7 @@
         <v>1</v>
       </c>
       <c r="AP59">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ59">
         <v>1.27</v>
@@ -13464,7 +13473,7 @@
         <v>125</v>
       </c>
       <c r="P60" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q60">
         <v>2.3</v>
@@ -13670,7 +13679,7 @@
         <v>85</v>
       </c>
       <c r="P61" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q61">
         <v>2.88</v>
@@ -13748,7 +13757,7 @@
         <v>2</v>
       </c>
       <c r="AP61">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ61">
         <v>1.53</v>
@@ -14082,7 +14091,7 @@
         <v>87</v>
       </c>
       <c r="P63" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q63">
         <v>2.63</v>
@@ -14163,7 +14172,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ63">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AR63">
         <v>1.21</v>
@@ -14288,7 +14297,7 @@
         <v>127</v>
       </c>
       <c r="P64" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q64">
         <v>1.42</v>
@@ -14369,7 +14378,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ64">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AR64">
         <v>3.13</v>
@@ -14572,10 +14581,10 @@
         <v>1.4</v>
       </c>
       <c r="AP65">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ65">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR65">
         <v>1.25</v>
@@ -14700,7 +14709,7 @@
         <v>128</v>
       </c>
       <c r="P66" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q66">
         <v>4</v>
@@ -14987,7 +14996,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ67">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR67">
         <v>2.85</v>
@@ -15318,7 +15327,7 @@
         <v>131</v>
       </c>
       <c r="P69" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15524,7 +15533,7 @@
         <v>85</v>
       </c>
       <c r="P70" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q70">
         <v>9</v>
@@ -15808,10 +15817,10 @@
         <v>1.33</v>
       </c>
       <c r="AP71">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ71">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR71">
         <v>1.39</v>
@@ -15936,7 +15945,7 @@
         <v>132</v>
       </c>
       <c r="P72" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q72">
         <v>7</v>
@@ -16014,7 +16023,7 @@
         <v>2.17</v>
       </c>
       <c r="AP72">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AQ72">
         <v>1.53</v>
@@ -16142,7 +16151,7 @@
         <v>133</v>
       </c>
       <c r="P73" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q73">
         <v>1.73</v>
@@ -16554,7 +16563,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q75">
         <v>2.88</v>
@@ -16966,7 +16975,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q77">
         <v>2.5</v>
@@ -17172,7 +17181,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q78">
         <v>3.1</v>
@@ -17378,7 +17387,7 @@
         <v>139</v>
       </c>
       <c r="P79" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q79">
         <v>2.75</v>
@@ -17456,7 +17465,7 @@
         <v>1.4</v>
       </c>
       <c r="AP79">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ79">
         <v>1</v>
@@ -17662,10 +17671,10 @@
         <v>2.17</v>
       </c>
       <c r="AP80">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ80">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AR80">
         <v>1.28</v>
@@ -17790,7 +17799,7 @@
         <v>140</v>
       </c>
       <c r="P81" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q81">
         <v>19</v>
@@ -17871,7 +17880,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ81">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AR81">
         <v>0.87</v>
@@ -18202,7 +18211,7 @@
         <v>142</v>
       </c>
       <c r="P83" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18283,7 +18292,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ83">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AR83">
         <v>1.47</v>
@@ -18408,7 +18417,7 @@
         <v>143</v>
       </c>
       <c r="P84" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q84">
         <v>11</v>
@@ -18489,7 +18498,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ84">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AR84">
         <v>1.66</v>
@@ -18614,7 +18623,7 @@
         <v>144</v>
       </c>
       <c r="P85" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q85">
         <v>4.75</v>
@@ -18901,7 +18910,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ86">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR86">
         <v>1.39</v>
@@ -19104,7 +19113,7 @@
         <v>1.17</v>
       </c>
       <c r="AP87">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ87">
         <v>0.73</v>
@@ -19516,7 +19525,7 @@
         <v>0.43</v>
       </c>
       <c r="AP89">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AQ89">
         <v>0.4</v>
@@ -19644,7 +19653,7 @@
         <v>148</v>
       </c>
       <c r="P90" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q90">
         <v>4.75</v>
@@ -19928,7 +19937,7 @@
         <v>1</v>
       </c>
       <c r="AP91">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ91">
         <v>0.73</v>
@@ -20056,7 +20065,7 @@
         <v>150</v>
       </c>
       <c r="P92" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q92">
         <v>2.88</v>
@@ -20137,7 +20146,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ92">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR92">
         <v>1.58</v>
@@ -20340,10 +20349,10 @@
         <v>2</v>
       </c>
       <c r="AP93">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AQ93">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AR93">
         <v>1.26</v>
@@ -20468,7 +20477,7 @@
         <v>151</v>
       </c>
       <c r="P94" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q94">
         <v>2.88</v>
@@ -20880,7 +20889,7 @@
         <v>153</v>
       </c>
       <c r="P96" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q96">
         <v>11</v>
@@ -20958,10 +20967,10 @@
         <v>2.57</v>
       </c>
       <c r="AP96">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AQ96">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AR96">
         <v>1.34</v>
@@ -21576,7 +21585,7 @@
         <v>1.25</v>
       </c>
       <c r="AP99">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ99">
         <v>1</v>
@@ -21704,7 +21713,7 @@
         <v>156</v>
       </c>
       <c r="P100" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q100">
         <v>1.73</v>
@@ -21910,7 +21919,7 @@
         <v>85</v>
       </c>
       <c r="P101" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q101">
         <v>3.4</v>
@@ -21991,7 +22000,7 @@
         <v>0.87</v>
       </c>
       <c r="AQ101">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR101">
         <v>1.77</v>
@@ -22116,7 +22125,7 @@
         <v>157</v>
       </c>
       <c r="P102" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q102">
         <v>3</v>
@@ -22194,7 +22203,7 @@
         <v>1.13</v>
       </c>
       <c r="AP102">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AQ102">
         <v>0.87</v>
@@ -22322,7 +22331,7 @@
         <v>158</v>
       </c>
       <c r="P103" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22403,7 +22412,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ103">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AR103">
         <v>1.45</v>
@@ -22606,7 +22615,7 @@
         <v>2</v>
       </c>
       <c r="AP104">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ104">
         <v>1.53</v>
@@ -22812,10 +22821,10 @@
         <v>2.25</v>
       </c>
       <c r="AP105">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ105">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AR105">
         <v>1.31</v>
@@ -23146,7 +23155,7 @@
         <v>162</v>
       </c>
       <c r="P107" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q107">
         <v>3</v>
@@ -23227,7 +23236,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ107">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR107">
         <v>1.55</v>
@@ -23352,7 +23361,7 @@
         <v>163</v>
       </c>
       <c r="P108" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q108">
         <v>2.75</v>
@@ -23764,7 +23773,7 @@
         <v>165</v>
       </c>
       <c r="P110" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q110">
         <v>2.4</v>
@@ -23842,7 +23851,7 @@
         <v>1.22</v>
       </c>
       <c r="AP110">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ110">
         <v>1.27</v>
@@ -24051,7 +24060,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ111">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AR111">
         <v>0.97</v>
@@ -24176,7 +24185,7 @@
         <v>167</v>
       </c>
       <c r="P112" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q112">
         <v>1.4</v>
@@ -24382,7 +24391,7 @@
         <v>168</v>
       </c>
       <c r="P113" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q113">
         <v>4.75</v>
@@ -24588,7 +24597,7 @@
         <v>98</v>
       </c>
       <c r="P114" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q114">
         <v>2</v>
@@ -24794,7 +24803,7 @@
         <v>85</v>
       </c>
       <c r="P115" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q115">
         <v>3.75</v>
@@ -25206,7 +25215,7 @@
         <v>169</v>
       </c>
       <c r="P117" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q117">
         <v>2.1</v>
@@ -25412,7 +25421,7 @@
         <v>170</v>
       </c>
       <c r="P118" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q118">
         <v>6</v>
@@ -25493,7 +25502,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ118">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AR118">
         <v>1.4</v>
@@ -25696,7 +25705,7 @@
         <v>1.1</v>
       </c>
       <c r="AP119">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AQ119">
         <v>1.27</v>
@@ -25905,7 +25914,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ120">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR120">
         <v>2.7</v>
@@ -26030,7 +26039,7 @@
         <v>172</v>
       </c>
       <c r="P121" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q121">
         <v>2.1</v>
@@ -26108,10 +26117,10 @@
         <v>1.5</v>
       </c>
       <c r="AP121">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ121">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR121">
         <v>1.88</v>
@@ -26520,7 +26529,7 @@
         <v>0.3</v>
       </c>
       <c r="AP123">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ123">
         <v>0.4</v>
@@ -26648,7 +26657,7 @@
         <v>174</v>
       </c>
       <c r="P124" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q124">
         <v>1.44</v>
@@ -26932,7 +26941,7 @@
         <v>0.67</v>
       </c>
       <c r="AP125">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ125">
         <v>1.07</v>
@@ -27138,10 +27147,10 @@
         <v>1.2</v>
       </c>
       <c r="AP126">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ126">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR126">
         <v>1.81</v>
@@ -27266,7 +27275,7 @@
         <v>85</v>
       </c>
       <c r="P127" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q127">
         <v>2.3</v>
@@ -27344,10 +27353,10 @@
         <v>1.8</v>
       </c>
       <c r="AP127">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ127">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AR127">
         <v>1.34</v>
@@ -27472,7 +27481,7 @@
         <v>139</v>
       </c>
       <c r="P128" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q128">
         <v>2.75</v>
@@ -27884,7 +27893,7 @@
         <v>85</v>
       </c>
       <c r="P130" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q130">
         <v>5.5</v>
@@ -27965,7 +27974,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ130">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AR130">
         <v>1.5</v>
@@ -28090,7 +28099,7 @@
         <v>177</v>
       </c>
       <c r="P131" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q131">
         <v>7</v>
@@ -28502,7 +28511,7 @@
         <v>85</v>
       </c>
       <c r="P133" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q133">
         <v>2.75</v>
@@ -28708,7 +28717,7 @@
         <v>179</v>
       </c>
       <c r="P134" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q134">
         <v>4.75</v>
@@ -28914,7 +28923,7 @@
         <v>180</v>
       </c>
       <c r="P135" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q135">
         <v>2.5</v>
@@ -29120,7 +29129,7 @@
         <v>120</v>
       </c>
       <c r="P136" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q136">
         <v>3.75</v>
@@ -29326,7 +29335,7 @@
         <v>181</v>
       </c>
       <c r="P137" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q137">
         <v>2.38</v>
@@ -29404,7 +29413,7 @@
         <v>1.36</v>
       </c>
       <c r="AP137">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ137">
         <v>1</v>
@@ -29613,7 +29622,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ138">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR138">
         <v>1.74</v>
@@ -29738,7 +29747,7 @@
         <v>183</v>
       </c>
       <c r="P139" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q139">
         <v>2.7</v>
@@ -29816,10 +29825,10 @@
         <v>1.91</v>
       </c>
       <c r="AP139">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ139">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AR139">
         <v>1.37</v>
@@ -30022,7 +30031,7 @@
         <v>1.82</v>
       </c>
       <c r="AP140">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ140">
         <v>1.53</v>
@@ -30562,7 +30571,7 @@
         <v>186</v>
       </c>
       <c r="P143" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q143">
         <v>2.1</v>
@@ -30640,7 +30649,7 @@
         <v>0.27</v>
       </c>
       <c r="AP143">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AQ143">
         <v>0.4</v>
@@ -30768,7 +30777,7 @@
         <v>187</v>
       </c>
       <c r="P144" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q144">
         <v>1.53</v>
@@ -30849,7 +30858,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ144">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR144">
         <v>2.6</v>
@@ -32210,7 +32219,7 @@
         <v>85</v>
       </c>
       <c r="P151" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q151">
         <v>8</v>
@@ -32291,7 +32300,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ151">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AR151">
         <v>1.4</v>
@@ -32416,7 +32425,7 @@
         <v>85</v>
       </c>
       <c r="P152" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q152">
         <v>6</v>
@@ -32494,10 +32503,10 @@
         <v>2.25</v>
       </c>
       <c r="AP152">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ152">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AR152">
         <v>1.39</v>
@@ -32700,10 +32709,10 @@
         <v>1.33</v>
       </c>
       <c r="AP153">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ153">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR153">
         <v>1.55</v>
@@ -33034,7 +33043,7 @@
         <v>193</v>
       </c>
       <c r="P155" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q155">
         <v>3.25</v>
@@ -33240,7 +33249,7 @@
         <v>85</v>
       </c>
       <c r="P156" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q156">
         <v>2.88</v>
@@ -33321,7 +33330,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ156">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR156">
         <v>1.42</v>
@@ -33446,7 +33455,7 @@
         <v>194</v>
       </c>
       <c r="P157" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q157">
         <v>2.63</v>
@@ -33652,7 +33661,7 @@
         <v>195</v>
       </c>
       <c r="P158" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q158">
         <v>3</v>
@@ -33730,7 +33739,7 @@
         <v>1.23</v>
       </c>
       <c r="AP158">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AQ158">
         <v>1.27</v>
@@ -34064,7 +34073,7 @@
         <v>197</v>
       </c>
       <c r="P160" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q160">
         <v>2.88</v>
@@ -34476,7 +34485,7 @@
         <v>199</v>
       </c>
       <c r="P162" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q162">
         <v>3</v>
@@ -34557,7 +34566,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ162">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AR162">
         <v>1.46</v>
@@ -34682,7 +34691,7 @@
         <v>200</v>
       </c>
       <c r="P163" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q163">
         <v>2.2</v>
@@ -34760,7 +34769,7 @@
         <v>1.15</v>
       </c>
       <c r="AP163">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ163">
         <v>1</v>
@@ -34966,7 +34975,7 @@
         <v>0.92</v>
       </c>
       <c r="AP164">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AQ164">
         <v>0.87</v>
@@ -35094,7 +35103,7 @@
         <v>202</v>
       </c>
       <c r="P165" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q165">
         <v>1.83</v>
@@ -35587,7 +35596,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ167">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AR167">
         <v>2.54</v>
@@ -35790,10 +35799,10 @@
         <v>1.23</v>
       </c>
       <c r="AP168">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AQ168">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AR168">
         <v>1.65</v>
@@ -35996,7 +36005,7 @@
         <v>1.57</v>
       </c>
       <c r="AP169">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ169">
         <v>1.53</v>
@@ -36330,7 +36339,7 @@
         <v>97</v>
       </c>
       <c r="P171" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q171">
         <v>3</v>
@@ -36408,7 +36417,7 @@
         <v>1.86</v>
       </c>
       <c r="AP171">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ171">
         <v>1.93</v>
@@ -36536,7 +36545,7 @@
         <v>206</v>
       </c>
       <c r="P172" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q172">
         <v>4</v>
@@ -36617,7 +36626,7 @@
         <v>0.87</v>
       </c>
       <c r="AQ172">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AR172">
         <v>1.51</v>
@@ -36948,7 +36957,7 @@
         <v>85</v>
       </c>
       <c r="P174" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q174">
         <v>6.75</v>
@@ -37029,7 +37038,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ174">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AR174">
         <v>1.5</v>
@@ -37154,7 +37163,7 @@
         <v>207</v>
       </c>
       <c r="P175" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q175">
         <v>3.4</v>
@@ -37360,7 +37369,7 @@
         <v>208</v>
       </c>
       <c r="P176" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q176">
         <v>2.05</v>
@@ -37566,7 +37575,7 @@
         <v>134</v>
       </c>
       <c r="P177" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q177">
         <v>3.64</v>
@@ -37723,6 +37732,830 @@
       </c>
       <c r="BP177">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="178" spans="1:68">
+      <c r="A178" s="1">
+        <v>177</v>
+      </c>
+      <c r="B178">
+        <v>7817216</v>
+      </c>
+      <c r="C178" t="s">
+        <v>68</v>
+      </c>
+      <c r="D178" t="s">
+        <v>69</v>
+      </c>
+      <c r="E178" s="2">
+        <v>45745.47916666666</v>
+      </c>
+      <c r="F178">
+        <v>8</v>
+      </c>
+      <c r="G178" t="s">
+        <v>74</v>
+      </c>
+      <c r="H178" t="s">
+        <v>73</v>
+      </c>
+      <c r="I178">
+        <v>0</v>
+      </c>
+      <c r="J178">
+        <v>0</v>
+      </c>
+      <c r="K178">
+        <v>0</v>
+      </c>
+      <c r="L178">
+        <v>1</v>
+      </c>
+      <c r="M178">
+        <v>0</v>
+      </c>
+      <c r="N178">
+        <v>1</v>
+      </c>
+      <c r="O178" t="s">
+        <v>209</v>
+      </c>
+      <c r="P178" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q178">
+        <v>4.2</v>
+      </c>
+      <c r="R178">
+        <v>2.3</v>
+      </c>
+      <c r="S178">
+        <v>2.25</v>
+      </c>
+      <c r="T178">
+        <v>1.28</v>
+      </c>
+      <c r="U178">
+        <v>3.34</v>
+      </c>
+      <c r="V178">
+        <v>2.36</v>
+      </c>
+      <c r="W178">
+        <v>1.52</v>
+      </c>
+      <c r="X178">
+        <v>5.2</v>
+      </c>
+      <c r="Y178">
+        <v>1.12</v>
+      </c>
+      <c r="Z178">
+        <v>3.79</v>
+      </c>
+      <c r="AA178">
+        <v>3.96</v>
+      </c>
+      <c r="AB178">
+        <v>1.81</v>
+      </c>
+      <c r="AC178">
+        <v>1.01</v>
+      </c>
+      <c r="AD178">
+        <v>11</v>
+      </c>
+      <c r="AE178">
+        <v>1.15</v>
+      </c>
+      <c r="AF178">
+        <v>4.3</v>
+      </c>
+      <c r="AG178">
+        <v>1.6</v>
+      </c>
+      <c r="AH178">
+        <v>2.2</v>
+      </c>
+      <c r="AI178">
+        <v>1.57</v>
+      </c>
+      <c r="AJ178">
+        <v>2.19</v>
+      </c>
+      <c r="AK178">
+        <v>1.96</v>
+      </c>
+      <c r="AL178">
+        <v>1.21</v>
+      </c>
+      <c r="AM178">
+        <v>1.2</v>
+      </c>
+      <c r="AN178">
+        <v>0.93</v>
+      </c>
+      <c r="AO178">
+        <v>1.29</v>
+      </c>
+      <c r="AP178">
+        <v>1.07</v>
+      </c>
+      <c r="AQ178">
+        <v>1.2</v>
+      </c>
+      <c r="AR178">
+        <v>1.48</v>
+      </c>
+      <c r="AS178">
+        <v>1.46</v>
+      </c>
+      <c r="AT178">
+        <v>2.94</v>
+      </c>
+      <c r="AU178">
+        <v>4</v>
+      </c>
+      <c r="AV178">
+        <v>3</v>
+      </c>
+      <c r="AW178">
+        <v>4</v>
+      </c>
+      <c r="AX178">
+        <v>4</v>
+      </c>
+      <c r="AY178">
+        <v>8</v>
+      </c>
+      <c r="AZ178">
+        <v>7</v>
+      </c>
+      <c r="BA178">
+        <v>1</v>
+      </c>
+      <c r="BB178">
+        <v>6</v>
+      </c>
+      <c r="BC178">
+        <v>7</v>
+      </c>
+      <c r="BD178">
+        <v>2.96</v>
+      </c>
+      <c r="BE178">
+        <v>8.5</v>
+      </c>
+      <c r="BF178">
+        <v>1.51</v>
+      </c>
+      <c r="BG178">
+        <v>1.3</v>
+      </c>
+      <c r="BH178">
+        <v>3.2</v>
+      </c>
+      <c r="BI178">
+        <v>1.48</v>
+      </c>
+      <c r="BJ178">
+        <v>2.39</v>
+      </c>
+      <c r="BK178">
+        <v>1.91</v>
+      </c>
+      <c r="BL178">
+        <v>1.85</v>
+      </c>
+      <c r="BM178">
+        <v>2.26</v>
+      </c>
+      <c r="BN178">
+        <v>1.54</v>
+      </c>
+      <c r="BO178">
+        <v>3</v>
+      </c>
+      <c r="BP178">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="179" spans="1:68">
+      <c r="A179" s="1">
+        <v>178</v>
+      </c>
+      <c r="B179">
+        <v>7817215</v>
+      </c>
+      <c r="C179" t="s">
+        <v>68</v>
+      </c>
+      <c r="D179" t="s">
+        <v>69</v>
+      </c>
+      <c r="E179" s="2">
+        <v>45745.47916666666</v>
+      </c>
+      <c r="F179">
+        <v>8</v>
+      </c>
+      <c r="G179" t="s">
+        <v>76</v>
+      </c>
+      <c r="H179" t="s">
+        <v>81</v>
+      </c>
+      <c r="I179">
+        <v>0</v>
+      </c>
+      <c r="J179">
+        <v>0</v>
+      </c>
+      <c r="K179">
+        <v>0</v>
+      </c>
+      <c r="L179">
+        <v>1</v>
+      </c>
+      <c r="M179">
+        <v>0</v>
+      </c>
+      <c r="N179">
+        <v>1</v>
+      </c>
+      <c r="O179" t="s">
+        <v>210</v>
+      </c>
+      <c r="P179" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q179">
+        <v>7.2</v>
+      </c>
+      <c r="R179">
+        <v>2.4</v>
+      </c>
+      <c r="S179">
+        <v>1.78</v>
+      </c>
+      <c r="T179">
+        <v>1.21</v>
+      </c>
+      <c r="U179">
+        <v>3.9</v>
+      </c>
+      <c r="V179">
+        <v>2.19</v>
+      </c>
+      <c r="W179">
+        <v>1.63</v>
+      </c>
+      <c r="X179">
+        <v>4.5</v>
+      </c>
+      <c r="Y179">
+        <v>1.16</v>
+      </c>
+      <c r="Z179">
+        <v>7</v>
+      </c>
+      <c r="AA179">
+        <v>4.5</v>
+      </c>
+      <c r="AB179">
+        <v>1.33</v>
+      </c>
+      <c r="AC179">
+        <v>1.01</v>
+      </c>
+      <c r="AD179">
+        <v>17</v>
+      </c>
+      <c r="AE179">
+        <v>1.09</v>
+      </c>
+      <c r="AF179">
+        <v>5.4</v>
+      </c>
+      <c r="AG179">
+        <v>1.5</v>
+      </c>
+      <c r="AH179">
+        <v>2.5</v>
+      </c>
+      <c r="AI179">
+        <v>1.68</v>
+      </c>
+      <c r="AJ179">
+        <v>2.01</v>
+      </c>
+      <c r="AK179">
+        <v>3.02</v>
+      </c>
+      <c r="AL179">
+        <v>1.14</v>
+      </c>
+      <c r="AM179">
+        <v>1.03</v>
+      </c>
+      <c r="AN179">
+        <v>2.07</v>
+      </c>
+      <c r="AO179">
+        <v>2.36</v>
+      </c>
+      <c r="AP179">
+        <v>2.13</v>
+      </c>
+      <c r="AQ179">
+        <v>2.2</v>
+      </c>
+      <c r="AR179">
+        <v>1.63</v>
+      </c>
+      <c r="AS179">
+        <v>2.18</v>
+      </c>
+      <c r="AT179">
+        <v>3.81</v>
+      </c>
+      <c r="AU179">
+        <v>3</v>
+      </c>
+      <c r="AV179">
+        <v>3</v>
+      </c>
+      <c r="AW179">
+        <v>4</v>
+      </c>
+      <c r="AX179">
+        <v>3</v>
+      </c>
+      <c r="AY179">
+        <v>7</v>
+      </c>
+      <c r="AZ179">
+        <v>6</v>
+      </c>
+      <c r="BA179">
+        <v>5</v>
+      </c>
+      <c r="BB179">
+        <v>4</v>
+      </c>
+      <c r="BC179">
+        <v>9</v>
+      </c>
+      <c r="BD179">
+        <v>0</v>
+      </c>
+      <c r="BE179">
+        <v>0</v>
+      </c>
+      <c r="BF179">
+        <v>0</v>
+      </c>
+      <c r="BG179">
+        <v>0</v>
+      </c>
+      <c r="BH179">
+        <v>0</v>
+      </c>
+      <c r="BI179">
+        <v>0</v>
+      </c>
+      <c r="BJ179">
+        <v>0</v>
+      </c>
+      <c r="BK179">
+        <v>0</v>
+      </c>
+      <c r="BL179">
+        <v>0</v>
+      </c>
+      <c r="BM179">
+        <v>0</v>
+      </c>
+      <c r="BN179">
+        <v>0</v>
+      </c>
+      <c r="BO179">
+        <v>0</v>
+      </c>
+      <c r="BP179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:68">
+      <c r="A180" s="1">
+        <v>179</v>
+      </c>
+      <c r="B180">
+        <v>7817213</v>
+      </c>
+      <c r="C180" t="s">
+        <v>68</v>
+      </c>
+      <c r="D180" t="s">
+        <v>69</v>
+      </c>
+      <c r="E180" s="2">
+        <v>45745.47916666666</v>
+      </c>
+      <c r="F180">
+        <v>8</v>
+      </c>
+      <c r="G180" t="s">
+        <v>77</v>
+      </c>
+      <c r="H180" t="s">
+        <v>75</v>
+      </c>
+      <c r="I180">
+        <v>0</v>
+      </c>
+      <c r="J180">
+        <v>0</v>
+      </c>
+      <c r="K180">
+        <v>0</v>
+      </c>
+      <c r="L180">
+        <v>0</v>
+      </c>
+      <c r="M180">
+        <v>0</v>
+      </c>
+      <c r="N180">
+        <v>0</v>
+      </c>
+      <c r="O180" t="s">
+        <v>85</v>
+      </c>
+      <c r="P180" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q180">
+        <v>3.46</v>
+      </c>
+      <c r="R180">
+        <v>2</v>
+      </c>
+      <c r="S180">
+        <v>3.04</v>
+      </c>
+      <c r="T180">
+        <v>1.42</v>
+      </c>
+      <c r="U180">
+        <v>2.65</v>
+      </c>
+      <c r="V180">
+        <v>3.14</v>
+      </c>
+      <c r="W180">
+        <v>1.31</v>
+      </c>
+      <c r="X180">
+        <v>7.8</v>
+      </c>
+      <c r="Y180">
+        <v>1.05</v>
+      </c>
+      <c r="Z180">
+        <v>2.71</v>
+      </c>
+      <c r="AA180">
+        <v>3.56</v>
+      </c>
+      <c r="AB180">
+        <v>2.39</v>
+      </c>
+      <c r="AC180">
+        <v>1.01</v>
+      </c>
+      <c r="AD180">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AE180">
+        <v>1.32</v>
+      </c>
+      <c r="AF180">
+        <v>2.88</v>
+      </c>
+      <c r="AG180">
+        <v>1.85</v>
+      </c>
+      <c r="AH180">
+        <v>1.75</v>
+      </c>
+      <c r="AI180">
+        <v>1.83</v>
+      </c>
+      <c r="AJ180">
+        <v>1.83</v>
+      </c>
+      <c r="AK180">
+        <v>1.5</v>
+      </c>
+      <c r="AL180">
+        <v>1.28</v>
+      </c>
+      <c r="AM180">
+        <v>1.38</v>
+      </c>
+      <c r="AN180">
+        <v>1.29</v>
+      </c>
+      <c r="AO180">
+        <v>1.21</v>
+      </c>
+      <c r="AP180">
+        <v>1.27</v>
+      </c>
+      <c r="AQ180">
+        <v>1.2</v>
+      </c>
+      <c r="AR180">
+        <v>1.34</v>
+      </c>
+      <c r="AS180">
+        <v>1.25</v>
+      </c>
+      <c r="AT180">
+        <v>2.59</v>
+      </c>
+      <c r="AU180">
+        <v>0</v>
+      </c>
+      <c r="AV180">
+        <v>2</v>
+      </c>
+      <c r="AW180">
+        <v>3</v>
+      </c>
+      <c r="AX180">
+        <v>6</v>
+      </c>
+      <c r="AY180">
+        <v>3</v>
+      </c>
+      <c r="AZ180">
+        <v>8</v>
+      </c>
+      <c r="BA180">
+        <v>5</v>
+      </c>
+      <c r="BB180">
+        <v>3</v>
+      </c>
+      <c r="BC180">
+        <v>8</v>
+      </c>
+      <c r="BD180">
+        <v>2</v>
+      </c>
+      <c r="BE180">
+        <v>5.95</v>
+      </c>
+      <c r="BF180">
+        <v>2.22</v>
+      </c>
+      <c r="BG180">
+        <v>1.44</v>
+      </c>
+      <c r="BH180">
+        <v>2.6</v>
+      </c>
+      <c r="BI180">
+        <v>1.76</v>
+      </c>
+      <c r="BJ180">
+        <v>1.97</v>
+      </c>
+      <c r="BK180">
+        <v>2.21</v>
+      </c>
+      <c r="BL180">
+        <v>1.59</v>
+      </c>
+      <c r="BM180">
+        <v>2.88</v>
+      </c>
+      <c r="BN180">
+        <v>1.36</v>
+      </c>
+      <c r="BO180">
+        <v>3.8</v>
+      </c>
+      <c r="BP180">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="181" spans="1:68">
+      <c r="A181" s="1">
+        <v>180</v>
+      </c>
+      <c r="B181">
+        <v>7817214</v>
+      </c>
+      <c r="C181" t="s">
+        <v>68</v>
+      </c>
+      <c r="D181" t="s">
+        <v>69</v>
+      </c>
+      <c r="E181" s="2">
+        <v>45745.47916666666</v>
+      </c>
+      <c r="F181">
+        <v>8</v>
+      </c>
+      <c r="G181" t="s">
+        <v>80</v>
+      </c>
+      <c r="H181" t="s">
+        <v>79</v>
+      </c>
+      <c r="I181">
+        <v>0</v>
+      </c>
+      <c r="J181">
+        <v>0</v>
+      </c>
+      <c r="K181">
+        <v>0</v>
+      </c>
+      <c r="L181">
+        <v>1</v>
+      </c>
+      <c r="M181">
+        <v>1</v>
+      </c>
+      <c r="N181">
+        <v>2</v>
+      </c>
+      <c r="O181" t="s">
+        <v>211</v>
+      </c>
+      <c r="P181" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q181">
+        <v>2.73</v>
+      </c>
+      <c r="R181">
+        <v>2.01</v>
+      </c>
+      <c r="S181">
+        <v>3.94</v>
+      </c>
+      <c r="T181">
+        <v>1.43</v>
+      </c>
+      <c r="U181">
+        <v>2.62</v>
+      </c>
+      <c r="V181">
+        <v>3.26</v>
+      </c>
+      <c r="W181">
+        <v>1.29</v>
+      </c>
+      <c r="X181">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y181">
+        <v>1.04</v>
+      </c>
+      <c r="Z181">
+        <v>2.06</v>
+      </c>
+      <c r="AA181">
+        <v>3.45</v>
+      </c>
+      <c r="AB181">
+        <v>3.39</v>
+      </c>
+      <c r="AC181">
+        <v>1.01</v>
+      </c>
+      <c r="AD181">
+        <v>8.6</v>
+      </c>
+      <c r="AE181">
+        <v>1.35</v>
+      </c>
+      <c r="AF181">
+        <v>2.74</v>
+      </c>
+      <c r="AG181">
+        <v>1.87</v>
+      </c>
+      <c r="AH181">
+        <v>1.87</v>
+      </c>
+      <c r="AI181">
+        <v>1.92</v>
+      </c>
+      <c r="AJ181">
+        <v>1.75</v>
+      </c>
+      <c r="AK181">
+        <v>1.28</v>
+      </c>
+      <c r="AL181">
+        <v>1.27</v>
+      </c>
+      <c r="AM181">
+        <v>1.65</v>
+      </c>
+      <c r="AN181">
+        <v>1.86</v>
+      </c>
+      <c r="AO181">
+        <v>1.71</v>
+      </c>
+      <c r="AP181">
+        <v>1.8</v>
+      </c>
+      <c r="AQ181">
+        <v>1.67</v>
+      </c>
+      <c r="AR181">
+        <v>1.53</v>
+      </c>
+      <c r="AS181">
+        <v>1.43</v>
+      </c>
+      <c r="AT181">
+        <v>2.96</v>
+      </c>
+      <c r="AU181">
+        <v>6</v>
+      </c>
+      <c r="AV181">
+        <v>5</v>
+      </c>
+      <c r="AW181">
+        <v>9</v>
+      </c>
+      <c r="AX181">
+        <v>7</v>
+      </c>
+      <c r="AY181">
+        <v>15</v>
+      </c>
+      <c r="AZ181">
+        <v>12</v>
+      </c>
+      <c r="BA181">
+        <v>7</v>
+      </c>
+      <c r="BB181">
+        <v>4</v>
+      </c>
+      <c r="BC181">
+        <v>11</v>
+      </c>
+      <c r="BD181">
+        <v>1.63</v>
+      </c>
+      <c r="BE181">
+        <v>7.9</v>
+      </c>
+      <c r="BF181">
+        <v>2.65</v>
+      </c>
+      <c r="BG181">
+        <v>1.45</v>
+      </c>
+      <c r="BH181">
+        <v>2.47</v>
+      </c>
+      <c r="BI181">
+        <v>1.82</v>
+      </c>
+      <c r="BJ181">
+        <v>1.94</v>
+      </c>
+      <c r="BK181">
+        <v>2.28</v>
+      </c>
+      <c r="BL181">
+        <v>1.53</v>
+      </c>
+      <c r="BM181">
+        <v>3</v>
+      </c>
+      <c r="BN181">
+        <v>1.33</v>
+      </c>
+      <c r="BO181">
+        <v>3.8</v>
+      </c>
+      <c r="BP181">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Wales Welsh Premier League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Wales Welsh Premier League_20242025.xlsx
@@ -21266,13 +21266,13 @@
         <v>-1</v>
       </c>
       <c r="BA97">
-        <v>13</v>
+        <v>-1</v>
       </c>
       <c r="BB97">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BC97">
-        <v>14</v>
+        <v>-1</v>
       </c>
       <c r="BD97">
         <v>0</v>
@@ -22496,10 +22496,10 @@
         <v>6</v>
       </c>
       <c r="AY103">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ103">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BA103">
         <v>7</v>
@@ -22702,10 +22702,10 @@
         <v>3</v>
       </c>
       <c r="AY104">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ104">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA104">
         <v>2</v>
@@ -22908,10 +22908,10 @@
         <v>11</v>
       </c>
       <c r="AY105">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ105">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="BA105">
         <v>3</v>
@@ -23117,7 +23117,7 @@
         <v>12</v>
       </c>
       <c r="AZ106">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA106">
         <v>3</v>
@@ -23526,10 +23526,10 @@
         <v>5</v>
       </c>
       <c r="AY108">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AZ108">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA108">
         <v>1</v>
@@ -23938,10 +23938,10 @@
         <v>3</v>
       </c>
       <c r="AY110">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ110">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA110">
         <v>1</v>
@@ -24144,10 +24144,10 @@
         <v>8</v>
       </c>
       <c r="AY111">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AZ111">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="BA111">
         <v>4</v>
@@ -24350,7 +24350,7 @@
         <v>2</v>
       </c>
       <c r="AY112">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AZ112">
         <v>8</v>
@@ -24556,7 +24556,7 @@
         <v>7</v>
       </c>
       <c r="AY113">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ113">
         <v>13</v>
@@ -24765,7 +24765,7 @@
         <v>11</v>
       </c>
       <c r="AZ114">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA114">
         <v>3</v>
@@ -24968,10 +24968,10 @@
         <v>6</v>
       </c>
       <c r="AY115">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AZ115">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="BA115">
         <v>6</v>
@@ -25177,7 +25177,7 @@
         <v>9</v>
       </c>
       <c r="AZ116">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA116">
         <v>4</v>
@@ -25380,10 +25380,10 @@
         <v>11</v>
       </c>
       <c r="AY117">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ117">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="BA117">
         <v>5</v>
@@ -25586,10 +25586,10 @@
         <v>5</v>
       </c>
       <c r="AY118">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ118">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="BA118">
         <v>3</v>
@@ -26410,7 +26410,7 @@
         <v>4</v>
       </c>
       <c r="AY122">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ122">
         <v>10</v>
@@ -26616,10 +26616,10 @@
         <v>3</v>
       </c>
       <c r="AY123">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AZ123">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA123">
         <v>7</v>
@@ -26822,7 +26822,7 @@
         <v>1</v>
       </c>
       <c r="AY124">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="AZ124">
         <v>5</v>
@@ -27028,7 +27028,7 @@
         <v>3</v>
       </c>
       <c r="AY125">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AZ125">
         <v>8</v>
@@ -27234,10 +27234,10 @@
         <v>8</v>
       </c>
       <c r="AY126">
+        <v>9</v>
+      </c>
+      <c r="AZ126">
         <v>11</v>
-      </c>
-      <c r="AZ126">
-        <v>15</v>
       </c>
       <c r="BA126">
         <v>4</v>
@@ -28270,13 +28270,13 @@
         <v>-1</v>
       </c>
       <c r="BA131">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BB131">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="BC131">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="BD131">
         <v>5.75</v>
@@ -41248,13 +41248,13 @@
         <v>-1</v>
       </c>
       <c r="BA194">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BB194">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="BC194">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BD194">
         <v>0</v>
